--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C71B1A1-CB28-7A43-B117-B9E86E285007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C681644-14AC-7B43-8E32-F011B0472B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="3" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="292">
   <si>
     <t>question_id</t>
   </si>
@@ -897,6 +897,24 @@
   </si>
   <si>
     <t>line_ppn_rate</t>
+  </si>
+  <si>
+    <t>q_draw_D</t>
+  </si>
+  <si>
+    <t>One gemstone is amethyst… draw a shape that contains it!</t>
+  </si>
+  <si>
+    <t>IMAGES/DRAW QUESTIONS/q_draw_D.png</t>
+  </si>
+  <si>
+    <t>IMAGES/DRAW QUESTIONS/q_draw_D_mask.png</t>
+  </si>
+  <si>
+    <t>THIS ONE'S AMETHYST:</t>
+  </si>
+  <si>
+    <t>IMAGES/DRAW QUESTIONS/q_draw_D_answer_screen.png</t>
   </si>
 </sst>
 </file>
@@ -4168,7 +4186,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D7EE002-C8BB-8E47-A415-52259E56BE73}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="39.5" customWidth="1"/>
@@ -4296,6 +4314,35 @@
         <v>284</v>
       </c>
     </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C5" s="86" t="s">
+        <v>288</v>
+      </c>
+      <c r="D5" s="86" t="s">
+        <v>289</v>
+      </c>
+      <c r="E5" s="86" t="s">
+        <v>268</v>
+      </c>
+      <c r="F5">
+        <v>90</v>
+      </c>
+      <c r="G5">
+        <v>1.25</v>
+      </c>
+      <c r="H5" s="86" t="s">
+        <v>290</v>
+      </c>
+      <c r="I5" t="s">
+        <v>291</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C681644-14AC-7B43-8E32-F011B0472B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF79072-2382-7945-A282-711AD685369B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="3" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -4276,7 +4276,7 @@
         <v>90</v>
       </c>
       <c r="G3">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="H3" s="86" t="s">
         <v>276</v>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF79072-2382-7945-A282-711AD685369B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C566E77C-DA78-C64C-8205-A01ECBD05037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="3" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="2" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -563,18 +563,12 @@
     <t>Betazed</t>
   </si>
   <si>
-    <t>Bajor</t>
-  </si>
-  <si>
     <t>Risa</t>
   </si>
   <si>
     <t>Vulcan</t>
   </si>
   <si>
-    <t>Xindus</t>
-  </si>
-  <si>
     <t>Romulus</t>
   </si>
   <si>
@@ -626,9 +620,6 @@
     <t>My Chemical Romance</t>
   </si>
   <si>
-    <t>Fallout Boy</t>
-  </si>
-  <si>
     <t>Capt. Lou Albano</t>
   </si>
   <si>
@@ -915,6 +906,15 @@
   </si>
   <si>
     <t>IMAGES/DRAW QUESTIONS/q_draw_D_answer_screen.png</t>
+  </si>
+  <si>
+    <t>Earth</t>
+  </si>
+  <si>
+    <t>Jupiter</t>
+  </si>
+  <si>
+    <t>The Beach Boys</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1875,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="83" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C2" s="80">
         <v>10</v>
@@ -2267,7 +2267,7 @@
         <v>42</v>
       </c>
       <c r="B10" s="83" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C10" s="80">
         <v>10</v>
@@ -2772,15 +2772,15 @@
         <v>93</v>
       </c>
       <c r="M7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B8" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C8" t="s">
         <v>89</v>
@@ -2801,13 +2801,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M8" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="33" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="T2" s="34" t="b">
         <v>1</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="63" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AF2" s="43" t="b">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>20</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F3" s="34" t="b">
         <v>1</v>
@@ -3127,13 +3127,13 @@
         <v>1</v>
       </c>
       <c r="Q3" s="35" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="R3" s="34" t="b">
         <v>1</v>
       </c>
       <c r="S3" s="35" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="T3" s="34" t="b">
         <v>1</v>
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="W3" s="36" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="X3" s="37" t="b">
         <v>0</v>
       </c>
       <c r="Y3" s="36" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="Z3" s="40" t="b">
         <v>0</v>
@@ -3192,7 +3192,7 @@
         <v>157</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C4" s="31" t="s">
         <v>129</v>
@@ -3243,7 +3243,7 @@
         <v>1</v>
       </c>
       <c r="S4" s="35" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="T4" s="34" t="b">
         <v>1</v>
@@ -3273,13 +3273,13 @@
         <v>0</v>
       </c>
       <c r="AC4" s="41" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AD4" s="42" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="41" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AF4" s="43" t="b">
         <v>0</v>
@@ -3302,7 +3302,7 @@
         <v>171</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C5" s="31" t="s">
         <v>129</v>
@@ -3323,96 +3323,96 @@
         <v>1</v>
       </c>
       <c r="I5" s="35" t="s">
+        <v>289</v>
+      </c>
+      <c r="J5" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="35" t="s">
         <v>174</v>
       </c>
-      <c r="J5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="35" t="s">
+      <c r="L5" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="L5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="35" t="s">
+      <c r="N5" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="P5" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="35" t="s">
         <v>176</v>
       </c>
-      <c r="N5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="35" t="s">
+      <c r="R5" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="T5" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="P5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="35" t="s">
+      <c r="V5" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" s="36" t="s">
         <v>178</v>
       </c>
-      <c r="R5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="T5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="U5" s="38" t="s">
+      <c r="X5" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z5" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="V5" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" s="36" t="s">
+      <c r="AB5" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="41" t="s">
+        <v>239</v>
+      </c>
+      <c r="AD5" s="42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="41" t="s">
         <v>180</v>
       </c>
-      <c r="X5" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="36" t="s">
-        <v>241</v>
-      </c>
-      <c r="Z5" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="38" t="s">
+      <c r="AF5" s="43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="30" t="s">
         <v>181</v>
       </c>
-      <c r="AB5" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="41" t="s">
-        <v>242</v>
-      </c>
-      <c r="AD5" s="42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="41" t="s">
+      <c r="AJ5" s="44" t="s">
         <v>182</v>
-      </c>
-      <c r="AF5" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="AJ5" s="44" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:36" s="45" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="61" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C6" s="31" t="s">
         <v>129</v>
@@ -3421,108 +3421,108 @@
         <v>20</v>
       </c>
       <c r="E6" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>186</v>
+      </c>
+      <c r="H6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="F6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="35" t="s">
+      <c r="J6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="35" t="s">
         <v>188</v>
       </c>
-      <c r="H6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="35" t="s">
+      <c r="L6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="N6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="35" t="s">
         <v>189</v>
       </c>
-      <c r="J6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="35" t="s">
+      <c r="P6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="L6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="35" t="s">
-        <v>223</v>
-      </c>
-      <c r="N6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="35" t="s">
+      <c r="R6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="T6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="V6" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="X6" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z6" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="P6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="R6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="35" t="s">
-        <v>243</v>
-      </c>
-      <c r="T6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" s="38" t="s">
+      <c r="AB6" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="41" t="s">
+        <v>248</v>
+      </c>
+      <c r="AD6" s="42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="AF6" s="43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="V6" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="36" t="s">
+      <c r="AJ6" s="44" t="s">
         <v>195</v>
-      </c>
-      <c r="X6" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="36" t="s">
-        <v>196</v>
-      </c>
-      <c r="Z6" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="AB6" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="41" t="s">
-        <v>251</v>
-      </c>
-      <c r="AD6" s="42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="AF6" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="AJ6" s="44" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:36" s="45" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="61" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>129</v>
@@ -3531,108 +3531,108 @@
         <v>20</v>
       </c>
       <c r="E7" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="F7" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="H7" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="J7" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="L7" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="N7" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="35" t="s">
         <v>224</v>
       </c>
-      <c r="F7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="35" t="s">
+      <c r="P7" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="35" t="s">
         <v>225</v>
       </c>
-      <c r="H7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="35" t="s">
+      <c r="R7" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="T7" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="V7" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="X7" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z7" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="AB7" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="AD7" s="42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="AF7" s="43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="AJ7" s="44" t="s">
         <v>201</v>
-      </c>
-      <c r="J7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="35" t="s">
-        <v>202</v>
-      </c>
-      <c r="L7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="35" t="s">
-        <v>226</v>
-      </c>
-      <c r="N7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="P7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="35" t="s">
-        <v>228</v>
-      </c>
-      <c r="R7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="T7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="V7" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="X7" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="Z7" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="AB7" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="AD7" s="42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="AF7" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="AJ7" s="44" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:36" s="29" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A8" s="62" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>129</v>
@@ -3641,100 +3641,100 @@
         <v>20</v>
       </c>
       <c r="E8" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="F8" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="H8" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="J8" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="F8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="19" t="s">
+      <c r="L8" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="N8" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="H8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="19" t="s">
+      <c r="P8" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="J8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="19" t="s">
+      <c r="R8" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="T8" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="L8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="N8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="19" t="s">
+      <c r="V8" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="P8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="19" t="s">
+      <c r="X8" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="R8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="S8" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="T8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" s="22" t="s">
+      <c r="Z8" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="AB8" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="V8" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="20" t="s">
+      <c r="AD8" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="X8" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="20" t="s">
+      <c r="AF8" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="Z8" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="AB8" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="25" t="s">
+      <c r="AJ8" s="28" t="s">
         <v>216</v>
-      </c>
-      <c r="AD8" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF8" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH8" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="AJ8" s="28" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:36" s="45" customFormat="1" x14ac:dyDescent="0.2">
@@ -4209,39 +4209,39 @@
         <v>58</v>
       </c>
       <c r="D1" s="85" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E1" s="85" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F1" s="85" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G1" s="85" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H1" s="85" t="s">
         <v>15</v>
       </c>
       <c r="I1" s="87" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="86" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="86" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2" s="86" t="s">
+        <v>264</v>
+      </c>
+      <c r="E2" s="86" t="s">
         <v>265</v>
-      </c>
-      <c r="B2" s="86" t="s">
-        <v>277</v>
-      </c>
-      <c r="C2" s="86" t="s">
-        <v>266</v>
-      </c>
-      <c r="D2" s="86" t="s">
-        <v>267</v>
-      </c>
-      <c r="E2" s="86" t="s">
-        <v>268</v>
       </c>
       <c r="F2" s="86">
         <v>90</v>
@@ -4250,27 +4250,27 @@
         <v>1.25</v>
       </c>
       <c r="H2" s="86" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C3" s="86" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D3" s="86" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E3" s="86" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -4279,27 +4279,27 @@
         <v>1.5</v>
       </c>
       <c r="H3" s="86" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" s="86" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" s="86" t="s">
         <v>279</v>
       </c>
-      <c r="B4" t="s">
-        <v>280</v>
-      </c>
-      <c r="C4" s="86" t="s">
-        <v>281</v>
-      </c>
-      <c r="D4" s="86" t="s">
-        <v>282</v>
-      </c>
       <c r="E4" s="86" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F4">
         <v>90</v>
@@ -4308,27 +4308,27 @@
         <v>1.25</v>
       </c>
       <c r="H4" s="86" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C5" s="86" t="s">
+        <v>285</v>
+      </c>
+      <c r="D5" s="86" t="s">
         <v>286</v>
       </c>
-      <c r="B5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C5" s="86" t="s">
-        <v>288</v>
-      </c>
-      <c r="D5" s="86" t="s">
-        <v>289</v>
-      </c>
       <c r="E5" s="86" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F5">
         <v>90</v>
@@ -4337,10 +4337,10 @@
         <v>1.25</v>
       </c>
       <c r="H5" s="86" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C566E77C-DA78-C64C-8205-A01ECBD05037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E896E28-0A04-4546-A705-3851CA072E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="2" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="274">
   <si>
     <t>question_id</t>
   </si>
@@ -590,45 +590,6 @@
     <t>SCIENCE FICTION</t>
   </si>
   <si>
-    <t>bonus_q_2008_hits</t>
-  </si>
-  <si>
-    <t>In 2008, which of these had a #1 hit on the Billboard Hot 100?</t>
-  </si>
-  <si>
-    <t>Flo Rida</t>
-  </si>
-  <si>
-    <t>Coldplay</t>
-  </si>
-  <si>
-    <t>Pink</t>
-  </si>
-  <si>
-    <t>Britney Spears</t>
-  </si>
-  <si>
-    <t>Katy Perry</t>
-  </si>
-  <si>
-    <t>T.I.</t>
-  </si>
-  <si>
-    <t>Green Day</t>
-  </si>
-  <si>
-    <t>My Chemical Romance</t>
-  </si>
-  <si>
-    <t>Capt. Lou Albano</t>
-  </si>
-  <si>
-    <t>These were #1 Billboard Hot 100 hits in 2008.</t>
-  </si>
-  <si>
-    <t>2008 MUSIC</t>
-  </si>
-  <si>
     <t>bonus_q_norway_snow</t>
   </si>
   <si>
@@ -701,9 +662,6 @@
     <t>What year was Velcro (A.K.A. "Hook &amp; Loop") invented?</t>
   </si>
   <si>
-    <t>Beyoncé</t>
-  </si>
-  <si>
     <t>Snø</t>
   </si>
   <si>
@@ -761,9 +719,6 @@
     <t>Kappa Rho</t>
   </si>
   <si>
-    <t>Leona Lewis</t>
-  </si>
-  <si>
     <t>Løssnø</t>
   </si>
   <si>
@@ -782,12 +737,6 @@
     <t>Tentacle</t>
   </si>
   <si>
-    <t>The Ink Spots</t>
-  </si>
-  <si>
-    <t>Mary J. Blige</t>
-  </si>
-  <si>
     <t>Polyculer</t>
   </si>
   <si>
@@ -912,9 +861,6 @@
   </si>
   <si>
     <t>Jupiter</t>
-  </si>
-  <si>
-    <t>The Beach Boys</t>
   </si>
 </sst>
 </file>
@@ -1866,16 +1812,14 @@
       <c r="P1" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="80" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q1" s="80"/>
     </row>
     <row r="2" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="80" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="83" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="C2" s="80">
         <v>10</v>
@@ -1897,16 +1841,16 @@
         <v>95</v>
       </c>
       <c r="J2" s="80">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K2" s="80">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L2" s="80">
         <v>35</v>
       </c>
       <c r="M2" s="80">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="N2" s="80"/>
       <c r="O2" s="80">
@@ -1915,10 +1859,7 @@
       <c r="P2" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="80">
-        <f>100-(I2/MIN(IF(C2&lt;&gt;"",C2,9999),IF(D2&lt;&gt;"",D2,9999),IF(E2&lt;&gt;"",E2,9999))*H2)</f>
-        <v>5</v>
-      </c>
+      <c r="Q2" s="80"/>
     </row>
     <row r="3" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="80" t="s">
@@ -1963,10 +1904,7 @@
       <c r="P3" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="Q3" s="80">
-        <f t="shared" ref="Q3:Q12" si="0">100-(I3/MIN(IF(C3&lt;&gt;"",C3,9999),IF(D3&lt;&gt;"",D3,9999),IF(E3&lt;&gt;"",E3,9999))*H3)</f>
-        <v>10</v>
-      </c>
+      <c r="Q3" s="80"/>
     </row>
     <row r="4" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="80" t="s">
@@ -2013,10 +1951,7 @@
       <c r="P4" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q4" s="80">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
+      <c r="Q4" s="80"/>
     </row>
     <row r="5" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="80" t="s">
@@ -2061,10 +1996,7 @@
       <c r="P5" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="Q5" s="80">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+      <c r="Q5" s="80"/>
     </row>
     <row r="6" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="80" t="s">
@@ -2109,10 +2041,7 @@
       <c r="P6" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="Q6" s="80">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+      <c r="Q6" s="80"/>
     </row>
     <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="80" t="s">
@@ -2159,10 +2088,7 @@
       <c r="P7" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="Q7" s="80">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+      <c r="Q7" s="80"/>
     </row>
     <row r="8" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="80" t="s">
@@ -2207,10 +2133,7 @@
       <c r="P8" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="Q8" s="80">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+      <c r="Q8" s="80"/>
     </row>
     <row r="9" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="80" t="s">
@@ -2257,17 +2180,14 @@
       <c r="P9" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="Q9" s="80">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+      <c r="Q9" s="80"/>
     </row>
     <row r="10" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="80" t="s">
         <v>42</v>
       </c>
       <c r="B10" s="83" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="C10" s="80">
         <v>10</v>
@@ -2305,10 +2225,7 @@
       <c r="P10" s="80" t="s">
         <v>43</v>
       </c>
-      <c r="Q10" s="80">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+      <c r="Q10" s="80"/>
     </row>
     <row r="11" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="80" t="s">
@@ -2353,10 +2270,7 @@
       <c r="P11" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="Q11" s="80">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
+      <c r="Q11" s="80"/>
     </row>
     <row r="12" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="80" t="s">
@@ -2405,10 +2319,7 @@
       <c r="P12" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="Q12" s="80">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+      <c r="Q12" s="80"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="80"/>
@@ -2772,15 +2683,15 @@
         <v>93</v>
       </c>
       <c r="M7" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="B8" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="C8" t="s">
         <v>89</v>
@@ -2801,13 +2712,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="M8" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -2817,7 +2728,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A722971B-16B6-2747-9012-3CB77F8500DE}">
-  <dimension ref="A1:AJ21"/>
+  <dimension ref="A1:AJ20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -3023,7 +2934,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="33" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="T2" s="34" t="b">
         <v>1</v>
@@ -3059,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="63" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="AF2" s="43" t="b">
         <v>0</v>
@@ -3091,7 +3002,7 @@
         <v>20</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="F3" s="34" t="b">
         <v>1</v>
@@ -3127,13 +3038,13 @@
         <v>1</v>
       </c>
       <c r="Q3" s="35" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="R3" s="34" t="b">
         <v>1</v>
       </c>
       <c r="S3" s="35" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="T3" s="34" t="b">
         <v>1</v>
@@ -3145,13 +3056,13 @@
         <v>0</v>
       </c>
       <c r="W3" s="36" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="X3" s="37" t="b">
         <v>0</v>
       </c>
       <c r="Y3" s="36" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="Z3" s="40" t="b">
         <v>0</v>
@@ -3192,7 +3103,7 @@
         <v>157</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="C4" s="31" t="s">
         <v>129</v>
@@ -3243,7 +3154,7 @@
         <v>1</v>
       </c>
       <c r="S4" s="35" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="T4" s="34" t="b">
         <v>1</v>
@@ -3273,13 +3184,13 @@
         <v>0</v>
       </c>
       <c r="AC4" s="41" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="AD4" s="42" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="41" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="AF4" s="43" t="b">
         <v>0</v>
@@ -3302,7 +3213,7 @@
         <v>171</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C5" s="31" t="s">
         <v>129</v>
@@ -3323,7 +3234,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="35" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="J5" s="34" t="b">
         <v>1</v>
@@ -3341,7 +3252,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="P5" s="34" t="b">
         <v>1</v>
@@ -3353,7 +3264,7 @@
         <v>1</v>
       </c>
       <c r="S5" s="35" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="T5" s="34" t="b">
         <v>1</v>
@@ -3371,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="Y5" s="36" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="Z5" s="40" t="b">
         <v>0</v>
@@ -3383,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="AC5" s="41" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="AD5" s="42" t="b">
         <v>0</v>
@@ -3421,321 +3332,245 @@
         <v>20</v>
       </c>
       <c r="E6" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="F6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="H6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="F6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="35" t="s">
+      <c r="J6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="H6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="35" t="s">
+      <c r="L6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="N6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="P6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="R6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="T6" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="V6" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="X6" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="Z6" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="AB6" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD6" s="42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="41" t="s">
+        <v>228</v>
+      </c>
+      <c r="AF6" s="43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="J6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="35" t="s">
+      <c r="AJ6" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="L6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="N6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="35" t="s">
+    </row>
+    <row r="7" spans="1:36" s="29" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="62" t="s">
         <v>189</v>
       </c>
-      <c r="P6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="35" t="s">
+      <c r="B7" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="R6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="T6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" s="38" t="s">
+      <c r="C7" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="16">
+        <v>20</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="F7" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="V6" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="36" t="s">
-        <v>291</v>
-      </c>
-      <c r="X6" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="36" t="s">
+      <c r="H7" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="Z6" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="38" t="s">
-        <v>191</v>
-      </c>
-      <c r="AB6" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="41" t="s">
-        <v>248</v>
-      </c>
-      <c r="AD6" s="42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="41" t="s">
-        <v>247</v>
-      </c>
-      <c r="AF6" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="30" t="s">
+      <c r="J7" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="AJ6" s="44" t="s">
+      <c r="L7" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="N7" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="19" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="7" spans="1:36" s="45" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A7" s="61" t="s">
+      <c r="P7" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="R7" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="T7" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="22" t="s">
         <v>197</v>
       </c>
-      <c r="C7" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="D7" s="32">
-        <v>20</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="F7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="H7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="35" t="s">
+      <c r="V7" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="J7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="35" t="s">
+      <c r="X7" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="L7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="35" t="s">
-        <v>223</v>
-      </c>
-      <c r="N7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="P7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="35" t="s">
-        <v>225</v>
-      </c>
-      <c r="R7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="T7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="38" t="s">
-        <v>226</v>
-      </c>
-      <c r="V7" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="X7" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z7" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="AB7" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="41" t="s">
+      <c r="Z7" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="AD7" s="42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="AF7" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="30" t="s">
+      <c r="AB7" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="AJ7" s="44" t="s">
+      <c r="AD7" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="25" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="8" spans="1:36" s="29" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A8" s="62" t="s">
+      <c r="AF7" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="AJ7" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="16">
-        <v>20</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="F8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="H8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="J8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="L8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="N8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="P8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="R8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="S8" s="33" t="s">
-        <v>245</v>
-      </c>
-      <c r="T8" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="V8" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="X8" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="Z8" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="AB8" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="AD8" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="AF8" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH8" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="AJ8" s="28" t="s">
-        <v>216</v>
-      </c>
+    </row>
+    <row r="8" spans="1:36" s="45" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="47"/>
+      <c r="B8" s="48"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="52"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="52"/>
+      <c r="R8" s="51"/>
+      <c r="S8" s="52"/>
+      <c r="T8" s="64"/>
+      <c r="U8" s="55"/>
+      <c r="V8" s="56"/>
+      <c r="W8" s="53"/>
+      <c r="X8" s="54"/>
+      <c r="Y8" s="53"/>
+      <c r="Z8" s="57"/>
+      <c r="AA8" s="55"/>
+      <c r="AB8" s="56"/>
+      <c r="AC8" s="58"/>
+      <c r="AD8" s="59"/>
+      <c r="AE8" s="58"/>
+      <c r="AF8" s="60"/>
+      <c r="AI8" s="48"/>
     </row>
     <row r="9" spans="1:36" s="45" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="47"/>
@@ -3907,7 +3742,7 @@
       <c r="AF13" s="60"/>
       <c r="AI13" s="48"/>
     </row>
-    <row r="14" spans="1:36" s="45" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" s="45" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="47"/>
       <c r="B14" s="48"/>
       <c r="D14" s="49"/>
@@ -3941,7 +3776,7 @@
       <c r="AF14" s="60"/>
       <c r="AI14" s="48"/>
     </row>
-    <row r="15" spans="1:36" s="45" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" s="45" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="47"/>
       <c r="B15" s="48"/>
       <c r="D15" s="49"/>
@@ -4145,40 +3980,6 @@
       <c r="AF20" s="60"/>
       <c r="AI20" s="48"/>
     </row>
-    <row r="21" spans="1:35" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="47"/>
-      <c r="B21" s="48"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="52"/>
-      <c r="L21" s="51"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="51"/>
-      <c r="O21" s="52"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="52"/>
-      <c r="R21" s="51"/>
-      <c r="S21" s="52"/>
-      <c r="T21" s="64"/>
-      <c r="U21" s="55"/>
-      <c r="V21" s="56"/>
-      <c r="W21" s="53"/>
-      <c r="X21" s="54"/>
-      <c r="Y21" s="53"/>
-      <c r="Z21" s="57"/>
-      <c r="AA21" s="55"/>
-      <c r="AB21" s="56"/>
-      <c r="AC21" s="58"/>
-      <c r="AD21" s="59"/>
-      <c r="AE21" s="58"/>
-      <c r="AF21" s="60"/>
-      <c r="AI21" s="48"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4209,39 +4010,39 @@
         <v>58</v>
       </c>
       <c r="D1" s="85" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="E1" s="85" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="F1" s="85" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="G1" s="85" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="H1" s="85" t="s">
         <v>15</v>
       </c>
       <c r="I1" s="87" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="86" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B2" s="86" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="C2" s="86" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="D2" s="86" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="E2" s="86" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="F2" s="86">
         <v>90</v>
@@ -4250,27 +4051,27 @@
         <v>1.25</v>
       </c>
       <c r="H2" s="86" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="I2" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="B3" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="C3" s="86" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="D3" s="86" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="E3" s="86" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -4279,27 +4080,27 @@
         <v>1.5</v>
       </c>
       <c r="H3" s="86" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="I3" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="B4" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="C4" s="86" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="D4" s="86" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="E4" s="86" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="F4">
         <v>90</v>
@@ -4308,27 +4109,27 @@
         <v>1.25</v>
       </c>
       <c r="H4" s="86" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="I4" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="B5" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="C5" s="86" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="D5" s="86" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="E5" s="86" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="F5">
         <v>90</v>
@@ -4337,10 +4138,10 @@
         <v>1.25</v>
       </c>
       <c r="H5" s="86" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="I5" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E896E28-0A04-4546-A705-3851CA072E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4ED15CC-40F5-3B47-8A2E-0E4034111440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -1838,7 +1838,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="80">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="J2" s="80">
         <v>10</v>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4ED15CC-40F5-3B47-8A2E-0E4034111440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E88979-5FB0-7446-9A8C-6924128ABF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -1835,7 +1835,7 @@
         <v>18</v>
       </c>
       <c r="H2" s="80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" s="80">
         <v>65</v>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E88979-5FB0-7446-9A8C-6924128ABF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A57F892-0D51-0D48-AA51-AEA63B766FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="280">
   <si>
     <t>question_id</t>
   </si>
@@ -861,6 +861,24 @@
   </si>
   <si>
     <t>Jupiter</t>
+  </si>
+  <si>
+    <t>In which month does Capricorn season start?</t>
+  </si>
+  <si>
+    <t>pinch_L</t>
+  </si>
+  <si>
+    <t>Capricorn season goes from late December to late January</t>
+  </si>
+  <si>
+    <t>pinch_m</t>
+  </si>
+  <si>
+    <t>What percentage of dogs are good boys?</t>
+  </si>
+  <si>
+    <t>110% of dogs are good boys. Even the girls. No more questions at this time.</t>
   </si>
 </sst>
 </file>
@@ -1163,7 +1181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1411,6 +1429,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1856,7 +1877,7 @@
       <c r="O2" s="80">
         <v>57</v>
       </c>
-      <c r="P2" s="80" t="s">
+      <c r="P2" s="88" t="s">
         <v>19</v>
       </c>
       <c r="Q2" s="80"/>
@@ -1901,7 +1922,7 @@
       <c r="O3" s="80">
         <v>4</v>
       </c>
-      <c r="P3" s="80" t="s">
+      <c r="P3" s="88" t="s">
         <v>22</v>
       </c>
       <c r="Q3" s="80"/>
@@ -1948,7 +1969,7 @@
       <c r="O4" s="80">
         <v>7</v>
       </c>
-      <c r="P4" s="80" t="s">
+      <c r="P4" s="88" t="s">
         <v>25</v>
       </c>
       <c r="Q4" s="80"/>
@@ -1993,7 +2014,7 @@
       <c r="O5" s="80">
         <v>600</v>
       </c>
-      <c r="P5" s="80" t="s">
+      <c r="P5" s="88" t="s">
         <v>28</v>
       </c>
       <c r="Q5" s="80"/>
@@ -2038,7 +2059,7 @@
       <c r="O6" s="80">
         <v>12</v>
       </c>
-      <c r="P6" s="80" t="s">
+      <c r="P6" s="88" t="s">
         <v>31</v>
       </c>
       <c r="Q6" s="80"/>
@@ -2085,7 +2106,7 @@
       <c r="O7" s="80">
         <v>10</v>
       </c>
-      <c r="P7" s="80" t="s">
+      <c r="P7" s="88" t="s">
         <v>34</v>
       </c>
       <c r="Q7" s="80"/>
@@ -2130,7 +2151,7 @@
       <c r="O8" s="80">
         <v>6</v>
       </c>
-      <c r="P8" s="80" t="s">
+      <c r="P8" s="88" t="s">
         <v>38</v>
       </c>
       <c r="Q8" s="80"/>
@@ -2177,7 +2198,7 @@
       <c r="O9" s="80">
         <v>73</v>
       </c>
-      <c r="P9" s="80" t="s">
+      <c r="P9" s="88" t="s">
         <v>41</v>
       </c>
       <c r="Q9" s="80"/>
@@ -2222,7 +2243,7 @@
       <c r="O10" s="80">
         <v>1955</v>
       </c>
-      <c r="P10" s="80" t="s">
+      <c r="P10" s="88" t="s">
         <v>43</v>
       </c>
       <c r="Q10" s="80"/>
@@ -2267,7 +2288,7 @@
       <c r="O11" s="80">
         <v>165</v>
       </c>
-      <c r="P11" s="80" t="s">
+      <c r="P11" s="88" t="s">
         <v>47</v>
       </c>
       <c r="Q11" s="80"/>
@@ -2316,47 +2337,99 @@
       <c r="O12" s="80">
         <v>89.99</v>
       </c>
-      <c r="P12" s="80" t="s">
+      <c r="P12" s="88" t="s">
         <v>51</v>
       </c>
       <c r="Q12" s="80"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" s="80"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="80"/>
+    <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="80" t="s">
+        <v>275</v>
+      </c>
+      <c r="B13" s="83" t="s">
+        <v>274</v>
+      </c>
+      <c r="C13" s="80">
+        <v>1</v>
+      </c>
       <c r="D13" s="80"/>
       <c r="E13" s="80"/>
       <c r="F13" s="80"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="80"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="80"/>
-      <c r="K13" s="80"/>
-      <c r="L13" s="80"/>
-      <c r="M13" s="80"/>
-      <c r="N13" s="80"/>
-      <c r="O13" s="80"/>
-      <c r="P13" s="80"/>
+      <c r="G13" s="84" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="80">
+        <v>10</v>
+      </c>
+      <c r="I13" s="80">
+        <v>9</v>
+      </c>
+      <c r="J13" s="80">
+        <v>1</v>
+      </c>
+      <c r="K13" s="80">
+        <v>12</v>
+      </c>
+      <c r="L13" s="80">
+        <v>1</v>
+      </c>
+      <c r="M13" s="80">
+        <v>3</v>
+      </c>
+      <c r="N13" s="80" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" s="80">
+        <v>12</v>
+      </c>
+      <c r="P13" s="88" t="s">
+        <v>276</v>
+      </c>
       <c r="Q13" s="80"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14" s="80"/>
-      <c r="B14" s="83"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80"/>
+    <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="80" t="s">
+        <v>277</v>
+      </c>
+      <c r="B14" s="83" t="s">
+        <v>278</v>
+      </c>
+      <c r="C14" s="80">
+        <v>100</v>
+      </c>
+      <c r="D14" s="80">
+        <v>5</v>
+      </c>
+      <c r="E14" s="80">
+        <v>1</v>
+      </c>
       <c r="F14" s="80"/>
       <c r="G14" s="84"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="80"/>
-      <c r="L14" s="80"/>
-      <c r="M14" s="80"/>
+      <c r="H14" s="80">
+        <v>1</v>
+      </c>
+      <c r="I14" s="80">
+        <v>95</v>
+      </c>
+      <c r="J14" s="80">
+        <v>10</v>
+      </c>
+      <c r="K14" s="80">
+        <v>110</v>
+      </c>
+      <c r="L14" s="80">
+        <v>25</v>
+      </c>
+      <c r="M14" s="80">
+        <v>75</v>
+      </c>
       <c r="N14" s="80"/>
-      <c r="O14" s="80"/>
-      <c r="P14" s="80"/>
+      <c r="O14" s="80">
+        <v>110</v>
+      </c>
+      <c r="P14" s="88" t="s">
+        <v>279</v>
+      </c>
       <c r="Q14" s="80"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A57F892-0D51-0D48-AA51-AEA63B766FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D341ED-495C-EE42-AB30-89B8FE36354F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="2" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="298">
   <si>
     <t>question_id</t>
   </si>
@@ -879,6 +879,60 @@
   </si>
   <si>
     <t>110% of dogs are good boys. Even the girls. No more questions at this time.</t>
+  </si>
+  <si>
+    <t>bonus_q_orioles</t>
+  </si>
+  <si>
+    <t>Which of these played baseball for the Baltimore Orioles ?</t>
+  </si>
+  <si>
+    <t>Cal Ripken Jr.</t>
+  </si>
+  <si>
+    <t>Frank Robinson</t>
+  </si>
+  <si>
+    <t>Eddie Murray</t>
+  </si>
+  <si>
+    <t>Mike Mussina</t>
+  </si>
+  <si>
+    <t>Boog Powell</t>
+  </si>
+  <si>
+    <t>Nick Markakis</t>
+  </si>
+  <si>
+    <t>Ken Griffey, Jr.</t>
+  </si>
+  <si>
+    <t>Nolan Ryan</t>
+  </si>
+  <si>
+    <t>Moochie Norris</t>
+  </si>
+  <si>
+    <t>Curt Blefary</t>
+  </si>
+  <si>
+    <t>Burt Clefairy</t>
+  </si>
+  <si>
+    <t>Bobson Dugnutt</t>
+  </si>
+  <si>
+    <t>Simon Belmont</t>
+  </si>
+  <si>
+    <t>Billy DaMarlin</t>
+  </si>
+  <si>
+    <t>These were all Baltimore Orioles:</t>
+  </si>
+  <si>
+    <t>BASEBALL</t>
   </si>
 </sst>
 </file>
@@ -962,7 +1016,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -997,6 +1051,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1186,9 +1246,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1226,9 +1283,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1272,9 +1326,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1319,9 +1370,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1371,9 +1419,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1432,6 +1477,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1776,7 +1836,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="57.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7" style="82" customWidth="1"/>
+    <col min="7" max="7" width="7" style="77" customWidth="1"/>
     <col min="8" max="8" width="18.5" customWidth="1"/>
     <col min="9" max="9" width="15.33203125" customWidth="1"/>
     <col min="10" max="10" width="9.6640625" customWidth="1"/>
@@ -1785,728 +1845,728 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="80" t="s">
+      <c r="A1" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="80" t="s">
+      <c r="D1" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="80" t="s">
+      <c r="E1" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="80" t="s">
+      <c r="F1" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="84" t="s">
+      <c r="G1" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="80" t="s">
+      <c r="H1" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="80" t="s">
+      <c r="I1" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="80" t="s">
+      <c r="J1" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="80" t="s">
+      <c r="K1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="80" t="s">
+      <c r="L1" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="80" t="s">
+      <c r="M1" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="80" t="s">
+      <c r="N1" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="80" t="s">
+      <c r="O1" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="80" t="s">
+      <c r="P1" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="80"/>
+      <c r="Q1" s="75"/>
     </row>
     <row r="2" spans="1:17" ht="34" x14ac:dyDescent="0.2">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="78" t="s">
         <v>204</v>
       </c>
-      <c r="C2" s="80">
+      <c r="C2" s="75">
         <v>10</v>
       </c>
-      <c r="D2" s="80">
+      <c r="D2" s="75">
         <v>5</v>
       </c>
-      <c r="E2" s="80">
-        <v>1</v>
-      </c>
-      <c r="F2" s="80"/>
-      <c r="G2" s="84" t="s">
+      <c r="E2" s="75">
+        <v>1</v>
+      </c>
+      <c r="F2" s="75"/>
+      <c r="G2" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="80">
+      <c r="H2" s="75">
         <v>2</v>
       </c>
-      <c r="I2" s="80">
+      <c r="I2" s="75">
         <v>65</v>
       </c>
-      <c r="J2" s="80">
+      <c r="J2" s="75">
         <v>10</v>
       </c>
-      <c r="K2" s="80">
+      <c r="K2" s="75">
         <v>80</v>
       </c>
-      <c r="L2" s="80">
+      <c r="L2" s="75">
         <v>35</v>
       </c>
-      <c r="M2" s="80">
+      <c r="M2" s="75">
         <v>70</v>
       </c>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80">
+      <c r="N2" s="75"/>
+      <c r="O2" s="75">
         <v>57</v>
       </c>
-      <c r="P2" s="88" t="s">
+      <c r="P2" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="80"/>
+      <c r="Q2" s="75"/>
     </row>
     <row r="3" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="80">
+      <c r="C3" s="75">
         <v>5</v>
       </c>
-      <c r="D3" s="80">
-        <v>1</v>
-      </c>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="84" t="s">
+      <c r="D3" s="75">
+        <v>1</v>
+      </c>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="80">
+      <c r="H3" s="75">
         <v>5</v>
       </c>
-      <c r="I3" s="80">
+      <c r="I3" s="75">
         <v>18</v>
       </c>
-      <c r="J3" s="80">
-        <v>0</v>
-      </c>
-      <c r="K3" s="80">
+      <c r="J3" s="75">
+        <v>0</v>
+      </c>
+      <c r="K3" s="75">
         <v>20</v>
       </c>
-      <c r="L3" s="80">
+      <c r="L3" s="75">
         <v>6</v>
       </c>
-      <c r="M3" s="80">
+      <c r="M3" s="75">
         <v>16</v>
       </c>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80">
+      <c r="N3" s="75"/>
+      <c r="O3" s="75">
         <v>4</v>
       </c>
-      <c r="P3" s="88" t="s">
+      <c r="P3" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="Q3" s="80"/>
+      <c r="Q3" s="75"/>
     </row>
     <row r="4" spans="1:17" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" s="80" t="s">
+      <c r="A4" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="80">
+      <c r="C4" s="75">
         <v>5</v>
       </c>
-      <c r="D4" s="80">
-        <v>1</v>
-      </c>
-      <c r="E4" s="80">
-        <v>1</v>
-      </c>
-      <c r="F4" s="80"/>
-      <c r="G4" s="84" t="s">
+      <c r="D4" s="75">
+        <v>1</v>
+      </c>
+      <c r="E4" s="75">
+        <v>1</v>
+      </c>
+      <c r="F4" s="75"/>
+      <c r="G4" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="80">
+      <c r="H4" s="75">
         <v>5</v>
       </c>
-      <c r="I4" s="80">
+      <c r="I4" s="75">
         <v>17</v>
       </c>
-      <c r="J4" s="80">
-        <v>0</v>
-      </c>
-      <c r="K4" s="80">
+      <c r="J4" s="75">
+        <v>0</v>
+      </c>
+      <c r="K4" s="75">
         <v>20</v>
       </c>
-      <c r="L4" s="80">
+      <c r="L4" s="75">
         <v>4</v>
       </c>
-      <c r="M4" s="80">
+      <c r="M4" s="75">
         <v>14</v>
       </c>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80">
+      <c r="N4" s="75"/>
+      <c r="O4" s="75">
         <v>7</v>
       </c>
-      <c r="P4" s="88" t="s">
+      <c r="P4" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="Q4" s="80"/>
+      <c r="Q4" s="75"/>
     </row>
     <row r="5" spans="1:17" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="80">
+      <c r="C5" s="75">
         <v>100</v>
       </c>
-      <c r="D5" s="80">
+      <c r="D5" s="75">
         <v>50</v>
       </c>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="84" t="s">
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="80">
+      <c r="H5" s="75">
         <v>5</v>
       </c>
-      <c r="I5" s="80">
+      <c r="I5" s="75">
         <v>900</v>
       </c>
-      <c r="J5" s="80">
+      <c r="J5" s="75">
         <v>300</v>
       </c>
-      <c r="K5" s="80">
+      <c r="K5" s="75">
         <v>1300</v>
       </c>
-      <c r="L5" s="80">
+      <c r="L5" s="75">
         <v>800</v>
       </c>
-      <c r="M5" s="80">
+      <c r="M5" s="75">
         <v>1000</v>
       </c>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80">
+      <c r="N5" s="75"/>
+      <c r="O5" s="75">
         <v>600</v>
       </c>
-      <c r="P5" s="88" t="s">
+      <c r="P5" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="Q5" s="80"/>
+      <c r="Q5" s="75"/>
     </row>
     <row r="6" spans="1:17" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="80">
+      <c r="C6" s="75">
         <v>5</v>
       </c>
-      <c r="D6" s="80">
-        <v>1</v>
-      </c>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="84" t="s">
+      <c r="D6" s="75">
+        <v>1</v>
+      </c>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="80">
+      <c r="H6" s="75">
         <v>2</v>
       </c>
-      <c r="I6" s="80">
+      <c r="I6" s="75">
         <v>45</v>
       </c>
-      <c r="J6" s="80">
-        <v>0</v>
-      </c>
-      <c r="K6" s="80">
+      <c r="J6" s="75">
+        <v>0</v>
+      </c>
+      <c r="K6" s="75">
         <v>50</v>
       </c>
-      <c r="L6" s="80">
+      <c r="L6" s="75">
         <v>20</v>
       </c>
-      <c r="M6" s="80">
+      <c r="M6" s="75">
         <v>30</v>
       </c>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80">
+      <c r="N6" s="75"/>
+      <c r="O6" s="75">
         <v>12</v>
       </c>
-      <c r="P6" s="88" t="s">
+      <c r="P6" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="Q6" s="80"/>
+      <c r="Q6" s="75"/>
     </row>
     <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="78" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="80">
+      <c r="C7" s="75">
         <v>5</v>
       </c>
-      <c r="D7" s="80">
-        <v>1</v>
-      </c>
-      <c r="E7" s="80">
-        <v>1</v>
-      </c>
-      <c r="F7" s="80"/>
-      <c r="G7" s="84" t="s">
+      <c r="D7" s="75">
+        <v>1</v>
+      </c>
+      <c r="E7" s="75">
+        <v>1</v>
+      </c>
+      <c r="F7" s="75"/>
+      <c r="G7" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="80">
+      <c r="H7" s="75">
         <v>2</v>
       </c>
-      <c r="I7" s="80">
+      <c r="I7" s="75">
         <v>45</v>
       </c>
-      <c r="J7" s="80">
+      <c r="J7" s="75">
         <v>5</v>
       </c>
-      <c r="K7" s="80">
+      <c r="K7" s="75">
         <v>55</v>
       </c>
-      <c r="L7" s="80">
+      <c r="L7" s="75">
         <v>20</v>
       </c>
-      <c r="M7" s="80">
+      <c r="M7" s="75">
         <v>40</v>
       </c>
-      <c r="N7" s="80"/>
-      <c r="O7" s="80">
+      <c r="N7" s="75"/>
+      <c r="O7" s="75">
         <v>10</v>
       </c>
-      <c r="P7" s="88" t="s">
+      <c r="P7" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="Q7" s="80"/>
+      <c r="Q7" s="75"/>
     </row>
     <row r="8" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="80">
-        <v>1</v>
-      </c>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="84" t="s">
+      <c r="C8" s="75">
+        <v>1</v>
+      </c>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="80">
+      <c r="H8" s="75">
         <v>10</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="75">
         <v>9</v>
       </c>
-      <c r="J8" s="80">
-        <v>1</v>
-      </c>
-      <c r="K8" s="80">
+      <c r="J8" s="75">
+        <v>1</v>
+      </c>
+      <c r="K8" s="75">
         <v>12</v>
       </c>
-      <c r="L8" s="80">
-        <v>1</v>
-      </c>
-      <c r="M8" s="80">
+      <c r="L8" s="75">
+        <v>1</v>
+      </c>
+      <c r="M8" s="75">
         <v>3</v>
       </c>
-      <c r="N8" s="80" t="s">
+      <c r="N8" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="O8" s="80">
+      <c r="O8" s="75">
         <v>6</v>
       </c>
-      <c r="P8" s="88" t="s">
+      <c r="P8" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="Q8" s="80"/>
+      <c r="Q8" s="75"/>
     </row>
     <row r="9" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="80">
+      <c r="C9" s="75">
         <v>10</v>
       </c>
-      <c r="D9" s="80">
+      <c r="D9" s="75">
         <v>5</v>
       </c>
-      <c r="E9" s="80">
-        <v>1</v>
-      </c>
-      <c r="F9" s="80"/>
-      <c r="G9" s="84" t="s">
+      <c r="E9" s="75">
+        <v>1</v>
+      </c>
+      <c r="F9" s="75"/>
+      <c r="G9" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="80">
-        <v>1</v>
-      </c>
-      <c r="I9" s="80">
+      <c r="H9" s="75">
+        <v>1</v>
+      </c>
+      <c r="I9" s="75">
         <v>95</v>
       </c>
-      <c r="J9" s="80">
+      <c r="J9" s="75">
         <v>20</v>
       </c>
-      <c r="K9" s="80">
+      <c r="K9" s="75">
         <v>120</v>
       </c>
-      <c r="L9" s="80">
+      <c r="L9" s="75">
         <v>20</v>
       </c>
-      <c r="M9" s="80">
+      <c r="M9" s="75">
         <v>40</v>
       </c>
-      <c r="N9" s="80"/>
-      <c r="O9" s="80">
+      <c r="N9" s="75"/>
+      <c r="O9" s="75">
         <v>73</v>
       </c>
-      <c r="P9" s="88" t="s">
+      <c r="P9" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="Q9" s="80"/>
+      <c r="Q9" s="75"/>
     </row>
     <row r="10" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="80" t="s">
+      <c r="A10" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="78" t="s">
         <v>206</v>
       </c>
-      <c r="C10" s="80">
+      <c r="C10" s="75">
         <v>10</v>
       </c>
-      <c r="D10" s="80">
+      <c r="D10" s="75">
         <v>5</v>
       </c>
-      <c r="E10" s="80"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="84" t="s">
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="80">
+      <c r="H10" s="75">
         <v>5</v>
       </c>
-      <c r="I10" s="80">
+      <c r="I10" s="75">
         <v>95</v>
       </c>
-      <c r="J10" s="80">
+      <c r="J10" s="75">
         <v>1880</v>
       </c>
-      <c r="K10" s="80">
+      <c r="K10" s="75">
         <v>1980</v>
       </c>
-      <c r="L10" s="80">
+      <c r="L10" s="75">
         <v>1900</v>
       </c>
-      <c r="M10" s="80">
+      <c r="M10" s="75">
         <v>1950</v>
       </c>
-      <c r="N10" s="80"/>
-      <c r="O10" s="80">
+      <c r="N10" s="75"/>
+      <c r="O10" s="75">
         <v>1955</v>
       </c>
-      <c r="P10" s="88" t="s">
+      <c r="P10" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="Q10" s="80"/>
+      <c r="Q10" s="75"/>
     </row>
     <row r="11" spans="1:17" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11" s="80" t="s">
+      <c r="A11" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="80">
+      <c r="C11" s="75">
         <v>15</v>
       </c>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="84" t="s">
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="80">
+      <c r="H11" s="75">
         <v>9</v>
       </c>
-      <c r="I11" s="80">
+      <c r="I11" s="75">
         <v>165</v>
       </c>
-      <c r="J11" s="80">
+      <c r="J11" s="75">
         <v>15</v>
       </c>
-      <c r="K11" s="80">
+      <c r="K11" s="75">
         <v>195</v>
       </c>
-      <c r="L11" s="80">
+      <c r="L11" s="75">
         <v>10</v>
       </c>
-      <c r="M11" s="80">
+      <c r="M11" s="75">
         <v>50</v>
       </c>
-      <c r="N11" s="80" t="s">
+      <c r="N11" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="O11" s="80">
+      <c r="O11" s="75">
         <v>165</v>
       </c>
-      <c r="P11" s="88" t="s">
+      <c r="P11" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="Q11" s="80"/>
+      <c r="Q11" s="75"/>
     </row>
     <row r="12" spans="1:17" ht="34" x14ac:dyDescent="0.2">
-      <c r="A12" s="80" t="s">
+      <c r="A12" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="80">
+      <c r="C12" s="75">
         <v>10</v>
       </c>
-      <c r="D12" s="80">
+      <c r="D12" s="75">
         <v>5</v>
       </c>
-      <c r="E12" s="80">
-        <v>1</v>
-      </c>
-      <c r="F12" s="80"/>
-      <c r="G12" s="84" t="s">
+      <c r="E12" s="75">
+        <v>1</v>
+      </c>
+      <c r="F12" s="75"/>
+      <c r="G12" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="80">
-        <v>1</v>
-      </c>
-      <c r="I12" s="80">
+      <c r="H12" s="75">
+        <v>1</v>
+      </c>
+      <c r="I12" s="75">
         <v>95</v>
       </c>
-      <c r="J12" s="80">
+      <c r="J12" s="75">
         <v>40</v>
       </c>
-      <c r="K12" s="80">
+      <c r="K12" s="75">
         <v>140</v>
       </c>
-      <c r="L12" s="80">
+      <c r="L12" s="75">
         <v>50</v>
       </c>
-      <c r="M12" s="80">
+      <c r="M12" s="75">
         <v>110</v>
       </c>
-      <c r="N12" s="80" t="s">
+      <c r="N12" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="O12" s="80">
+      <c r="O12" s="75">
         <v>89.99</v>
       </c>
-      <c r="P12" s="88" t="s">
+      <c r="P12" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="Q12" s="80"/>
+      <c r="Q12" s="75"/>
     </row>
     <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="80" t="s">
+      <c r="A13" s="75" t="s">
         <v>275</v>
       </c>
-      <c r="B13" s="83" t="s">
+      <c r="B13" s="78" t="s">
         <v>274</v>
       </c>
-      <c r="C13" s="80">
-        <v>1</v>
-      </c>
-      <c r="D13" s="80"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="84" t="s">
+      <c r="C13" s="75">
+        <v>1</v>
+      </c>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="80">
+      <c r="H13" s="75">
         <v>10</v>
       </c>
-      <c r="I13" s="80">
+      <c r="I13" s="75">
         <v>9</v>
       </c>
-      <c r="J13" s="80">
-        <v>1</v>
-      </c>
-      <c r="K13" s="80">
+      <c r="J13" s="75">
+        <v>1</v>
+      </c>
+      <c r="K13" s="75">
         <v>12</v>
       </c>
-      <c r="L13" s="80">
-        <v>1</v>
-      </c>
-      <c r="M13" s="80">
+      <c r="L13" s="75">
+        <v>1</v>
+      </c>
+      <c r="M13" s="75">
         <v>3</v>
       </c>
-      <c r="N13" s="80" t="s">
+      <c r="N13" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="O13" s="80">
+      <c r="O13" s="75">
         <v>12</v>
       </c>
-      <c r="P13" s="88" t="s">
+      <c r="P13" s="83" t="s">
         <v>276</v>
       </c>
-      <c r="Q13" s="80"/>
+      <c r="Q13" s="75"/>
     </row>
     <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="80" t="s">
+      <c r="A14" s="75" t="s">
         <v>277</v>
       </c>
-      <c r="B14" s="83" t="s">
+      <c r="B14" s="78" t="s">
         <v>278</v>
       </c>
-      <c r="C14" s="80">
+      <c r="C14" s="75">
         <v>100</v>
       </c>
-      <c r="D14" s="80">
+      <c r="D14" s="75">
         <v>5</v>
       </c>
-      <c r="E14" s="80">
-        <v>1</v>
-      </c>
-      <c r="F14" s="80"/>
-      <c r="G14" s="84"/>
-      <c r="H14" s="80">
-        <v>1</v>
-      </c>
-      <c r="I14" s="80">
+      <c r="E14" s="75">
+        <v>1</v>
+      </c>
+      <c r="F14" s="75"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="75">
+        <v>1</v>
+      </c>
+      <c r="I14" s="75">
         <v>95</v>
       </c>
-      <c r="J14" s="80">
+      <c r="J14" s="75">
         <v>10</v>
       </c>
-      <c r="K14" s="80">
+      <c r="K14" s="75">
         <v>110</v>
       </c>
-      <c r="L14" s="80">
+      <c r="L14" s="75">
         <v>25</v>
       </c>
-      <c r="M14" s="80">
+      <c r="M14" s="75">
         <v>75</v>
       </c>
-      <c r="N14" s="80"/>
-      <c r="O14" s="80">
+      <c r="N14" s="75"/>
+      <c r="O14" s="75">
         <v>110</v>
       </c>
-      <c r="P14" s="88" t="s">
+      <c r="P14" s="83" t="s">
         <v>279</v>
       </c>
-      <c r="Q14" s="80"/>
+      <c r="Q14" s="75"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" s="80"/>
-      <c r="B15" s="83"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="84"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="80"/>
-      <c r="L15" s="80"/>
-      <c r="M15" s="80"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="80"/>
-      <c r="Q15" s="80"/>
+      <c r="A15" s="75"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="75"/>
+      <c r="L15" s="75"/>
+      <c r="M15" s="75"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="75"/>
+      <c r="P15" s="75"/>
+      <c r="Q15" s="75"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16" s="80"/>
-      <c r="B16" s="83"/>
-      <c r="C16" s="80"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="80"/>
-      <c r="G16" s="84"/>
-      <c r="H16" s="80"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="80"/>
-      <c r="K16" s="80"/>
-      <c r="L16" s="80"/>
-      <c r="M16" s="80"/>
-      <c r="N16" s="80"/>
-      <c r="O16" s="80"/>
-      <c r="P16" s="80"/>
-      <c r="Q16" s="80"/>
+      <c r="A16" s="75"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="75"/>
+      <c r="I16" s="75"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="75"/>
+      <c r="L16" s="75"/>
+      <c r="M16" s="75"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="75"/>
+      <c r="P16" s="75"/>
+      <c r="Q16" s="75"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A17" s="80"/>
-      <c r="B17" s="83"/>
-      <c r="C17" s="80"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="84"/>
-      <c r="H17" s="80"/>
-      <c r="I17" s="80"/>
-      <c r="J17" s="80"/>
-      <c r="K17" s="80"/>
-      <c r="L17" s="80"/>
-      <c r="M17" s="80"/>
-      <c r="N17" s="80"/>
-      <c r="O17" s="80"/>
-      <c r="P17" s="80"/>
-      <c r="Q17" s="80"/>
+      <c r="A17" s="75"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="75"/>
+      <c r="I17" s="75"/>
+      <c r="J17" s="75"/>
+      <c r="K17" s="75"/>
+      <c r="L17" s="75"/>
+      <c r="M17" s="75"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="75"/>
+      <c r="P17" s="75"/>
+      <c r="Q17" s="75"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A18" s="80"/>
-      <c r="B18" s="83"/>
-      <c r="C18" s="80"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="80"/>
-      <c r="G18" s="84"/>
-      <c r="H18" s="80"/>
-      <c r="I18" s="80"/>
-      <c r="J18" s="80"/>
-      <c r="K18" s="80"/>
-      <c r="L18" s="80"/>
-      <c r="M18" s="80"/>
-      <c r="N18" s="80"/>
-      <c r="O18" s="80"/>
-      <c r="P18" s="80"/>
-      <c r="Q18" s="80"/>
+      <c r="A18" s="75"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="79"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="75"/>
+      <c r="J18" s="75"/>
+      <c r="K18" s="75"/>
+      <c r="L18" s="75"/>
+      <c r="M18" s="75"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="75"/>
+      <c r="P18" s="75"/>
+      <c r="Q18" s="75"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2806,1252 +2866,1328 @@
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="39.1640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20" style="4" customWidth="1"/>
-    <col min="6" max="6" width="7.5" style="5" customWidth="1"/>
-    <col min="7" max="7" width="19.1640625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="6.6640625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" style="6" customWidth="1"/>
-    <col min="10" max="10" width="7.1640625" style="5" customWidth="1"/>
-    <col min="11" max="11" width="16" style="6" customWidth="1"/>
-    <col min="12" max="12" width="7.83203125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="15.1640625" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8" style="5" customWidth="1"/>
-    <col min="15" max="15" width="15.5" style="6" customWidth="1"/>
-    <col min="16" max="16" width="7.1640625" style="5" customWidth="1"/>
-    <col min="17" max="17" width="17.1640625" style="6" customWidth="1"/>
-    <col min="18" max="18" width="7" style="5" customWidth="1"/>
-    <col min="19" max="19" width="19" style="6" customWidth="1"/>
-    <col min="20" max="20" width="7.1640625" style="65" customWidth="1"/>
-    <col min="21" max="21" width="21.33203125" style="9" customWidth="1"/>
-    <col min="22" max="22" width="10.83203125" style="10"/>
-    <col min="23" max="23" width="18.83203125" style="7" customWidth="1"/>
-    <col min="24" max="24" width="10.83203125" style="8"/>
-    <col min="25" max="25" width="23.33203125" style="7" customWidth="1"/>
-    <col min="26" max="26" width="10.83203125" style="11"/>
-    <col min="27" max="27" width="15.5" style="9" customWidth="1"/>
-    <col min="28" max="28" width="10.83203125" style="10"/>
-    <col min="29" max="29" width="15.6640625" style="12" customWidth="1"/>
-    <col min="30" max="30" width="10.83203125" style="13"/>
-    <col min="31" max="31" width="15.83203125" style="12" customWidth="1"/>
-    <col min="32" max="32" width="9" style="3" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="88" customWidth="1"/>
+    <col min="5" max="5" width="20" style="3" customWidth="1"/>
+    <col min="6" max="6" width="7.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="19.1640625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="7.1640625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="16" style="5" customWidth="1"/>
+    <col min="12" max="12" width="7.83203125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="15.1640625" style="5" customWidth="1"/>
+    <col min="14" max="14" width="8" style="4" customWidth="1"/>
+    <col min="15" max="15" width="15.5" style="5" customWidth="1"/>
+    <col min="16" max="16" width="7.1640625" style="4" customWidth="1"/>
+    <col min="17" max="17" width="17.1640625" style="5" customWidth="1"/>
+    <col min="18" max="18" width="7" style="4" customWidth="1"/>
+    <col min="19" max="19" width="19" style="5" customWidth="1"/>
+    <col min="20" max="20" width="7.1640625" style="61" customWidth="1"/>
+    <col min="21" max="21" width="21.33203125" style="8" customWidth="1"/>
+    <col min="22" max="22" width="10.83203125" style="9"/>
+    <col min="23" max="23" width="18.83203125" style="6" customWidth="1"/>
+    <col min="24" max="24" width="10.83203125" style="7"/>
+    <col min="25" max="25" width="23.33203125" style="6" customWidth="1"/>
+    <col min="26" max="26" width="10.83203125" style="10"/>
+    <col min="27" max="27" width="15.5" style="8" customWidth="1"/>
+    <col min="28" max="28" width="10.83203125" style="9"/>
+    <col min="29" max="29" width="15.6640625" style="11" customWidth="1"/>
+    <col min="30" max="30" width="10.83203125" style="12"/>
+    <col min="31" max="31" width="15.83203125" style="11" customWidth="1"/>
+    <col min="32" max="32" width="9" style="2" customWidth="1"/>
     <col min="33" max="33" width="7.83203125" customWidth="1"/>
     <col min="34" max="34" width="13.83203125" customWidth="1"/>
     <col min="35" max="35" width="32.33203125" style="1" customWidth="1"/>
     <col min="36" max="36" width="28.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="66" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A1" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="66" t="s">
+    <row r="1" spans="1:36" s="62" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A1" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="D1" s="84" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="69" t="s">
+      <c r="F1" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="G1" s="70" t="s">
+      <c r="G1" s="65" t="s">
         <v>98</v>
       </c>
-      <c r="H1" s="69" t="s">
+      <c r="H1" s="64" t="s">
         <v>99</v>
       </c>
-      <c r="I1" s="70" t="s">
+      <c r="I1" s="65" t="s">
         <v>100</v>
       </c>
-      <c r="J1" s="69" t="s">
+      <c r="J1" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="K1" s="70" t="s">
+      <c r="K1" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="L1" s="71" t="s">
+      <c r="L1" s="66" t="s">
         <v>103</v>
       </c>
-      <c r="M1" s="70" t="s">
+      <c r="M1" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="N1" s="71" t="s">
+      <c r="N1" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="O1" s="70" t="s">
+      <c r="O1" s="65" t="s">
         <v>106</v>
       </c>
-      <c r="P1" s="71" t="s">
+      <c r="P1" s="66" t="s">
         <v>107</v>
       </c>
-      <c r="Q1" s="70" t="s">
+      <c r="Q1" s="65" t="s">
         <v>108</v>
       </c>
-      <c r="R1" s="71" t="s">
+      <c r="R1" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="S1" s="70" t="s">
+      <c r="S1" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="T1" s="81" t="s">
+      <c r="T1" s="76" t="s">
         <v>111</v>
       </c>
-      <c r="U1" s="72" t="s">
+      <c r="U1" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="V1" s="73" t="s">
+      <c r="V1" s="68" t="s">
         <v>113</v>
       </c>
-      <c r="W1" s="74" t="s">
+      <c r="W1" s="69" t="s">
         <v>114</v>
       </c>
-      <c r="X1" s="75" t="s">
+      <c r="X1" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="Y1" s="74" t="s">
+      <c r="Y1" s="69" t="s">
         <v>116</v>
       </c>
-      <c r="Z1" s="76" t="s">
+      <c r="Z1" s="71" t="s">
         <v>117</v>
       </c>
-      <c r="AA1" s="72" t="s">
+      <c r="AA1" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="AB1" s="73" t="s">
+      <c r="AB1" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="AC1" s="77" t="s">
+      <c r="AC1" s="72" t="s">
         <v>120</v>
       </c>
-      <c r="AD1" s="78" t="s">
+      <c r="AD1" s="73" t="s">
         <v>121</v>
       </c>
-      <c r="AE1" s="77" t="s">
+      <c r="AE1" s="72" t="s">
         <v>122</v>
       </c>
-      <c r="AF1" s="79" t="s">
+      <c r="AF1" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="AG1" s="66" t="s">
+      <c r="AG1" s="62" t="s">
         <v>124</v>
       </c>
-      <c r="AH1" s="66" t="s">
+      <c r="AH1" s="62" t="s">
         <v>125</v>
       </c>
-      <c r="AI1" s="66" t="s">
+      <c r="AI1" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="AJ1" s="66" t="s">
+      <c r="AJ1" s="62" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:36" s="45" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A2" s="61" t="s">
+    <row r="2" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A2" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="D2" s="32">
+      <c r="D2" s="85">
         <v>20</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="35" t="s">
+      <c r="F2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="H2" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="35" t="s">
+      <c r="H2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="J2" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" s="35" t="s">
+      <c r="J2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="L2" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" s="35" t="s">
+      <c r="L2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="N2" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" s="35" t="s">
+      <c r="N2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="P2" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="35" t="s">
+      <c r="P2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="R2" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S2" s="33" t="s">
+      <c r="R2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="T2" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="U2" s="36" t="s">
+      <c r="T2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="V2" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="W2" s="36" t="s">
+      <c r="V2" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="X2" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="36" t="s">
+      <c r="X2" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="Z2" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="38" t="s">
+      <c r="Z2" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="AB2" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="41" t="s">
+      <c r="AB2" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="AD2" s="42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="63" t="s">
+      <c r="AD2" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="59" t="s">
         <v>218</v>
       </c>
-      <c r="AF2" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="30" t="s">
+      <c r="AF2" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="AJ2" s="44" t="s">
+      <c r="AJ2" s="41" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:36" s="45" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="61" t="s">
+    <row r="3" spans="1:36" s="42" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A3" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="85">
         <v>20</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="F3" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="35" t="s">
+      <c r="F3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="H3" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="35" t="s">
+      <c r="H3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="J3" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" s="35" t="s">
+      <c r="J3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="L3" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="35" t="s">
+      <c r="L3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="N3" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" s="35" t="s">
+      <c r="N3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="P3" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="35" t="s">
+      <c r="P3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="32" t="s">
         <v>235</v>
       </c>
-      <c r="R3" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" s="35" t="s">
+      <c r="R3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="T3" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="U3" s="38" t="s">
+      <c r="T3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="V3" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="W3" s="36" t="s">
+      <c r="V3" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="X3" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="36" t="s">
+      <c r="X3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="33" t="s">
         <v>233</v>
       </c>
-      <c r="Z3" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="38" t="s">
+      <c r="Z3" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="AB3" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="41" t="s">
+      <c r="AB3" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="AD3" s="42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="41" t="s">
+      <c r="AD3" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="AF3" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH3" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI3" s="30" t="s">
+      <c r="AF3" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="AJ3" s="44" t="s">
+      <c r="AJ3" s="41" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="4" spans="1:36" s="45" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" s="61" t="s">
+    <row r="4" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A4" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="43" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="85">
         <v>20</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="F4" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="35" t="s">
+      <c r="F4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="H4" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="35" t="s">
+      <c r="H4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="J4" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" s="35" t="s">
+      <c r="J4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="L4" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" s="35" t="s">
+      <c r="L4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="N4" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="35" t="s">
+      <c r="N4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="P4" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="35" t="s">
+      <c r="P4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="R4" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S4" s="35" t="s">
+      <c r="R4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" s="32" t="s">
         <v>221</v>
       </c>
-      <c r="T4" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="U4" s="38" t="s">
+      <c r="T4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="V4" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="36" t="s">
+      <c r="V4" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="X4" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="36" t="s">
+      <c r="X4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="Z4" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="38" t="s">
+      <c r="Z4" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="AB4" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="41" t="s">
+      <c r="AB4" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="AD4" s="42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="41" t="s">
+      <c r="AD4" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="38" t="s">
         <v>222</v>
       </c>
-      <c r="AF4" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI4" s="30" t="s">
+      <c r="AF4" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="AJ4" s="44" t="s">
+      <c r="AJ4" s="41" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="45" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="61" t="s">
+    <row r="5" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="57" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="85">
         <v>20</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="F5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="35" t="s">
+      <c r="F5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="H5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="35" t="s">
+      <c r="H5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="J5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="35" t="s">
+      <c r="J5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="L5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="35" t="s">
+      <c r="L5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="N5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="35" t="s">
+      <c r="N5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="P5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="35" t="s">
+      <c r="P5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="R5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" s="35" t="s">
+      <c r="R5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="T5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="U5" s="38" t="s">
+      <c r="T5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="V5" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" s="36" t="s">
+      <c r="V5" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="X5" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="36" t="s">
+      <c r="X5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="Z5" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="38" t="s">
+      <c r="Z5" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="AB5" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="41" t="s">
+      <c r="AB5" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="AD5" s="42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="41" t="s">
+      <c r="AD5" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="AF5" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="30" t="s">
+      <c r="AF5" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="AJ5" s="44" t="s">
+      <c r="AJ5" s="41" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="6" spans="1:36" s="45" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="61" t="s">
+    <row r="6" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A6" s="57" t="s">
         <v>183</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="85">
         <v>20</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="F6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="35" t="s">
+      <c r="F6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="32" t="s">
         <v>208</v>
       </c>
-      <c r="H6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="35" t="s">
+      <c r="H6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="J6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="35" t="s">
+      <c r="J6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="L6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="35" t="s">
+      <c r="L6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="32" t="s">
         <v>209</v>
       </c>
-      <c r="N6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="35" t="s">
+      <c r="N6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="32" t="s">
         <v>210</v>
       </c>
-      <c r="P6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="35" t="s">
+      <c r="P6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="R6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="33" t="s">
+      <c r="R6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="T6" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" s="38" t="s">
+      <c r="T6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="35" t="s">
         <v>212</v>
       </c>
-      <c r="V6" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="36" t="s">
+      <c r="V6" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="X6" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="36" t="s">
+      <c r="X6" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="33" t="s">
         <v>227</v>
       </c>
-      <c r="Z6" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="38" t="s">
+      <c r="Z6" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="35" t="s">
         <v>214</v>
       </c>
-      <c r="AB6" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="41" t="s">
+      <c r="AB6" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="AD6" s="42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="41" t="s">
+      <c r="AD6" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="AF6" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="30" t="s">
+      <c r="AF6" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="AJ6" s="44" t="s">
+      <c r="AJ6" s="41" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:36" s="29" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="62" t="s">
+    <row r="7" spans="1:36" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="58" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="86">
         <v>20</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="F7" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="19" t="s">
+      <c r="F7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="H7" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="19" t="s">
+      <c r="H7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="J7" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="19" t="s">
+      <c r="J7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="L7" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="19" t="s">
+      <c r="L7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="N7" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="19" t="s">
+      <c r="N7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="P7" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="19" t="s">
+      <c r="P7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="R7" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="33" t="s">
+      <c r="R7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="T7" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="22" t="s">
+      <c r="T7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="V7" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="20" t="s">
+      <c r="V7" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="X7" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="20" t="s">
+      <c r="X7" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="Z7" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="22" t="s">
+      <c r="Z7" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="AB7" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="25" t="s">
+      <c r="AB7" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="AD7" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="25" t="s">
+      <c r="AD7" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="23" t="s">
         <v>201</v>
       </c>
-      <c r="AF7" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="14" t="s">
+      <c r="AF7" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="AJ7" s="28" t="s">
+      <c r="AJ7" s="26" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="47"/>
-      <c r="B8" s="48"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="52"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="52"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="52"/>
-      <c r="R8" s="51"/>
-      <c r="S8" s="52"/>
-      <c r="T8" s="64"/>
-      <c r="U8" s="55"/>
-      <c r="V8" s="56"/>
-      <c r="W8" s="53"/>
-      <c r="X8" s="54"/>
-      <c r="Y8" s="53"/>
-      <c r="Z8" s="57"/>
-      <c r="AA8" s="55"/>
-      <c r="AB8" s="56"/>
-      <c r="AC8" s="58"/>
-      <c r="AD8" s="59"/>
-      <c r="AE8" s="58"/>
-      <c r="AF8" s="60"/>
-      <c r="AI8" s="48"/>
-    </row>
-    <row r="9" spans="1:36" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="47"/>
-      <c r="B9" s="48"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="51"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="52"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="52"/>
-      <c r="T9" s="64"/>
-      <c r="U9" s="55"/>
-      <c r="V9" s="56"/>
-      <c r="W9" s="53"/>
-      <c r="X9" s="54"/>
-      <c r="Y9" s="53"/>
-      <c r="Z9" s="57"/>
-      <c r="AA9" s="55"/>
-      <c r="AB9" s="56"/>
-      <c r="AC9" s="58"/>
-      <c r="AD9" s="59"/>
-      <c r="AE9" s="58"/>
-      <c r="AF9" s="60"/>
-      <c r="AI9" s="48"/>
-    </row>
-    <row r="10" spans="1:36" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="47"/>
-      <c r="B10" s="48"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="52"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="52"/>
-      <c r="R10" s="51"/>
-      <c r="S10" s="52"/>
-      <c r="T10" s="64"/>
-      <c r="U10" s="55"/>
-      <c r="V10" s="56"/>
-      <c r="W10" s="53"/>
-      <c r="X10" s="54"/>
-      <c r="Y10" s="53"/>
-      <c r="Z10" s="57"/>
-      <c r="AA10" s="55"/>
-      <c r="AB10" s="56"/>
-      <c r="AC10" s="58"/>
-      <c r="AD10" s="59"/>
-      <c r="AE10" s="58"/>
-      <c r="AF10" s="60"/>
-      <c r="AI10" s="48"/>
-    </row>
-    <row r="11" spans="1:36" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="47"/>
-      <c r="B11" s="48"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="51"/>
-      <c r="O11" s="52"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="52"/>
-      <c r="R11" s="51"/>
-      <c r="S11" s="52"/>
-      <c r="T11" s="64"/>
-      <c r="U11" s="55"/>
-      <c r="V11" s="56"/>
-      <c r="W11" s="53"/>
-      <c r="X11" s="54"/>
-      <c r="Y11" s="53"/>
-      <c r="Z11" s="57"/>
-      <c r="AA11" s="55"/>
-      <c r="AB11" s="56"/>
-      <c r="AC11" s="58"/>
-      <c r="AD11" s="59"/>
-      <c r="AE11" s="58"/>
-      <c r="AF11" s="60"/>
-      <c r="AI11" s="48"/>
-    </row>
-    <row r="12" spans="1:36" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="47"/>
-      <c r="B12" s="48"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="51"/>
-      <c r="O12" s="52"/>
-      <c r="P12" s="51"/>
-      <c r="Q12" s="52"/>
-      <c r="R12" s="51"/>
-      <c r="S12" s="52"/>
-      <c r="T12" s="64"/>
-      <c r="U12" s="55"/>
-      <c r="V12" s="56"/>
-      <c r="W12" s="53"/>
-      <c r="X12" s="54"/>
-      <c r="Y12" s="53"/>
-      <c r="Z12" s="57"/>
-      <c r="AA12" s="55"/>
-      <c r="AB12" s="56"/>
-      <c r="AC12" s="58"/>
-      <c r="AD12" s="59"/>
-      <c r="AE12" s="58"/>
-      <c r="AF12" s="60"/>
-      <c r="AI12" s="48"/>
-    </row>
-    <row r="13" spans="1:36" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="47"/>
-      <c r="B13" s="48"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="51"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="51"/>
-      <c r="O13" s="52"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="52"/>
-      <c r="R13" s="51"/>
-      <c r="S13" s="52"/>
-      <c r="T13" s="64"/>
-      <c r="U13" s="55"/>
-      <c r="V13" s="56"/>
-      <c r="W13" s="53"/>
-      <c r="X13" s="54"/>
-      <c r="Y13" s="53"/>
-      <c r="Z13" s="57"/>
-      <c r="AA13" s="55"/>
-      <c r="AB13" s="56"/>
-      <c r="AC13" s="58"/>
-      <c r="AD13" s="59"/>
-      <c r="AE13" s="58"/>
-      <c r="AF13" s="60"/>
-      <c r="AI13" s="48"/>
-    </row>
-    <row r="14" spans="1:36" s="45" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="47"/>
-      <c r="B14" s="48"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="51"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="51"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="52"/>
-      <c r="R14" s="51"/>
-      <c r="S14" s="52"/>
-      <c r="T14" s="64"/>
-      <c r="U14" s="55"/>
-      <c r="V14" s="56"/>
-      <c r="W14" s="53"/>
-      <c r="X14" s="54"/>
-      <c r="Y14" s="53"/>
-      <c r="Z14" s="57"/>
-      <c r="AA14" s="55"/>
-      <c r="AB14" s="56"/>
-      <c r="AC14" s="58"/>
-      <c r="AD14" s="59"/>
-      <c r="AE14" s="58"/>
-      <c r="AF14" s="60"/>
-      <c r="AI14" s="48"/>
-    </row>
-    <row r="15" spans="1:36" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="47"/>
-      <c r="B15" s="48"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="52"/>
-      <c r="L15" s="51"/>
-      <c r="M15" s="52"/>
-      <c r="N15" s="51"/>
-      <c r="O15" s="52"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="52"/>
-      <c r="R15" s="51"/>
-      <c r="S15" s="52"/>
-      <c r="T15" s="64"/>
-      <c r="U15" s="55"/>
-      <c r="V15" s="56"/>
-      <c r="W15" s="53"/>
-      <c r="X15" s="54"/>
-      <c r="Y15" s="53"/>
-      <c r="Z15" s="57"/>
-      <c r="AA15" s="55"/>
-      <c r="AB15" s="56"/>
-      <c r="AC15" s="58"/>
-      <c r="AD15" s="59"/>
-      <c r="AE15" s="58"/>
-      <c r="AF15" s="60"/>
-      <c r="AI15" s="48"/>
-    </row>
-    <row r="16" spans="1:36" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="47"/>
-      <c r="B16" s="48"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="51"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="51"/>
-      <c r="O16" s="52"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="52"/>
-      <c r="R16" s="51"/>
-      <c r="S16" s="52"/>
-      <c r="T16" s="64"/>
-      <c r="U16" s="55"/>
-      <c r="V16" s="56"/>
-      <c r="W16" s="53"/>
-      <c r="X16" s="54"/>
-      <c r="Y16" s="53"/>
-      <c r="Z16" s="57"/>
-      <c r="AA16" s="55"/>
-      <c r="AB16" s="56"/>
-      <c r="AC16" s="58"/>
-      <c r="AD16" s="59"/>
-      <c r="AE16" s="58"/>
-      <c r="AF16" s="60"/>
-      <c r="AI16" s="48"/>
-    </row>
-    <row r="17" spans="1:35" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="47"/>
-      <c r="B17" s="48"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="51"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="51"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="52"/>
-      <c r="R17" s="51"/>
-      <c r="S17" s="52"/>
-      <c r="T17" s="64"/>
-      <c r="U17" s="55"/>
-      <c r="V17" s="56"/>
-      <c r="W17" s="53"/>
-      <c r="X17" s="54"/>
-      <c r="Y17" s="53"/>
-      <c r="Z17" s="57"/>
-      <c r="AA17" s="55"/>
-      <c r="AB17" s="56"/>
-      <c r="AC17" s="58"/>
-      <c r="AD17" s="59"/>
-      <c r="AE17" s="58"/>
-      <c r="AF17" s="60"/>
-      <c r="AI17" s="48"/>
-    </row>
-    <row r="18" spans="1:35" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="47"/>
-      <c r="B18" s="48"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="51"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="51"/>
-      <c r="O18" s="52"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="52"/>
-      <c r="R18" s="51"/>
-      <c r="S18" s="52"/>
-      <c r="T18" s="64"/>
-      <c r="U18" s="55"/>
-      <c r="V18" s="56"/>
-      <c r="W18" s="53"/>
-      <c r="X18" s="54"/>
-      <c r="Y18" s="53"/>
-      <c r="Z18" s="57"/>
-      <c r="AA18" s="55"/>
-      <c r="AB18" s="56"/>
-      <c r="AC18" s="58"/>
-      <c r="AD18" s="59"/>
-      <c r="AE18" s="58"/>
-      <c r="AF18" s="60"/>
-      <c r="AI18" s="48"/>
-    </row>
-    <row r="19" spans="1:35" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="47"/>
-      <c r="B19" s="48"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="52"/>
-      <c r="L19" s="51"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="52"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="52"/>
-      <c r="R19" s="51"/>
-      <c r="S19" s="52"/>
-      <c r="T19" s="64"/>
-      <c r="U19" s="55"/>
-      <c r="V19" s="56"/>
-      <c r="W19" s="53"/>
-      <c r="X19" s="54"/>
-      <c r="Y19" s="53"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="55"/>
-      <c r="AB19" s="56"/>
-      <c r="AC19" s="58"/>
-      <c r="AD19" s="59"/>
-      <c r="AE19" s="58"/>
-      <c r="AF19" s="60"/>
-      <c r="AI19" s="48"/>
-    </row>
-    <row r="20" spans="1:35" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="47"/>
-      <c r="B20" s="48"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="52"/>
-      <c r="L20" s="51"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="51"/>
-      <c r="O20" s="52"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="52"/>
-      <c r="R20" s="51"/>
-      <c r="S20" s="52"/>
-      <c r="T20" s="64"/>
-      <c r="U20" s="55"/>
-      <c r="V20" s="56"/>
-      <c r="W20" s="53"/>
-      <c r="X20" s="54"/>
-      <c r="Y20" s="53"/>
-      <c r="Z20" s="57"/>
-      <c r="AA20" s="55"/>
-      <c r="AB20" s="56"/>
-      <c r="AC20" s="58"/>
-      <c r="AD20" s="59"/>
-      <c r="AE20" s="58"/>
-      <c r="AF20" s="60"/>
-      <c r="AI20" s="48"/>
+    <row r="8" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A8" s="44" t="s">
+        <v>280</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="86">
+        <v>20</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>282</v>
+      </c>
+      <c r="F8" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="48" t="s">
+        <v>291</v>
+      </c>
+      <c r="H8" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="48" t="s">
+        <v>283</v>
+      </c>
+      <c r="J8" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="48" t="s">
+        <v>290</v>
+      </c>
+      <c r="L8" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="48" t="s">
+        <v>284</v>
+      </c>
+      <c r="N8" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="48" t="s">
+        <v>285</v>
+      </c>
+      <c r="P8" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="48" t="s">
+        <v>286</v>
+      </c>
+      <c r="R8" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="48" t="s">
+        <v>287</v>
+      </c>
+      <c r="T8" s="60" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="51" t="s">
+        <v>294</v>
+      </c>
+      <c r="V8" s="52" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="49" t="s">
+        <v>293</v>
+      </c>
+      <c r="X8" s="50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="49" t="s">
+        <v>295</v>
+      </c>
+      <c r="Z8" s="53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="51" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB8" s="52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="54" t="s">
+        <v>289</v>
+      </c>
+      <c r="AD8" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="54" t="s">
+        <v>292</v>
+      </c>
+      <c r="AF8" s="56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="45" t="s">
+        <v>296</v>
+      </c>
+      <c r="AJ8" s="42" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="44"/>
+      <c r="B9" s="45"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="47"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="47"/>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="60"/>
+      <c r="U9" s="51"/>
+      <c r="V9" s="52"/>
+      <c r="W9" s="49"/>
+      <c r="X9" s="50"/>
+      <c r="Y9" s="49"/>
+      <c r="Z9" s="53"/>
+      <c r="AA9" s="51"/>
+      <c r="AB9" s="52"/>
+      <c r="AC9" s="54"/>
+      <c r="AD9" s="55"/>
+      <c r="AE9" s="54"/>
+      <c r="AF9" s="56"/>
+      <c r="AI9" s="45"/>
+    </row>
+    <row r="10" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="44"/>
+      <c r="B10" s="45"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="47"/>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="47"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="60"/>
+      <c r="U10" s="51"/>
+      <c r="V10" s="52"/>
+      <c r="W10" s="49"/>
+      <c r="X10" s="50"/>
+      <c r="Y10" s="49"/>
+      <c r="Z10" s="53"/>
+      <c r="AA10" s="51"/>
+      <c r="AB10" s="52"/>
+      <c r="AC10" s="54"/>
+      <c r="AD10" s="55"/>
+      <c r="AE10" s="54"/>
+      <c r="AF10" s="56"/>
+      <c r="AI10" s="45"/>
+    </row>
+    <row r="11" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="44"/>
+      <c r="B11" s="45"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="47"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="47"/>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="47"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="60"/>
+      <c r="U11" s="51"/>
+      <c r="V11" s="52"/>
+      <c r="W11" s="49"/>
+      <c r="X11" s="50"/>
+      <c r="Y11" s="49"/>
+      <c r="Z11" s="53"/>
+      <c r="AA11" s="51"/>
+      <c r="AB11" s="52"/>
+      <c r="AC11" s="54"/>
+      <c r="AD11" s="55"/>
+      <c r="AE11" s="54"/>
+      <c r="AF11" s="56"/>
+      <c r="AI11" s="45"/>
+    </row>
+    <row r="12" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="44"/>
+      <c r="B12" s="45"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="60"/>
+      <c r="U12" s="51"/>
+      <c r="V12" s="52"/>
+      <c r="W12" s="49"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="49"/>
+      <c r="Z12" s="53"/>
+      <c r="AA12" s="51"/>
+      <c r="AB12" s="52"/>
+      <c r="AC12" s="54"/>
+      <c r="AD12" s="55"/>
+      <c r="AE12" s="54"/>
+      <c r="AF12" s="56"/>
+      <c r="AI12" s="45"/>
+    </row>
+    <row r="13" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="44"/>
+      <c r="B13" s="45"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="48"/>
+      <c r="P13" s="47"/>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="60"/>
+      <c r="U13" s="51"/>
+      <c r="V13" s="52"/>
+      <c r="W13" s="49"/>
+      <c r="X13" s="50"/>
+      <c r="Y13" s="49"/>
+      <c r="Z13" s="53"/>
+      <c r="AA13" s="51"/>
+      <c r="AB13" s="52"/>
+      <c r="AC13" s="54"/>
+      <c r="AD13" s="55"/>
+      <c r="AE13" s="54"/>
+      <c r="AF13" s="56"/>
+      <c r="AI13" s="45"/>
+    </row>
+    <row r="14" spans="1:36" s="42" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="44"/>
+      <c r="B14" s="45"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="48"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="48"/>
+      <c r="R14" s="47"/>
+      <c r="S14" s="48"/>
+      <c r="T14" s="60"/>
+      <c r="U14" s="51"/>
+      <c r="V14" s="52"/>
+      <c r="W14" s="49"/>
+      <c r="X14" s="50"/>
+      <c r="Y14" s="49"/>
+      <c r="Z14" s="53"/>
+      <c r="AA14" s="51"/>
+      <c r="AB14" s="52"/>
+      <c r="AC14" s="54"/>
+      <c r="AD14" s="55"/>
+      <c r="AE14" s="54"/>
+      <c r="AF14" s="56"/>
+      <c r="AI14" s="45"/>
+    </row>
+    <row r="15" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="44"/>
+      <c r="B15" s="45"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="47"/>
+      <c r="O15" s="48"/>
+      <c r="P15" s="47"/>
+      <c r="Q15" s="48"/>
+      <c r="R15" s="47"/>
+      <c r="S15" s="48"/>
+      <c r="T15" s="60"/>
+      <c r="U15" s="51"/>
+      <c r="V15" s="52"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="50"/>
+      <c r="Y15" s="49"/>
+      <c r="Z15" s="53"/>
+      <c r="AA15" s="51"/>
+      <c r="AB15" s="52"/>
+      <c r="AC15" s="54"/>
+      <c r="AD15" s="55"/>
+      <c r="AE15" s="54"/>
+      <c r="AF15" s="56"/>
+      <c r="AI15" s="45"/>
+    </row>
+    <row r="16" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="44"/>
+      <c r="B16" s="45"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="48"/>
+      <c r="N16" s="47"/>
+      <c r="O16" s="48"/>
+      <c r="P16" s="47"/>
+      <c r="Q16" s="48"/>
+      <c r="R16" s="47"/>
+      <c r="S16" s="48"/>
+      <c r="T16" s="60"/>
+      <c r="U16" s="51"/>
+      <c r="V16" s="52"/>
+      <c r="W16" s="49"/>
+      <c r="X16" s="50"/>
+      <c r="Y16" s="49"/>
+      <c r="Z16" s="53"/>
+      <c r="AA16" s="51"/>
+      <c r="AB16" s="52"/>
+      <c r="AC16" s="54"/>
+      <c r="AD16" s="55"/>
+      <c r="AE16" s="54"/>
+      <c r="AF16" s="56"/>
+      <c r="AI16" s="45"/>
+    </row>
+    <row r="17" spans="1:35" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="44"/>
+      <c r="B17" s="45"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="47"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="47"/>
+      <c r="O17" s="48"/>
+      <c r="P17" s="47"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="47"/>
+      <c r="S17" s="48"/>
+      <c r="T17" s="60"/>
+      <c r="U17" s="51"/>
+      <c r="V17" s="52"/>
+      <c r="W17" s="49"/>
+      <c r="X17" s="50"/>
+      <c r="Y17" s="49"/>
+      <c r="Z17" s="53"/>
+      <c r="AA17" s="51"/>
+      <c r="AB17" s="52"/>
+      <c r="AC17" s="54"/>
+      <c r="AD17" s="55"/>
+      <c r="AE17" s="54"/>
+      <c r="AF17" s="56"/>
+      <c r="AI17" s="45"/>
+    </row>
+    <row r="18" spans="1:35" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="44"/>
+      <c r="B18" s="45"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="47"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="47"/>
+      <c r="O18" s="48"/>
+      <c r="P18" s="47"/>
+      <c r="Q18" s="48"/>
+      <c r="R18" s="47"/>
+      <c r="S18" s="48"/>
+      <c r="T18" s="60"/>
+      <c r="U18" s="51"/>
+      <c r="V18" s="52"/>
+      <c r="W18" s="49"/>
+      <c r="X18" s="50"/>
+      <c r="Y18" s="49"/>
+      <c r="Z18" s="53"/>
+      <c r="AA18" s="51"/>
+      <c r="AB18" s="52"/>
+      <c r="AC18" s="54"/>
+      <c r="AD18" s="55"/>
+      <c r="AE18" s="54"/>
+      <c r="AF18" s="56"/>
+      <c r="AI18" s="45"/>
+    </row>
+    <row r="19" spans="1:35" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="44"/>
+      <c r="B19" s="45"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="47"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="47"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="51"/>
+      <c r="V19" s="52"/>
+      <c r="W19" s="49"/>
+      <c r="X19" s="50"/>
+      <c r="Y19" s="49"/>
+      <c r="Z19" s="53"/>
+      <c r="AA19" s="51"/>
+      <c r="AB19" s="52"/>
+      <c r="AC19" s="54"/>
+      <c r="AD19" s="55"/>
+      <c r="AE19" s="54"/>
+      <c r="AF19" s="56"/>
+      <c r="AI19" s="45"/>
+    </row>
+    <row r="20" spans="1:35" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="44"/>
+      <c r="B20" s="45"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="48"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="48"/>
+      <c r="P20" s="47"/>
+      <c r="Q20" s="48"/>
+      <c r="R20" s="47"/>
+      <c r="S20" s="48"/>
+      <c r="T20" s="60"/>
+      <c r="U20" s="51"/>
+      <c r="V20" s="52"/>
+      <c r="W20" s="49"/>
+      <c r="X20" s="50"/>
+      <c r="Y20" s="49"/>
+      <c r="Z20" s="53"/>
+      <c r="AA20" s="51"/>
+      <c r="AB20" s="52"/>
+      <c r="AC20" s="54"/>
+      <c r="AD20" s="55"/>
+      <c r="AE20" s="54"/>
+      <c r="AF20" s="56"/>
+      <c r="AI20" s="45"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4073,57 +4209,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="85" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="85" t="s">
+      <c r="A1" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="85" t="s">
+      <c r="D1" s="80" t="s">
         <v>242</v>
       </c>
-      <c r="E1" s="85" t="s">
+      <c r="E1" s="80" t="s">
         <v>243</v>
       </c>
-      <c r="F1" s="85" t="s">
+      <c r="F1" s="80" t="s">
         <v>244</v>
       </c>
-      <c r="G1" s="85" t="s">
+      <c r="G1" s="80" t="s">
         <v>265</v>
       </c>
-      <c r="H1" s="85" t="s">
+      <c r="H1" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="87" t="s">
+      <c r="I1" s="82" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="81" t="s">
         <v>245</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="81" t="s">
         <v>257</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="81" t="s">
         <v>246</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="D2" s="81" t="s">
         <v>247</v>
       </c>
-      <c r="E2" s="86" t="s">
+      <c r="E2" s="81" t="s">
         <v>248</v>
       </c>
-      <c r="F2" s="86">
+      <c r="F2" s="81">
         <v>90</v>
       </c>
-      <c r="G2" s="86">
+      <c r="G2" s="81">
         <v>1.25</v>
       </c>
-      <c r="H2" s="86" t="s">
+      <c r="H2" s="81" t="s">
         <v>249</v>
       </c>
       <c r="I2" t="s">
@@ -4137,13 +4273,13 @@
       <c r="B3" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="86" t="s">
+      <c r="C3" s="81" t="s">
         <v>253</v>
       </c>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="81" t="s">
         <v>254</v>
       </c>
-      <c r="E3" s="86" t="s">
+      <c r="E3" s="81" t="s">
         <v>248</v>
       </c>
       <c r="F3">
@@ -4152,7 +4288,7 @@
       <c r="G3">
         <v>1.5</v>
       </c>
-      <c r="H3" s="86" t="s">
+      <c r="H3" s="81" t="s">
         <v>256</v>
       </c>
       <c r="I3" t="s">
@@ -4166,13 +4302,13 @@
       <c r="B4" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="81" t="s">
         <v>261</v>
       </c>
-      <c r="D4" s="86" t="s">
+      <c r="D4" s="81" t="s">
         <v>262</v>
       </c>
-      <c r="E4" s="86" t="s">
+      <c r="E4" s="81" t="s">
         <v>248</v>
       </c>
       <c r="F4">
@@ -4181,7 +4317,7 @@
       <c r="G4">
         <v>1.25</v>
       </c>
-      <c r="H4" s="86" t="s">
+      <c r="H4" s="81" t="s">
         <v>263</v>
       </c>
       <c r="I4" t="s">
@@ -4195,13 +4331,13 @@
       <c r="B5" t="s">
         <v>267</v>
       </c>
-      <c r="C5" s="86" t="s">
+      <c r="C5" s="81" t="s">
         <v>268</v>
       </c>
-      <c r="D5" s="86" t="s">
+      <c r="D5" s="81" t="s">
         <v>269</v>
       </c>
-      <c r="E5" s="86" t="s">
+      <c r="E5" s="81" t="s">
         <v>248</v>
       </c>
       <c r="F5">
@@ -4210,7 +4346,7 @@
       <c r="G5">
         <v>1.25</v>
       </c>
-      <c r="H5" s="86" t="s">
+      <c r="H5" s="81" t="s">
         <v>270</v>
       </c>
       <c r="I5" t="s">

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D341ED-495C-EE42-AB30-89B8FE36354F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38EE472B-6C24-BA4A-9C41-62B9609F9C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="2" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="301">
   <si>
     <t>question_id</t>
   </si>
@@ -182,9 +182,6 @@
     <t>time</t>
   </si>
   <si>
-    <t>Guinness's longest recorded fart was 2 min, 42 sec (162 sec)</t>
-  </si>
-  <si>
     <t>pinch_K</t>
   </si>
   <si>
@@ -869,9 +866,6 @@
     <t>pinch_L</t>
   </si>
   <si>
-    <t>Capricorn season goes from late December to late January</t>
-  </si>
-  <si>
     <t>pinch_m</t>
   </si>
   <si>
@@ -933,6 +927,21 @@
   </si>
   <si>
     <t>BASEBALL</t>
+  </si>
+  <si>
+    <t>How many amendments have been added to the US Constitution?</t>
+  </si>
+  <si>
+    <t>pinch_n</t>
+  </si>
+  <si>
+    <t>27 amendments have been added to the US constitution.</t>
+  </si>
+  <si>
+    <t>Capricorn season goes from late December to late January.</t>
+  </si>
+  <si>
+    <t>Guinness's longest recorded fart was 2 minutes, 42 seconds.</t>
   </si>
 </sst>
 </file>
@@ -1241,7 +1250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1493,6 +1502,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1841,6 +1851,7 @@
     <col min="9" max="9" width="15.33203125" customWidth="1"/>
     <col min="10" max="10" width="9.6640625" customWidth="1"/>
     <col min="14" max="14" width="8.5" customWidth="1"/>
+    <col min="16" max="16" width="25.6640625" customWidth="1"/>
     <col min="17" max="17" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1900,7 +1911,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="78" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C2" s="75">
         <v>10</v>
@@ -2268,7 +2279,7 @@
         <v>42</v>
       </c>
       <c r="B10" s="78" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C10" s="75">
         <v>10</v>
@@ -2349,16 +2360,16 @@
         <v>165</v>
       </c>
       <c r="P11" s="83" t="s">
-        <v>47</v>
+        <v>300</v>
       </c>
       <c r="Q11" s="75"/>
     </row>
     <row r="12" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="78" t="s">
         <v>48</v>
-      </c>
-      <c r="B12" s="78" t="s">
-        <v>49</v>
       </c>
       <c r="C12" s="75">
         <v>10</v>
@@ -2392,22 +2403,22 @@
         <v>110</v>
       </c>
       <c r="N12" s="75" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O12" s="75">
         <v>89.99</v>
       </c>
       <c r="P12" s="83" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q12" s="75"/>
     </row>
     <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="75" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B13" s="78" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C13" s="75">
         <v>1</v>
@@ -2443,16 +2454,16 @@
         <v>12</v>
       </c>
       <c r="P13" s="83" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="Q13" s="75"/>
     </row>
     <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="75" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C14" s="75">
         <v>100</v>
@@ -2464,7 +2475,9 @@
         <v>1</v>
       </c>
       <c r="F14" s="75"/>
-      <c r="G14" s="79"/>
+      <c r="G14" s="79" t="s">
+        <v>18</v>
+      </c>
       <c r="H14" s="75">
         <v>1</v>
       </c>
@@ -2488,27 +2501,53 @@
         <v>110</v>
       </c>
       <c r="P14" s="83" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Q14" s="75"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" s="75"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
+    <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="75" t="s">
+        <v>297</v>
+      </c>
+      <c r="B15" s="78" t="s">
+        <v>296</v>
+      </c>
+      <c r="C15" s="75">
+        <v>5</v>
+      </c>
+      <c r="D15" s="75">
+        <v>1</v>
+      </c>
       <c r="E15" s="75"/>
       <c r="F15" s="75"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="75"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="75"/>
-      <c r="M15" s="75"/>
+      <c r="G15" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="75">
+        <v>2</v>
+      </c>
+      <c r="I15" s="75">
+        <v>45</v>
+      </c>
+      <c r="J15" s="75">
+        <v>10</v>
+      </c>
+      <c r="K15" s="75">
+        <v>60</v>
+      </c>
+      <c r="L15" s="75">
+        <v>15</v>
+      </c>
+      <c r="M15" s="75">
+        <v>45</v>
+      </c>
       <c r="N15" s="75"/>
-      <c r="O15" s="75"/>
-      <c r="P15" s="75"/>
+      <c r="O15" s="75">
+        <v>27</v>
+      </c>
+      <c r="P15" s="83" t="s">
+        <v>298</v>
+      </c>
       <c r="Q15" s="75"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
@@ -2591,22 +2630,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" t="s">
-        <v>57</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
@@ -2615,10 +2654,10 @@
         <v>16</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="M1" t="s">
         <v>15</v>
@@ -2626,25 +2665,25 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
         <v>60</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>61</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>62</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>63</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>64</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>65</v>
-      </c>
-      <c r="G2" t="s">
-        <v>66</v>
       </c>
       <c r="H2">
         <v>9</v>
@@ -2658,25 +2697,25 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" t="s">
         <v>67</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" t="s">
         <v>68</v>
       </c>
-      <c r="C3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>69</v>
-      </c>
-      <c r="G3" t="s">
-        <v>70</v>
       </c>
       <c r="H3">
         <v>9</v>
@@ -2690,25 +2729,25 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" t="s">
         <v>71</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>72</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>73</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" t="s">
         <v>74</v>
       </c>
-      <c r="E4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>75</v>
-      </c>
-      <c r="G4" t="s">
-        <v>76</v>
       </c>
       <c r="H4">
         <v>9</v>
@@ -2722,25 +2761,25 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s">
         <v>77</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" t="s">
         <v>78</v>
       </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>79</v>
-      </c>
-      <c r="G5" t="s">
-        <v>80</v>
       </c>
       <c r="H5">
         <v>9</v>
@@ -2754,25 +2793,25 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
         <v>81</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>82</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>83</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" t="s">
         <v>84</v>
       </c>
-      <c r="E6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>85</v>
-      </c>
-      <c r="G6" t="s">
-        <v>86</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -2786,19 +2825,19 @@
     </row>
     <row r="7" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" t="s">
         <v>87</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>88</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>89</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>90</v>
-      </c>
-      <c r="G7" t="s">
-        <v>91</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -2810,30 +2849,30 @@
         <v>10</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="M7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" t="s">
         <v>89</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>90</v>
-      </c>
-      <c r="G8" t="s">
-        <v>91</v>
       </c>
       <c r="H8">
         <v>9</v>
@@ -2845,13 +2884,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -2909,876 +2948,876 @@
         <v>1</v>
       </c>
       <c r="C1" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="84" t="s">
+      <c r="E1" s="63" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="F1" s="64" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="G1" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="G1" s="65" t="s">
+      <c r="H1" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="H1" s="64" t="s">
+      <c r="I1" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="I1" s="65" t="s">
+      <c r="J1" s="64" t="s">
         <v>100</v>
       </c>
-      <c r="J1" s="64" t="s">
+      <c r="K1" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="K1" s="65" t="s">
+      <c r="L1" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="L1" s="66" t="s">
+      <c r="M1" s="65" t="s">
         <v>103</v>
       </c>
-      <c r="M1" s="65" t="s">
+      <c r="N1" s="66" t="s">
         <v>104</v>
       </c>
-      <c r="N1" s="66" t="s">
+      <c r="O1" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="O1" s="65" t="s">
+      <c r="P1" s="66" t="s">
         <v>106</v>
       </c>
-      <c r="P1" s="66" t="s">
+      <c r="Q1" s="65" t="s">
         <v>107</v>
       </c>
-      <c r="Q1" s="65" t="s">
+      <c r="R1" s="66" t="s">
         <v>108</v>
       </c>
-      <c r="R1" s="66" t="s">
+      <c r="S1" s="65" t="s">
         <v>109</v>
       </c>
-      <c r="S1" s="65" t="s">
+      <c r="T1" s="76" t="s">
         <v>110</v>
       </c>
-      <c r="T1" s="76" t="s">
+      <c r="U1" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="U1" s="67" t="s">
+      <c r="V1" s="68" t="s">
         <v>112</v>
       </c>
-      <c r="V1" s="68" t="s">
+      <c r="W1" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="W1" s="69" t="s">
+      <c r="X1" s="70" t="s">
         <v>114</v>
       </c>
-      <c r="X1" s="70" t="s">
+      <c r="Y1" s="69" t="s">
         <v>115</v>
       </c>
-      <c r="Y1" s="69" t="s">
+      <c r="Z1" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="Z1" s="71" t="s">
+      <c r="AA1" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="AA1" s="67" t="s">
+      <c r="AB1" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="AB1" s="68" t="s">
+      <c r="AC1" s="72" t="s">
         <v>119</v>
       </c>
-      <c r="AC1" s="72" t="s">
+      <c r="AD1" s="73" t="s">
         <v>120</v>
       </c>
-      <c r="AD1" s="73" t="s">
+      <c r="AE1" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="AE1" s="72" t="s">
+      <c r="AF1" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="AF1" s="74" t="s">
+      <c r="AG1" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="AG1" s="62" t="s">
+      <c r="AH1" s="62" t="s">
         <v>124</v>
-      </c>
-      <c r="AH1" s="62" t="s">
-        <v>125</v>
       </c>
       <c r="AI1" s="62" t="s">
         <v>15</v>
       </c>
       <c r="AJ1" s="62" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="C2" s="29" t="s">
         <v>128</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>129</v>
       </c>
       <c r="D2" s="85">
         <v>20</v>
       </c>
       <c r="E2" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="32" t="s">
+      <c r="H2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="H2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="32" t="s">
+      <c r="J2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="J2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" s="32" t="s">
+      <c r="L2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="L2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" s="32" t="s">
+      <c r="N2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="N2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" s="32" t="s">
+      <c r="P2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="P2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="32" t="s">
+      <c r="R2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="T2" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="R2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S2" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="T2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="U2" s="33" t="s">
+      <c r="V2" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="V2" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W2" s="33" t="s">
+      <c r="X2" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="X2" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="33" t="s">
+      <c r="Z2" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="Z2" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="35" t="s">
+      <c r="AB2" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="AB2" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="38" t="s">
+      <c r="AD2" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="59" t="s">
+        <v>217</v>
+      </c>
+      <c r="AF2" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="AD2" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="AF2" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="28" t="s">
+      <c r="AJ2" s="41" t="s">
         <v>142</v>
-      </c>
-      <c r="AJ2" s="41" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:36" s="42" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A3" s="57" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="B3" s="28" t="s">
-        <v>145</v>
-      </c>
       <c r="C3" s="29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D3" s="85">
         <v>20</v>
       </c>
       <c r="E3" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="F3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="J3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="L3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="N3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="P3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="F3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="H3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="J3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="L3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="N3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" s="32" t="s">
+      <c r="R3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="T3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="P3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="R3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="T3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="U3" s="35" t="s">
+      <c r="V3" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="X3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z3" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="V3" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W3" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="X3" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="Z3" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="35" t="s">
+      <c r="AB3" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="AB3" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="38" t="s">
+      <c r="AD3" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="AD3" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="38" t="s">
+      <c r="AF3" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="AF3" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH3" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI3" s="28" t="s">
+      <c r="AJ3" s="41" t="s">
         <v>155</v>
-      </c>
-      <c r="AJ3" s="41" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="57" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D4" s="85">
         <v>20</v>
       </c>
       <c r="E4" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="F4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="F4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="32" t="s">
+      <c r="H4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="H4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="32" t="s">
+      <c r="J4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="J4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" s="32" t="s">
+      <c r="L4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="L4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" s="32" t="s">
+      <c r="N4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="N4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="32" t="s">
+      <c r="P4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="P4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="32" t="s">
+      <c r="R4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="T4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="R4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S4" s="32" t="s">
+      <c r="V4" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="X4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z4" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB4" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="AD4" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="38" t="s">
         <v>221</v>
       </c>
-      <c r="T4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="U4" s="35" t="s">
-        <v>165</v>
-      </c>
-      <c r="V4" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="X4" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="Z4" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="35" t="s">
+      <c r="AF4" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="AB4" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="AD4" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="AF4" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI4" s="28" t="s">
+      <c r="AJ4" s="41" t="s">
         <v>169</v>
-      </c>
-      <c r="AJ4" s="41" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D5" s="85">
         <v>20</v>
       </c>
       <c r="E5" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="F5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="F5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="32" t="s">
+      <c r="H5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="J5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="H5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="32" t="s">
+      <c r="L5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="N5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="J5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="L5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="32" t="s">
+      <c r="P5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="N5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="P5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="32" t="s">
+      <c r="R5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="T5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" s="35" t="s">
         <v>176</v>
       </c>
-      <c r="R5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" s="32" t="s">
+      <c r="V5" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="X5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="T5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="U5" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="V5" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" s="33" t="s">
+      <c r="Z5" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="35" t="s">
         <v>178</v>
       </c>
-      <c r="X5" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="33" t="s">
+      <c r="AB5" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="Z5" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="35" t="s">
+      <c r="AD5" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="AB5" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="AD5" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="38" t="s">
+      <c r="AF5" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="AF5" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="28" t="s">
+      <c r="AJ5" s="41" t="s">
         <v>181</v>
-      </c>
-      <c r="AJ5" s="41" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="B6" s="28" t="s">
-        <v>184</v>
-      </c>
       <c r="C6" s="29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D6" s="85">
         <v>20</v>
       </c>
       <c r="E6" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="F6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="F6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="32" t="s">
+      <c r="H6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="J6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="L6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="32" t="s">
         <v>208</v>
       </c>
-      <c r="H6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="J6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="32" t="s">
+      <c r="N6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="P6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="R6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="T6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="V6" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="X6" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="Z6" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="AB6" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="AD6" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="AF6" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="L6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="N6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="P6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="R6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="T6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="V6" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="X6" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="Z6" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB6" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="AD6" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="AF6" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="28" t="s">
+      <c r="AJ6" s="41" t="s">
         <v>187</v>
-      </c>
-      <c r="AJ6" s="41" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:36" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A7" s="58" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>190</v>
-      </c>
       <c r="C7" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D7" s="86">
         <v>20</v>
       </c>
       <c r="E7" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="F7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="17" t="s">
+      <c r="H7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="H7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="17" t="s">
+      <c r="J7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="J7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="17" t="s">
+      <c r="L7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="N7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="L7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="N7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="17" t="s">
+      <c r="P7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="P7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="17" t="s">
+      <c r="R7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="T7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="R7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="T7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="20" t="s">
+      <c r="V7" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="V7" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="18" t="s">
+      <c r="X7" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="X7" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="18" t="s">
+      <c r="Z7" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="AB7" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="Z7" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="AB7" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="23" t="s">
+      <c r="AD7" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="AD7" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="23" t="s">
+      <c r="AF7" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="AF7" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="13" t="s">
+      <c r="AJ7" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="AJ7" s="26" t="s">
-        <v>203</v>
-      </c>
     </row>
     <row r="8" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A8" s="44" t="s">
-        <v>280</v>
+      <c r="A8" s="89" t="s">
+        <v>278</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D8" s="86">
         <v>20</v>
       </c>
       <c r="E8" s="46" t="s">
+        <v>280</v>
+      </c>
+      <c r="F8" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="48" t="s">
+        <v>289</v>
+      </c>
+      <c r="H8" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="48" t="s">
+        <v>281</v>
+      </c>
+      <c r="J8" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="48" t="s">
+        <v>288</v>
+      </c>
+      <c r="L8" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="48" t="s">
         <v>282</v>
       </c>
-      <c r="F8" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="48" t="s">
+      <c r="N8" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="48" t="s">
+        <v>283</v>
+      </c>
+      <c r="P8" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="48" t="s">
+        <v>284</v>
+      </c>
+      <c r="R8" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="48" t="s">
+        <v>285</v>
+      </c>
+      <c r="T8" s="60" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="51" t="s">
+        <v>292</v>
+      </c>
+      <c r="V8" s="52" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="49" t="s">
         <v>291</v>
       </c>
-      <c r="H8" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="48" t="s">
-        <v>283</v>
-      </c>
-      <c r="J8" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="48" t="s">
+      <c r="X8" s="50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="49" t="s">
+        <v>293</v>
+      </c>
+      <c r="Z8" s="53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="51" t="s">
+        <v>286</v>
+      </c>
+      <c r="AB8" s="52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="54" t="s">
+        <v>287</v>
+      </c>
+      <c r="AD8" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="54" t="s">
         <v>290</v>
       </c>
-      <c r="L8" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="48" t="s">
-        <v>284</v>
-      </c>
-      <c r="N8" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="48" t="s">
-        <v>285</v>
-      </c>
-      <c r="P8" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="48" t="s">
-        <v>286</v>
-      </c>
-      <c r="R8" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="S8" s="48" t="s">
-        <v>287</v>
-      </c>
-      <c r="T8" s="60" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" s="51" t="s">
+      <c r="AF8" s="56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="45" t="s">
         <v>294</v>
       </c>
-      <c r="V8" s="52" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="49" t="s">
-        <v>293</v>
-      </c>
-      <c r="X8" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="49" t="s">
+      <c r="AJ8" s="42" t="s">
         <v>295</v>
-      </c>
-      <c r="Z8" s="53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="51" t="s">
-        <v>288</v>
-      </c>
-      <c r="AB8" s="52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="54" t="s">
-        <v>289</v>
-      </c>
-      <c r="AD8" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="54" t="s">
-        <v>292</v>
-      </c>
-      <c r="AF8" s="56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH8" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="45" t="s">
-        <v>296</v>
-      </c>
-      <c r="AJ8" s="42" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
@@ -4216,42 +4255,42 @@
         <v>1</v>
       </c>
       <c r="C1" s="80" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D1" s="80" t="s">
+        <v>241</v>
+      </c>
+      <c r="E1" s="80" t="s">
         <v>242</v>
       </c>
-      <c r="E1" s="80" t="s">
+      <c r="F1" s="80" t="s">
         <v>243</v>
       </c>
-      <c r="F1" s="80" t="s">
-        <v>244</v>
-      </c>
       <c r="G1" s="80" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1" s="80" t="s">
         <v>15</v>
       </c>
       <c r="I1" s="82" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="81" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" s="81" t="s">
+        <v>256</v>
+      </c>
+      <c r="C2" s="81" t="s">
         <v>245</v>
       </c>
-      <c r="B2" s="81" t="s">
-        <v>257</v>
-      </c>
-      <c r="C2" s="81" t="s">
+      <c r="D2" s="81" t="s">
         <v>246</v>
       </c>
-      <c r="D2" s="81" t="s">
+      <c r="E2" s="81" t="s">
         <v>247</v>
-      </c>
-      <c r="E2" s="81" t="s">
-        <v>248</v>
       </c>
       <c r="F2" s="81">
         <v>90</v>
@@ -4260,27 +4299,27 @@
         <v>1.25</v>
       </c>
       <c r="H2" s="81" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C3" s="81" t="s">
         <v>252</v>
       </c>
-      <c r="B3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C3" s="81" t="s">
+      <c r="D3" s="81" t="s">
         <v>253</v>
       </c>
-      <c r="D3" s="81" t="s">
-        <v>254</v>
-      </c>
       <c r="E3" s="81" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -4289,27 +4328,27 @@
         <v>1.5</v>
       </c>
       <c r="H3" s="81" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B4" t="s">
         <v>259</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="81" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="81" t="s">
+      <c r="D4" s="81" t="s">
         <v>261</v>
       </c>
-      <c r="D4" s="81" t="s">
-        <v>262</v>
-      </c>
       <c r="E4" s="81" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F4">
         <v>90</v>
@@ -4318,27 +4357,27 @@
         <v>1.25</v>
       </c>
       <c r="H4" s="81" t="s">
+        <v>262</v>
+      </c>
+      <c r="I4" t="s">
         <v>263</v>
-      </c>
-      <c r="I4" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B5" t="s">
         <v>266</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" s="81" t="s">
         <v>267</v>
       </c>
-      <c r="C5" s="81" t="s">
+      <c r="D5" s="81" t="s">
         <v>268</v>
       </c>
-      <c r="D5" s="81" t="s">
-        <v>269</v>
-      </c>
       <c r="E5" s="81" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F5">
         <v>90</v>
@@ -4347,10 +4386,10 @@
         <v>1.25</v>
       </c>
       <c r="H5" s="81" t="s">
+        <v>269</v>
+      </c>
+      <c r="I5" t="s">
         <v>270</v>
-      </c>
-      <c r="I5" t="s">
-        <v>271</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38EE472B-6C24-BA4A-9C41-62B9609F9C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230690CC-A1DE-E84F-9984-8CD13D3E483C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="2" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="322">
   <si>
     <t>question_id</t>
   </si>
@@ -942,6 +942,69 @@
   </si>
   <si>
     <t>Guinness's longest recorded fart was 2 minutes, 42 seconds.</t>
+  </si>
+  <si>
+    <t>Guess what number I'm thinking.</t>
+  </si>
+  <si>
+    <t>pinch_o</t>
+  </si>
+  <si>
+    <t>I was thinking of 42. It wasn't reall a trivia question, I just wanted to see if you could guess it.</t>
+  </si>
+  <si>
+    <t>Which of these are actual Elvis Presley song titles?</t>
+  </si>
+  <si>
+    <t>bonus_q_elvis</t>
+  </si>
+  <si>
+    <t>Do the Clam</t>
+  </si>
+  <si>
+    <t>Blue Suede Shoes</t>
+  </si>
+  <si>
+    <t>Big Boots</t>
+  </si>
+  <si>
+    <t>Yoga is as Yoga Does</t>
+  </si>
+  <si>
+    <t>Heartbreak Hotel</t>
+  </si>
+  <si>
+    <t>Confidence</t>
+  </si>
+  <si>
+    <t>If I Can Dream</t>
+  </si>
+  <si>
+    <t>Burnin' Love</t>
+  </si>
+  <si>
+    <t>Honestly Sincere</t>
+  </si>
+  <si>
+    <t>Peanut Butter Mama</t>
+  </si>
+  <si>
+    <t>Jumpsuit Blues</t>
+  </si>
+  <si>
+    <t>Red Suede Socks</t>
+  </si>
+  <si>
+    <t>Folsom Prison Blues</t>
+  </si>
+  <si>
+    <t>ELVIS</t>
+  </si>
+  <si>
+    <t>These were all Elvis songs:</t>
+  </si>
+  <si>
+    <t>Don't Be Mean</t>
   </si>
 </sst>
 </file>
@@ -1502,7 +1565,9 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2550,23 +2615,51 @@
       </c>
       <c r="Q15" s="75"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16" s="75"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="75"/>
-      <c r="D16" s="75"/>
-      <c r="E16" s="75"/>
+    <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="75" t="s">
+        <v>302</v>
+      </c>
+      <c r="B16" s="78" t="s">
+        <v>301</v>
+      </c>
+      <c r="C16" s="75">
+        <v>10</v>
+      </c>
+      <c r="D16" s="75">
+        <v>5</v>
+      </c>
+      <c r="E16" s="75">
+        <v>1</v>
+      </c>
       <c r="F16" s="75"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="75"/>
-      <c r="J16" s="75"/>
-      <c r="K16" s="75"/>
-      <c r="L16" s="75"/>
-      <c r="M16" s="75"/>
+      <c r="G16" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="75">
+        <v>1</v>
+      </c>
+      <c r="I16" s="75">
+        <v>95</v>
+      </c>
+      <c r="J16" s="75">
+        <v>0</v>
+      </c>
+      <c r="K16" s="75">
+        <v>100</v>
+      </c>
+      <c r="L16" s="75">
+        <v>30</v>
+      </c>
+      <c r="M16" s="75">
+        <v>50</v>
+      </c>
       <c r="N16" s="75"/>
-      <c r="O16" s="75"/>
-      <c r="P16" s="75"/>
+      <c r="O16" s="75">
+        <v>42</v>
+      </c>
+      <c r="P16" s="83" t="s">
+        <v>303</v>
+      </c>
       <c r="Q16" s="75"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
@@ -2912,7 +3005,7 @@
     <col min="8" max="8" width="6.6640625" style="4" customWidth="1"/>
     <col min="9" max="9" width="18.6640625" style="5" customWidth="1"/>
     <col min="10" max="10" width="7.1640625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="16" style="5" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" style="5" customWidth="1"/>
     <col min="12" max="12" width="7.83203125" style="4" customWidth="1"/>
     <col min="13" max="13" width="15.1640625" style="5" customWidth="1"/>
     <col min="14" max="14" width="8" style="4" customWidth="1"/>
@@ -2932,7 +3025,7 @@
     <col min="28" max="28" width="10.83203125" style="9"/>
     <col min="29" max="29" width="15.6640625" style="11" customWidth="1"/>
     <col min="30" max="30" width="10.83203125" style="12"/>
-    <col min="31" max="31" width="15.83203125" style="11" customWidth="1"/>
+    <col min="31" max="31" width="18" style="11" customWidth="1"/>
     <col min="32" max="32" width="9" style="2" customWidth="1"/>
     <col min="33" max="33" width="7.83203125" customWidth="1"/>
     <col min="34" max="34" width="13.83203125" customWidth="1"/>
@@ -3710,11 +3803,11 @@
         <v>202</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A8" s="89" t="s">
+    <row r="8" spans="1:36" s="41" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A8" s="57" t="s">
         <v>278</v>
       </c>
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="28" t="s">
         <v>279</v>
       </c>
       <c r="C8" s="14" t="s">
@@ -3723,88 +3816,88 @@
       <c r="D8" s="86">
         <v>20</v>
       </c>
-      <c r="E8" s="46" t="s">
+      <c r="E8" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="F8" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="48" t="s">
+      <c r="F8" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="H8" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="48" t="s">
+      <c r="H8" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="J8" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="48" t="s">
+      <c r="J8" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="32" t="s">
         <v>288</v>
       </c>
-      <c r="L8" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="48" t="s">
+      <c r="L8" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="N8" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="48" t="s">
+      <c r="N8" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="32" t="s">
         <v>283</v>
       </c>
-      <c r="P8" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="48" t="s">
+      <c r="P8" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="R8" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="S8" s="48" t="s">
+      <c r="R8" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="32" t="s">
         <v>285</v>
       </c>
-      <c r="T8" s="60" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" s="51" t="s">
+      <c r="T8" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="V8" s="52" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="49" t="s">
+      <c r="V8" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="33" t="s">
         <v>291</v>
       </c>
-      <c r="X8" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="49" t="s">
+      <c r="X8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="Z8" s="53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="51" t="s">
+      <c r="Z8" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="AB8" s="52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="54" t="s">
+      <c r="AB8" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="AD8" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="54" t="s">
+      <c r="AD8" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="38" t="s">
         <v>290</v>
       </c>
-      <c r="AF8" s="56" t="b">
+      <c r="AF8" s="40" t="b">
         <v>0</v>
       </c>
       <c r="AG8" s="26" t="b">
@@ -3813,46 +3906,122 @@
       <c r="AH8" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="AI8" s="45" t="s">
+      <c r="AI8" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="AJ8" s="42" t="s">
+      <c r="AJ8" s="41" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="9" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="44"/>
-      <c r="B9" s="45"/>
-      <c r="D9" s="87"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="47"/>
-      <c r="O9" s="48"/>
-      <c r="P9" s="47"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="60"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="52"/>
-      <c r="W9" s="49"/>
-      <c r="X9" s="50"/>
-      <c r="Y9" s="49"/>
-      <c r="Z9" s="53"/>
-      <c r="AA9" s="51"/>
-      <c r="AB9" s="52"/>
-      <c r="AC9" s="54"/>
-      <c r="AD9" s="55"/>
-      <c r="AE9" s="54"/>
-      <c r="AF9" s="56"/>
-      <c r="AI9" s="45"/>
+    <row r="9" spans="1:36" s="41" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A9" s="57" t="s">
+        <v>305</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>304</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" s="86">
+        <v>20</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>306</v>
+      </c>
+      <c r="F9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>307</v>
+      </c>
+      <c r="H9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>308</v>
+      </c>
+      <c r="J9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="32" t="s">
+        <v>309</v>
+      </c>
+      <c r="L9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="N9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="P9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="32" t="s">
+        <v>312</v>
+      </c>
+      <c r="R9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="T9" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="35" t="s">
+        <v>314</v>
+      </c>
+      <c r="V9" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="X9" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="33" t="s">
+        <v>321</v>
+      </c>
+      <c r="Z9" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="35" t="s">
+        <v>316</v>
+      </c>
+      <c r="AB9" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="38" t="s">
+        <v>317</v>
+      </c>
+      <c r="AD9" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="38" t="s">
+        <v>318</v>
+      </c>
+      <c r="AF9" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="AJ9" s="41" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="10" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="44"/>
@@ -3886,7 +4055,6 @@
       <c r="AD10" s="55"/>
       <c r="AE10" s="54"/>
       <c r="AF10" s="56"/>
-      <c r="AI10" s="45"/>
     </row>
     <row r="11" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="44"/>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230690CC-A1DE-E84F-9984-8CD13D3E483C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72083351-C407-2F46-848F-0F233E20EED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="2" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -950,9 +950,6 @@
     <t>pinch_o</t>
   </si>
   <si>
-    <t>I was thinking of 42. It wasn't reall a trivia question, I just wanted to see if you could guess it.</t>
-  </si>
-  <si>
     <t>Which of these are actual Elvis Presley song titles?</t>
   </si>
   <si>
@@ -1005,6 +1002,9 @@
   </si>
   <si>
     <t>Don't Be Mean</t>
+  </si>
+  <si>
+    <t>I was thinking of 42. It wasn't really a trivia question, I just wanted to see if you could guess it.</t>
   </si>
 </sst>
 </file>
@@ -2658,7 +2658,7 @@
         <v>42</v>
       </c>
       <c r="P16" s="83" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="Q16" s="75"/>
     </row>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="9" spans="1:36" s="41" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="57" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>128</v>
@@ -3927,100 +3927,100 @@
         <v>20</v>
       </c>
       <c r="E9" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="F9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="F9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="32" t="s">
+      <c r="H9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="32" t="s">
         <v>307</v>
       </c>
-      <c r="H9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="32" t="s">
+      <c r="J9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="32" t="s">
         <v>308</v>
       </c>
-      <c r="J9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="32" t="s">
+      <c r="L9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="32" t="s">
         <v>309</v>
       </c>
-      <c r="L9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="32" t="s">
+      <c r="N9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="32" t="s">
         <v>310</v>
       </c>
-      <c r="N9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="32" t="s">
+      <c r="P9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="32" t="s">
         <v>311</v>
       </c>
-      <c r="P9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="32" t="s">
+      <c r="R9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="32" t="s">
         <v>312</v>
       </c>
-      <c r="R9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" s="32" t="s">
+      <c r="T9" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="35" t="s">
         <v>313</v>
       </c>
-      <c r="T9" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="U9" s="35" t="s">
+      <c r="V9" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="V9" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="33" t="s">
+      <c r="X9" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="Z9" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="X9" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="33" t="s">
-        <v>321</v>
-      </c>
-      <c r="Z9" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="35" t="s">
+      <c r="AB9" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="38" t="s">
         <v>316</v>
       </c>
-      <c r="AB9" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="38" t="s">
+      <c r="AD9" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="AD9" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="38" t="s">
+      <c r="AF9" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="28" t="s">
+        <v>319</v>
+      </c>
+      <c r="AJ9" s="41" t="s">
         <v>318</v>
-      </c>
-      <c r="AF9" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH9" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI9" s="28" t="s">
-        <v>320</v>
-      </c>
-      <c r="AJ9" s="41" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72083351-C407-2F46-848F-0F233E20EED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCEB638-5D13-6448-9CB5-15C2E6016383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="360">
   <si>
     <t>question_id</t>
   </si>
@@ -1005,6 +1005,120 @@
   </si>
   <si>
     <t>I was thinking of 42. It wasn't really a trivia question, I just wanted to see if you could guess it.</t>
+  </si>
+  <si>
+    <t>Which of these songs is from one of Disney's "Frozen" movies?</t>
+  </si>
+  <si>
+    <t>pinch_p</t>
+  </si>
+  <si>
+    <t>bonus_q_frozen</t>
+  </si>
+  <si>
+    <t>Which are real song titles from one of Disney's "Frozen" movies?</t>
+  </si>
+  <si>
+    <t>Do You Want to Build a Snowman?</t>
+  </si>
+  <si>
+    <t>Frozen Heart</t>
+  </si>
+  <si>
+    <t>Let it Go</t>
+  </si>
+  <si>
+    <t>Fixer Upper</t>
+  </si>
+  <si>
+    <t>The Next Right Thing</t>
+  </si>
+  <si>
+    <t>Reindeer(s) Are Better than People</t>
+  </si>
+  <si>
+    <t>We Don't Talk About Brunhilda</t>
+  </si>
+  <si>
+    <t>Show Yourself</t>
+  </si>
+  <si>
+    <t>Love is an Open Door</t>
+  </si>
+  <si>
+    <t>Solstice (Title Theme)</t>
+  </si>
+  <si>
+    <t>My Second Cousin, Frosty</t>
+  </si>
+  <si>
+    <t>Lost in the Snow</t>
+  </si>
+  <si>
+    <t>Sled for your Life</t>
+  </si>
+  <si>
+    <t>Ice Princess</t>
+  </si>
+  <si>
+    <t>DISNEY MUSIC</t>
+  </si>
+  <si>
+    <t>There are all songs from Frozen/Frozen 2:</t>
+  </si>
+  <si>
+    <t>bonus_q_dinosaur</t>
+  </si>
+  <si>
+    <t>Tyrannosaurus Rex</t>
+  </si>
+  <si>
+    <t>Velociraptor</t>
+  </si>
+  <si>
+    <t>Stegosaurus</t>
+  </si>
+  <si>
+    <t>Spinosaurus</t>
+  </si>
+  <si>
+    <t>Allosaurus</t>
+  </si>
+  <si>
+    <t>Pegomastax</t>
+  </si>
+  <si>
+    <t>Iguanodon</t>
+  </si>
+  <si>
+    <t>Georgesauros</t>
+  </si>
+  <si>
+    <t>Maphiadon</t>
+  </si>
+  <si>
+    <t>DINOSAURS</t>
+  </si>
+  <si>
+    <t>These are real dinosaur species:</t>
+  </si>
+  <si>
+    <t>Arkansaurus</t>
+  </si>
+  <si>
+    <t>Bulbasaurus</t>
+  </si>
+  <si>
+    <t>Which of these were actual dinosaurs?</t>
+  </si>
+  <si>
+    <t>Ithinkshesaurus</t>
+  </si>
+  <si>
+    <t>Eptasaurus</t>
+  </si>
+  <si>
+    <t>Baftasaurus</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1241,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1313,7 +1427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1352,9 +1466,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1395,9 +1506,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1550,23 +1658,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1911,7 +2046,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="57.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7" style="77" customWidth="1"/>
+    <col min="7" max="7" width="7" style="75" customWidth="1"/>
     <col min="8" max="8" width="18.5" customWidth="1"/>
     <col min="9" max="9" width="15.33203125" customWidth="1"/>
     <col min="10" max="10" width="9.6640625" customWidth="1"/>
@@ -1921,784 +2056,788 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="75" t="s">
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="79" t="s">
+      <c r="G1" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="75" t="s">
+      <c r="H1" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="75" t="s">
+      <c r="I1" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="75" t="s">
+      <c r="J1" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="75" t="s">
+      <c r="K1" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="75" t="s">
+      <c r="L1" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="75" t="s">
+      <c r="M1" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="75" t="s">
+      <c r="N1" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="75" t="s">
+      <c r="O1" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="75" t="s">
+      <c r="P1" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="75"/>
+      <c r="Q1" s="73"/>
     </row>
     <row r="2" spans="1:17" ht="34" x14ac:dyDescent="0.2">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="76" t="s">
         <v>203</v>
       </c>
-      <c r="C2" s="75">
+      <c r="C2" s="73">
         <v>10</v>
       </c>
-      <c r="D2" s="75">
+      <c r="D2" s="73">
         <v>5</v>
       </c>
-      <c r="E2" s="75">
-        <v>1</v>
-      </c>
-      <c r="F2" s="75"/>
-      <c r="G2" s="79" t="s">
+      <c r="E2" s="73">
+        <v>1</v>
+      </c>
+      <c r="F2" s="73"/>
+      <c r="G2" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="75">
+      <c r="H2" s="73">
         <v>2</v>
       </c>
-      <c r="I2" s="75">
+      <c r="I2" s="73">
         <v>65</v>
       </c>
-      <c r="J2" s="75">
+      <c r="J2" s="73">
         <v>10</v>
       </c>
-      <c r="K2" s="75">
+      <c r="K2" s="73">
         <v>80</v>
       </c>
-      <c r="L2" s="75">
+      <c r="L2" s="73">
         <v>35</v>
       </c>
-      <c r="M2" s="75">
+      <c r="M2" s="73">
         <v>70</v>
       </c>
-      <c r="N2" s="75"/>
-      <c r="O2" s="75">
+      <c r="N2" s="73"/>
+      <c r="O2" s="73">
         <v>57</v>
       </c>
-      <c r="P2" s="83" t="s">
+      <c r="P2" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="75"/>
+      <c r="Q2" s="73"/>
     </row>
     <row r="3" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="75">
+      <c r="C3" s="73">
         <v>5</v>
       </c>
-      <c r="D3" s="75">
-        <v>1</v>
-      </c>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="79" t="s">
+      <c r="D3" s="73">
+        <v>1</v>
+      </c>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="75">
+      <c r="H3" s="73">
         <v>5</v>
       </c>
-      <c r="I3" s="75">
+      <c r="I3" s="73">
         <v>18</v>
       </c>
-      <c r="J3" s="75">
-        <v>0</v>
-      </c>
-      <c r="K3" s="75">
+      <c r="J3" s="73">
+        <v>0</v>
+      </c>
+      <c r="K3" s="73">
         <v>20</v>
       </c>
-      <c r="L3" s="75">
+      <c r="L3" s="73">
         <v>6</v>
       </c>
-      <c r="M3" s="75">
+      <c r="M3" s="73">
         <v>16</v>
       </c>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73">
         <v>4</v>
       </c>
-      <c r="P3" s="83" t="s">
+      <c r="P3" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="Q3" s="75"/>
+      <c r="Q3" s="73"/>
     </row>
     <row r="4" spans="1:17" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="78" t="s">
+      <c r="B4" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="75">
+      <c r="C4" s="73">
         <v>5</v>
       </c>
-      <c r="D4" s="75">
-        <v>1</v>
-      </c>
-      <c r="E4" s="75">
-        <v>1</v>
-      </c>
-      <c r="F4" s="75"/>
-      <c r="G4" s="79" t="s">
+      <c r="D4" s="73">
+        <v>1</v>
+      </c>
+      <c r="E4" s="73">
+        <v>1</v>
+      </c>
+      <c r="F4" s="73"/>
+      <c r="G4" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="75">
+      <c r="H4" s="73">
         <v>5</v>
       </c>
-      <c r="I4" s="75">
+      <c r="I4" s="73">
         <v>17</v>
       </c>
-      <c r="J4" s="75">
-        <v>0</v>
-      </c>
-      <c r="K4" s="75">
+      <c r="J4" s="73">
+        <v>0</v>
+      </c>
+      <c r="K4" s="73">
         <v>20</v>
       </c>
-      <c r="L4" s="75">
+      <c r="L4" s="73">
         <v>4</v>
       </c>
-      <c r="M4" s="75">
+      <c r="M4" s="73">
         <v>14</v>
       </c>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75">
+      <c r="N4" s="73"/>
+      <c r="O4" s="73">
         <v>7</v>
       </c>
-      <c r="P4" s="83" t="s">
+      <c r="P4" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="Q4" s="75"/>
+      <c r="Q4" s="73"/>
     </row>
     <row r="5" spans="1:17" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="75">
+      <c r="C5" s="73">
         <v>100</v>
       </c>
-      <c r="D5" s="75">
+      <c r="D5" s="73">
         <v>50</v>
       </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="79" t="s">
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="75">
+      <c r="H5" s="73">
         <v>5</v>
       </c>
-      <c r="I5" s="75">
+      <c r="I5" s="73">
         <v>900</v>
       </c>
-      <c r="J5" s="75">
+      <c r="J5" s="73">
         <v>300</v>
       </c>
-      <c r="K5" s="75">
+      <c r="K5" s="73">
         <v>1300</v>
       </c>
-      <c r="L5" s="75">
+      <c r="L5" s="73">
         <v>800</v>
       </c>
-      <c r="M5" s="75">
+      <c r="M5" s="73">
         <v>1000</v>
       </c>
-      <c r="N5" s="75"/>
-      <c r="O5" s="75">
+      <c r="N5" s="73"/>
+      <c r="O5" s="73">
         <v>600</v>
       </c>
-      <c r="P5" s="83" t="s">
+      <c r="P5" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="Q5" s="75"/>
+      <c r="Q5" s="73"/>
     </row>
     <row r="6" spans="1:17" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="75">
+      <c r="C6" s="73">
         <v>5</v>
       </c>
-      <c r="D6" s="75">
-        <v>1</v>
-      </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="79" t="s">
+      <c r="D6" s="73">
+        <v>1</v>
+      </c>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="75">
+      <c r="H6" s="73">
         <v>2</v>
       </c>
-      <c r="I6" s="75">
+      <c r="I6" s="73">
         <v>45</v>
       </c>
-      <c r="J6" s="75">
-        <v>0</v>
-      </c>
-      <c r="K6" s="75">
+      <c r="J6" s="73">
+        <v>0</v>
+      </c>
+      <c r="K6" s="73">
         <v>50</v>
       </c>
-      <c r="L6" s="75">
+      <c r="L6" s="73">
         <v>20</v>
       </c>
-      <c r="M6" s="75">
+      <c r="M6" s="73">
         <v>30</v>
       </c>
-      <c r="N6" s="75"/>
-      <c r="O6" s="75">
+      <c r="N6" s="73"/>
+      <c r="O6" s="73">
         <v>12</v>
       </c>
-      <c r="P6" s="83" t="s">
+      <c r="P6" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="Q6" s="75"/>
+      <c r="Q6" s="73"/>
     </row>
     <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="78" t="s">
+      <c r="B7" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="75">
+      <c r="C7" s="73">
         <v>5</v>
       </c>
-      <c r="D7" s="75">
-        <v>1</v>
-      </c>
-      <c r="E7" s="75">
-        <v>1</v>
-      </c>
-      <c r="F7" s="75"/>
-      <c r="G7" s="79" t="s">
+      <c r="D7" s="73">
+        <v>1</v>
+      </c>
+      <c r="E7" s="73">
+        <v>1</v>
+      </c>
+      <c r="F7" s="73"/>
+      <c r="G7" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="75">
+      <c r="H7" s="73">
         <v>2</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="73">
         <v>45</v>
       </c>
-      <c r="J7" s="75">
+      <c r="J7" s="73">
         <v>5</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="73">
         <v>55</v>
       </c>
-      <c r="L7" s="75">
+      <c r="L7" s="73">
         <v>20</v>
       </c>
-      <c r="M7" s="75">
+      <c r="M7" s="73">
         <v>40</v>
       </c>
-      <c r="N7" s="75"/>
-      <c r="O7" s="75">
+      <c r="N7" s="73"/>
+      <c r="O7" s="73">
         <v>10</v>
       </c>
-      <c r="P7" s="83" t="s">
+      <c r="P7" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="Q7" s="75"/>
+      <c r="Q7" s="73"/>
     </row>
     <row r="8" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="75">
-        <v>1</v>
-      </c>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="79" t="s">
+      <c r="C8" s="73">
+        <v>1</v>
+      </c>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="75">
+      <c r="H8" s="73">
         <v>10</v>
       </c>
-      <c r="I8" s="75">
+      <c r="I8" s="73">
         <v>9</v>
       </c>
-      <c r="J8" s="75">
-        <v>1</v>
-      </c>
-      <c r="K8" s="75">
+      <c r="J8" s="73">
+        <v>1</v>
+      </c>
+      <c r="K8" s="73">
         <v>12</v>
       </c>
-      <c r="L8" s="75">
-        <v>1</v>
-      </c>
-      <c r="M8" s="75">
+      <c r="L8" s="73">
+        <v>1</v>
+      </c>
+      <c r="M8" s="73">
         <v>3</v>
       </c>
-      <c r="N8" s="75" t="s">
+      <c r="N8" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="O8" s="75">
+      <c r="O8" s="73">
         <v>6</v>
       </c>
-      <c r="P8" s="83" t="s">
+      <c r="P8" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="Q8" s="75"/>
+      <c r="Q8" s="73"/>
     </row>
     <row r="9" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="75" t="s">
+      <c r="A9" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="75">
+      <c r="C9" s="73">
         <v>10</v>
       </c>
-      <c r="D9" s="75">
+      <c r="D9" s="73">
         <v>5</v>
       </c>
-      <c r="E9" s="75">
-        <v>1</v>
-      </c>
-      <c r="F9" s="75"/>
-      <c r="G9" s="79" t="s">
+      <c r="E9" s="73">
+        <v>1</v>
+      </c>
+      <c r="F9" s="73"/>
+      <c r="G9" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="75">
-        <v>1</v>
-      </c>
-      <c r="I9" s="75">
+      <c r="H9" s="73">
+        <v>1</v>
+      </c>
+      <c r="I9" s="73">
         <v>95</v>
       </c>
-      <c r="J9" s="75">
+      <c r="J9" s="73">
         <v>20</v>
       </c>
-      <c r="K9" s="75">
+      <c r="K9" s="73">
         <v>120</v>
       </c>
-      <c r="L9" s="75">
+      <c r="L9" s="73">
         <v>20</v>
       </c>
-      <c r="M9" s="75">
+      <c r="M9" s="73">
         <v>40</v>
       </c>
-      <c r="N9" s="75"/>
-      <c r="O9" s="75">
+      <c r="N9" s="73"/>
+      <c r="O9" s="73">
         <v>73</v>
       </c>
-      <c r="P9" s="83" t="s">
+      <c r="P9" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="Q9" s="75"/>
+      <c r="Q9" s="73"/>
     </row>
     <row r="10" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="75" t="s">
+      <c r="A10" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="78" t="s">
+      <c r="B10" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="C10" s="75">
+      <c r="C10" s="73">
         <v>10</v>
       </c>
-      <c r="D10" s="75">
+      <c r="D10" s="73">
         <v>5</v>
       </c>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="79" t="s">
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="75">
+      <c r="H10" s="73">
         <v>5</v>
       </c>
-      <c r="I10" s="75">
+      <c r="I10" s="73">
         <v>95</v>
       </c>
-      <c r="J10" s="75">
+      <c r="J10" s="73">
         <v>1880</v>
       </c>
-      <c r="K10" s="75">
+      <c r="K10" s="73">
         <v>1980</v>
       </c>
-      <c r="L10" s="75">
+      <c r="L10" s="73">
         <v>1900</v>
       </c>
-      <c r="M10" s="75">
+      <c r="M10" s="73">
         <v>1950</v>
       </c>
-      <c r="N10" s="75"/>
-      <c r="O10" s="75">
+      <c r="N10" s="73"/>
+      <c r="O10" s="73">
         <v>1955</v>
       </c>
-      <c r="P10" s="83" t="s">
+      <c r="P10" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="Q10" s="75"/>
+      <c r="Q10" s="73"/>
     </row>
     <row r="11" spans="1:17" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11" s="75" t="s">
+      <c r="A11" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="78" t="s">
+      <c r="B11" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="75">
+      <c r="C11" s="73">
         <v>15</v>
       </c>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="79" t="s">
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="75">
+      <c r="H11" s="73">
         <v>9</v>
       </c>
-      <c r="I11" s="75">
+      <c r="I11" s="73">
         <v>165</v>
       </c>
-      <c r="J11" s="75">
+      <c r="J11" s="73">
         <v>15</v>
       </c>
-      <c r="K11" s="75">
+      <c r="K11" s="73">
         <v>195</v>
       </c>
-      <c r="L11" s="75">
+      <c r="L11" s="73">
         <v>10</v>
       </c>
-      <c r="M11" s="75">
+      <c r="M11" s="73">
         <v>50</v>
       </c>
-      <c r="N11" s="75" t="s">
+      <c r="N11" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="O11" s="75">
+      <c r="O11" s="73">
         <v>165</v>
       </c>
-      <c r="P11" s="83" t="s">
+      <c r="P11" s="81" t="s">
         <v>300</v>
       </c>
-      <c r="Q11" s="75"/>
+      <c r="Q11" s="73"/>
     </row>
     <row r="12" spans="1:17" ht="34" x14ac:dyDescent="0.2">
-      <c r="A12" s="75" t="s">
+      <c r="A12" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="78" t="s">
+      <c r="B12" s="76" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="75">
+      <c r="C12" s="73">
         <v>10</v>
       </c>
-      <c r="D12" s="75">
+      <c r="D12" s="73">
         <v>5</v>
       </c>
-      <c r="E12" s="75">
-        <v>1</v>
-      </c>
-      <c r="F12" s="75"/>
-      <c r="G12" s="79" t="s">
+      <c r="E12" s="73">
+        <v>1</v>
+      </c>
+      <c r="F12" s="73"/>
+      <c r="G12" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="75">
-        <v>1</v>
-      </c>
-      <c r="I12" s="75">
+      <c r="H12" s="73">
+        <v>1</v>
+      </c>
+      <c r="I12" s="73">
         <v>95</v>
       </c>
-      <c r="J12" s="75">
+      <c r="J12" s="73">
         <v>40</v>
       </c>
-      <c r="K12" s="75">
+      <c r="K12" s="73">
         <v>140</v>
       </c>
-      <c r="L12" s="75">
+      <c r="L12" s="73">
         <v>50</v>
       </c>
-      <c r="M12" s="75">
+      <c r="M12" s="73">
         <v>110</v>
       </c>
-      <c r="N12" s="75" t="s">
+      <c r="N12" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="O12" s="75">
+      <c r="O12" s="73">
         <v>89.99</v>
       </c>
-      <c r="P12" s="83" t="s">
+      <c r="P12" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="Q12" s="75"/>
+      <c r="Q12" s="73"/>
     </row>
     <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="73" t="s">
         <v>274</v>
       </c>
-      <c r="B13" s="78" t="s">
+      <c r="B13" s="76" t="s">
         <v>273</v>
       </c>
-      <c r="C13" s="75">
-        <v>1</v>
-      </c>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="79" t="s">
+      <c r="C13" s="73">
+        <v>1</v>
+      </c>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="75">
+      <c r="H13" s="73">
         <v>10</v>
       </c>
-      <c r="I13" s="75">
+      <c r="I13" s="73">
         <v>9</v>
       </c>
-      <c r="J13" s="75">
-        <v>1</v>
-      </c>
-      <c r="K13" s="75">
+      <c r="J13" s="73">
+        <v>1</v>
+      </c>
+      <c r="K13" s="73">
         <v>12</v>
       </c>
-      <c r="L13" s="75">
-        <v>1</v>
-      </c>
-      <c r="M13" s="75">
+      <c r="L13" s="73">
+        <v>1</v>
+      </c>
+      <c r="M13" s="73">
         <v>3</v>
       </c>
-      <c r="N13" s="75" t="s">
+      <c r="N13" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="O13" s="75">
+      <c r="O13" s="73">
         <v>12</v>
       </c>
-      <c r="P13" s="83" t="s">
+      <c r="P13" s="81" t="s">
         <v>299</v>
       </c>
-      <c r="Q13" s="75"/>
+      <c r="Q13" s="73"/>
     </row>
     <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="75" t="s">
+      <c r="A14" s="73" t="s">
         <v>275</v>
       </c>
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="76" t="s">
         <v>276</v>
       </c>
-      <c r="C14" s="75">
+      <c r="C14" s="73">
         <v>100</v>
       </c>
-      <c r="D14" s="75">
+      <c r="D14" s="73">
         <v>5</v>
       </c>
-      <c r="E14" s="75">
-        <v>1</v>
-      </c>
-      <c r="F14" s="75"/>
-      <c r="G14" s="79" t="s">
+      <c r="E14" s="73">
+        <v>1</v>
+      </c>
+      <c r="F14" s="73"/>
+      <c r="G14" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="75">
-        <v>1</v>
-      </c>
-      <c r="I14" s="75">
+      <c r="H14" s="73">
+        <v>1</v>
+      </c>
+      <c r="I14" s="73">
         <v>95</v>
       </c>
-      <c r="J14" s="75">
+      <c r="J14" s="73">
         <v>10</v>
       </c>
-      <c r="K14" s="75">
+      <c r="K14" s="73">
         <v>110</v>
       </c>
-      <c r="L14" s="75">
+      <c r="L14" s="73">
         <v>25</v>
       </c>
-      <c r="M14" s="75">
+      <c r="M14" s="73">
         <v>75</v>
       </c>
-      <c r="N14" s="75"/>
-      <c r="O14" s="75">
+      <c r="N14" s="73"/>
+      <c r="O14" s="73">
         <v>110</v>
       </c>
-      <c r="P14" s="83" t="s">
+      <c r="P14" s="81" t="s">
         <v>277</v>
       </c>
-      <c r="Q14" s="75"/>
+      <c r="Q14" s="73"/>
     </row>
     <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="75" t="s">
+      <c r="A15" s="73" t="s">
         <v>297</v>
       </c>
-      <c r="B15" s="78" t="s">
+      <c r="B15" s="76" t="s">
         <v>296</v>
       </c>
-      <c r="C15" s="75">
+      <c r="C15" s="73">
         <v>5</v>
       </c>
-      <c r="D15" s="75">
-        <v>1</v>
-      </c>
-      <c r="E15" s="75"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="79" t="s">
+      <c r="D15" s="73">
+        <v>1</v>
+      </c>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="75">
+      <c r="H15" s="73">
         <v>2</v>
       </c>
-      <c r="I15" s="75">
+      <c r="I15" s="73">
         <v>45</v>
       </c>
-      <c r="J15" s="75">
+      <c r="J15" s="73">
         <v>10</v>
       </c>
-      <c r="K15" s="75">
+      <c r="K15" s="73">
         <v>60</v>
       </c>
-      <c r="L15" s="75">
+      <c r="L15" s="73">
         <v>15</v>
       </c>
-      <c r="M15" s="75">
+      <c r="M15" s="73">
         <v>45</v>
       </c>
-      <c r="N15" s="75"/>
-      <c r="O15" s="75">
+      <c r="N15" s="73"/>
+      <c r="O15" s="73">
         <v>27</v>
       </c>
-      <c r="P15" s="83" t="s">
+      <c r="P15" s="81" t="s">
         <v>298</v>
       </c>
-      <c r="Q15" s="75"/>
+      <c r="Q15" s="73"/>
     </row>
     <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="75" t="s">
+      <c r="A16" s="73" t="s">
         <v>302</v>
       </c>
-      <c r="B16" s="78" t="s">
+      <c r="B16" s="76" t="s">
         <v>301</v>
       </c>
-      <c r="C16" s="75">
+      <c r="C16" s="73">
         <v>10</v>
       </c>
-      <c r="D16" s="75">
+      <c r="D16" s="73">
         <v>5</v>
       </c>
-      <c r="E16" s="75">
-        <v>1</v>
-      </c>
-      <c r="F16" s="75"/>
-      <c r="G16" s="79" t="s">
+      <c r="E16" s="73">
+        <v>1</v>
+      </c>
+      <c r="F16" s="73"/>
+      <c r="G16" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="75">
-        <v>1</v>
-      </c>
-      <c r="I16" s="75">
+      <c r="H16" s="73">
+        <v>1</v>
+      </c>
+      <c r="I16" s="73">
         <v>95</v>
       </c>
-      <c r="J16" s="75">
-        <v>0</v>
-      </c>
-      <c r="K16" s="75">
+      <c r="J16" s="73">
+        <v>0</v>
+      </c>
+      <c r="K16" s="73">
         <v>100</v>
       </c>
-      <c r="L16" s="75">
+      <c r="L16" s="73">
         <v>30</v>
       </c>
-      <c r="M16" s="75">
+      <c r="M16" s="73">
         <v>50</v>
       </c>
-      <c r="N16" s="75"/>
-      <c r="O16" s="75">
+      <c r="N16" s="73"/>
+      <c r="O16" s="73">
         <v>42</v>
       </c>
-      <c r="P16" s="83" t="s">
+      <c r="P16" s="81" t="s">
         <v>321</v>
       </c>
-      <c r="Q16" s="75"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A17" s="75"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="75"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="75"/>
-      <c r="F17" s="75"/>
-      <c r="G17" s="79"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="75"/>
-      <c r="J17" s="75"/>
-      <c r="K17" s="75"/>
-      <c r="L17" s="75"/>
-      <c r="M17" s="75"/>
-      <c r="N17" s="75"/>
-      <c r="O17" s="75"/>
-      <c r="P17" s="75"/>
-      <c r="Q17" s="75"/>
+      <c r="Q16" s="73"/>
+    </row>
+    <row r="17" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="73" t="s">
+        <v>323</v>
+      </c>
+      <c r="B17" s="76" t="s">
+        <v>322</v>
+      </c>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="73"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="73"/>
+      <c r="Q17" s="73"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A18" s="75"/>
-      <c r="B18" s="78"/>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="75"/>
-      <c r="F18" s="75"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="75"/>
-      <c r="J18" s="75"/>
-      <c r="K18" s="75"/>
-      <c r="L18" s="75"/>
-      <c r="M18" s="75"/>
-      <c r="N18" s="75"/>
-      <c r="O18" s="75"/>
-      <c r="P18" s="75"/>
-      <c r="Q18" s="75"/>
+      <c r="A18" s="73"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="73"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="73"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="73"/>
+      <c r="O18" s="73"/>
+      <c r="P18" s="73"/>
+      <c r="Q18" s="73"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2998,8 +3137,9 @@
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="39.1640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="88" customWidth="1"/>
-    <col min="5" max="5" width="20" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="97"/>
+    <col min="4" max="4" width="6.5" style="98" customWidth="1"/>
+    <col min="5" max="5" width="31.83203125" style="3" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="4" customWidth="1"/>
     <col min="7" max="7" width="19.1640625" style="5" customWidth="1"/>
     <col min="8" max="8" width="6.6640625" style="4" customWidth="1"/>
@@ -3007,15 +3147,15 @@
     <col min="10" max="10" width="7.1640625" style="4" customWidth="1"/>
     <col min="11" max="11" width="18.33203125" style="5" customWidth="1"/>
     <col min="12" max="12" width="7.83203125" style="4" customWidth="1"/>
-    <col min="13" max="13" width="15.1640625" style="5" customWidth="1"/>
+    <col min="13" max="13" width="19.5" style="5" customWidth="1"/>
     <col min="14" max="14" width="8" style="4" customWidth="1"/>
-    <col min="15" max="15" width="15.5" style="5" customWidth="1"/>
+    <col min="15" max="15" width="29.33203125" style="5" customWidth="1"/>
     <col min="16" max="16" width="7.1640625" style="4" customWidth="1"/>
     <col min="17" max="17" width="17.1640625" style="5" customWidth="1"/>
     <col min="18" max="18" width="7" style="4" customWidth="1"/>
     <col min="19" max="19" width="19" style="5" customWidth="1"/>
-    <col min="20" max="20" width="7.1640625" style="61" customWidth="1"/>
-    <col min="21" max="21" width="21.33203125" style="8" customWidth="1"/>
+    <col min="20" max="20" width="7.1640625" style="59" customWidth="1"/>
+    <col min="21" max="21" width="26" style="8" customWidth="1"/>
     <col min="22" max="22" width="10.83203125" style="9"/>
     <col min="23" max="23" width="18.83203125" style="6" customWidth="1"/>
     <col min="24" max="24" width="10.83203125" style="7"/>
@@ -3033,1368 +3173,1526 @@
     <col min="36" max="36" width="28.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="62" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A1" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="62" t="s">
+    <row r="1" spans="1:36" s="60" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A1" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="88" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="84" t="s">
+      <c r="D1" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="65" t="s">
+      <c r="G1" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="64" t="s">
+      <c r="H1" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="65" t="s">
+      <c r="I1" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="J1" s="64" t="s">
+      <c r="J1" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="K1" s="65" t="s">
+      <c r="K1" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="L1" s="66" t="s">
+      <c r="L1" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="M1" s="65" t="s">
+      <c r="M1" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="N1" s="66" t="s">
+      <c r="N1" s="64" t="s">
         <v>104</v>
       </c>
-      <c r="O1" s="65" t="s">
+      <c r="O1" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="P1" s="66" t="s">
+      <c r="P1" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="Q1" s="65" t="s">
+      <c r="Q1" s="63" t="s">
         <v>107</v>
       </c>
-      <c r="R1" s="66" t="s">
+      <c r="R1" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="S1" s="65" t="s">
+      <c r="S1" s="63" t="s">
         <v>109</v>
       </c>
-      <c r="T1" s="76" t="s">
+      <c r="T1" s="74" t="s">
         <v>110</v>
       </c>
-      <c r="U1" s="67" t="s">
+      <c r="U1" s="65" t="s">
         <v>111</v>
       </c>
-      <c r="V1" s="68" t="s">
+      <c r="V1" s="66" t="s">
         <v>112</v>
       </c>
-      <c r="W1" s="69" t="s">
+      <c r="W1" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="X1" s="70" t="s">
+      <c r="X1" s="68" t="s">
         <v>114</v>
       </c>
-      <c r="Y1" s="69" t="s">
+      <c r="Y1" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="Z1" s="71" t="s">
+      <c r="Z1" s="69" t="s">
         <v>116</v>
       </c>
-      <c r="AA1" s="67" t="s">
+      <c r="AA1" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="AB1" s="68" t="s">
+      <c r="AB1" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="AC1" s="72" t="s">
+      <c r="AC1" s="70" t="s">
         <v>119</v>
       </c>
-      <c r="AD1" s="73" t="s">
+      <c r="AD1" s="71" t="s">
         <v>120</v>
       </c>
-      <c r="AE1" s="72" t="s">
+      <c r="AE1" s="70" t="s">
         <v>121</v>
       </c>
-      <c r="AF1" s="74" t="s">
+      <c r="AF1" s="72" t="s">
         <v>122</v>
       </c>
-      <c r="AG1" s="62" t="s">
+      <c r="AG1" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="AH1" s="62" t="s">
+      <c r="AH1" s="60" t="s">
         <v>124</v>
       </c>
-      <c r="AI1" s="62" t="s">
+      <c r="AI1" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="AJ1" s="62" t="s">
+      <c r="AJ1" s="60" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
+    <row r="2" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A2" s="55" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="90" t="s">
         <v>128</v>
       </c>
-      <c r="D2" s="85">
+      <c r="D2" s="91">
         <v>20</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="F2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="32" t="s">
+      <c r="F2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="H2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="32" t="s">
+      <c r="H2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="J2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" s="32" t="s">
+      <c r="J2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="L2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" s="32" t="s">
+      <c r="L2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="N2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" s="32" t="s">
+      <c r="N2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="P2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="32" t="s">
+      <c r="P2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="R2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S2" s="30" t="s">
+      <c r="R2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="T2" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="U2" s="33" t="s">
+      <c r="T2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="V2" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W2" s="33" t="s">
+      <c r="V2" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="X2" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="33" t="s">
+      <c r="X2" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="Z2" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="35" t="s">
+      <c r="Z2" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="AB2" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="38" t="s">
+      <c r="AB2" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="AD2" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="59" t="s">
+      <c r="AD2" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="57" t="s">
         <v>217</v>
       </c>
-      <c r="AF2" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="28" t="s">
+      <c r="AF2" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="AJ2" s="41" t="s">
+      <c r="AJ2" s="39" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:36" s="42" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="57" t="s">
+    <row r="3" spans="1:36" s="40" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A3" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="90" t="s">
         <v>128</v>
       </c>
-      <c r="D3" s="85">
+      <c r="D3" s="91">
         <v>20</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="28" t="s">
         <v>233</v>
       </c>
-      <c r="F3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="32" t="s">
+      <c r="F3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="H3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="32" t="s">
+      <c r="H3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="J3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" s="32" t="s">
+      <c r="J3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="L3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="32" t="s">
+      <c r="L3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="N3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" s="32" t="s">
+      <c r="N3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="P3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="32" t="s">
+      <c r="P3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="R3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" s="32" t="s">
+      <c r="R3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="T3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="U3" s="35" t="s">
+      <c r="T3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="V3" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W3" s="33" t="s">
+      <c r="V3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="X3" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="33" t="s">
+      <c r="X3" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="Z3" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="35" t="s">
+      <c r="Z3" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="AB3" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="38" t="s">
+      <c r="AB3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="AD3" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="38" t="s">
+      <c r="AD3" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="AF3" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH3" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI3" s="28" t="s">
+      <c r="AF3" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="AJ3" s="41" t="s">
+      <c r="AJ3" s="39" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="4" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" s="57" t="s">
+    <row r="4" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A4" s="55" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="90" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="85">
+      <c r="D4" s="91">
         <v>20</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="F4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="32" t="s">
+      <c r="F4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="H4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="32" t="s">
+      <c r="H4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="J4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" s="32" t="s">
+      <c r="J4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="L4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" s="32" t="s">
+      <c r="L4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="N4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="32" t="s">
+      <c r="N4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="P4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="32" t="s">
+      <c r="P4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="R4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S4" s="32" t="s">
+      <c r="R4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="T4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="U4" s="35" t="s">
+      <c r="T4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="V4" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="33" t="s">
+      <c r="V4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="X4" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="33" t="s">
+      <c r="X4" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="Z4" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="35" t="s">
+      <c r="Z4" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="AB4" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="38" t="s">
+      <c r="AB4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="36" t="s">
         <v>230</v>
       </c>
-      <c r="AD4" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="38" t="s">
+      <c r="AD4" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="36" t="s">
         <v>221</v>
       </c>
-      <c r="AF4" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI4" s="28" t="s">
+      <c r="AF4" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="27" t="s">
         <v>168</v>
       </c>
-      <c r="AJ4" s="41" t="s">
+      <c r="AJ4" s="39" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="57" t="s">
+    <row r="5" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="55" t="s">
         <v>170</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="90" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="85">
+      <c r="D5" s="91">
         <v>20</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="F5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="32" t="s">
+      <c r="F5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="H5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="32" t="s">
+      <c r="H5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="30" t="s">
         <v>271</v>
       </c>
-      <c r="J5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="32" t="s">
+      <c r="J5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="L5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="32" t="s">
+      <c r="L5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="N5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="32" t="s">
+      <c r="N5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="P5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="32" t="s">
+      <c r="P5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="R5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" s="32" t="s">
+      <c r="R5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="T5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="U5" s="35" t="s">
+      <c r="T5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="V5" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" s="33" t="s">
+      <c r="V5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="X5" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="33" t="s">
+      <c r="X5" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="Z5" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="35" t="s">
+      <c r="Z5" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="AB5" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="38" t="s">
+      <c r="AB5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="36" t="s">
         <v>224</v>
       </c>
-      <c r="AD5" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="38" t="s">
+      <c r="AD5" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="AF5" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="28" t="s">
+      <c r="AF5" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="AJ5" s="41" t="s">
+      <c r="AJ5" s="39" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="6" spans="1:36" s="42" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="57" t="s">
+    <row r="6" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A6" s="55" t="s">
         <v>182</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="90" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="85">
+      <c r="D6" s="91">
         <v>20</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="F6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="32" t="s">
+      <c r="F6" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="H6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="32" t="s">
+      <c r="H6" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="J6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="32" t="s">
+      <c r="J6" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="L6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="32" t="s">
+      <c r="L6" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="N6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="32" t="s">
+      <c r="N6" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="P6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="32" t="s">
+      <c r="P6" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="R6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="30" t="s">
+      <c r="R6" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="T6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" s="35" t="s">
+      <c r="T6" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="V6" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="33" t="s">
+      <c r="V6" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="X6" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="33" t="s">
+      <c r="X6" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="Z6" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="35" t="s">
+      <c r="Z6" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="AB6" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="38" t="s">
+      <c r="AB6" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="AD6" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="38" t="s">
+      <c r="AD6" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="AF6" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="28" t="s">
+      <c r="AF6" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="AJ6" s="41" t="s">
+      <c r="AJ6" s="39" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="7" spans="1:36" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="58" t="s">
+    <row r="7" spans="1:36" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="56" t="s">
         <v>188</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="92" t="s">
         <v>128</v>
       </c>
-      <c r="D7" s="86">
+      <c r="D7" s="93">
         <v>20</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="F7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="17" t="s">
+      <c r="F7" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="H7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="17" t="s">
+      <c r="H7" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="J7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="17" t="s">
+      <c r="J7" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="L7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="17" t="s">
+      <c r="L7" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="N7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="17" t="s">
+      <c r="N7" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="P7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="17" t="s">
+      <c r="P7" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="R7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="30" t="s">
+      <c r="R7" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="T7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="20" t="s">
+      <c r="T7" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="V7" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="18" t="s">
+      <c r="V7" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="X7" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="18" t="s">
+      <c r="X7" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="Z7" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="20" t="s">
+      <c r="Z7" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="AB7" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="23" t="s">
+      <c r="AB7" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="AD7" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="23" t="s">
+      <c r="AD7" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="AF7" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="26" t="b">
+      <c r="AF7" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="25" t="b">
         <v>1</v>
       </c>
       <c r="AI7" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="AJ7" s="26" t="s">
+      <c r="AJ7" s="25" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="41" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A8" s="57" t="s">
+    <row r="8" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A8" s="55" t="s">
         <v>278</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="27" t="s">
         <v>279</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="92" t="s">
         <v>128</v>
       </c>
-      <c r="D8" s="86">
+      <c r="D8" s="93">
         <v>20</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="28" t="s">
         <v>280</v>
       </c>
-      <c r="F8" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="32" t="s">
+      <c r="F8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="H8" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="32" t="s">
+      <c r="H8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="J8" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="32" t="s">
+      <c r="J8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="L8" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="32" t="s">
+      <c r="L8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="30" t="s">
         <v>282</v>
       </c>
-      <c r="N8" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="32" t="s">
+      <c r="N8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="P8" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="32" t="s">
+      <c r="P8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="R8" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S8" s="32" t="s">
+      <c r="R8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="T8" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" s="35" t="s">
+      <c r="T8" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="V8" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="33" t="s">
+      <c r="V8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="X8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="33" t="s">
+      <c r="X8" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="Z8" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="35" t="s">
+      <c r="Z8" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="33" t="s">
         <v>286</v>
       </c>
-      <c r="AB8" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="38" t="s">
+      <c r="AB8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="36" t="s">
         <v>287</v>
       </c>
-      <c r="AD8" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="38" t="s">
+      <c r="AD8" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="36" t="s">
         <v>290</v>
       </c>
-      <c r="AF8" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH8" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="28" t="s">
+      <c r="AF8" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="27" t="s">
         <v>294</v>
       </c>
-      <c r="AJ8" s="41" t="s">
+      <c r="AJ8" s="39" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="9" spans="1:36" s="41" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A9" s="57" t="s">
+    <row r="9" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A9" s="55" t="s">
         <v>304</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="27" t="s">
         <v>303</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="92" t="s">
         <v>128</v>
       </c>
-      <c r="D9" s="86">
+      <c r="D9" s="93">
         <v>20</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="F9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="32" t="s">
+      <c r="F9" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="30" t="s">
         <v>306</v>
       </c>
-      <c r="H9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="32" t="s">
+      <c r="H9" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="J9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="32" t="s">
+      <c r="J9" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="30" t="s">
         <v>308</v>
       </c>
-      <c r="L9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="32" t="s">
+      <c r="L9" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="30" t="s">
         <v>309</v>
       </c>
-      <c r="N9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="32" t="s">
+      <c r="N9" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="30" t="s">
         <v>310</v>
       </c>
-      <c r="P9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="32" t="s">
+      <c r="P9" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="R9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" s="32" t="s">
+      <c r="R9" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="30" t="s">
         <v>312</v>
       </c>
-      <c r="T9" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="U9" s="35" t="s">
+      <c r="T9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="33" t="s">
         <v>313</v>
       </c>
-      <c r="V9" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="33" t="s">
+      <c r="V9" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="X9" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="33" t="s">
+      <c r="X9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="Z9" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="35" t="s">
+      <c r="Z9" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="AB9" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="38" t="s">
+      <c r="AB9" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="36" t="s">
         <v>316</v>
       </c>
-      <c r="AD9" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="38" t="s">
+      <c r="AD9" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="36" t="s">
         <v>317</v>
       </c>
-      <c r="AF9" s="40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH9" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI9" s="28" t="s">
+      <c r="AF9" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="27" t="s">
         <v>319</v>
       </c>
-      <c r="AJ9" s="41" t="s">
+      <c r="AJ9" s="39" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="44"/>
-      <c r="B10" s="45"/>
-      <c r="D10" s="87"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="48"/>
-      <c r="P10" s="47"/>
-      <c r="Q10" s="48"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="48"/>
-      <c r="T10" s="60"/>
-      <c r="U10" s="51"/>
-      <c r="V10" s="52"/>
-      <c r="W10" s="49"/>
-      <c r="X10" s="50"/>
-      <c r="Y10" s="49"/>
-      <c r="Z10" s="53"/>
-      <c r="AA10" s="51"/>
-      <c r="AB10" s="52"/>
-      <c r="AC10" s="54"/>
-      <c r="AD10" s="55"/>
-      <c r="AE10" s="54"/>
-      <c r="AF10" s="56"/>
-    </row>
-    <row r="11" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="44"/>
-      <c r="B11" s="45"/>
-      <c r="D11" s="87"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="47"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="47"/>
-      <c r="O11" s="48"/>
-      <c r="P11" s="47"/>
-      <c r="Q11" s="48"/>
-      <c r="R11" s="47"/>
-      <c r="S11" s="48"/>
-      <c r="T11" s="60"/>
-      <c r="U11" s="51"/>
-      <c r="V11" s="52"/>
-      <c r="W11" s="49"/>
-      <c r="X11" s="50"/>
-      <c r="Y11" s="49"/>
-      <c r="Z11" s="53"/>
-      <c r="AA11" s="51"/>
-      <c r="AB11" s="52"/>
-      <c r="AC11" s="54"/>
-      <c r="AD11" s="55"/>
-      <c r="AE11" s="54"/>
-      <c r="AF11" s="56"/>
-      <c r="AI11" s="45"/>
-    </row>
-    <row r="12" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="44"/>
-      <c r="B12" s="45"/>
-      <c r="D12" s="87"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="48"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="48"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="48"/>
-      <c r="T12" s="60"/>
-      <c r="U12" s="51"/>
-      <c r="V12" s="52"/>
-      <c r="W12" s="49"/>
-      <c r="X12" s="50"/>
-      <c r="Y12" s="49"/>
-      <c r="Z12" s="53"/>
-      <c r="AA12" s="51"/>
-      <c r="AB12" s="52"/>
-      <c r="AC12" s="54"/>
-      <c r="AD12" s="55"/>
-      <c r="AE12" s="54"/>
-      <c r="AF12" s="56"/>
-      <c r="AI12" s="45"/>
-    </row>
-    <row r="13" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="44"/>
-      <c r="B13" s="45"/>
-      <c r="D13" s="87"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="48"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="48"/>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="48"/>
-      <c r="R13" s="47"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="60"/>
-      <c r="U13" s="51"/>
-      <c r="V13" s="52"/>
-      <c r="W13" s="49"/>
-      <c r="X13" s="50"/>
-      <c r="Y13" s="49"/>
-      <c r="Z13" s="53"/>
-      <c r="AA13" s="51"/>
-      <c r="AB13" s="52"/>
-      <c r="AC13" s="54"/>
-      <c r="AD13" s="55"/>
-      <c r="AE13" s="54"/>
-      <c r="AF13" s="56"/>
-      <c r="AI13" s="45"/>
-    </row>
-    <row r="14" spans="1:36" s="42" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="44"/>
-      <c r="B14" s="45"/>
-      <c r="D14" s="87"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="48"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="48"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="48"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="48"/>
-      <c r="T14" s="60"/>
-      <c r="U14" s="51"/>
-      <c r="V14" s="52"/>
-      <c r="W14" s="49"/>
-      <c r="X14" s="50"/>
-      <c r="Y14" s="49"/>
-      <c r="Z14" s="53"/>
-      <c r="AA14" s="51"/>
-      <c r="AB14" s="52"/>
-      <c r="AC14" s="54"/>
-      <c r="AD14" s="55"/>
-      <c r="AE14" s="54"/>
-      <c r="AF14" s="56"/>
-      <c r="AI14" s="45"/>
-    </row>
-    <row r="15" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="44"/>
-      <c r="B15" s="45"/>
-      <c r="D15" s="87"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="48"/>
-      <c r="N15" s="47"/>
-      <c r="O15" s="48"/>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="48"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="48"/>
-      <c r="T15" s="60"/>
-      <c r="U15" s="51"/>
-      <c r="V15" s="52"/>
-      <c r="W15" s="49"/>
-      <c r="X15" s="50"/>
-      <c r="Y15" s="49"/>
-      <c r="Z15" s="53"/>
-      <c r="AA15" s="51"/>
-      <c r="AB15" s="52"/>
-      <c r="AC15" s="54"/>
-      <c r="AD15" s="55"/>
-      <c r="AE15" s="54"/>
-      <c r="AF15" s="56"/>
-      <c r="AI15" s="45"/>
-    </row>
-    <row r="16" spans="1:36" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="44"/>
-      <c r="B16" s="45"/>
-      <c r="D16" s="87"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="47"/>
-      <c r="M16" s="48"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="48"/>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="48"/>
-      <c r="R16" s="47"/>
-      <c r="S16" s="48"/>
-      <c r="T16" s="60"/>
-      <c r="U16" s="51"/>
-      <c r="V16" s="52"/>
-      <c r="W16" s="49"/>
-      <c r="X16" s="50"/>
-      <c r="Y16" s="49"/>
-      <c r="Z16" s="53"/>
-      <c r="AA16" s="51"/>
-      <c r="AB16" s="52"/>
-      <c r="AC16" s="54"/>
-      <c r="AD16" s="55"/>
-      <c r="AE16" s="54"/>
-      <c r="AF16" s="56"/>
-      <c r="AI16" s="45"/>
-    </row>
-    <row r="17" spans="1:35" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="44"/>
-      <c r="B17" s="45"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="47"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="47"/>
-      <c r="M17" s="48"/>
-      <c r="N17" s="47"/>
-      <c r="O17" s="48"/>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="48"/>
-      <c r="R17" s="47"/>
-      <c r="S17" s="48"/>
-      <c r="T17" s="60"/>
-      <c r="U17" s="51"/>
-      <c r="V17" s="52"/>
-      <c r="W17" s="49"/>
-      <c r="X17" s="50"/>
-      <c r="Y17" s="49"/>
-      <c r="Z17" s="53"/>
-      <c r="AA17" s="51"/>
-      <c r="AB17" s="52"/>
-      <c r="AC17" s="54"/>
-      <c r="AD17" s="55"/>
-      <c r="AE17" s="54"/>
-      <c r="AF17" s="56"/>
-      <c r="AI17" s="45"/>
-    </row>
-    <row r="18" spans="1:35" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="44"/>
-      <c r="B18" s="45"/>
-      <c r="D18" s="87"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="47"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="47"/>
-      <c r="O18" s="48"/>
-      <c r="P18" s="47"/>
-      <c r="Q18" s="48"/>
-      <c r="R18" s="47"/>
-      <c r="S18" s="48"/>
-      <c r="T18" s="60"/>
-      <c r="U18" s="51"/>
-      <c r="V18" s="52"/>
-      <c r="W18" s="49"/>
-      <c r="X18" s="50"/>
-      <c r="Y18" s="49"/>
-      <c r="Z18" s="53"/>
-      <c r="AA18" s="51"/>
-      <c r="AB18" s="52"/>
-      <c r="AC18" s="54"/>
-      <c r="AD18" s="55"/>
-      <c r="AE18" s="54"/>
-      <c r="AF18" s="56"/>
-      <c r="AI18" s="45"/>
-    </row>
-    <row r="19" spans="1:35" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="44"/>
-      <c r="B19" s="45"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="47"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="47"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="47"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="60"/>
-      <c r="U19" s="51"/>
-      <c r="V19" s="52"/>
-      <c r="W19" s="49"/>
-      <c r="X19" s="50"/>
-      <c r="Y19" s="49"/>
-      <c r="Z19" s="53"/>
-      <c r="AA19" s="51"/>
-      <c r="AB19" s="52"/>
-      <c r="AC19" s="54"/>
-      <c r="AD19" s="55"/>
-      <c r="AE19" s="54"/>
-      <c r="AF19" s="56"/>
-      <c r="AI19" s="45"/>
-    </row>
-    <row r="20" spans="1:35" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="44"/>
-      <c r="B20" s="45"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="48"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="47"/>
-      <c r="O20" s="48"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="48"/>
-      <c r="R20" s="47"/>
-      <c r="S20" s="48"/>
-      <c r="T20" s="60"/>
-      <c r="U20" s="51"/>
-      <c r="V20" s="52"/>
-      <c r="W20" s="49"/>
-      <c r="X20" s="50"/>
-      <c r="Y20" s="49"/>
-      <c r="Z20" s="53"/>
-      <c r="AA20" s="51"/>
-      <c r="AB20" s="52"/>
-      <c r="AC20" s="54"/>
-      <c r="AD20" s="55"/>
-      <c r="AE20" s="54"/>
-      <c r="AF20" s="56"/>
-      <c r="AI20" s="45"/>
+    <row r="10" spans="1:36" s="85" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A10" s="87" t="s">
+        <v>324</v>
+      </c>
+      <c r="B10" s="84" t="s">
+        <v>325</v>
+      </c>
+      <c r="C10" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="93">
+        <v>20</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="F10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="H10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>328</v>
+      </c>
+      <c r="J10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="28" t="s">
+        <v>329</v>
+      </c>
+      <c r="L10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="N10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="P10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="28" t="s">
+        <v>333</v>
+      </c>
+      <c r="R10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="T10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="V10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="33" t="s">
+        <v>335</v>
+      </c>
+      <c r="X10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="33" t="s">
+        <v>336</v>
+      </c>
+      <c r="Z10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="33" t="s">
+        <v>337</v>
+      </c>
+      <c r="AB10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="33" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="33" t="s">
+        <v>339</v>
+      </c>
+      <c r="AF10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="27" t="s">
+        <v>341</v>
+      </c>
+      <c r="AJ10" s="39" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" s="40" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="82" t="s">
+        <v>342</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="C11" s="95"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="44" t="s">
+        <v>343</v>
+      </c>
+      <c r="F11" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="46" t="s">
+        <v>344</v>
+      </c>
+      <c r="H11" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="46" t="s">
+        <v>345</v>
+      </c>
+      <c r="J11" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" s="46" t="s">
+        <v>346</v>
+      </c>
+      <c r="L11" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="46" t="s">
+        <v>347</v>
+      </c>
+      <c r="N11" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" s="46" t="s">
+        <v>354</v>
+      </c>
+      <c r="P11" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="R11" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S11" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="T11" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U11" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="V11" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W11" s="47" t="s">
+        <v>357</v>
+      </c>
+      <c r="X11" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="47" t="s">
+        <v>359</v>
+      </c>
+      <c r="Z11" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="49" t="s">
+        <v>351</v>
+      </c>
+      <c r="AB11" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="52" t="s">
+        <v>350</v>
+      </c>
+      <c r="AD11" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="52" t="s">
+        <v>358</v>
+      </c>
+      <c r="AF11" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH11" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI11" s="27" t="s">
+        <v>353</v>
+      </c>
+      <c r="AJ11" s="39" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="42"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="58"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="47"/>
+      <c r="X12" s="48"/>
+      <c r="Y12" s="47"/>
+      <c r="Z12" s="51"/>
+      <c r="AA12" s="49"/>
+      <c r="AB12" s="50"/>
+      <c r="AC12" s="52"/>
+      <c r="AD12" s="53"/>
+      <c r="AE12" s="52"/>
+      <c r="AF12" s="54"/>
+      <c r="AI12" s="43"/>
+    </row>
+    <row r="13" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="42"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="45"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="45"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="45"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="58"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="50"/>
+      <c r="W13" s="47"/>
+      <c r="X13" s="48"/>
+      <c r="Y13" s="47"/>
+      <c r="Z13" s="51"/>
+      <c r="AA13" s="49"/>
+      <c r="AB13" s="50"/>
+      <c r="AC13" s="52"/>
+      <c r="AD13" s="53"/>
+      <c r="AE13" s="52"/>
+      <c r="AF13" s="54"/>
+      <c r="AI13" s="43"/>
+    </row>
+    <row r="14" spans="1:36" s="40" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="42"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="45"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="45"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="45"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="45"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="58"/>
+      <c r="U14" s="49"/>
+      <c r="V14" s="50"/>
+      <c r="W14" s="47"/>
+      <c r="X14" s="48"/>
+      <c r="Y14" s="47"/>
+      <c r="Z14" s="51"/>
+      <c r="AA14" s="49"/>
+      <c r="AB14" s="50"/>
+      <c r="AC14" s="52"/>
+      <c r="AD14" s="53"/>
+      <c r="AE14" s="52"/>
+      <c r="AF14" s="54"/>
+      <c r="AI14" s="43"/>
+    </row>
+    <row r="15" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="42"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="96"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="45"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="45"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="45"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="58"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="50"/>
+      <c r="W15" s="47"/>
+      <c r="X15" s="48"/>
+      <c r="Y15" s="47"/>
+      <c r="Z15" s="51"/>
+      <c r="AA15" s="49"/>
+      <c r="AB15" s="50"/>
+      <c r="AC15" s="52"/>
+      <c r="AD15" s="53"/>
+      <c r="AE15" s="52"/>
+      <c r="AF15" s="54"/>
+      <c r="AI15" s="43"/>
+    </row>
+    <row r="16" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="42"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="45"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="46"/>
+      <c r="P16" s="45"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="45"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="58"/>
+      <c r="U16" s="49"/>
+      <c r="V16" s="50"/>
+      <c r="W16" s="47"/>
+      <c r="X16" s="48"/>
+      <c r="Y16" s="47"/>
+      <c r="Z16" s="51"/>
+      <c r="AA16" s="49"/>
+      <c r="AB16" s="50"/>
+      <c r="AC16" s="52"/>
+      <c r="AD16" s="53"/>
+      <c r="AE16" s="52"/>
+      <c r="AF16" s="54"/>
+      <c r="AI16" s="43"/>
+    </row>
+    <row r="17" spans="1:35" s="40" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="42"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="96"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="45"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="45"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="45"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="58"/>
+      <c r="U17" s="49"/>
+      <c r="V17" s="50"/>
+      <c r="W17" s="47"/>
+      <c r="X17" s="48"/>
+      <c r="Y17" s="47"/>
+      <c r="Z17" s="51"/>
+      <c r="AA17" s="49"/>
+      <c r="AB17" s="50"/>
+      <c r="AC17" s="52"/>
+      <c r="AD17" s="53"/>
+      <c r="AE17" s="52"/>
+      <c r="AF17" s="54"/>
+      <c r="AI17" s="43"/>
+    </row>
+    <row r="18" spans="1:35" s="40" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="42"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="45"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="45"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="58"/>
+      <c r="U18" s="49"/>
+      <c r="V18" s="50"/>
+      <c r="W18" s="47"/>
+      <c r="X18" s="48"/>
+      <c r="Y18" s="47"/>
+      <c r="Z18" s="51"/>
+      <c r="AA18" s="49"/>
+      <c r="AB18" s="50"/>
+      <c r="AC18" s="52"/>
+      <c r="AD18" s="53"/>
+      <c r="AE18" s="52"/>
+      <c r="AF18" s="54"/>
+      <c r="AI18" s="43"/>
+    </row>
+    <row r="19" spans="1:35" s="40" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="42"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="96"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="45"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="45"/>
+      <c r="O19" s="46"/>
+      <c r="P19" s="45"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="45"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="58"/>
+      <c r="U19" s="49"/>
+      <c r="V19" s="50"/>
+      <c r="W19" s="47"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="47"/>
+      <c r="Z19" s="51"/>
+      <c r="AA19" s="49"/>
+      <c r="AB19" s="50"/>
+      <c r="AC19" s="52"/>
+      <c r="AD19" s="53"/>
+      <c r="AE19" s="52"/>
+      <c r="AF19" s="54"/>
+      <c r="AI19" s="43"/>
+    </row>
+    <row r="20" spans="1:35" s="40" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="42"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="46"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="45"/>
+      <c r="S20" s="46"/>
+      <c r="T20" s="58"/>
+      <c r="U20" s="49"/>
+      <c r="V20" s="50"/>
+      <c r="W20" s="47"/>
+      <c r="X20" s="48"/>
+      <c r="Y20" s="47"/>
+      <c r="Z20" s="51"/>
+      <c r="AA20" s="49"/>
+      <c r="AB20" s="50"/>
+      <c r="AC20" s="52"/>
+      <c r="AD20" s="53"/>
+      <c r="AE20" s="52"/>
+      <c r="AF20" s="54"/>
+      <c r="AI20" s="43"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4416,57 +4714,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="80" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="80" t="s">
+      <c r="A1" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="80" t="s">
+      <c r="D1" s="78" t="s">
         <v>241</v>
       </c>
-      <c r="E1" s="80" t="s">
+      <c r="E1" s="78" t="s">
         <v>242</v>
       </c>
-      <c r="F1" s="80" t="s">
+      <c r="F1" s="78" t="s">
         <v>243</v>
       </c>
-      <c r="G1" s="80" t="s">
+      <c r="G1" s="78" t="s">
         <v>264</v>
       </c>
-      <c r="H1" s="80" t="s">
+      <c r="H1" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="82" t="s">
+      <c r="I1" s="80" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="79" t="s">
         <v>244</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="79" t="s">
         <v>256</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="79" t="s">
         <v>245</v>
       </c>
-      <c r="D2" s="81" t="s">
+      <c r="D2" s="79" t="s">
         <v>246</v>
       </c>
-      <c r="E2" s="81" t="s">
+      <c r="E2" s="79" t="s">
         <v>247</v>
       </c>
-      <c r="F2" s="81">
+      <c r="F2" s="79">
         <v>90</v>
       </c>
-      <c r="G2" s="81">
+      <c r="G2" s="79">
         <v>1.25</v>
       </c>
-      <c r="H2" s="81" t="s">
+      <c r="H2" s="79" t="s">
         <v>248</v>
       </c>
       <c r="I2" t="s">
@@ -4480,13 +4778,13 @@
       <c r="B3" t="s">
         <v>257</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="79" t="s">
         <v>252</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="79" t="s">
         <v>253</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="E3" s="79" t="s">
         <v>247</v>
       </c>
       <c r="F3">
@@ -4495,7 +4793,7 @@
       <c r="G3">
         <v>1.5</v>
       </c>
-      <c r="H3" s="81" t="s">
+      <c r="H3" s="79" t="s">
         <v>255</v>
       </c>
       <c r="I3" t="s">
@@ -4509,13 +4807,13 @@
       <c r="B4" t="s">
         <v>259</v>
       </c>
-      <c r="C4" s="81" t="s">
+      <c r="C4" s="79" t="s">
         <v>260</v>
       </c>
-      <c r="D4" s="81" t="s">
+      <c r="D4" s="79" t="s">
         <v>261</v>
       </c>
-      <c r="E4" s="81" t="s">
+      <c r="E4" s="79" t="s">
         <v>247</v>
       </c>
       <c r="F4">
@@ -4524,7 +4822,7 @@
       <c r="G4">
         <v>1.25</v>
       </c>
-      <c r="H4" s="81" t="s">
+      <c r="H4" s="79" t="s">
         <v>262</v>
       </c>
       <c r="I4" t="s">
@@ -4538,13 +4836,13 @@
       <c r="B5" t="s">
         <v>266</v>
       </c>
-      <c r="C5" s="81" t="s">
+      <c r="C5" s="79" t="s">
         <v>267</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="79" t="s">
         <v>268</v>
       </c>
-      <c r="E5" s="81" t="s">
+      <c r="E5" s="79" t="s">
         <v>247</v>
       </c>
       <c r="F5">
@@ -4553,7 +4851,7 @@
       <c r="G5">
         <v>1.25</v>
       </c>
-      <c r="H5" s="81" t="s">
+      <c r="H5" s="79" t="s">
         <v>269</v>
       </c>
       <c r="I5" t="s">

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCEB638-5D13-6448-9CB5-15C2E6016383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3029BCED-42A5-0B41-93AF-CDD87B9CEE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="2" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="342">
   <si>
     <t>question_id</t>
   </si>
@@ -587,24 +587,6 @@
     <t>SCIENCE FICTION</t>
   </si>
   <si>
-    <t>bonus_q_norway_snow</t>
-  </si>
-  <si>
-    <t>Which of these are Norwegian words for "snow"?</t>
-  </si>
-  <si>
-    <t>Slaps</t>
-  </si>
-  <si>
-    <t>Skare</t>
-  </si>
-  <si>
-    <t>These are Noregian words for "snow".</t>
-  </si>
-  <si>
-    <t>SCANDINAVIA</t>
-  </si>
-  <si>
     <t>bonus_q_ikea</t>
   </si>
   <si>
@@ -659,33 +641,6 @@
     <t>What year was Velcro (A.K.A. "Hook &amp; Loop") invented?</t>
   </si>
   <si>
-    <t>Snø</t>
-  </si>
-  <si>
-    <t>Nysnø</t>
-  </si>
-  <si>
-    <t>Fokksnø</t>
-  </si>
-  <si>
-    <t>Kram snø</t>
-  </si>
-  <si>
-    <t>Sørpe</t>
-  </si>
-  <si>
-    <t>Flåkens</t>
-  </si>
-  <si>
-    <t>Snøbizness</t>
-  </si>
-  <si>
-    <t>Slëëten</t>
-  </si>
-  <si>
-    <t>Slippurï</t>
-  </si>
-  <si>
     <t>Poäng</t>
   </si>
   <si>
@@ -714,15 +669,6 @@
   </si>
   <si>
     <t>Kappa Rho</t>
-  </si>
-  <si>
-    <t>Løssnø</t>
-  </si>
-  <si>
-    <t>Fallensnø</t>
-  </si>
-  <si>
-    <t>Snǒklar</t>
   </si>
   <si>
     <t>Screpps</t>
@@ -2111,7 +2057,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C2" s="73">
         <v>10</v>
@@ -2479,7 +2425,7 @@
         <v>42</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C10" s="73">
         <v>10</v>
@@ -2560,7 +2506,7 @@
         <v>165</v>
       </c>
       <c r="P11" s="81" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="Q11" s="73"/>
     </row>
@@ -2615,10 +2561,10 @@
     </row>
     <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="73" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="C13" s="73">
         <v>1</v>
@@ -2654,16 +2600,16 @@
         <v>12</v>
       </c>
       <c r="P13" s="81" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="Q13" s="73"/>
     </row>
     <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="73" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="B14" s="76" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="C14" s="73">
         <v>100</v>
@@ -2701,16 +2647,16 @@
         <v>110</v>
       </c>
       <c r="P14" s="81" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="Q14" s="73"/>
     </row>
     <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="73" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="C15" s="73">
         <v>5</v>
@@ -2746,16 +2692,16 @@
         <v>27</v>
       </c>
       <c r="P15" s="81" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="Q15" s="73"/>
     </row>
     <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="73" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="C16" s="73">
         <v>10</v>
@@ -2793,16 +2739,16 @@
         <v>42</v>
       </c>
       <c r="P16" s="81" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="Q16" s="73"/>
     </row>
     <row r="17" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="73" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="C17" s="73"/>
       <c r="D17" s="73"/>
@@ -3087,15 +3033,15 @@
         <v>92</v>
       </c>
       <c r="M7" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="B8" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="C8" t="s">
         <v>88</v>
@@ -3116,13 +3062,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="M8" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3132,7 +3078,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A722971B-16B6-2747-9012-3CB77F8500DE}">
-  <dimension ref="A1:AJ20"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -3339,7 +3285,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="28" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="T2" s="29" t="b">
         <v>1</v>
@@ -3375,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="57" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="AF2" s="38" t="b">
         <v>0</v>
@@ -3407,7 +3353,7 @@
         <v>20</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="F3" s="29" t="b">
         <v>1</v>
@@ -3443,13 +3389,13 @@
         <v>1</v>
       </c>
       <c r="Q3" s="30" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="R3" s="29" t="b">
         <v>1</v>
       </c>
       <c r="S3" s="30" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="T3" s="29" t="b">
         <v>1</v>
@@ -3461,13 +3407,13 @@
         <v>0</v>
       </c>
       <c r="W3" s="31" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="X3" s="32" t="b">
         <v>0</v>
       </c>
       <c r="Y3" s="31" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="Z3" s="35" t="b">
         <v>0</v>
@@ -3508,7 +3454,7 @@
         <v>156</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C4" s="90" t="s">
         <v>128</v>
@@ -3559,7 +3505,7 @@
         <v>1</v>
       </c>
       <c r="S4" s="30" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="T4" s="29" t="b">
         <v>1</v>
@@ -3589,13 +3535,13 @@
         <v>0</v>
       </c>
       <c r="AC4" s="36" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="AD4" s="37" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="36" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="AF4" s="38" t="b">
         <v>0</v>
@@ -3618,7 +3564,7 @@
         <v>170</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C5" s="90" t="s">
         <v>128</v>
@@ -3639,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="J5" s="29" t="b">
         <v>1</v>
@@ -3657,7 +3603,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="30" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="P5" s="29" t="b">
         <v>1</v>
@@ -3669,7 +3615,7 @@
         <v>1</v>
       </c>
       <c r="S5" s="30" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="T5" s="29" t="b">
         <v>1</v>
@@ -3687,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="Y5" s="31" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="Z5" s="35" t="b">
         <v>0</v>
@@ -3699,7 +3645,7 @@
         <v>0</v>
       </c>
       <c r="AC5" s="36" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="AD5" s="37" t="b">
         <v>0</v>
@@ -3723,122 +3669,122 @@
         <v>181</v>
       </c>
     </row>
-    <row r="6" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="55" t="s">
+    <row r="6" spans="1:36" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A6" s="56" t="s">
         <v>182</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="C6" s="90" t="s">
+      <c r="C6" s="92" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="91">
+      <c r="D6" s="93">
         <v>20</v>
       </c>
-      <c r="E6" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="F6" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="H6" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="30" t="s">
+      <c r="E6" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="J6" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="30" t="s">
+      <c r="F6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="L6" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="N6" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="P6" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="30" t="s">
+      <c r="H6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="J6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="L6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="N6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="P6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="R6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="T6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="V6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="X6" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z6" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="R6" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="T6" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="V6" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="X6" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="Z6" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="AB6" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="36" t="s">
-        <v>214</v>
-      </c>
-      <c r="AD6" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="AF6" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="AJ6" s="39" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="56" t="s">
-        <v>188</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>189</v>
+      <c r="AB6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="AD6" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="AF6" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="AJ6" s="25" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A7" s="55" t="s">
+        <v>260</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>261</v>
       </c>
       <c r="C7" s="92" t="s">
         <v>128</v>
@@ -3846,88 +3792,88 @@
       <c r="D7" s="93">
         <v>20</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="F7" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="H7" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="J7" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="L7" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="N7" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="P7" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="R7" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="T7" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="V7" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="X7" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z7" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="AB7" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="AD7" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="AF7" s="24" t="b">
+      <c r="E7" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="F7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="H7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="J7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="L7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="N7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="P7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="R7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="T7" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="33" t="s">
+        <v>274</v>
+      </c>
+      <c r="V7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="X7" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z7" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="AB7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="36" t="s">
+        <v>269</v>
+      </c>
+      <c r="AD7" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="36" t="s">
+        <v>272</v>
+      </c>
+      <c r="AF7" s="38" t="b">
         <v>0</v>
       </c>
       <c r="AG7" s="25" t="b">
@@ -3936,19 +3882,19 @@
       <c r="AH7" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="AI7" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="AJ7" s="25" t="s">
-        <v>202</v>
+      <c r="AI7" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="AJ7" s="39" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="55" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C8" s="92" t="s">
         <v>128</v>
@@ -3957,85 +3903,85 @@
         <v>20</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="F8" s="29" t="b">
         <v>1</v>
       </c>
       <c r="G8" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="H8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="H8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="30" t="s">
-        <v>281</v>
-      </c>
       <c r="J8" s="29" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="30" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L8" s="29" t="b">
         <v>1</v>
       </c>
       <c r="M8" s="30" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="N8" s="29" t="b">
         <v>1</v>
       </c>
       <c r="O8" s="30" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="P8" s="29" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="R8" s="29" t="b">
         <v>1</v>
       </c>
       <c r="S8" s="30" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="T8" s="83" t="b">
         <v>1</v>
       </c>
       <c r="U8" s="33" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="V8" s="34" t="b">
         <v>0</v>
       </c>
       <c r="W8" s="31" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="X8" s="32" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="31" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="Z8" s="35" t="b">
         <v>0</v>
       </c>
       <c r="AA8" s="33" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="AB8" s="34" t="b">
         <v>0</v>
       </c>
       <c r="AC8" s="36" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AD8" s="37" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="36" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="AF8" s="38" t="b">
         <v>0</v>
@@ -4047,337 +3993,262 @@
         <v>1</v>
       </c>
       <c r="AI8" s="27" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="AJ8" s="39" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A9" s="55" t="s">
-        <v>304</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>303</v>
-      </c>
-      <c r="C9" s="92" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" s="85" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A9" s="87" t="s">
+        <v>306</v>
+      </c>
+      <c r="B9" s="84" t="s">
+        <v>307</v>
+      </c>
+      <c r="C9" s="94" t="s">
         <v>128</v>
       </c>
       <c r="D9" s="93">
         <v>20</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="F9" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>306</v>
-      </c>
-      <c r="H9" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="30" t="s">
-        <v>307</v>
-      </c>
-      <c r="J9" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="30" t="s">
         <v>308</v>
       </c>
-      <c r="L9" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="F9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="N9" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="30" t="s">
+      <c r="H9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="28" t="s">
         <v>310</v>
       </c>
-      <c r="P9" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="30" t="s">
+      <c r="J9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="R9" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" s="30" t="s">
+      <c r="L9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="28" t="s">
         <v>312</v>
       </c>
+      <c r="N9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="P9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="28" t="s">
+        <v>315</v>
+      </c>
+      <c r="R9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="28" t="s">
+        <v>316</v>
+      </c>
       <c r="T9" s="83" t="b">
         <v>1</v>
       </c>
       <c r="U9" s="33" t="s">
-        <v>313</v>
-      </c>
-      <c r="V9" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="31" t="s">
         <v>314</v>
       </c>
+      <c r="V9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="33" t="s">
+        <v>317</v>
+      </c>
       <c r="X9" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="Y9" s="31" t="s">
+      <c r="Y9" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="AB9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="33" t="s">
         <v>320</v>
       </c>
-      <c r="Z9" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="33" t="s">
-        <v>315</v>
-      </c>
-      <c r="AB9" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="36" t="s">
-        <v>316</v>
-      </c>
-      <c r="AD9" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="36" t="s">
-        <v>317</v>
-      </c>
-      <c r="AF9" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="25" t="b">
+      <c r="AD9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="33" t="s">
+        <v>321</v>
+      </c>
+      <c r="AF9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="86" t="b">
         <v>1</v>
       </c>
       <c r="AH9" s="25" t="b">
         <v>1</v>
       </c>
       <c r="AI9" s="27" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AJ9" s="39" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" s="85" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A10" s="87" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" s="40" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="82" t="s">
         <v>324</v>
       </c>
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="43" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" s="95"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="44" t="s">
         <v>325</v>
       </c>
-      <c r="C10" s="94" t="s">
-        <v>128</v>
-      </c>
-      <c r="D10" s="93">
-        <v>20</v>
-      </c>
-      <c r="E10" s="28" t="s">
+      <c r="F10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="46" t="s">
         <v>326</v>
       </c>
-      <c r="F10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="28" t="s">
+      <c r="H10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="46" t="s">
         <v>327</v>
       </c>
-      <c r="H10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="28" t="s">
+      <c r="J10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="46" t="s">
         <v>328</v>
       </c>
-      <c r="J10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="28" t="s">
+      <c r="L10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="46" t="s">
         <v>329</v>
       </c>
-      <c r="L10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="28" t="s">
+      <c r="N10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="46" t="s">
+        <v>336</v>
+      </c>
+      <c r="P10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="46" t="s">
         <v>330</v>
       </c>
-      <c r="N10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" s="28" t="s">
+      <c r="R10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" s="46" t="s">
         <v>331</v>
       </c>
-      <c r="P10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="28" t="s">
+      <c r="T10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="49" t="s">
+        <v>337</v>
+      </c>
+      <c r="V10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="47" t="s">
+        <v>339</v>
+      </c>
+      <c r="X10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="47" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="49" t="s">
         <v>333</v>
       </c>
-      <c r="R10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10" s="28" t="s">
+      <c r="AB10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="52" t="s">
+        <v>332</v>
+      </c>
+      <c r="AD10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="52" t="s">
+        <v>340</v>
+      </c>
+      <c r="AF10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="AJ10" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="T10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="V10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" s="33" t="s">
-        <v>335</v>
-      </c>
-      <c r="X10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="33" t="s">
-        <v>336</v>
-      </c>
-      <c r="Z10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="33" t="s">
-        <v>337</v>
-      </c>
-      <c r="AB10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="33" t="s">
-        <v>338</v>
-      </c>
-      <c r="AD10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="33" t="s">
-        <v>339</v>
-      </c>
-      <c r="AF10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="27" t="s">
-        <v>341</v>
-      </c>
-      <c r="AJ10" s="39" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36" s="40" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="82" t="s">
-        <v>342</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>356</v>
-      </c>
+    </row>
+    <row r="11" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="42"/>
+      <c r="B11" s="43"/>
       <c r="C11" s="95"/>
       <c r="D11" s="96"/>
-      <c r="E11" s="44" t="s">
-        <v>343</v>
-      </c>
-      <c r="F11" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="46" t="s">
-        <v>344</v>
-      </c>
-      <c r="H11" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="46" t="s">
-        <v>345</v>
-      </c>
-      <c r="J11" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="46" t="s">
-        <v>346</v>
-      </c>
-      <c r="L11" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" s="46" t="s">
-        <v>347</v>
-      </c>
-      <c r="N11" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O11" s="46" t="s">
-        <v>354</v>
-      </c>
-      <c r="P11" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="46" t="s">
-        <v>348</v>
-      </c>
-      <c r="R11" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S11" s="46" t="s">
-        <v>349</v>
-      </c>
-      <c r="T11" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U11" s="49" t="s">
-        <v>355</v>
-      </c>
-      <c r="V11" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W11" s="47" t="s">
-        <v>357</v>
-      </c>
-      <c r="X11" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="47" t="s">
-        <v>359</v>
-      </c>
-      <c r="Z11" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="49" t="s">
-        <v>351</v>
-      </c>
-      <c r="AB11" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="52" t="s">
-        <v>350</v>
-      </c>
-      <c r="AD11" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="52" t="s">
-        <v>358</v>
-      </c>
-      <c r="AF11" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH11" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI11" s="27" t="s">
-        <v>353</v>
-      </c>
-      <c r="AJ11" s="39" t="s">
-        <v>352</v>
-      </c>
+      <c r="E11" s="44"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="45"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="45"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="45"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="45"/>
+      <c r="S11" s="46"/>
+      <c r="T11" s="58"/>
+      <c r="U11" s="49"/>
+      <c r="V11" s="50"/>
+      <c r="W11" s="47"/>
+      <c r="X11" s="48"/>
+      <c r="Y11" s="47"/>
+      <c r="Z11" s="51"/>
+      <c r="AA11" s="49"/>
+      <c r="AB11" s="50"/>
+      <c r="AC11" s="52"/>
+      <c r="AD11" s="53"/>
+      <c r="AE11" s="52"/>
+      <c r="AF11" s="54"/>
+      <c r="AI11" s="43"/>
     </row>
     <row r="12" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42"/>
@@ -4414,7 +4285,7 @@
       <c r="AF12" s="54"/>
       <c r="AI12" s="43"/>
     </row>
-    <row r="13" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" s="40" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="95"/>
@@ -4449,7 +4320,7 @@
       <c r="AF13" s="54"/>
       <c r="AI13" s="43"/>
     </row>
-    <row r="14" spans="1:36" s="40" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="95"/>
@@ -4659,41 +4530,6 @@
       <c r="AF19" s="54"/>
       <c r="AI19" s="43"/>
     </row>
-    <row r="20" spans="1:35" s="40" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="42"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="95"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="45"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="45"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="46"/>
-      <c r="P20" s="45"/>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="45"/>
-      <c r="S20" s="46"/>
-      <c r="T20" s="58"/>
-      <c r="U20" s="49"/>
-      <c r="V20" s="50"/>
-      <c r="W20" s="47"/>
-      <c r="X20" s="48"/>
-      <c r="Y20" s="47"/>
-      <c r="Z20" s="51"/>
-      <c r="AA20" s="49"/>
-      <c r="AB20" s="50"/>
-      <c r="AC20" s="52"/>
-      <c r="AD20" s="53"/>
-      <c r="AE20" s="52"/>
-      <c r="AF20" s="54"/>
-      <c r="AI20" s="43"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4724,39 +4560,39 @@
         <v>57</v>
       </c>
       <c r="D1" s="78" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="E1" s="78" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="F1" s="78" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="G1" s="78" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="H1" s="78" t="s">
         <v>15</v>
       </c>
       <c r="I1" s="80" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="79" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C2" s="79" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="D2" s="79" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="E2" s="79" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="F2" s="79">
         <v>90</v>
@@ -4765,27 +4601,27 @@
         <v>1.25</v>
       </c>
       <c r="H2" s="79" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="I2" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="B3" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="C3" s="79" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="D3" s="79" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="E3" s="79" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -4794,27 +4630,27 @@
         <v>1.5</v>
       </c>
       <c r="H3" s="79" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="I3" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C4" s="79" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="D4" s="79" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="E4" s="79" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="F4">
         <v>90</v>
@@ -4823,27 +4659,27 @@
         <v>1.25</v>
       </c>
       <c r="H4" s="79" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="I4" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="B5" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="C5" s="79" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="D5" s="79" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="E5" s="79" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="F5">
         <v>90</v>
@@ -4852,10 +4688,10 @@
         <v>1.25</v>
       </c>
       <c r="H5" s="79" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="I5" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3029BCED-42A5-0B41-93AF-CDD87B9CEE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D62C42-D6F8-5443-B6C2-32B62E556D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="2" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="1" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="346">
   <si>
     <t>question_id</t>
   </si>
@@ -1065,6 +1065,18 @@
   </si>
   <si>
     <t>Baftasaurus</t>
+  </si>
+  <si>
+    <t>map_q_6</t>
+  </si>
+  <si>
+    <t>Which country is Hungary?</t>
+  </si>
+  <si>
+    <t>Germany,Czech Republic,Austria,Switzerland,Slovakia,Hungary,Denmark,Netherlands,Belgium,Luxembourg</t>
+  </si>
+  <si>
+    <t>Hungary</t>
   </si>
 </sst>
 </file>
@@ -2792,7 +2804,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0380E023-4B0F-5D41-A3D5-4A6D015B3367}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.83203125" customWidth="1"/>
@@ -3001,21 +3013,27 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>342</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>343</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="D7" t="s">
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>89</v>
+        <v>63</v>
+      </c>
+      <c r="F7" t="s">
+        <v>344</v>
       </c>
       <c r="G7" t="s">
-        <v>90</v>
+        <v>345</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -3026,22 +3044,13 @@
       <c r="J7">
         <v>10</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M7" t="s">
-        <v>221</v>
-      </c>
     </row>
     <row r="8" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>219</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>217</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
         <v>88</v>
@@ -3062,12 +3071,47 @@
         <v>10</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H9">
+        <v>9</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M9" t="s">
         <v>222</v>
       </c>
     </row>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D62C42-D6F8-5443-B6C2-32B62E556D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FB7697-7B7A-4648-8233-49A2A9DEB1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="1" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="344">
   <si>
     <t>question_id</t>
   </si>
@@ -951,12 +951,6 @@
   </si>
   <si>
     <t>I was thinking of 42. It wasn't really a trivia question, I just wanted to see if you could guess it.</t>
-  </si>
-  <si>
-    <t>Which of these songs is from one of Disney's "Frozen" movies?</t>
-  </si>
-  <si>
-    <t>pinch_p</t>
   </si>
   <si>
     <t>bonus_q_frozen</t>
@@ -2755,13 +2749,9 @@
       </c>
       <c r="Q16" s="73"/>
     </row>
-    <row r="17" spans="1:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="73" t="s">
-        <v>305</v>
-      </c>
-      <c r="B17" s="76" t="s">
-        <v>304</v>
-      </c>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17" s="73"/>
+      <c r="B17" s="76"/>
       <c r="C17" s="73"/>
       <c r="D17" s="73"/>
       <c r="E17" s="73"/>
@@ -3015,10 +3005,10 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C7" t="s">
         <v>72</v>
@@ -3030,10 +3020,10 @@
         <v>63</v>
       </c>
       <c r="F7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -4045,10 +4035,10 @@
     </row>
     <row r="9" spans="1:36" s="85" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="87" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C9" s="94" t="s">
         <v>128</v>
@@ -4057,206 +4047,206 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="s">
+        <v>306</v>
+      </c>
+      <c r="F9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>307</v>
+      </c>
+      <c r="H9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="28" t="s">
         <v>308</v>
       </c>
-      <c r="F9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="28" t="s">
+      <c r="J9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="H9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="28" t="s">
+      <c r="L9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="28" t="s">
         <v>310</v>
       </c>
-      <c r="J9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="28" t="s">
+      <c r="N9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="L9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="28" t="s">
+      <c r="P9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="R9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="28" t="s">
+        <v>314</v>
+      </c>
+      <c r="T9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="33" t="s">
         <v>312</v>
       </c>
-      <c r="N9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="28" t="s">
-        <v>313</v>
-      </c>
-      <c r="P9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="28" t="s">
+      <c r="V9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="R9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" s="28" t="s">
+      <c r="X9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="T9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U9" s="33" t="s">
-        <v>314</v>
-      </c>
-      <c r="V9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="33" t="s">
+      <c r="Z9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="X9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="33" t="s">
+      <c r="AB9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="33" t="s">
         <v>318</v>
       </c>
-      <c r="Z9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="33" t="s">
+      <c r="AD9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="33" t="s">
         <v>319</v>
       </c>
-      <c r="AB9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="33" t="s">
+      <c r="AF9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="27" t="s">
+        <v>321</v>
+      </c>
+      <c r="AJ9" s="39" t="s">
         <v>320</v>
-      </c>
-      <c r="AD9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="33" t="s">
-        <v>321</v>
-      </c>
-      <c r="AF9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH9" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI9" s="27" t="s">
-        <v>323</v>
-      </c>
-      <c r="AJ9" s="39" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:36" s="40" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="82" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C10" s="95"/>
       <c r="D10" s="96"/>
       <c r="E10" s="44" t="s">
+        <v>323</v>
+      </c>
+      <c r="F10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="H10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="46" t="s">
         <v>325</v>
       </c>
-      <c r="F10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="46" t="s">
+      <c r="J10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="46" t="s">
         <v>326</v>
       </c>
-      <c r="H10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="46" t="s">
+      <c r="L10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="46" t="s">
         <v>327</v>
       </c>
-      <c r="J10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="46" t="s">
+      <c r="N10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="P10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="46" t="s">
         <v>328</v>
       </c>
-      <c r="L10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="46" t="s">
+      <c r="R10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" s="46" t="s">
         <v>329</v>
       </c>
-      <c r="N10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" s="46" t="s">
-        <v>336</v>
-      </c>
-      <c r="P10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="46" t="s">
+      <c r="T10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="49" t="s">
+        <v>335</v>
+      </c>
+      <c r="V10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="47" t="s">
+        <v>337</v>
+      </c>
+      <c r="X10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="47" t="s">
+        <v>339</v>
+      </c>
+      <c r="Z10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="49" t="s">
+        <v>331</v>
+      </c>
+      <c r="AB10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="52" t="s">
         <v>330</v>
       </c>
-      <c r="R10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10" s="46" t="s">
-        <v>331</v>
-      </c>
-      <c r="T10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10" s="49" t="s">
-        <v>337</v>
-      </c>
-      <c r="V10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" s="47" t="s">
-        <v>339</v>
-      </c>
-      <c r="X10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="47" t="s">
-        <v>341</v>
-      </c>
-      <c r="Z10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="49" t="s">
+      <c r="AD10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="52" t="s">
+        <v>338</v>
+      </c>
+      <c r="AF10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="27" t="s">
         <v>333</v>
       </c>
-      <c r="AB10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="52" t="s">
+      <c r="AJ10" s="39" t="s">
         <v>332</v>
-      </c>
-      <c r="AD10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="52" t="s">
-        <v>340</v>
-      </c>
-      <c r="AF10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="27" t="s">
-        <v>335</v>
-      </c>
-      <c r="AJ10" s="39" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="11" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FB7697-7B7A-4648-8233-49A2A9DEB1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E64A0F-87F5-204B-92EA-BCDFB9DFBF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="344">
   <si>
     <t>question_id</t>
   </si>
@@ -59,9 +59,6 @@
     <t>snap_interval</t>
   </si>
   <si>
-    <t>format_type</t>
-  </si>
-  <si>
     <t>points_per_extra_unit</t>
   </si>
   <si>
@@ -95,9 +92,6 @@
     <t>pinch_A</t>
   </si>
   <si>
-    <t>INTEGER</t>
-  </si>
-  <si>
     <t>The word "Bye" is sung 57 times in "Bye Bye Bye".</t>
   </si>
   <si>
@@ -1071,6 +1065,12 @@
   </si>
   <si>
     <t>Hungary</t>
+  </si>
+  <si>
+    <t>seasoning</t>
+  </si>
+  <si>
+    <t>role</t>
   </si>
 </sst>
 </file>
@@ -1379,7 +1379,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1654,6 +1654,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1998,7 +2001,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="57.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7" style="75" customWidth="1"/>
+    <col min="7" max="7" width="12.5" style="75" customWidth="1"/>
     <col min="8" max="8" width="18.5" customWidth="1"/>
     <col min="9" max="9" width="15.33203125" customWidth="1"/>
     <col min="10" max="10" width="9.6640625" customWidth="1"/>
@@ -2026,44 +2029,44 @@
       <c r="F1" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="99" t="s">
+        <v>343</v>
+      </c>
+      <c r="H1" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="73" t="s">
+      <c r="I1" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="73" t="s">
+      <c r="J1" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="73" t="s">
+      <c r="K1" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="73" t="s">
+      <c r="L1" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="73" t="s">
+      <c r="M1" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="73" t="s">
+      <c r="N1" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="73" t="s">
+      <c r="O1" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="73" t="s">
+      <c r="P1" s="73" t="s">
         <v>14</v>
-      </c>
-      <c r="P1" s="73" t="s">
-        <v>15</v>
       </c>
       <c r="Q1" s="73"/>
     </row>
     <row r="2" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C2" s="73">
         <v>10</v>
@@ -2075,9 +2078,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="73"/>
-      <c r="G2" s="77" t="s">
-        <v>18</v>
-      </c>
+      <c r="G2" s="77"/>
       <c r="H2" s="73">
         <v>2</v>
       </c>
@@ -2101,16 +2102,16 @@
         <v>57</v>
       </c>
       <c r="P2" s="81" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q2" s="73"/>
     </row>
     <row r="3" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="73" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B3" s="76" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3" s="73">
         <v>5</v>
@@ -2120,9 +2121,7 @@
       </c>
       <c r="E3" s="73"/>
       <c r="F3" s="73"/>
-      <c r="G3" s="77" t="s">
-        <v>18</v>
-      </c>
+      <c r="G3" s="77"/>
       <c r="H3" s="73">
         <v>5</v>
       </c>
@@ -2146,16 +2145,16 @@
         <v>4</v>
       </c>
       <c r="P3" s="81" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q3" s="73"/>
     </row>
     <row r="4" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="73" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" s="76" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="73">
         <v>5</v>
@@ -2168,7 +2167,7 @@
       </c>
       <c r="F4" s="73"/>
       <c r="G4" s="77" t="s">
-        <v>18</v>
+        <v>342</v>
       </c>
       <c r="H4" s="73">
         <v>5</v>
@@ -2193,16 +2192,16 @@
         <v>7</v>
       </c>
       <c r="P4" s="81" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q4" s="73"/>
     </row>
     <row r="5" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="73" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" s="76" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="73">
         <v>100</v>
@@ -2212,9 +2211,7 @@
       </c>
       <c r="E5" s="73"/>
       <c r="F5" s="73"/>
-      <c r="G5" s="77" t="s">
-        <v>18</v>
-      </c>
+      <c r="G5" s="77"/>
       <c r="H5" s="73">
         <v>5</v>
       </c>
@@ -2238,16 +2235,16 @@
         <v>600</v>
       </c>
       <c r="P5" s="81" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q5" s="73"/>
     </row>
     <row r="6" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="73" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B6" s="76" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6" s="73">
         <v>5</v>
@@ -2257,9 +2254,7 @@
       </c>
       <c r="E6" s="73"/>
       <c r="F6" s="73"/>
-      <c r="G6" s="77" t="s">
-        <v>18</v>
-      </c>
+      <c r="G6" s="77"/>
       <c r="H6" s="73">
         <v>2</v>
       </c>
@@ -2283,16 +2278,16 @@
         <v>12</v>
       </c>
       <c r="P6" s="81" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q6" s="73"/>
     </row>
     <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="73" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B7" s="76" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7" s="73">
         <v>5</v>
@@ -2304,9 +2299,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="73"/>
-      <c r="G7" s="77" t="s">
-        <v>18</v>
-      </c>
+      <c r="G7" s="77"/>
       <c r="H7" s="73">
         <v>2</v>
       </c>
@@ -2330,16 +2323,16 @@
         <v>10</v>
       </c>
       <c r="P7" s="81" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q7" s="73"/>
     </row>
     <row r="8" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="73" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B8" s="76" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" s="73">
         <v>1</v>
@@ -2347,9 +2340,7 @@
       <c r="D8" s="73"/>
       <c r="E8" s="73"/>
       <c r="F8" s="73"/>
-      <c r="G8" s="77" t="s">
-        <v>18</v>
-      </c>
+      <c r="G8" s="77"/>
       <c r="H8" s="73">
         <v>10</v>
       </c>
@@ -2369,22 +2360,22 @@
         <v>3</v>
       </c>
       <c r="N8" s="73" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O8" s="73">
         <v>6</v>
       </c>
       <c r="P8" s="81" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q8" s="73"/>
     </row>
     <row r="9" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="73" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" s="76" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9" s="73">
         <v>10</v>
@@ -2396,9 +2387,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="73"/>
-      <c r="G9" s="77" t="s">
-        <v>18</v>
-      </c>
+      <c r="G9" s="77"/>
       <c r="H9" s="73">
         <v>1</v>
       </c>
@@ -2422,16 +2411,16 @@
         <v>73</v>
       </c>
       <c r="P9" s="81" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q9" s="73"/>
     </row>
     <row r="10" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="73" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C10" s="73">
         <v>10</v>
@@ -2441,9 +2430,7 @@
       </c>
       <c r="E10" s="73"/>
       <c r="F10" s="73"/>
-      <c r="G10" s="77" t="s">
-        <v>18</v>
-      </c>
+      <c r="G10" s="77"/>
       <c r="H10" s="73">
         <v>5</v>
       </c>
@@ -2467,16 +2454,16 @@
         <v>1955</v>
       </c>
       <c r="P10" s="81" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q10" s="73"/>
     </row>
     <row r="11" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="73" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B11" s="76" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C11" s="73">
         <v>15</v>
@@ -2485,7 +2472,7 @@
       <c r="E11" s="73"/>
       <c r="F11" s="73"/>
       <c r="G11" s="77" t="s">
-        <v>18</v>
+        <v>342</v>
       </c>
       <c r="H11" s="73">
         <v>9</v>
@@ -2506,22 +2493,22 @@
         <v>50</v>
       </c>
       <c r="N11" s="73" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O11" s="73">
         <v>165</v>
       </c>
       <c r="P11" s="81" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Q11" s="73"/>
     </row>
     <row r="12" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="73" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C12" s="73">
         <v>10</v>
@@ -2533,9 +2520,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="73"/>
-      <c r="G12" s="77" t="s">
-        <v>18</v>
-      </c>
+      <c r="G12" s="77"/>
       <c r="H12" s="73">
         <v>1</v>
       </c>
@@ -2555,22 +2540,22 @@
         <v>110</v>
       </c>
       <c r="N12" s="73" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O12" s="73">
         <v>89.99</v>
       </c>
       <c r="P12" s="81" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q12" s="73"/>
     </row>
     <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="73" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C13" s="73">
         <v>1</v>
@@ -2578,9 +2563,7 @@
       <c r="D13" s="73"/>
       <c r="E13" s="73"/>
       <c r="F13" s="73"/>
-      <c r="G13" s="77" t="s">
-        <v>18</v>
-      </c>
+      <c r="G13" s="77"/>
       <c r="H13" s="73">
         <v>10</v>
       </c>
@@ -2600,22 +2583,22 @@
         <v>3</v>
       </c>
       <c r="N13" s="73" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O13" s="73">
         <v>12</v>
       </c>
       <c r="P13" s="81" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="Q13" s="73"/>
     </row>
     <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="73" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B14" s="76" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C14" s="73">
         <v>100</v>
@@ -2628,7 +2611,7 @@
       </c>
       <c r="F14" s="73"/>
       <c r="G14" s="77" t="s">
-        <v>18</v>
+        <v>342</v>
       </c>
       <c r="H14" s="73">
         <v>1</v>
@@ -2653,16 +2636,16 @@
         <v>110</v>
       </c>
       <c r="P14" s="81" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Q14" s="73"/>
     </row>
     <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="73" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C15" s="73">
         <v>5</v>
@@ -2672,9 +2655,7 @@
       </c>
       <c r="E15" s="73"/>
       <c r="F15" s="73"/>
-      <c r="G15" s="77" t="s">
-        <v>18</v>
-      </c>
+      <c r="G15" s="77"/>
       <c r="H15" s="73">
         <v>2</v>
       </c>
@@ -2698,16 +2679,16 @@
         <v>27</v>
       </c>
       <c r="P15" s="81" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="Q15" s="73"/>
     </row>
     <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="73" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C16" s="73">
         <v>10</v>
@@ -2720,7 +2701,7 @@
       </c>
       <c r="F16" s="73"/>
       <c r="G16" s="77" t="s">
-        <v>18</v>
+        <v>342</v>
       </c>
       <c r="H16" s="73">
         <v>1</v>
@@ -2745,7 +2726,7 @@
         <v>42</v>
       </c>
       <c r="P16" s="81" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Q16" s="73"/>
     </row>
@@ -2810,60 +2791,60 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="M1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
         <v>59</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>61</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>62</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>63</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" t="s">
-        <v>65</v>
       </c>
       <c r="H2">
         <v>9</v>
@@ -2877,25 +2858,25 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" t="s">
         <v>66</v>
       </c>
-      <c r="B3" t="s">
+      <c r="G3" t="s">
         <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" t="s">
-        <v>69</v>
       </c>
       <c r="H3">
         <v>9</v>
@@ -2909,25 +2890,25 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" t="s">
         <v>70</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>71</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" t="s">
         <v>72</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>73</v>
-      </c>
-      <c r="E4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" t="s">
-        <v>75</v>
       </c>
       <c r="H4">
         <v>9</v>
@@ -2941,25 +2922,25 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" t="s">
         <v>76</v>
       </c>
-      <c r="B5" t="s">
+      <c r="G5" t="s">
         <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G5" t="s">
-        <v>79</v>
       </c>
       <c r="H5">
         <v>9</v>
@@ -2973,25 +2954,25 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
         <v>80</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>81</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" t="s">
         <v>82</v>
       </c>
-      <c r="D6" t="s">
+      <c r="G6" t="s">
         <v>83</v>
-      </c>
-      <c r="E6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" t="s">
-        <v>85</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -3005,25 +2986,25 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>338</v>
+      </c>
+      <c r="B7" t="s">
+        <v>339</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" t="s">
         <v>340</v>
       </c>
-      <c r="B7" t="s">
+      <c r="G7" t="s">
         <v>341</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G7" t="s">
-        <v>343</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -3037,19 +3018,19 @@
     </row>
     <row r="8" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s">
         <v>86</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
         <v>87</v>
       </c>
-      <c r="C8" t="s">
+      <c r="G8" t="s">
         <v>88</v>
-      </c>
-      <c r="E8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G8" t="s">
-        <v>90</v>
       </c>
       <c r="H8">
         <v>9</v>
@@ -3061,30 +3042,30 @@
         <v>10</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" t="s">
         <v>88</v>
-      </c>
-      <c r="E9" t="s">
-        <v>89</v>
-      </c>
-      <c r="G9" t="s">
-        <v>90</v>
       </c>
       <c r="H9">
         <v>9</v>
@@ -3096,13 +3077,13 @@
         <v>10</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="M9" t="s">
         <v>220</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="M9" t="s">
-        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3161,1092 +3142,1092 @@
         <v>1</v>
       </c>
       <c r="C1" s="88" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="89" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="89" t="s">
+      <c r="F1" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="61" t="s">
+      <c r="G1" s="63" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="62" t="s">
+      <c r="H1" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="63" t="s">
+      <c r="I1" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="62" t="s">
+      <c r="J1" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="63" t="s">
+      <c r="K1" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="J1" s="62" t="s">
+      <c r="L1" s="64" t="s">
         <v>100</v>
       </c>
-      <c r="K1" s="63" t="s">
+      <c r="M1" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="L1" s="64" t="s">
+      <c r="N1" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="M1" s="63" t="s">
+      <c r="O1" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="N1" s="64" t="s">
+      <c r="P1" s="64" t="s">
         <v>104</v>
       </c>
-      <c r="O1" s="63" t="s">
+      <c r="Q1" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="P1" s="64" t="s">
+      <c r="R1" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="Q1" s="63" t="s">
+      <c r="S1" s="63" t="s">
         <v>107</v>
       </c>
-      <c r="R1" s="64" t="s">
+      <c r="T1" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="S1" s="63" t="s">
+      <c r="U1" s="65" t="s">
         <v>109</v>
       </c>
-      <c r="T1" s="74" t="s">
+      <c r="V1" s="66" t="s">
         <v>110</v>
       </c>
-      <c r="U1" s="65" t="s">
+      <c r="W1" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="V1" s="66" t="s">
+      <c r="X1" s="68" t="s">
         <v>112</v>
       </c>
-      <c r="W1" s="67" t="s">
+      <c r="Y1" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="X1" s="68" t="s">
+      <c r="Z1" s="69" t="s">
         <v>114</v>
       </c>
-      <c r="Y1" s="67" t="s">
+      <c r="AA1" s="65" t="s">
         <v>115</v>
       </c>
-      <c r="Z1" s="69" t="s">
+      <c r="AB1" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="AA1" s="65" t="s">
+      <c r="AC1" s="70" t="s">
         <v>117</v>
       </c>
-      <c r="AB1" s="66" t="s">
+      <c r="AD1" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="AC1" s="70" t="s">
+      <c r="AE1" s="70" t="s">
         <v>119</v>
       </c>
-      <c r="AD1" s="71" t="s">
+      <c r="AF1" s="72" t="s">
         <v>120</v>
       </c>
-      <c r="AE1" s="70" t="s">
+      <c r="AG1" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="AF1" s="72" t="s">
+      <c r="AH1" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="AG1" s="60" t="s">
+      <c r="AI1" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ1" s="60" t="s">
         <v>123</v>
-      </c>
-      <c r="AH1" s="60" t="s">
-        <v>124</v>
-      </c>
-      <c r="AI1" s="60" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ1" s="60" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="90" t="s">
         <v>126</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="C2" s="90" t="s">
-        <v>128</v>
       </c>
       <c r="D2" s="91">
         <v>20</v>
       </c>
       <c r="E2" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="H2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="F2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="30" t="s">
+      <c r="J2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="H2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="30" t="s">
+      <c r="L2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="J2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" s="30" t="s">
+      <c r="N2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="L2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" s="30" t="s">
+      <c r="P2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="N2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" s="30" t="s">
+      <c r="R2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="T2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="P2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="30" t="s">
+      <c r="V2" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="R2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S2" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="T2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U2" s="31" t="s">
+      <c r="X2" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="V2" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W2" s="31" t="s">
+      <c r="Z2" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="X2" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="31" t="s">
+      <c r="AB2" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="Z2" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="33" t="s">
+      <c r="AD2" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="AF2" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="AB2" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="36" t="s">
+      <c r="AJ2" s="39" t="s">
         <v>140</v>
-      </c>
-      <c r="AD2" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="57" t="s">
-        <v>202</v>
-      </c>
-      <c r="AF2" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="AJ2" s="39" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:36" s="40" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A3" s="55" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C3" s="90" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D3" s="91">
         <v>20</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F3" s="29" t="b">
         <v>1</v>
       </c>
       <c r="G3" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="H3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="J3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="H3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="30" t="s">
+      <c r="L3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="J3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" s="30" t="s">
+      <c r="N3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="L3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="30" t="s">
+      <c r="P3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="R3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="T3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="N3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" s="30" t="s">
+      <c r="V3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" s="31" t="s">
+        <v>211</v>
+      </c>
+      <c r="X3" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z3" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="P3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="R3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="T3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U3" s="33" t="s">
+      <c r="AB3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="V3" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W3" s="31" t="s">
-        <v>213</v>
-      </c>
-      <c r="X3" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z3" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="33" t="s">
+      <c r="AD3" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="AB3" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="36" t="s">
+      <c r="AF3" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="AD3" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="36" t="s">
+      <c r="AJ3" s="39" t="s">
         <v>153</v>
-      </c>
-      <c r="AF3" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH3" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI3" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="AJ3" s="39" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C4" s="90" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D4" s="91">
         <v>20</v>
       </c>
       <c r="E4" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="F4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="30" t="s">
+      <c r="J4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="H4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="30" t="s">
+      <c r="L4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="J4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" s="30" t="s">
+      <c r="N4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="L4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" s="30" t="s">
+      <c r="P4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="N4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="30" t="s">
+      <c r="R4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="T4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="P4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="30" t="s">
+      <c r="V4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="R4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S4" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="T4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U4" s="33" t="s">
+      <c r="X4" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="V4" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="31" t="s">
+      <c r="Z4" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="X4" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="31" t="s">
+      <c r="AB4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="AD4" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="36" t="s">
+        <v>204</v>
+      </c>
+      <c r="AF4" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="Z4" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="33" t="s">
+      <c r="AJ4" s="39" t="s">
         <v>167</v>
-      </c>
-      <c r="AB4" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="36" t="s">
-        <v>212</v>
-      </c>
-      <c r="AD4" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="36" t="s">
-        <v>206</v>
-      </c>
-      <c r="AF4" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI4" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="AJ4" s="39" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="55" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C5" s="90" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D5" s="91">
         <v>20</v>
       </c>
       <c r="E5" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="F5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="H5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="J5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="F5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="30" t="s">
+      <c r="L5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="H5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="J5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="30" t="s">
+      <c r="N5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="P5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="L5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="30" t="s">
+      <c r="R5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="T5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="N5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="P5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="30" t="s">
+      <c r="V5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="R5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" s="30" t="s">
+      <c r="X5" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z5" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="36" t="s">
         <v>207</v>
       </c>
-      <c r="T5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U5" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="V5" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" s="31" t="s">
+      <c r="AD5" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="X5" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="Z5" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="33" t="s">
+      <c r="AF5" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="AB5" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="AD5" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="36" t="s">
+      <c r="AJ5" s="39" t="s">
         <v>179</v>
-      </c>
-      <c r="AF5" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="AJ5" s="39" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:36" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A6" s="56" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C6" s="92" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D6" s="93">
         <v>20</v>
       </c>
       <c r="E6" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="F6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="H6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="F6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="16" t="s">
+      <c r="J6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="H6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="16" t="s">
+      <c r="L6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="N6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="J6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="16" t="s">
+      <c r="P6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="L6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="N6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="16" t="s">
+      <c r="R6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="T6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="P6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="16" t="s">
+      <c r="V6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="R6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="28" t="s">
-        <v>211</v>
-      </c>
-      <c r="T6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" s="19" t="s">
+      <c r="X6" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="V6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="17" t="s">
+      <c r="Z6" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="X6" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="17" t="s">
+      <c r="AD6" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="Z6" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="AB6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="22" t="s">
+      <c r="AF6" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="AD6" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="22" t="s">
+      <c r="AJ6" s="25" t="s">
         <v>194</v>
-      </c>
-      <c r="AF6" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="AJ6" s="25" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="55" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C7" s="92" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D7" s="93">
         <v>20</v>
       </c>
       <c r="E7" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="F7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="H7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="J7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="L7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="F7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="30" t="s">
+      <c r="N7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="P7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="R7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="T7" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="V7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="H7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="J7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="30" t="s">
+      <c r="X7" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="Z7" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="AB7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="AD7" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="36" t="s">
         <v>270</v>
       </c>
-      <c r="L7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="N7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="P7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="30" t="s">
-        <v>266</v>
-      </c>
-      <c r="R7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="30" t="s">
-        <v>267</v>
-      </c>
-      <c r="T7" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="33" t="s">
+      <c r="AF7" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="V7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="X7" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="31" t="s">
+      <c r="AJ7" s="39" t="s">
         <v>275</v>
-      </c>
-      <c r="Z7" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="AB7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="AD7" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="AF7" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="27" t="s">
-        <v>276</v>
-      </c>
-      <c r="AJ7" s="39" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="55" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C8" s="92" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D8" s="93">
         <v>20</v>
       </c>
       <c r="E8" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="F8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="H8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="F8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="30" t="s">
+      <c r="J8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="H8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="30" t="s">
+      <c r="L8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="J8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="30" t="s">
+      <c r="N8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="L8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="30" t="s">
+      <c r="P8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="30" t="s">
         <v>291</v>
       </c>
-      <c r="N8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="30" t="s">
+      <c r="R8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="30" t="s">
         <v>292</v>
       </c>
-      <c r="P8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="30" t="s">
+      <c r="T8" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="R8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S8" s="30" t="s">
+      <c r="V8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="31" t="s">
         <v>294</v>
       </c>
-      <c r="T8" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" s="33" t="s">
+      <c r="X8" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="Z8" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="V8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="31" t="s">
+      <c r="AB8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="36" t="s">
         <v>296</v>
       </c>
-      <c r="X8" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="31" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z8" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="33" t="s">
+      <c r="AD8" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="36" t="s">
         <v>297</v>
       </c>
-      <c r="AB8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="36" t="s">
+      <c r="AF8" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="AJ8" s="39" t="s">
         <v>298</v>
-      </c>
-      <c r="AD8" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="36" t="s">
-        <v>299</v>
-      </c>
-      <c r="AF8" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH8" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="AJ8" s="39" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:36" s="85" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="87" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C9" s="94" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D9" s="93">
         <v>20</v>
       </c>
       <c r="E9" s="28" t="s">
+        <v>304</v>
+      </c>
+      <c r="F9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>305</v>
+      </c>
+      <c r="H9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="F9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="28" t="s">
+      <c r="J9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="H9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="28" t="s">
+      <c r="L9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="28" t="s">
         <v>308</v>
       </c>
-      <c r="J9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="28" t="s">
+      <c r="N9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="L9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="28" t="s">
+      <c r="P9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="R9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="T9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="33" t="s">
         <v>310</v>
       </c>
-      <c r="N9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="P9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="28" t="s">
+      <c r="V9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="33" t="s">
         <v>313</v>
       </c>
-      <c r="R9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" s="28" t="s">
+      <c r="X9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="T9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U9" s="33" t="s">
-        <v>312</v>
-      </c>
-      <c r="V9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="33" t="s">
+      <c r="Z9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="X9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="33" t="s">
+      <c r="AB9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="Z9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="33" t="s">
+      <c r="AD9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="AB9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="33" t="s">
+      <c r="AF9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="27" t="s">
+        <v>319</v>
+      </c>
+      <c r="AJ9" s="39" t="s">
         <v>318</v>
-      </c>
-      <c r="AD9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="33" t="s">
-        <v>319</v>
-      </c>
-      <c r="AF9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH9" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI9" s="27" t="s">
-        <v>321</v>
-      </c>
-      <c r="AJ9" s="39" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:36" s="40" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="82" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C10" s="95"/>
       <c r="D10" s="96"/>
       <c r="E10" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="F10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="H10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="46" t="s">
         <v>323</v>
       </c>
-      <c r="F10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="46" t="s">
+      <c r="J10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="46" t="s">
         <v>324</v>
       </c>
-      <c r="H10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="46" t="s">
+      <c r="L10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="46" t="s">
         <v>325</v>
       </c>
-      <c r="J10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="46" t="s">
+      <c r="N10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="46" t="s">
+        <v>332</v>
+      </c>
+      <c r="P10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="46" t="s">
         <v>326</v>
       </c>
-      <c r="L10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="46" t="s">
+      <c r="R10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" s="46" t="s">
         <v>327</v>
       </c>
-      <c r="N10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" s="46" t="s">
-        <v>334</v>
-      </c>
-      <c r="P10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="46" t="s">
+      <c r="T10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="49" t="s">
+        <v>333</v>
+      </c>
+      <c r="V10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="X10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="47" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="49" t="s">
+        <v>329</v>
+      </c>
+      <c r="AB10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="52" t="s">
         <v>328</v>
       </c>
-      <c r="R10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10" s="46" t="s">
-        <v>329</v>
-      </c>
-      <c r="T10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10" s="49" t="s">
-        <v>335</v>
-      </c>
-      <c r="V10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" s="47" t="s">
-        <v>337</v>
-      </c>
-      <c r="X10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="47" t="s">
-        <v>339</v>
-      </c>
-      <c r="Z10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="49" t="s">
+      <c r="AD10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="52" t="s">
+        <v>336</v>
+      </c>
+      <c r="AF10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="27" t="s">
         <v>331</v>
       </c>
-      <c r="AB10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="52" t="s">
+      <c r="AJ10" s="39" t="s">
         <v>330</v>
-      </c>
-      <c r="AD10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="52" t="s">
-        <v>338</v>
-      </c>
-      <c r="AF10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="27" t="s">
-        <v>333</v>
-      </c>
-      <c r="AJ10" s="39" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
@@ -4591,42 +4572,42 @@
         <v>1</v>
       </c>
       <c r="C1" s="78" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D1" s="78" t="s">
+        <v>221</v>
+      </c>
+      <c r="E1" s="78" t="s">
+        <v>222</v>
+      </c>
+      <c r="F1" s="78" t="s">
         <v>223</v>
       </c>
-      <c r="E1" s="78" t="s">
-        <v>224</v>
-      </c>
-      <c r="F1" s="78" t="s">
-        <v>225</v>
-      </c>
       <c r="G1" s="78" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H1" s="78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I1" s="80" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="79" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="C2" s="79" t="s">
+        <v>225</v>
+      </c>
+      <c r="D2" s="79" t="s">
         <v>226</v>
       </c>
-      <c r="B2" s="79" t="s">
-        <v>238</v>
-      </c>
-      <c r="C2" s="79" t="s">
+      <c r="E2" s="79" t="s">
         <v>227</v>
-      </c>
-      <c r="D2" s="79" t="s">
-        <v>228</v>
-      </c>
-      <c r="E2" s="79" t="s">
-        <v>229</v>
       </c>
       <c r="F2" s="79">
         <v>90</v>
@@ -4635,27 +4616,27 @@
         <v>1.25</v>
       </c>
       <c r="H2" s="79" t="s">
+        <v>228</v>
+      </c>
+      <c r="I2" t="s">
         <v>230</v>
-      </c>
-      <c r="I2" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" s="79" t="s">
+        <v>232</v>
+      </c>
+      <c r="D3" s="79" t="s">
         <v>233</v>
       </c>
-      <c r="B3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C3" s="79" t="s">
-        <v>234</v>
-      </c>
-      <c r="D3" s="79" t="s">
-        <v>235</v>
-      </c>
       <c r="E3" s="79" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -4664,27 +4645,27 @@
         <v>1.5</v>
       </c>
       <c r="H3" s="79" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" s="79" t="s">
         <v>240</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" s="79" t="s">
         <v>241</v>
       </c>
-      <c r="C4" s="79" t="s">
-        <v>242</v>
-      </c>
-      <c r="D4" s="79" t="s">
-        <v>243</v>
-      </c>
       <c r="E4" s="79" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F4">
         <v>90</v>
@@ -4693,27 +4674,27 @@
         <v>1.25</v>
       </c>
       <c r="H4" s="79" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C5" s="79" t="s">
         <v>247</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" s="79" t="s">
         <v>248</v>
       </c>
-      <c r="C5" s="79" t="s">
-        <v>249</v>
-      </c>
-      <c r="D5" s="79" t="s">
-        <v>250</v>
-      </c>
       <c r="E5" s="79" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F5">
         <v>90</v>
@@ -4722,10 +4703,10 @@
         <v>1.25</v>
       </c>
       <c r="H5" s="79" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E64A0F-87F5-204B-92EA-BCDFB9DFBF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B743EA6B-2728-9C45-BECA-4D9925B0B90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="1" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -1061,9 +1061,6 @@
     <t>Which country is Hungary?</t>
   </si>
   <si>
-    <t>Germany,Czech Republic,Austria,Switzerland,Slovakia,Hungary,Denmark,Netherlands,Belgium,Luxembourg</t>
-  </si>
-  <si>
     <t>Hungary</t>
   </si>
   <si>
@@ -1071,6 +1068,9 @@
   </si>
   <si>
     <t>role</t>
+  </si>
+  <si>
+    <t>Germany,Czechia,Austria,Switzerland,Slovakia,Hungary,Denmark,Netherlands,Belgium,Luxembourg</t>
   </si>
 </sst>
 </file>
@@ -2030,7 +2030,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="99" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1" s="73" t="s">
         <v>6</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="F4" s="73"/>
       <c r="G4" s="77" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H4" s="73">
         <v>5</v>
@@ -2472,7 +2472,7 @@
       <c r="E11" s="73"/>
       <c r="F11" s="73"/>
       <c r="G11" s="77" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H11" s="73">
         <v>9</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="F14" s="73"/>
       <c r="G14" s="77" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H14" s="73">
         <v>1</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="F16" s="73"/>
       <c r="G16" s="77" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H16" s="73">
         <v>1</v>
@@ -3001,10 +3001,10 @@
         <v>61</v>
       </c>
       <c r="F7" t="s">
+        <v>343</v>
+      </c>
+      <c r="G7" t="s">
         <v>340</v>
-      </c>
-      <c r="G7" t="s">
-        <v>341</v>
       </c>
       <c r="H7">
         <v>9</v>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B743EA6B-2728-9C45-BECA-4D9925B0B90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9189FE3-9F46-3D4A-B630-FC07ED45B73F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="1" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -1070,7 +1070,7 @@
     <t>role</t>
   </si>
   <si>
-    <t>Germany,Czechia,Austria,Switzerland,Slovakia,Hungary,Denmark,Netherlands,Belgium,Luxembourg</t>
+    <t>Germany,Czechia,Austria,Switzerland,Slovakia,Hungary,Denmark,Netherlands,Belgium,Luxembourg,Poland</t>
   </si>
 </sst>
 </file>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9189FE3-9F46-3D4A-B630-FC07ED45B73F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9626B8A-DF79-A14E-A55D-791FDFE8728E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="1" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -257,9 +257,6 @@
     <t>naturalEarth</t>
   </si>
   <si>
-    <t>Somalia,Ethiopia,Djibouti,Eritrea,Kenya,South Sudan,Sudan,Tanzania,Egypt,Libya</t>
-  </si>
-  <si>
     <t>Somalia</t>
   </si>
   <si>
@@ -1071,6 +1068,9 @@
   </si>
   <si>
     <t>Germany,Czechia,Austria,Switzerland,Slovakia,Hungary,Denmark,Netherlands,Belgium,Luxembourg,Poland</t>
+  </si>
+  <si>
+    <t>Somalia,Ethiopia,Djibouti,Eritrea,Kenya,South Sudan,Sudan,Tanzania,Egypt,Libya,Chad,Uganda</t>
   </si>
 </sst>
 </file>
@@ -2030,7 +2030,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="99" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1" s="73" t="s">
         <v>6</v>
@@ -2066,7 +2066,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C2" s="73">
         <v>10</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="F4" s="73"/>
       <c r="G4" s="77" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H4" s="73">
         <v>5</v>
@@ -2420,7 +2420,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C10" s="73">
         <v>10</v>
@@ -2472,7 +2472,7 @@
       <c r="E11" s="73"/>
       <c r="F11" s="73"/>
       <c r="G11" s="77" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H11" s="73">
         <v>9</v>
@@ -2499,7 +2499,7 @@
         <v>165</v>
       </c>
       <c r="P11" s="81" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q11" s="73"/>
     </row>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="73" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C13" s="73">
         <v>1</v>
@@ -2589,16 +2589,16 @@
         <v>12</v>
       </c>
       <c r="P13" s="81" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q13" s="73"/>
     </row>
     <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="73" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" s="76" t="s">
         <v>255</v>
-      </c>
-      <c r="B14" s="76" t="s">
-        <v>256</v>
       </c>
       <c r="C14" s="73">
         <v>100</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="F14" s="73"/>
       <c r="G14" s="77" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H14" s="73">
         <v>1</v>
@@ -2636,16 +2636,16 @@
         <v>110</v>
       </c>
       <c r="P14" s="81" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q14" s="73"/>
     </row>
     <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="73" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C15" s="73">
         <v>5</v>
@@ -2679,16 +2679,16 @@
         <v>27</v>
       </c>
       <c r="P15" s="81" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q15" s="73"/>
     </row>
     <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="73" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C16" s="73">
         <v>10</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="F16" s="73"/>
       <c r="G16" s="77" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H16" s="73">
         <v>1</v>
@@ -2726,7 +2726,7 @@
         <v>42</v>
       </c>
       <c r="P16" s="81" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q16" s="73"/>
     </row>
@@ -2779,6 +2779,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.83203125" customWidth="1"/>
+    <col min="6" max="6" width="44.83203125" customWidth="1"/>
     <col min="11" max="11" width="29.5" style="1" customWidth="1"/>
     <col min="12" max="12" width="10.83203125" style="1"/>
   </cols>
@@ -2905,10 +2906,10 @@
         <v>61</v>
       </c>
       <c r="F4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G4" t="s">
         <v>72</v>
-      </c>
-      <c r="G4" t="s">
-        <v>73</v>
       </c>
       <c r="H4">
         <v>9</v>
@@ -2922,10 +2923,10 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" t="s">
         <v>74</v>
-      </c>
-      <c r="B5" t="s">
-        <v>75</v>
       </c>
       <c r="C5" t="s">
         <v>70</v>
@@ -2937,10 +2938,10 @@
         <v>61</v>
       </c>
       <c r="F5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" t="s">
         <v>76</v>
-      </c>
-      <c r="G5" t="s">
-        <v>77</v>
       </c>
       <c r="H5">
         <v>9</v>
@@ -2954,25 +2955,25 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" t="s">
         <v>78</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>79</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>80</v>
-      </c>
-      <c r="D6" t="s">
-        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>61</v>
       </c>
       <c r="F6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" t="s">
         <v>82</v>
-      </c>
-      <c r="G6" t="s">
-        <v>83</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -2986,10 +2987,10 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B7" t="s">
         <v>338</v>
-      </c>
-      <c r="B7" t="s">
-        <v>339</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
@@ -3001,10 +3002,10 @@
         <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -3018,19 +3019,19 @@
     </row>
     <row r="8" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" t="s">
         <v>84</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>85</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>86</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>87</v>
-      </c>
-      <c r="G8" t="s">
-        <v>88</v>
       </c>
       <c r="H8">
         <v>9</v>
@@ -3042,30 +3043,30 @@
         <v>10</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="M8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" t="s">
         <v>86</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>87</v>
-      </c>
-      <c r="G9" t="s">
-        <v>88</v>
       </c>
       <c r="H9">
         <v>9</v>
@@ -3077,13 +3078,13 @@
         <v>10</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -3142,1092 +3143,1092 @@
         <v>1</v>
       </c>
       <c r="C1" s="88" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="89" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="89" t="s">
+      <c r="E1" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="61" t="s">
+      <c r="F1" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="62" t="s">
+      <c r="G1" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="63" t="s">
+      <c r="H1" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="62" t="s">
+      <c r="I1" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="63" t="s">
+      <c r="J1" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="J1" s="62" t="s">
+      <c r="K1" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="K1" s="63" t="s">
+      <c r="L1" s="64" t="s">
         <v>99</v>
       </c>
-      <c r="L1" s="64" t="s">
+      <c r="M1" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="M1" s="63" t="s">
+      <c r="N1" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="N1" s="64" t="s">
+      <c r="O1" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="O1" s="63" t="s">
+      <c r="P1" s="64" t="s">
         <v>103</v>
       </c>
-      <c r="P1" s="64" t="s">
+      <c r="Q1" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="Q1" s="63" t="s">
+      <c r="R1" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="R1" s="64" t="s">
+      <c r="S1" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="S1" s="63" t="s">
+      <c r="T1" s="74" t="s">
         <v>107</v>
       </c>
-      <c r="T1" s="74" t="s">
+      <c r="U1" s="65" t="s">
         <v>108</v>
       </c>
-      <c r="U1" s="65" t="s">
+      <c r="V1" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="V1" s="66" t="s">
+      <c r="W1" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="W1" s="67" t="s">
+      <c r="X1" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="X1" s="68" t="s">
+      <c r="Y1" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="Y1" s="67" t="s">
+      <c r="Z1" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="Z1" s="69" t="s">
+      <c r="AA1" s="65" t="s">
         <v>114</v>
       </c>
-      <c r="AA1" s="65" t="s">
+      <c r="AB1" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="AB1" s="66" t="s">
+      <c r="AC1" s="70" t="s">
         <v>116</v>
       </c>
-      <c r="AC1" s="70" t="s">
+      <c r="AD1" s="71" t="s">
         <v>117</v>
       </c>
-      <c r="AD1" s="71" t="s">
+      <c r="AE1" s="70" t="s">
         <v>118</v>
       </c>
-      <c r="AE1" s="70" t="s">
+      <c r="AF1" s="72" t="s">
         <v>119</v>
       </c>
-      <c r="AF1" s="72" t="s">
+      <c r="AG1" s="60" t="s">
         <v>120</v>
       </c>
-      <c r="AG1" s="60" t="s">
+      <c r="AH1" s="60" t="s">
         <v>121</v>
-      </c>
-      <c r="AH1" s="60" t="s">
-        <v>122</v>
       </c>
       <c r="AI1" s="60" t="s">
         <v>14</v>
       </c>
       <c r="AJ1" s="60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="C2" s="90" t="s">
         <v>125</v>
-      </c>
-      <c r="C2" s="90" t="s">
-        <v>126</v>
       </c>
       <c r="D2" s="91">
         <v>20</v>
       </c>
       <c r="E2" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="F2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="30" t="s">
+      <c r="H2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="H2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="30" t="s">
+      <c r="J2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="J2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" s="30" t="s">
+      <c r="L2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="L2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" s="30" t="s">
+      <c r="N2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="N2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" s="30" t="s">
+      <c r="P2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="P2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="30" t="s">
+      <c r="R2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="T2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="R2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S2" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="T2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U2" s="31" t="s">
+      <c r="V2" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="V2" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W2" s="31" t="s">
+      <c r="X2" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="X2" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="31" t="s">
+      <c r="Z2" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="Z2" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="33" t="s">
+      <c r="AB2" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="AB2" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="36" t="s">
+      <c r="AD2" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="57" t="s">
+        <v>199</v>
+      </c>
+      <c r="AF2" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="AD2" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="57" t="s">
-        <v>200</v>
-      </c>
-      <c r="AF2" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="27" t="s">
+      <c r="AJ2" s="39" t="s">
         <v>139</v>
-      </c>
-      <c r="AJ2" s="39" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:36" s="40" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A3" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="27" t="s">
-        <v>142</v>
-      </c>
       <c r="C3" s="90" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D3" s="91">
         <v>20</v>
       </c>
       <c r="E3" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="F3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="H3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="J3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="L3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="N3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="P3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="F3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="H3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="J3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="L3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="N3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" s="30" t="s">
+      <c r="R3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="T3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="P3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="R3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="T3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U3" s="33" t="s">
+      <c r="V3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="X3" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="31" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z3" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="V3" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W3" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="X3" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="Z3" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="33" t="s">
+      <c r="AB3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="AB3" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="36" t="s">
+      <c r="AD3" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="AD3" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="36" t="s">
+      <c r="AF3" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="AF3" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH3" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI3" s="27" t="s">
+      <c r="AJ3" s="39" t="s">
         <v>152</v>
-      </c>
-      <c r="AJ3" s="39" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C4" s="90" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="91">
         <v>20</v>
       </c>
       <c r="E4" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="F4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="30" t="s">
+      <c r="H4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="H4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="30" t="s">
+      <c r="J4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" s="30" t="s">
+      <c r="L4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="L4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" s="30" t="s">
+      <c r="N4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="N4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="30" t="s">
+      <c r="P4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="P4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="30" t="s">
+      <c r="R4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="T4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="R4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S4" s="30" t="s">
+      <c r="V4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="X4" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z4" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD4" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="36" t="s">
         <v>203</v>
       </c>
-      <c r="T4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U4" s="33" t="s">
-        <v>162</v>
-      </c>
-      <c r="V4" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="X4" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z4" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="33" t="s">
+      <c r="AF4" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="AB4" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="AD4" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="AF4" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI4" s="27" t="s">
+      <c r="AJ4" s="39" t="s">
         <v>166</v>
-      </c>
-      <c r="AJ4" s="39" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="55" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C5" s="90" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D5" s="91">
         <v>20</v>
       </c>
       <c r="E5" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="F5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="F5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="30" t="s">
+      <c r="H5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="J5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="30" t="s">
+      <c r="L5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="N5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="J5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="L5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="30" t="s">
+      <c r="P5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="N5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="P5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="30" t="s">
+      <c r="R5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="T5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="R5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" s="30" t="s">
+      <c r="V5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="X5" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="31" t="s">
         <v>205</v>
       </c>
-      <c r="T5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U5" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="V5" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" s="31" t="s">
+      <c r="Z5" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="X5" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="31" t="s">
+      <c r="AB5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="Z5" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="33" t="s">
+      <c r="AD5" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="AB5" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="AD5" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="36" t="s">
+      <c r="AF5" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="AF5" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="27" t="s">
+      <c r="AJ5" s="39" t="s">
         <v>178</v>
-      </c>
-      <c r="AJ5" s="39" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:36" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A6" s="56" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>181</v>
-      </c>
       <c r="C6" s="92" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D6" s="93">
         <v>20</v>
       </c>
       <c r="E6" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="F6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="F6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="16" t="s">
+      <c r="H6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="H6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="16" t="s">
+      <c r="J6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="J6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="16" t="s">
+      <c r="L6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="N6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="L6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="N6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="16" t="s">
+      <c r="P6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="P6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="16" t="s">
+      <c r="R6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="T6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="R6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="T6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" s="19" t="s">
+      <c r="V6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="V6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="17" t="s">
+      <c r="X6" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="X6" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="17" t="s">
+      <c r="Z6" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="Z6" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="AB6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="22" t="s">
+      <c r="AD6" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="AD6" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="22" t="s">
+      <c r="AF6" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="AF6" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="13" t="s">
+      <c r="AJ6" s="25" t="s">
         <v>193</v>
-      </c>
-      <c r="AJ6" s="25" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="55" t="s">
+        <v>257</v>
+      </c>
+      <c r="B7" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="B7" s="27" t="s">
-        <v>259</v>
-      </c>
       <c r="C7" s="92" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D7" s="93">
         <v>20</v>
       </c>
       <c r="E7" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="F7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="H7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="30" t="s">
         <v>260</v>
       </c>
-      <c r="F7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="30" t="s">
+      <c r="J7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="L7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="N7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="P7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="R7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="T7" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="V7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="X7" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="Z7" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="36" t="s">
+        <v>266</v>
+      </c>
+      <c r="AD7" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="36" t="s">
         <v>269</v>
       </c>
-      <c r="H7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="J7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="L7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="N7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="P7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="R7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="T7" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="33" t="s">
-        <v>272</v>
-      </c>
-      <c r="V7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="X7" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="31" t="s">
+      <c r="AF7" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="Z7" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="AB7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="36" t="s">
-        <v>267</v>
-      </c>
-      <c r="AD7" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="36" t="s">
-        <v>270</v>
-      </c>
-      <c r="AF7" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="27" t="s">
+      <c r="AJ7" s="39" t="s">
         <v>274</v>
-      </c>
-      <c r="AJ7" s="39" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="55" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C8" s="92" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D8" s="93">
         <v>20</v>
       </c>
       <c r="E8" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="F8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="F8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="30" t="s">
+      <c r="H8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="H8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="30" t="s">
+      <c r="J8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="J8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="30" t="s">
+      <c r="L8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="L8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="30" t="s">
+      <c r="N8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="N8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="30" t="s">
+      <c r="P8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="P8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="30" t="s">
+      <c r="R8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="30" t="s">
         <v>291</v>
       </c>
-      <c r="R8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S8" s="30" t="s">
+      <c r="T8" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="T8" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" s="33" t="s">
+      <c r="V8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="V8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="31" t="s">
+      <c r="X8" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z8" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="X8" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="31" t="s">
-        <v>300</v>
-      </c>
-      <c r="Z8" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="33" t="s">
+      <c r="AB8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="36" t="s">
         <v>295</v>
       </c>
-      <c r="AB8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="36" t="s">
+      <c r="AD8" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="36" t="s">
         <v>296</v>
       </c>
-      <c r="AD8" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="36" t="s">
+      <c r="AF8" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="AJ8" s="39" t="s">
         <v>297</v>
-      </c>
-      <c r="AF8" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH8" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="AJ8" s="39" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:36" s="85" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="87" t="s">
+        <v>301</v>
+      </c>
+      <c r="B9" s="84" t="s">
         <v>302</v>
       </c>
-      <c r="B9" s="84" t="s">
-        <v>303</v>
-      </c>
       <c r="C9" s="94" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D9" s="93">
         <v>20</v>
       </c>
       <c r="E9" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="F9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="F9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="28" t="s">
+      <c r="H9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="H9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="28" t="s">
+      <c r="J9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="J9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="28" t="s">
+      <c r="L9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="L9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="28" t="s">
+      <c r="N9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="28" t="s">
         <v>308</v>
       </c>
-      <c r="N9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="28" t="s">
+      <c r="P9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="R9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="T9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="P9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="R9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" s="28" t="s">
+      <c r="V9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="33" t="s">
         <v>312</v>
       </c>
-      <c r="T9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U9" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="V9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="33" t="s">
+      <c r="X9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="33" t="s">
         <v>313</v>
       </c>
-      <c r="X9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="33" t="s">
+      <c r="Z9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="Z9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="33" t="s">
+      <c r="AB9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="AB9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="33" t="s">
+      <c r="AD9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="AD9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="33" t="s">
+      <c r="AF9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="AJ9" s="39" t="s">
         <v>317</v>
-      </c>
-      <c r="AF9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH9" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI9" s="27" t="s">
-        <v>319</v>
-      </c>
-      <c r="AJ9" s="39" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:36" s="40" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="82" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C10" s="95"/>
       <c r="D10" s="96"/>
       <c r="E10" s="44" t="s">
+        <v>320</v>
+      </c>
+      <c r="F10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="46" t="s">
         <v>321</v>
       </c>
-      <c r="F10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="46" t="s">
+      <c r="H10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="46" t="s">
         <v>322</v>
       </c>
-      <c r="H10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="46" t="s">
+      <c r="J10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="46" t="s">
         <v>323</v>
       </c>
-      <c r="J10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="46" t="s">
+      <c r="L10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="46" t="s">
         <v>324</v>
       </c>
-      <c r="L10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="46" t="s">
+      <c r="N10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="P10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="46" t="s">
         <v>325</v>
       </c>
-      <c r="N10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" s="46" t="s">
+      <c r="R10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" s="46" t="s">
+        <v>326</v>
+      </c>
+      <c r="T10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="49" t="s">
         <v>332</v>
       </c>
-      <c r="P10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="46" t="s">
-        <v>326</v>
-      </c>
-      <c r="R10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10" s="46" t="s">
+      <c r="V10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="47" t="s">
+        <v>334</v>
+      </c>
+      <c r="X10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="Z10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="49" t="s">
+        <v>328</v>
+      </c>
+      <c r="AB10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="52" t="s">
         <v>327</v>
       </c>
-      <c r="T10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10" s="49" t="s">
-        <v>333</v>
-      </c>
-      <c r="V10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" s="47" t="s">
+      <c r="AD10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="52" t="s">
         <v>335</v>
       </c>
-      <c r="X10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="47" t="s">
-        <v>337</v>
-      </c>
-      <c r="Z10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="49" t="s">
+      <c r="AF10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="AJ10" s="39" t="s">
         <v>329</v>
-      </c>
-      <c r="AB10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="52" t="s">
-        <v>328</v>
-      </c>
-      <c r="AD10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="52" t="s">
-        <v>336</v>
-      </c>
-      <c r="AF10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="27" t="s">
-        <v>331</v>
-      </c>
-      <c r="AJ10" s="39" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
@@ -4575,39 +4576,39 @@
         <v>55</v>
       </c>
       <c r="D1" s="78" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1" s="78" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="78" t="s">
+      <c r="F1" s="78" t="s">
         <v>222</v>
       </c>
-      <c r="F1" s="78" t="s">
-        <v>223</v>
-      </c>
       <c r="G1" s="78" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H1" s="78" t="s">
         <v>14</v>
       </c>
       <c r="I1" s="80" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="79" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2" s="79" t="s">
+        <v>235</v>
+      </c>
+      <c r="C2" s="79" t="s">
         <v>224</v>
       </c>
-      <c r="B2" s="79" t="s">
-        <v>236</v>
-      </c>
-      <c r="C2" s="79" t="s">
+      <c r="D2" s="79" t="s">
         <v>225</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="E2" s="79" t="s">
         <v>226</v>
-      </c>
-      <c r="E2" s="79" t="s">
-        <v>227</v>
       </c>
       <c r="F2" s="79">
         <v>90</v>
@@ -4616,27 +4617,27 @@
         <v>1.25</v>
       </c>
       <c r="H2" s="79" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C3" s="79" t="s">
         <v>231</v>
       </c>
-      <c r="B3" t="s">
-        <v>237</v>
-      </c>
-      <c r="C3" s="79" t="s">
+      <c r="D3" s="79" t="s">
         <v>232</v>
       </c>
-      <c r="D3" s="79" t="s">
-        <v>233</v>
-      </c>
       <c r="E3" s="79" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -4645,27 +4646,27 @@
         <v>1.5</v>
       </c>
       <c r="H3" s="79" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B4" t="s">
         <v>238</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="79" t="s">
         <v>239</v>
       </c>
-      <c r="C4" s="79" t="s">
+      <c r="D4" s="79" t="s">
         <v>240</v>
       </c>
-      <c r="D4" s="79" t="s">
-        <v>241</v>
-      </c>
       <c r="E4" s="79" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F4">
         <v>90</v>
@@ -4674,27 +4675,27 @@
         <v>1.25</v>
       </c>
       <c r="H4" s="79" t="s">
+        <v>241</v>
+      </c>
+      <c r="I4" t="s">
         <v>242</v>
-      </c>
-      <c r="I4" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B5" t="s">
         <v>245</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" s="79" t="s">
         <v>246</v>
       </c>
-      <c r="C5" s="79" t="s">
+      <c r="D5" s="79" t="s">
         <v>247</v>
       </c>
-      <c r="D5" s="79" t="s">
-        <v>248</v>
-      </c>
       <c r="E5" s="79" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F5">
         <v>90</v>
@@ -4703,10 +4704,10 @@
         <v>1.25</v>
       </c>
       <c r="H5" s="79" t="s">
+        <v>248</v>
+      </c>
+      <c r="I5" t="s">
         <v>249</v>
-      </c>
-      <c r="I5" t="s">
-        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9626B8A-DF79-A14E-A55D-791FDFE8728E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C78E5A7-1ED5-1541-854C-F22F0B22E21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="1" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="3" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -452,9 +452,6 @@
     <t>Peter Cushing</t>
   </si>
   <si>
-    <t>Alastair Davies</t>
-  </si>
-  <si>
     <t>These people have all been the Prime Minister of the UK:</t>
   </si>
   <si>
@@ -1071,6 +1068,9 @@
   </si>
   <si>
     <t>Somalia,Ethiopia,Djibouti,Eritrea,Kenya,South Sudan,Sudan,Tanzania,Egypt,Libya,Chad,Uganda</t>
+  </si>
+  <si>
+    <t>Lord Edmund Blackadder</t>
   </si>
 </sst>
 </file>
@@ -2030,7 +2030,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="99" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1" s="73" t="s">
         <v>6</v>
@@ -2066,7 +2066,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C2" s="73">
         <v>10</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="F4" s="73"/>
       <c r="G4" s="77" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H4" s="73">
         <v>5</v>
@@ -2420,7 +2420,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C10" s="73">
         <v>10</v>
@@ -2472,7 +2472,7 @@
       <c r="E11" s="73"/>
       <c r="F11" s="73"/>
       <c r="G11" s="77" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H11" s="73">
         <v>9</v>
@@ -2499,7 +2499,7 @@
         <v>165</v>
       </c>
       <c r="P11" s="81" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q11" s="73"/>
     </row>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="73" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C13" s="73">
         <v>1</v>
@@ -2589,16 +2589,16 @@
         <v>12</v>
       </c>
       <c r="P13" s="81" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q13" s="73"/>
     </row>
     <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="73" t="s">
+        <v>253</v>
+      </c>
+      <c r="B14" s="76" t="s">
         <v>254</v>
-      </c>
-      <c r="B14" s="76" t="s">
-        <v>255</v>
       </c>
       <c r="C14" s="73">
         <v>100</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="F14" s="73"/>
       <c r="G14" s="77" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H14" s="73">
         <v>1</v>
@@ -2636,16 +2636,16 @@
         <v>110</v>
       </c>
       <c r="P14" s="81" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q14" s="73"/>
     </row>
     <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="73" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C15" s="73">
         <v>5</v>
@@ -2679,16 +2679,16 @@
         <v>27</v>
       </c>
       <c r="P15" s="81" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q15" s="73"/>
     </row>
     <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="73" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C16" s="73">
         <v>10</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="F16" s="73"/>
       <c r="G16" s="77" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H16" s="73">
         <v>1</v>
@@ -2726,7 +2726,7 @@
         <v>42</v>
       </c>
       <c r="P16" s="81" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q16" s="73"/>
     </row>
@@ -2906,7 +2906,7 @@
         <v>61</v>
       </c>
       <c r="F4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G4" t="s">
         <v>72</v>
@@ -2987,10 +2987,10 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B7" t="s">
         <v>337</v>
-      </c>
-      <c r="B7" t="s">
-        <v>338</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
@@ -3002,10 +3002,10 @@
         <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -3049,15 +3049,15 @@
         <v>89</v>
       </c>
       <c r="M8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C9" t="s">
         <v>85</v>
@@ -3078,13 +3078,13 @@
         <v>10</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3301,7 +3301,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="T2" s="29" t="b">
         <v>1</v>
@@ -3330,37 +3330,37 @@
       <c r="AB2" s="34" t="b">
         <v>0</v>
       </c>
-      <c r="AC2" s="36" t="s">
+      <c r="AC2" s="57" t="s">
+        <v>343</v>
+      </c>
+      <c r="AD2" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="AF2" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="AD2" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="57" t="s">
-        <v>199</v>
-      </c>
-      <c r="AF2" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="27" t="s">
+      <c r="AJ2" s="39" t="s">
         <v>138</v>
-      </c>
-      <c r="AJ2" s="39" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:36" s="40" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A3" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="27" t="s">
         <v>140</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>141</v>
       </c>
       <c r="C3" s="90" t="s">
         <v>125</v>
@@ -3369,108 +3369,108 @@
         <v>20</v>
       </c>
       <c r="E3" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="F3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="H3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="J3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="L3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="N3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="P3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="F3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="H3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="J3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="L3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="N3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" s="30" t="s">
+      <c r="R3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="T3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="P3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="R3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="T3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U3" s="33" t="s">
+      <c r="V3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="X3" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="Z3" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="V3" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W3" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="X3" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="Z3" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="33" t="s">
+      <c r="AB3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="AB3" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="36" t="s">
+      <c r="AD3" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="AD3" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="36" t="s">
+      <c r="AF3" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="AF3" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH3" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI3" s="27" t="s">
+      <c r="AJ3" s="39" t="s">
         <v>151</v>
-      </c>
-      <c r="AJ3" s="39" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C4" s="90" t="s">
         <v>125</v>
@@ -3479,108 +3479,108 @@
         <v>20</v>
       </c>
       <c r="E4" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="F4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="30" t="s">
+      <c r="H4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="30" t="s">
+      <c r="J4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="J4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" s="30" t="s">
+      <c r="L4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="L4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" s="30" t="s">
+      <c r="N4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="N4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="30" t="s">
+      <c r="P4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="P4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="30" t="s">
+      <c r="R4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="T4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="R4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S4" s="30" t="s">
+      <c r="V4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="X4" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z4" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="36" t="s">
+        <v>208</v>
+      </c>
+      <c r="AD4" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="36" t="s">
         <v>202</v>
       </c>
-      <c r="T4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U4" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="V4" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="X4" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z4" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="33" t="s">
+      <c r="AF4" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="AB4" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="AD4" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="36" t="s">
-        <v>203</v>
-      </c>
-      <c r="AF4" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI4" s="27" t="s">
+      <c r="AJ4" s="39" t="s">
         <v>165</v>
-      </c>
-      <c r="AJ4" s="39" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C5" s="90" t="s">
         <v>125</v>
@@ -3589,108 +3589,108 @@
         <v>20</v>
       </c>
       <c r="E5" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="F5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="F5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="30" t="s">
+      <c r="H5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="J5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="H5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="30" t="s">
+      <c r="L5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="N5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="J5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="L5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="30" t="s">
+      <c r="P5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="N5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="P5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="30" t="s">
+      <c r="R5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="T5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="R5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" s="30" t="s">
+      <c r="V5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="X5" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="T5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U5" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="V5" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" s="31" t="s">
+      <c r="Z5" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="X5" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="31" t="s">
+      <c r="AB5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="Z5" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="33" t="s">
+      <c r="AD5" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="AB5" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="36" t="s">
-        <v>206</v>
-      </c>
-      <c r="AD5" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="36" t="s">
+      <c r="AF5" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="AF5" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="27" t="s">
+      <c r="AJ5" s="39" t="s">
         <v>177</v>
-      </c>
-      <c r="AJ5" s="39" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:36" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A6" s="56" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>179</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>180</v>
       </c>
       <c r="C6" s="92" t="s">
         <v>125</v>
@@ -3699,108 +3699,108 @@
         <v>20</v>
       </c>
       <c r="E6" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="F6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="F6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="16" t="s">
+      <c r="H6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="H6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="16" t="s">
+      <c r="J6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="J6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="16" t="s">
+      <c r="L6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="N6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="L6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="N6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="16" t="s">
+      <c r="P6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="P6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="16" t="s">
+      <c r="R6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="T6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="R6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="T6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" s="19" t="s">
+      <c r="V6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="V6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="17" t="s">
+      <c r="X6" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="X6" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="17" t="s">
+      <c r="Z6" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="AB6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="Z6" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="22" t="s">
+      <c r="AD6" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="AD6" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="22" t="s">
+      <c r="AF6" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="AF6" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="13" t="s">
+      <c r="AJ6" s="25" t="s">
         <v>192</v>
-      </c>
-      <c r="AJ6" s="25" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="55" t="s">
+        <v>256</v>
+      </c>
+      <c r="B7" s="27" t="s">
         <v>257</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>258</v>
       </c>
       <c r="C7" s="92" t="s">
         <v>125</v>
@@ -3809,108 +3809,108 @@
         <v>20</v>
       </c>
       <c r="E7" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="F7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="H7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="30" t="s">
         <v>259</v>
       </c>
-      <c r="F7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="30" t="s">
+      <c r="J7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="L7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="N7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="P7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="R7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="T7" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="V7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="X7" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="31" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z7" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="AD7" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="36" t="s">
         <v>268</v>
       </c>
-      <c r="H7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="J7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="30" t="s">
-        <v>267</v>
-      </c>
-      <c r="L7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="N7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="P7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="R7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="T7" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="33" t="s">
-        <v>271</v>
-      </c>
-      <c r="V7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="X7" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="31" t="s">
+      <c r="AF7" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="27" t="s">
         <v>272</v>
       </c>
-      <c r="Z7" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="AB7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="36" t="s">
-        <v>266</v>
-      </c>
-      <c r="AD7" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="AF7" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="27" t="s">
+      <c r="AJ7" s="39" t="s">
         <v>273</v>
-      </c>
-      <c r="AJ7" s="39" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="55" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C8" s="92" t="s">
         <v>125</v>
@@ -3919,108 +3919,108 @@
         <v>20</v>
       </c>
       <c r="E8" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="F8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="F8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="30" t="s">
+      <c r="H8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="H8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="30" t="s">
+      <c r="J8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="J8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="30" t="s">
+      <c r="L8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="L8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="30" t="s">
+      <c r="N8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="N8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="30" t="s">
+      <c r="P8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="P8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="30" t="s">
+      <c r="R8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="R8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S8" s="30" t="s">
+      <c r="T8" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="33" t="s">
         <v>291</v>
       </c>
-      <c r="T8" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" s="33" t="s">
+      <c r="V8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="31" t="s">
         <v>292</v>
       </c>
-      <c r="V8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="31" t="s">
+      <c r="X8" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="Z8" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="X8" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z8" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="33" t="s">
+      <c r="AB8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="AB8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="36" t="s">
+      <c r="AD8" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="36" t="s">
         <v>295</v>
       </c>
-      <c r="AD8" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="36" t="s">
+      <c r="AF8" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="AJ8" s="39" t="s">
         <v>296</v>
-      </c>
-      <c r="AF8" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH8" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="AJ8" s="39" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:36" s="85" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="87" t="s">
+        <v>300</v>
+      </c>
+      <c r="B9" s="84" t="s">
         <v>301</v>
-      </c>
-      <c r="B9" s="84" t="s">
-        <v>302</v>
       </c>
       <c r="C9" s="94" t="s">
         <v>125</v>
@@ -4029,206 +4029,206 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="F9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="F9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="28" t="s">
+      <c r="H9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="H9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="28" t="s">
+      <c r="J9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="J9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="28" t="s">
+      <c r="L9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="L9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="28" t="s">
+      <c r="N9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="N9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="28" t="s">
+      <c r="P9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="R9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="T9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="P9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="R9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" s="28" t="s">
+      <c r="V9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="33" t="s">
         <v>311</v>
       </c>
-      <c r="T9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U9" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="V9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="33" t="s">
+      <c r="X9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="33" t="s">
         <v>312</v>
       </c>
-      <c r="X9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="33" t="s">
+      <c r="Z9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="33" t="s">
         <v>313</v>
       </c>
-      <c r="Z9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="33" t="s">
+      <c r="AB9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="AB9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="33" t="s">
+      <c r="AD9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="AD9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="33" t="s">
+      <c r="AF9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="AJ9" s="39" t="s">
         <v>316</v>
-      </c>
-      <c r="AF9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH9" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI9" s="27" t="s">
-        <v>318</v>
-      </c>
-      <c r="AJ9" s="39" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:36" s="40" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="82" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C10" s="95"/>
       <c r="D10" s="96"/>
       <c r="E10" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="F10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="46" t="s">
         <v>320</v>
       </c>
-      <c r="F10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="46" t="s">
+      <c r="H10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="46" t="s">
         <v>321</v>
       </c>
-      <c r="H10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="46" t="s">
+      <c r="J10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="46" t="s">
         <v>322</v>
       </c>
-      <c r="J10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="46" t="s">
+      <c r="L10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="46" t="s">
         <v>323</v>
       </c>
-      <c r="L10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="46" t="s">
+      <c r="N10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="P10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="46" t="s">
         <v>324</v>
       </c>
-      <c r="N10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" s="46" t="s">
+      <c r="R10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="T10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="49" t="s">
         <v>331</v>
       </c>
-      <c r="P10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="46" t="s">
-        <v>325</v>
-      </c>
-      <c r="R10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10" s="46" t="s">
+      <c r="V10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="47" t="s">
+        <v>333</v>
+      </c>
+      <c r="X10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="Z10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="49" t="s">
+        <v>327</v>
+      </c>
+      <c r="AB10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="52" t="s">
         <v>326</v>
       </c>
-      <c r="T10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10" s="49" t="s">
-        <v>332</v>
-      </c>
-      <c r="V10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" s="47" t="s">
+      <c r="AD10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="52" t="s">
         <v>334</v>
       </c>
-      <c r="X10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="47" t="s">
-        <v>336</v>
-      </c>
-      <c r="Z10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="49" t="s">
+      <c r="AF10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="27" t="s">
+        <v>329</v>
+      </c>
+      <c r="AJ10" s="39" t="s">
         <v>328</v>
-      </c>
-      <c r="AB10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="52" t="s">
-        <v>327</v>
-      </c>
-      <c r="AD10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="AF10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="AJ10" s="39" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
@@ -4576,138 +4576,138 @@
         <v>55</v>
       </c>
       <c r="D1" s="78" t="s">
+        <v>219</v>
+      </c>
+      <c r="E1" s="78" t="s">
         <v>220</v>
       </c>
-      <c r="E1" s="78" t="s">
+      <c r="F1" s="78" t="s">
         <v>221</v>
       </c>
-      <c r="F1" s="78" t="s">
-        <v>222</v>
-      </c>
       <c r="G1" s="78" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H1" s="78" t="s">
         <v>14</v>
       </c>
       <c r="I1" s="80" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="79" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="79" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="79" t="s">
         <v>223</v>
       </c>
-      <c r="B2" s="79" t="s">
-        <v>235</v>
-      </c>
-      <c r="C2" s="79" t="s">
+      <c r="D2" s="79" t="s">
         <v>224</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="E2" s="79" t="s">
         <v>225</v>
-      </c>
-      <c r="E2" s="79" t="s">
-        <v>226</v>
       </c>
       <c r="F2" s="79">
         <v>90</v>
       </c>
       <c r="G2" s="79">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="H2" s="79" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" s="79" t="s">
         <v>230</v>
       </c>
-      <c r="B3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C3" s="79" t="s">
+      <c r="D3" s="79" t="s">
         <v>231</v>
       </c>
-      <c r="D3" s="79" t="s">
-        <v>232</v>
-      </c>
       <c r="E3" s="79" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F3">
         <v>90</v>
       </c>
       <c r="G3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H3" s="79" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4" t="s">
         <v>237</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="79" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="79" t="s">
+      <c r="D4" s="79" t="s">
         <v>239</v>
       </c>
-      <c r="D4" s="79" t="s">
-        <v>240</v>
-      </c>
       <c r="E4" s="79" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F4">
         <v>90</v>
       </c>
       <c r="G4">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="H4" s="79" t="s">
+        <v>240</v>
+      </c>
+      <c r="I4" t="s">
         <v>241</v>
-      </c>
-      <c r="I4" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" t="s">
         <v>244</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" s="79" t="s">
         <v>245</v>
       </c>
-      <c r="C5" s="79" t="s">
+      <c r="D5" s="79" t="s">
         <v>246</v>
       </c>
-      <c r="D5" s="79" t="s">
-        <v>247</v>
-      </c>
       <c r="E5" s="79" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F5">
         <v>90</v>
       </c>
       <c r="G5">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="H5" s="79" t="s">
+        <v>247</v>
+      </c>
+      <c r="I5" t="s">
         <v>248</v>
-      </c>
-      <c r="I5" t="s">
-        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C78E5A7-1ED5-1541-854C-F22F0B22E21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28B9782-AA5E-C344-9C43-219C51037484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="3" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="1" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="348">
   <si>
     <t>question_id</t>
   </si>
@@ -1071,6 +1071,18 @@
   </si>
   <si>
     <t>Lord Edmund Blackadder</t>
+  </si>
+  <si>
+    <t>map_q_7</t>
+  </si>
+  <si>
+    <t>Maine,New Hampshire, Vermont, Massachusetts, Rhode Island, Connecticut, New York, New Jersey, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Which state is New Hampshire?</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
   </si>
 </sst>
 </file>
@@ -2775,11 +2787,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0380E023-4B0F-5D41-A3D5-4A6D015B3367}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.83203125" customWidth="1"/>
-    <col min="6" max="6" width="44.83203125" customWidth="1"/>
+    <col min="6" max="6" width="44.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
     <col min="11" max="11" width="29.5" style="1" customWidth="1"/>
     <col min="12" max="12" width="10.83203125" style="1"/>
   </cols>
@@ -2800,7 +2813,7 @@
       <c r="E1" t="s">
         <v>51</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="G1" t="s">
@@ -2825,7 +2838,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -2841,7 +2854,7 @@
       <c r="E2" t="s">
         <v>61</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>62</v>
       </c>
       <c r="G2" t="s">
@@ -2857,7 +2870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -2873,7 +2886,7 @@
       <c r="E3" t="s">
         <v>61</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>66</v>
       </c>
       <c r="G3" t="s">
@@ -2889,7 +2902,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -2905,7 +2918,7 @@
       <c r="E4" t="s">
         <v>61</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>342</v>
       </c>
       <c r="G4" t="s">
@@ -2921,7 +2934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -2937,7 +2950,7 @@
       <c r="E5" t="s">
         <v>61</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>75</v>
       </c>
       <c r="G5" t="s">
@@ -2953,7 +2966,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -2969,7 +2982,7 @@
       <c r="E6" t="s">
         <v>61</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>81</v>
       </c>
       <c r="G6" t="s">
@@ -2985,7 +2998,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>336</v>
       </c>
@@ -3001,7 +3014,7 @@
       <c r="E7" t="s">
         <v>61</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>341</v>
       </c>
       <c r="G7" t="s">
@@ -3017,21 +3030,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>344</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>346</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
+        <v>60</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
+        <v>61</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="G8" t="s">
-        <v>87</v>
+        <v>347</v>
       </c>
       <c r="H8">
         <v>9</v>
@@ -3042,22 +3061,13 @@
       <c r="J8">
         <v>10</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="M8" t="s">
-        <v>217</v>
-      </c>
     </row>
     <row r="9" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>213</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
         <v>85</v>
@@ -3078,12 +3088,47 @@
         <v>10</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M9" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10">
+        <v>9</v>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+      <c r="J10">
+        <v>10</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M10" t="s">
         <v>218</v>
       </c>
     </row>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28B9782-AA5E-C344-9C43-219C51037484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD580EB0-9DA6-AC45-B78E-496765DF98DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="1" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="354">
   <si>
     <t>question_id</t>
   </si>
@@ -941,6 +941,9 @@
     <t>I was thinking of 42. It wasn't really a trivia question, I just wanted to see if you could guess it.</t>
   </si>
   <si>
+    <t>pinch_p</t>
+  </si>
+  <si>
     <t>bonus_q_frozen</t>
   </si>
   <si>
@@ -1083,6 +1086,21 @@
   </si>
   <si>
     <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>What's the square root of 8649?</t>
+  </si>
+  <si>
+    <t>As everyone knows, the square root of 8649.</t>
+  </si>
+  <si>
+    <t>How many members are in the US house of representatives?</t>
+  </si>
+  <si>
+    <t>pinch_q</t>
+  </si>
+  <si>
+    <t>There are 435 members of the house.</t>
   </si>
 </sst>
 </file>
@@ -2013,6 +2031,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="57.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
     <col min="7" max="7" width="12.5" style="75" customWidth="1"/>
     <col min="8" max="8" width="18.5" customWidth="1"/>
     <col min="9" max="9" width="15.33203125" customWidth="1"/>
@@ -2042,7 +2061,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="99" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1" s="73" t="s">
         <v>6</v>
@@ -2179,7 +2198,7 @@
       </c>
       <c r="F4" s="73"/>
       <c r="G4" s="77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H4" s="73">
         <v>5</v>
@@ -2484,7 +2503,7 @@
       <c r="E11" s="73"/>
       <c r="F11" s="73"/>
       <c r="G11" s="77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H11" s="73">
         <v>9</v>
@@ -2613,7 +2632,7 @@
         <v>254</v>
       </c>
       <c r="C14" s="73">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D14" s="73">
         <v>5</v>
@@ -2623,7 +2642,7 @@
       </c>
       <c r="F14" s="73"/>
       <c r="G14" s="77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H14" s="73">
         <v>1</v>
@@ -2713,7 +2732,7 @@
       </c>
       <c r="F16" s="73"/>
       <c r="G16" s="77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H16" s="73">
         <v>1</v>
@@ -2742,42 +2761,96 @@
       </c>
       <c r="Q16" s="73"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A17" s="73"/>
-      <c r="B17" s="76"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
+    <row r="17" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="73" t="s">
+        <v>300</v>
+      </c>
+      <c r="B17" s="76" t="s">
+        <v>349</v>
+      </c>
+      <c r="C17" s="73">
+        <v>10</v>
+      </c>
+      <c r="D17" s="73">
+        <v>5</v>
+      </c>
+      <c r="E17" s="73">
+        <v>1</v>
+      </c>
       <c r="F17" s="73"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="73"/>
-      <c r="J17" s="73"/>
-      <c r="K17" s="73"/>
-      <c r="L17" s="73"/>
-      <c r="M17" s="73"/>
+      <c r="G17" s="77" t="s">
+        <v>340</v>
+      </c>
+      <c r="H17" s="73">
+        <v>1</v>
+      </c>
+      <c r="I17" s="73">
+        <v>95</v>
+      </c>
+      <c r="J17" s="73">
+        <v>0</v>
+      </c>
+      <c r="K17" s="73">
+        <v>100</v>
+      </c>
+      <c r="L17" s="73">
+        <v>25</v>
+      </c>
+      <c r="M17" s="73">
+        <v>75</v>
+      </c>
       <c r="N17" s="73"/>
-      <c r="O17" s="73"/>
-      <c r="P17" s="73"/>
+      <c r="O17" s="73">
+        <v>93</v>
+      </c>
+      <c r="P17" s="81" t="s">
+        <v>350</v>
+      </c>
       <c r="Q17" s="73"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A18" s="73"/>
-      <c r="B18" s="76"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
+    <row r="18" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="73" t="s">
+        <v>352</v>
+      </c>
+      <c r="B18" s="76" t="s">
+        <v>351</v>
+      </c>
+      <c r="C18" s="73">
+        <v>50</v>
+      </c>
+      <c r="D18" s="73">
+        <v>10</v>
+      </c>
+      <c r="E18" s="73">
+        <v>5</v>
+      </c>
       <c r="F18" s="73"/>
       <c r="G18" s="77"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="73"/>
-      <c r="J18" s="73"/>
-      <c r="K18" s="73"/>
-      <c r="L18" s="73"/>
-      <c r="M18" s="73"/>
+      <c r="H18" s="73">
+        <v>1</v>
+      </c>
+      <c r="I18" s="73">
+        <v>475</v>
+      </c>
+      <c r="J18" s="73">
+        <v>100</v>
+      </c>
+      <c r="K18" s="73">
+        <v>600</v>
+      </c>
+      <c r="L18" s="73">
+        <v>150</v>
+      </c>
+      <c r="M18" s="73">
+        <v>300</v>
+      </c>
       <c r="N18" s="73"/>
-      <c r="O18" s="73"/>
-      <c r="P18" s="73"/>
+      <c r="O18" s="73">
+        <v>435</v>
+      </c>
+      <c r="P18" s="73" t="s">
+        <v>353</v>
+      </c>
       <c r="Q18" s="73"/>
     </row>
   </sheetData>
@@ -2919,7 +2992,7 @@
         <v>61</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G4" t="s">
         <v>72</v>
@@ -3000,10 +3073,10 @@
     </row>
     <row r="7" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
@@ -3015,10 +3088,10 @@
         <v>61</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -3032,10 +3105,10 @@
     </row>
     <row r="8" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C8" t="s">
         <v>59</v>
@@ -3047,10 +3120,10 @@
         <v>61</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H8">
         <v>9</v>
@@ -3376,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="AC2" s="57" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AD2" s="37" t="b">
         <v>0</v>
@@ -4062,10 +4135,10 @@
     </row>
     <row r="9" spans="1:36" s="85" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="87" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C9" s="94" t="s">
         <v>125</v>
@@ -4074,85 +4147,85 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F9" s="83" t="b">
         <v>1</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H9" s="83" t="b">
         <v>1</v>
       </c>
       <c r="I9" s="28" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J9" s="83" t="b">
         <v>1</v>
       </c>
       <c r="K9" s="28" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L9" s="83" t="b">
         <v>1</v>
       </c>
       <c r="M9" s="28" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N9" s="83" t="b">
         <v>1</v>
       </c>
       <c r="O9" s="28" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P9" s="83" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="R9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="T9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="R9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="T9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U9" s="33" t="s">
-        <v>308</v>
-      </c>
       <c r="V9" s="32" t="b">
         <v>0</v>
       </c>
       <c r="W9" s="33" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="X9" s="32" t="b">
         <v>0</v>
       </c>
       <c r="Y9" s="33" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Z9" s="32" t="b">
         <v>0</v>
       </c>
       <c r="AA9" s="33" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AB9" s="32" t="b">
         <v>0</v>
       </c>
       <c r="AC9" s="33" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AD9" s="32" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="33" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AF9" s="32" t="b">
         <v>0</v>
@@ -4164,116 +4237,116 @@
         <v>1</v>
       </c>
       <c r="AI9" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="AJ9" s="39" t="s">
         <v>317</v>
-      </c>
-      <c r="AJ9" s="39" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:36" s="40" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="82" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C10" s="95"/>
       <c r="D10" s="96"/>
       <c r="E10" s="44" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F10" s="83" t="b">
         <v>1</v>
       </c>
       <c r="G10" s="46" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H10" s="83" t="b">
         <v>1</v>
       </c>
       <c r="I10" s="46" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J10" s="83" t="b">
         <v>1</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L10" s="83" t="b">
         <v>1</v>
       </c>
       <c r="M10" s="46" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N10" s="83" t="b">
         <v>1</v>
       </c>
       <c r="O10" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="P10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="R10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" s="46" t="s">
+        <v>326</v>
+      </c>
+      <c r="T10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="49" t="s">
+        <v>332</v>
+      </c>
+      <c r="V10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="47" t="s">
+        <v>334</v>
+      </c>
+      <c r="X10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="Z10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="49" t="s">
+        <v>328</v>
+      </c>
+      <c r="AB10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="52" t="s">
+        <v>327</v>
+      </c>
+      <c r="AD10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="AF10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="27" t="s">
         <v>330</v>
       </c>
-      <c r="P10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="46" t="s">
-        <v>324</v>
-      </c>
-      <c r="R10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10" s="46" t="s">
-        <v>325</v>
-      </c>
-      <c r="T10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10" s="49" t="s">
-        <v>331</v>
-      </c>
-      <c r="V10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" s="47" t="s">
-        <v>333</v>
-      </c>
-      <c r="X10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="47" t="s">
-        <v>335</v>
-      </c>
-      <c r="Z10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="49" t="s">
-        <v>327</v>
-      </c>
-      <c r="AB10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="52" t="s">
-        <v>326</v>
-      </c>
-      <c r="AD10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="52" t="s">
-        <v>334</v>
-      </c>
-      <c r="AF10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="27" t="s">
+      <c r="AJ10" s="39" t="s">
         <v>329</v>
-      </c>
-      <c r="AJ10" s="39" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="11" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD580EB0-9DA6-AC45-B78E-496765DF98DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407DDE02-563E-F04D-8460-6FF5428F2E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="372">
   <si>
     <t>question_id</t>
   </si>
@@ -1101,6 +1101,60 @@
   </si>
   <si>
     <t>There are 435 members of the house.</t>
+  </si>
+  <si>
+    <t>pinch_r</t>
+  </si>
+  <si>
+    <t>In what month was Julius Caesar assassinated?</t>
+  </si>
+  <si>
+    <t>Julius Caesar was killed on "The Ides of March".</t>
+  </si>
+  <si>
+    <t>pinch_s</t>
+  </si>
+  <si>
+    <t>In Manhattan, a theatre must have at least this many seats to be considered "Off-Broadway"</t>
+  </si>
+  <si>
+    <t>Which month is named after the Roman god of war?</t>
+  </si>
+  <si>
+    <t>March was named after Mars, the Roman god of war.</t>
+  </si>
+  <si>
+    <t>"Off-Broadway" technically starts at 100 seats (anything less is "Off-Off").</t>
+  </si>
+  <si>
+    <t>pinch_t</t>
+  </si>
+  <si>
+    <t>During which month is Earth closest to the Sun?</t>
+  </si>
+  <si>
+    <t>Earth is closest to the Sun in January (when it reaches "Perihelion").</t>
+  </si>
+  <si>
+    <t>pinch_u</t>
+  </si>
+  <si>
+    <t>pinch_v</t>
+  </si>
+  <si>
+    <t>Usain Bolt finished the 100-meter dash in 9.58 seconds.</t>
+  </si>
+  <si>
+    <t>How seconds did Usain Bolt's fastest 100-meter dash take? (rounded to the nearest second)</t>
+  </si>
+  <si>
+    <t>Jimi Hendrix, Janis Joplin, and Kurt Cobain all died at the same age. How old were they?</t>
+  </si>
+  <si>
+    <t>pinch_w</t>
+  </si>
+  <si>
+    <t>Jimi Hendrix, Janis Joplin, and Kurt Cobain all died at the age of 27.</t>
   </si>
 </sst>
 </file>
@@ -2027,7 +2081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB832CB-3912-F247-8D46-62AA3D5AE696}">
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="57.6640625" style="1" customWidth="1"/>
@@ -2376,7 +2430,7 @@
         <v>10</v>
       </c>
       <c r="I8" s="73">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8" s="73">
         <v>1</v>
@@ -2599,7 +2653,7 @@
         <v>10</v>
       </c>
       <c r="I13" s="73">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" s="73">
         <v>1</v>
@@ -2848,10 +2902,262 @@
       <c r="O18" s="73">
         <v>435</v>
       </c>
-      <c r="P18" s="73" t="s">
+      <c r="P18" s="81" t="s">
         <v>353</v>
       </c>
       <c r="Q18" s="73"/>
+    </row>
+    <row r="19" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+      <c r="A19" s="73" t="s">
+        <v>354</v>
+      </c>
+      <c r="B19" s="76" t="s">
+        <v>358</v>
+      </c>
+      <c r="C19" s="73">
+        <v>50</v>
+      </c>
+      <c r="D19" s="73">
+        <v>10</v>
+      </c>
+      <c r="E19" s="73">
+        <v>5</v>
+      </c>
+      <c r="F19" s="73"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="73">
+        <v>1</v>
+      </c>
+      <c r="I19" s="73">
+        <v>475</v>
+      </c>
+      <c r="J19" s="73">
+        <v>100</v>
+      </c>
+      <c r="K19" s="73">
+        <v>600</v>
+      </c>
+      <c r="L19" s="73">
+        <v>150</v>
+      </c>
+      <c r="M19" s="73">
+        <v>300</v>
+      </c>
+      <c r="N19" s="73"/>
+      <c r="O19" s="73">
+        <v>100</v>
+      </c>
+      <c r="P19" s="81" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="73" t="s">
+        <v>357</v>
+      </c>
+      <c r="B20" s="76" t="s">
+        <v>355</v>
+      </c>
+      <c r="C20" s="73">
+        <v>1</v>
+      </c>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="73">
+        <v>10</v>
+      </c>
+      <c r="I20" s="73">
+        <v>10</v>
+      </c>
+      <c r="J20" s="73">
+        <v>1</v>
+      </c>
+      <c r="K20" s="73">
+        <v>12</v>
+      </c>
+      <c r="L20" s="73">
+        <v>1</v>
+      </c>
+      <c r="M20" s="73">
+        <v>3</v>
+      </c>
+      <c r="N20" t="s">
+        <v>35</v>
+      </c>
+      <c r="O20" s="73">
+        <v>3</v>
+      </c>
+      <c r="P20" s="81" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="73" t="s">
+        <v>362</v>
+      </c>
+      <c r="B21" s="76" t="s">
+        <v>359</v>
+      </c>
+      <c r="C21" s="73">
+        <v>1</v>
+      </c>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="73">
+        <v>10</v>
+      </c>
+      <c r="I21" s="73">
+        <v>10</v>
+      </c>
+      <c r="J21" s="73">
+        <v>1</v>
+      </c>
+      <c r="K21" s="73">
+        <v>12</v>
+      </c>
+      <c r="L21" s="73">
+        <v>1</v>
+      </c>
+      <c r="M21" s="73">
+        <v>3</v>
+      </c>
+      <c r="N21" t="s">
+        <v>35</v>
+      </c>
+      <c r="O21" s="73">
+        <v>3</v>
+      </c>
+      <c r="P21" s="81" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="73" t="s">
+        <v>365</v>
+      </c>
+      <c r="B22" s="76" t="s">
+        <v>363</v>
+      </c>
+      <c r="C22" s="73">
+        <v>1</v>
+      </c>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="73">
+        <v>10</v>
+      </c>
+      <c r="I22" s="73">
+        <v>10</v>
+      </c>
+      <c r="J22" s="73">
+        <v>1</v>
+      </c>
+      <c r="K22" s="73">
+        <v>12</v>
+      </c>
+      <c r="L22" s="73">
+        <v>1</v>
+      </c>
+      <c r="M22" s="73">
+        <v>3</v>
+      </c>
+      <c r="N22" t="s">
+        <v>35</v>
+      </c>
+      <c r="O22" s="73">
+        <v>1</v>
+      </c>
+      <c r="P22" s="81" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+      <c r="A23" s="73" t="s">
+        <v>366</v>
+      </c>
+      <c r="B23" s="76" t="s">
+        <v>368</v>
+      </c>
+      <c r="C23" s="73">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="H23" s="73">
+        <v>2.5</v>
+      </c>
+      <c r="I23" s="73">
+        <v>38</v>
+      </c>
+      <c r="J23" s="73">
+        <v>0</v>
+      </c>
+      <c r="K23" s="73">
+        <v>40</v>
+      </c>
+      <c r="L23" s="73">
+        <v>5</v>
+      </c>
+      <c r="M23" s="73">
+        <v>35</v>
+      </c>
+      <c r="O23" s="73">
+        <v>10</v>
+      </c>
+      <c r="P23" s="81" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+      <c r="A24" s="73" t="s">
+        <v>370</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C24" s="73">
+        <v>10</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="H24" s="73">
+        <v>5</v>
+      </c>
+      <c r="I24" s="73">
+        <v>19</v>
+      </c>
+      <c r="J24" s="73">
+        <v>20</v>
+      </c>
+      <c r="K24" s="73">
+        <v>40</v>
+      </c>
+      <c r="L24" s="73">
+        <v>25</v>
+      </c>
+      <c r="M24" s="73">
+        <v>35</v>
+      </c>
+      <c r="O24" s="73">
+        <v>27</v>
+      </c>
+      <c r="P24" t="s">
+        <v>371</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407DDE02-563E-F04D-8460-6FF5428F2E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EABC2BA-D779-1C45-AC30-F13807F220E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="2" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="375">
   <si>
     <t>question_id</t>
   </si>
@@ -947,9 +947,6 @@
     <t>bonus_q_frozen</t>
   </si>
   <si>
-    <t>Which are real song titles from one of Disney's "Frozen" movies?</t>
-  </si>
-  <si>
     <t>Do You Want to Build a Snowman?</t>
   </si>
   <si>
@@ -1155,6 +1152,18 @@
   </si>
   <si>
     <t>Jimi Hendrix, Janis Joplin, and Kurt Cobain all died at the age of 27.</t>
+  </si>
+  <si>
+    <t>pinch_x</t>
+  </si>
+  <si>
+    <t>According to a cartoon Owl: "A-one, a-two, a-three!"</t>
+  </si>
+  <si>
+    <t>How many licks does it take to get to the center of a Tootsie Pop?</t>
+  </si>
+  <si>
+    <t>Which are real song titles from Disney's "Frozen" movies?</t>
   </si>
 </sst>
 </file>
@@ -2081,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB832CB-3912-F247-8D46-62AA3D5AE696}">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="57.6640625" style="1" customWidth="1"/>
@@ -2115,7 +2124,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="99" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1" s="73" t="s">
         <v>6</v>
@@ -2252,7 +2261,7 @@
       </c>
       <c r="F4" s="73"/>
       <c r="G4" s="77" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H4" s="73">
         <v>5</v>
@@ -2557,7 +2566,7 @@
       <c r="E11" s="73"/>
       <c r="F11" s="73"/>
       <c r="G11" s="77" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H11" s="73">
         <v>9</v>
@@ -2696,7 +2705,7 @@
       </c>
       <c r="F14" s="73"/>
       <c r="G14" s="77" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H14" s="73">
         <v>1</v>
@@ -2786,7 +2795,7 @@
       </c>
       <c r="F16" s="73"/>
       <c r="G16" s="77" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H16" s="73">
         <v>1</v>
@@ -2820,7 +2829,7 @@
         <v>300</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C17" s="73">
         <v>10</v>
@@ -2833,7 +2842,7 @@
       </c>
       <c r="F17" s="73"/>
       <c r="G17" s="77" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H17" s="73">
         <v>1</v>
@@ -2858,16 +2867,16 @@
         <v>93</v>
       </c>
       <c r="P17" s="81" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q17" s="73"/>
     </row>
     <row r="18" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="73" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B18" s="76" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C18" s="73">
         <v>50</v>
@@ -2903,16 +2912,16 @@
         <v>435</v>
       </c>
       <c r="P18" s="81" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q18" s="73"/>
     </row>
     <row r="19" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A19" s="73" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B19" s="76" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C19" s="73">
         <v>50</v>
@@ -2948,15 +2957,15 @@
         <v>100</v>
       </c>
       <c r="P19" s="81" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="73" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C20" s="73">
         <v>1</v>
@@ -2990,15 +2999,15 @@
         <v>3</v>
       </c>
       <c r="P20" s="81" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="73" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B21" s="76" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C21" s="73">
         <v>1</v>
@@ -3032,15 +3041,15 @@
         <v>3</v>
       </c>
       <c r="P21" s="81" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="73" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B22" s="76" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C22" s="73">
         <v>1</v>
@@ -3074,15 +3083,15 @@
         <v>1</v>
       </c>
       <c r="P22" s="81" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="73" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B23" s="76" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C23" s="73">
         <v>10</v>
@@ -3115,15 +3124,15 @@
         <v>10</v>
       </c>
       <c r="P23" s="81" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="73" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C24" s="73">
         <v>10</v>
@@ -3156,7 +3165,51 @@
         <v>27</v>
       </c>
       <c r="P24" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="73" t="s">
         <v>371</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="73">
+        <v>10</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="G25" s="75" t="s">
+        <v>339</v>
+      </c>
+      <c r="H25" s="73">
+        <v>1</v>
+      </c>
+      <c r="I25" s="73">
+        <v>95</v>
+      </c>
+      <c r="J25" s="73">
+        <v>0</v>
+      </c>
+      <c r="K25" s="73">
+        <v>100</v>
+      </c>
+      <c r="L25" s="73">
+        <v>20</v>
+      </c>
+      <c r="M25" s="73">
+        <v>80</v>
+      </c>
+      <c r="O25" s="73">
+        <v>3</v>
+      </c>
+      <c r="P25" s="81" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3298,7 +3351,7 @@
         <v>61</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G4" t="s">
         <v>72</v>
@@ -3379,10 +3432,10 @@
     </row>
     <row r="7" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B7" t="s">
         <v>337</v>
-      </c>
-      <c r="B7" t="s">
-        <v>338</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
@@ -3394,10 +3447,10 @@
         <v>61</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -3411,10 +3464,10 @@
     </row>
     <row r="8" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C8" t="s">
         <v>59</v>
@@ -3426,10 +3479,10 @@
         <v>61</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H8">
         <v>9</v>
@@ -3755,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="AC2" s="57" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AD2" s="37" t="b">
         <v>0</v>
@@ -4444,7 +4497,7 @@
         <v>301</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>302</v>
+        <v>374</v>
       </c>
       <c r="C9" s="94" t="s">
         <v>125</v>
@@ -4453,206 +4506,206 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="F9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="F9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="28" t="s">
+      <c r="H9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="H9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="28" t="s">
+      <c r="J9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="J9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="28" t="s">
+      <c r="L9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="L9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="28" t="s">
+      <c r="N9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="N9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="28" t="s">
+      <c r="P9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="R9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="T9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="P9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="R9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" s="28" t="s">
+      <c r="V9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="33" t="s">
         <v>311</v>
       </c>
-      <c r="T9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U9" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="V9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="33" t="s">
+      <c r="X9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="33" t="s">
         <v>312</v>
       </c>
-      <c r="X9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="33" t="s">
+      <c r="Z9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="33" t="s">
         <v>313</v>
       </c>
-      <c r="Z9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="33" t="s">
+      <c r="AB9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="AB9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="33" t="s">
+      <c r="AD9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="AD9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="33" t="s">
+      <c r="AF9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="AJ9" s="39" t="s">
         <v>316</v>
-      </c>
-      <c r="AF9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH9" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI9" s="27" t="s">
-        <v>318</v>
-      </c>
-      <c r="AJ9" s="39" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:36" s="40" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="82" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C10" s="95"/>
       <c r="D10" s="96"/>
       <c r="E10" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="F10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="46" t="s">
         <v>320</v>
       </c>
-      <c r="F10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="46" t="s">
+      <c r="H10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="46" t="s">
         <v>321</v>
       </c>
-      <c r="H10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="46" t="s">
+      <c r="J10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="46" t="s">
         <v>322</v>
       </c>
-      <c r="J10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="46" t="s">
+      <c r="L10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="46" t="s">
         <v>323</v>
       </c>
-      <c r="L10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="46" t="s">
+      <c r="N10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="P10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="46" t="s">
         <v>324</v>
       </c>
-      <c r="N10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" s="46" t="s">
+      <c r="R10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="T10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="49" t="s">
         <v>331</v>
       </c>
-      <c r="P10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="46" t="s">
-        <v>325</v>
-      </c>
-      <c r="R10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10" s="46" t="s">
+      <c r="V10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="47" t="s">
+        <v>333</v>
+      </c>
+      <c r="X10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="Z10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="49" t="s">
+        <v>327</v>
+      </c>
+      <c r="AB10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="52" t="s">
         <v>326</v>
       </c>
-      <c r="T10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10" s="49" t="s">
-        <v>332</v>
-      </c>
-      <c r="V10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" s="47" t="s">
+      <c r="AD10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="52" t="s">
         <v>334</v>
       </c>
-      <c r="X10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="47" t="s">
-        <v>336</v>
-      </c>
-      <c r="Z10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="49" t="s">
+      <c r="AF10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="27" t="s">
+        <v>329</v>
+      </c>
+      <c r="AJ10" s="39" t="s">
         <v>328</v>
-      </c>
-      <c r="AB10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="52" t="s">
-        <v>327</v>
-      </c>
-      <c r="AD10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="AF10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="AJ10" s="39" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EABC2BA-D779-1C45-AC30-F13807F220E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CC4BEA-8AB2-294C-908F-C30B11714805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="2" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="3" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="390">
   <si>
     <t>question_id</t>
   </si>
@@ -1164,6 +1164,51 @@
   </si>
   <si>
     <t>Which are real song titles from Disney's "Frozen" movies?</t>
+  </si>
+  <si>
+    <t>What year was Basketball invented?</t>
+  </si>
+  <si>
+    <t>pinch_y</t>
+  </si>
+  <si>
+    <t>Basketball was invented in 1891.</t>
+  </si>
+  <si>
+    <t>How many episodes of &lt;i&gt;Breaking Bad&lt;/i&gt; aired over its 5 seasons?</t>
+  </si>
+  <si>
+    <t>pinch_z</t>
+  </si>
+  <si>
+    <t>62 episodes of &lt;i&gt;Breaking Bad&lt;/i&gt; aired between 2005 and 2008.</t>
+  </si>
+  <si>
+    <t>On the Periodic Table of Elements, what number is Helium?</t>
+  </si>
+  <si>
+    <t>pinch_a2</t>
+  </si>
+  <si>
+    <t>The atomic number of Helium is 2.</t>
+  </si>
+  <si>
+    <t>q_draw_E</t>
+  </si>
+  <si>
+    <t>Which element is Hydrogen? Draw a shape that contains it!</t>
+  </si>
+  <si>
+    <t>IMAGES/DRAW QUESTIONS/q_draw_E.png</t>
+  </si>
+  <si>
+    <t>IMAGES/DRAW QUESTIONS/q_draw_E_mask.png</t>
+  </si>
+  <si>
+    <t>THIS ONE'S HYDROGEN:</t>
+  </si>
+  <si>
+    <t>IMAGES/DRAW QUESTIONS/q_draw_E_answer_screen.png</t>
   </si>
 </sst>
 </file>
@@ -2090,7 +2135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB832CB-3912-F247-8D46-62AA3D5AE696}">
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="57.6640625" style="1" customWidth="1"/>
@@ -2519,14 +2564,14 @@
       <c r="C10" s="73">
         <v>10</v>
       </c>
-      <c r="D10" s="73">
+      <c r="D10">
         <v>5</v>
       </c>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="77"/>
+      <c r="E10">
+        <v>1</v>
+      </c>
       <c r="H10" s="73">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" s="73">
         <v>95</v>
@@ -3210,6 +3255,129 @@
       </c>
       <c r="P25" s="81" t="s">
         <v>372</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A26" s="73" t="s">
+        <v>376</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C26" s="73">
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="H26" s="73">
+        <v>1</v>
+      </c>
+      <c r="I26" s="73">
+        <v>95</v>
+      </c>
+      <c r="J26" s="73">
+        <v>1850</v>
+      </c>
+      <c r="K26" s="73">
+        <v>1950</v>
+      </c>
+      <c r="L26" s="73">
+        <v>1875</v>
+      </c>
+      <c r="M26" s="73">
+        <v>1935</v>
+      </c>
+      <c r="O26" s="73">
+        <v>1891</v>
+      </c>
+      <c r="P26" s="81" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A27" s="73" t="s">
+        <v>379</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C27" s="73">
+        <v>10</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="H27" s="73">
+        <v>1</v>
+      </c>
+      <c r="I27" s="73">
+        <v>95</v>
+      </c>
+      <c r="J27" s="73">
+        <v>50</v>
+      </c>
+      <c r="K27" s="73">
+        <v>150</v>
+      </c>
+      <c r="L27" s="73">
+        <v>55</v>
+      </c>
+      <c r="M27" s="73">
+        <v>95</v>
+      </c>
+      <c r="O27" s="73">
+        <v>62</v>
+      </c>
+      <c r="P27" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="73" t="s">
+        <v>382</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C28" s="73">
+        <v>10</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="H28" s="73">
+        <v>1</v>
+      </c>
+      <c r="I28" s="73">
+        <v>95</v>
+      </c>
+      <c r="J28" s="73">
+        <v>0</v>
+      </c>
+      <c r="K28" s="73">
+        <v>100</v>
+      </c>
+      <c r="L28" s="73">
+        <v>40</v>
+      </c>
+      <c r="M28" s="73">
+        <v>80</v>
+      </c>
+      <c r="O28" s="73">
+        <v>2</v>
+      </c>
+      <c r="P28" s="81" t="s">
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -5030,7 +5198,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D7EE002-C8BB-8E47-A415-52259E56BE73}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="39.5" customWidth="1"/>
@@ -5187,6 +5355,35 @@
         <v>248</v>
       </c>
     </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>384</v>
+      </c>
+      <c r="B6" t="s">
+        <v>385</v>
+      </c>
+      <c r="C6" s="79" t="s">
+        <v>386</v>
+      </c>
+      <c r="D6" s="79" t="s">
+        <v>387</v>
+      </c>
+      <c r="E6" s="79" t="s">
+        <v>225</v>
+      </c>
+      <c r="F6">
+        <v>80</v>
+      </c>
+      <c r="G6">
+        <v>1.4</v>
+      </c>
+      <c r="H6" s="79" t="s">
+        <v>388</v>
+      </c>
+      <c r="I6" t="s">
+        <v>389</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CC4BEA-8AB2-294C-908F-C30B11714805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B576CC88-B1F6-474D-9AB1-62628A79410E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="3" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="740" yWindow="3400" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -1076,9 +1076,6 @@
     <t>map_q_7</t>
   </si>
   <si>
-    <t>Maine,New Hampshire, Vermont, Massachusetts, Rhode Island, Connecticut, New York, New Jersey, Pennsylvania</t>
-  </si>
-  <si>
     <t>Which state is New Hampshire?</t>
   </si>
   <si>
@@ -1142,9 +1139,6 @@
     <t>Usain Bolt finished the 100-meter dash in 9.58 seconds.</t>
   </si>
   <si>
-    <t>How seconds did Usain Bolt's fastest 100-meter dash take? (rounded to the nearest second)</t>
-  </si>
-  <si>
     <t>Jimi Hendrix, Janis Joplin, and Kurt Cobain all died at the same age. How old were they?</t>
   </si>
   <si>
@@ -1209,6 +1203,12 @@
   </si>
   <si>
     <t>IMAGES/DRAW QUESTIONS/q_draw_E_answer_screen.png</t>
+  </si>
+  <si>
+    <t>Maine,New Hampshire, Vermont, Massachusetts, Rhode Island, Connecticut, New York, New Jersey, Pennsylvania,Delaware</t>
+  </si>
+  <si>
+    <t>How many seconds did Usain Bolt's fastest 100-meter dash take? (rounded to the nearest second)</t>
   </si>
 </sst>
 </file>
@@ -2874,7 +2874,7 @@
         <v>300</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C17" s="73">
         <v>10</v>
@@ -2912,16 +2912,16 @@
         <v>93</v>
       </c>
       <c r="P17" s="81" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q17" s="73"/>
     </row>
     <row r="18" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="73" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B18" s="76" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C18" s="73">
         <v>50</v>
@@ -2957,16 +2957,16 @@
         <v>435</v>
       </c>
       <c r="P18" s="81" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q18" s="73"/>
     </row>
     <row r="19" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A19" s="73" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B19" s="76" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C19" s="73">
         <v>50</v>
@@ -3002,15 +3002,15 @@
         <v>100</v>
       </c>
       <c r="P19" s="81" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="73" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C20" s="73">
         <v>1</v>
@@ -3044,15 +3044,15 @@
         <v>3</v>
       </c>
       <c r="P20" s="81" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="73" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B21" s="76" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C21" s="73">
         <v>1</v>
@@ -3086,15 +3086,15 @@
         <v>3</v>
       </c>
       <c r="P21" s="81" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="73" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B22" s="76" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C22" s="73">
         <v>1</v>
@@ -3128,15 +3128,15 @@
         <v>1</v>
       </c>
       <c r="P22" s="81" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="73" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B23" s="76" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="C23" s="73">
         <v>10</v>
@@ -3169,15 +3169,15 @@
         <v>10</v>
       </c>
       <c r="P23" s="81" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="73" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C24" s="73">
         <v>10</v>
@@ -3210,15 +3210,15 @@
         <v>27</v>
       </c>
       <c r="P24" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="73" t="s">
+        <v>369</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="C25" s="73">
         <v>10</v>
@@ -3254,15 +3254,15 @@
         <v>3</v>
       </c>
       <c r="P25" s="81" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="73" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C26" s="73">
         <v>10</v>
@@ -3295,15 +3295,15 @@
         <v>1891</v>
       </c>
       <c r="P26" s="81" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="73" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C27" s="73">
         <v>10</v>
@@ -3336,15 +3336,15 @@
         <v>62</v>
       </c>
       <c r="P27" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="73" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C28" s="73">
         <v>10</v>
@@ -3377,7 +3377,7 @@
         <v>2</v>
       </c>
       <c r="P28" s="81" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -3635,7 +3635,7 @@
         <v>344</v>
       </c>
       <c r="B8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C8" t="s">
         <v>59</v>
@@ -3647,10 +3647,10 @@
         <v>61</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>345</v>
+        <v>388</v>
       </c>
       <c r="G8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H8">
         <v>9</v>
@@ -4665,7 +4665,7 @@
         <v>301</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C9" s="94" t="s">
         <v>125</v>
@@ -5357,16 +5357,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>382</v>
+      </c>
+      <c r="B6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C6" s="79" t="s">
         <v>384</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" s="79" t="s">
         <v>385</v>
-      </c>
-      <c r="C6" s="79" t="s">
-        <v>386</v>
-      </c>
-      <c r="D6" s="79" t="s">
-        <v>387</v>
       </c>
       <c r="E6" s="79" t="s">
         <v>225</v>
@@ -5378,10 +5378,10 @@
         <v>1.4</v>
       </c>
       <c r="H6" s="79" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="I6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B576CC88-B1F6-474D-9AB1-62628A79410E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032BAFC4-3962-A341-A034-7D9200336A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="740" yWindow="3400" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -1109,9 +1109,6 @@
     <t>pinch_s</t>
   </si>
   <si>
-    <t>In Manhattan, a theatre must have at least this many seats to be considered "Off-Broadway"</t>
-  </si>
-  <si>
     <t>Which month is named after the Roman god of war?</t>
   </si>
   <si>
@@ -1209,6 +1206,9 @@
   </si>
   <si>
     <t>How many seconds did Usain Bolt's fastest 100-meter dash take? (rounded to the nearest second)</t>
+  </si>
+  <si>
+    <t>In Manhattan, a theater must have at least this many seats to be considered "Off-Broadway"</t>
   </si>
 </sst>
 </file>
@@ -2966,7 +2966,7 @@
         <v>352</v>
       </c>
       <c r="B19" s="76" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C19" s="73">
         <v>50</v>
@@ -3002,7 +3002,7 @@
         <v>100</v>
       </c>
       <c r="P19" s="81" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="17" x14ac:dyDescent="0.2">
@@ -3049,10 +3049,10 @@
     </row>
     <row r="21" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="73" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B21" s="76" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C21" s="73">
         <v>1</v>
@@ -3086,15 +3086,15 @@
         <v>3</v>
       </c>
       <c r="P21" s="81" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="73" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B22" s="76" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C22" s="73">
         <v>1</v>
@@ -3128,15 +3128,15 @@
         <v>1</v>
       </c>
       <c r="P22" s="81" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="73" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B23" s="76" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C23" s="73">
         <v>10</v>
@@ -3169,15 +3169,15 @@
         <v>10</v>
       </c>
       <c r="P23" s="81" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="73" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C24" s="73">
         <v>10</v>
@@ -3210,15 +3210,15 @@
         <v>27</v>
       </c>
       <c r="P24" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="73" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C25" s="73">
         <v>10</v>
@@ -3254,15 +3254,15 @@
         <v>3</v>
       </c>
       <c r="P25" s="81" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="73" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C26" s="73">
         <v>10</v>
@@ -3295,15 +3295,15 @@
         <v>1891</v>
       </c>
       <c r="P26" s="81" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="73" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C27" s="73">
         <v>10</v>
@@ -3336,15 +3336,15 @@
         <v>62</v>
       </c>
       <c r="P27" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="73" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C28" s="73">
         <v>10</v>
@@ -3377,7 +3377,7 @@
         <v>2</v>
       </c>
       <c r="P28" s="81" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -3647,7 +3647,7 @@
         <v>61</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G8" t="s">
         <v>346</v>
@@ -4665,7 +4665,7 @@
         <v>301</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C9" s="94" t="s">
         <v>125</v>
@@ -5357,16 +5357,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B6" t="s">
         <v>382</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="79" t="s">
         <v>383</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="D6" s="79" t="s">
         <v>384</v>
-      </c>
-      <c r="D6" s="79" t="s">
-        <v>385</v>
       </c>
       <c r="E6" s="79" t="s">
         <v>225</v>
@@ -5378,10 +5378,10 @@
         <v>1.4</v>
       </c>
       <c r="H6" s="79" t="s">
+        <v>385</v>
+      </c>
+      <c r="I6" t="s">
         <v>386</v>
-      </c>
-      <c r="I6" t="s">
-        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032BAFC4-3962-A341-A034-7D9200336A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698148C9-1148-6F42-8D5B-DFE3DC1F953E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="740" yWindow="3400" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -2219,7 +2219,7 @@
       <c r="F2" s="73"/>
       <c r="G2" s="77"/>
       <c r="H2" s="73">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I2" s="73">
         <v>65</v>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698148C9-1148-6F42-8D5B-DFE3DC1F953E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA973E9-BAEF-294E-91D3-0E5947821922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -1085,9 +1085,6 @@
     <t>What's the square root of 8649?</t>
   </si>
   <si>
-    <t>As everyone knows, the square root of 8649.</t>
-  </si>
-  <si>
     <t>How many members are in the US house of representatives?</t>
   </si>
   <si>
@@ -1209,6 +1206,9 @@
   </si>
   <si>
     <t>In Manhattan, a theater must have at least this many seats to be considered "Off-Broadway"</t>
+  </si>
+  <si>
+    <t>As literally everyone knows from an early age, the square root of 8649 is 93.</t>
   </si>
 </sst>
 </file>
@@ -2912,16 +2912,16 @@
         <v>93</v>
       </c>
       <c r="P17" s="81" t="s">
-        <v>348</v>
+        <v>389</v>
       </c>
       <c r="Q17" s="73"/>
     </row>
     <row r="18" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="73" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B18" s="76" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C18" s="73">
         <v>50</v>
@@ -2957,16 +2957,16 @@
         <v>435</v>
       </c>
       <c r="P18" s="81" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q18" s="73"/>
     </row>
     <row r="19" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A19" s="73" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B19" s="76" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C19" s="73">
         <v>50</v>
@@ -3002,15 +3002,15 @@
         <v>100</v>
       </c>
       <c r="P19" s="81" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="73" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C20" s="73">
         <v>1</v>
@@ -3044,15 +3044,15 @@
         <v>3</v>
       </c>
       <c r="P20" s="81" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="73" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B21" s="76" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C21" s="73">
         <v>1</v>
@@ -3086,15 +3086,15 @@
         <v>3</v>
       </c>
       <c r="P21" s="81" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="73" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B22" s="76" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C22" s="73">
         <v>1</v>
@@ -3128,15 +3128,15 @@
         <v>1</v>
       </c>
       <c r="P22" s="81" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="73" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B23" s="76" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C23" s="73">
         <v>10</v>
@@ -3169,15 +3169,15 @@
         <v>10</v>
       </c>
       <c r="P23" s="81" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="73" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C24" s="73">
         <v>10</v>
@@ -3210,15 +3210,15 @@
         <v>27</v>
       </c>
       <c r="P24" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="73" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C25" s="73">
         <v>10</v>
@@ -3254,15 +3254,15 @@
         <v>3</v>
       </c>
       <c r="P25" s="81" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="73" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C26" s="73">
         <v>10</v>
@@ -3295,15 +3295,15 @@
         <v>1891</v>
       </c>
       <c r="P26" s="81" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="73" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C27" s="73">
         <v>10</v>
@@ -3336,15 +3336,15 @@
         <v>62</v>
       </c>
       <c r="P27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="73" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C28" s="73">
         <v>10</v>
@@ -3377,7 +3377,7 @@
         <v>2</v>
       </c>
       <c r="P28" s="81" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -3647,7 +3647,7 @@
         <v>61</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G8" t="s">
         <v>346</v>
@@ -4665,7 +4665,7 @@
         <v>301</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C9" s="94" t="s">
         <v>125</v>
@@ -5357,16 +5357,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B6" t="s">
         <v>381</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="79" t="s">
         <v>382</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="D6" s="79" t="s">
         <v>383</v>
-      </c>
-      <c r="D6" s="79" t="s">
-        <v>384</v>
       </c>
       <c r="E6" s="79" t="s">
         <v>225</v>
@@ -5378,10 +5378,10 @@
         <v>1.4</v>
       </c>
       <c r="H6" s="79" t="s">
+        <v>384</v>
+      </c>
+      <c r="I6" t="s">
         <v>385</v>
-      </c>
-      <c r="I6" t="s">
-        <v>386</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA973E9-BAEF-294E-91D3-0E5947821922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59CFD83-A10D-2140-8C02-AA9598F62CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -2986,10 +2986,10 @@
         <v>475</v>
       </c>
       <c r="J19" s="73">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K19" s="73">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="L19" s="73">
         <v>150</v>
@@ -3180,12 +3180,9 @@
         <v>364</v>
       </c>
       <c r="C24" s="73">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>5</v>
-      </c>
-      <c r="E24">
         <v>1</v>
       </c>
       <c r="H24" s="73">

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59CFD83-A10D-2140-8C02-AA9598F62CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0DF959-C404-5D4D-B9D8-4C51980548DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="3" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -743,12 +743,6 @@
     <t>THIS SHOT IS CHARTREUSE:</t>
   </si>
   <si>
-    <t>One of these triangles is carmine-colored. Draw a shape that contains it!</t>
-  </si>
-  <si>
-    <t>One of these shots is a chartreuse… draw a shape that contains it!</t>
-  </si>
-  <si>
     <t>q_draw_C</t>
   </si>
   <si>
@@ -1209,6 +1203,12 @@
   </si>
   <si>
     <t>As literally everyone knows from an early age, the square root of 8649 is 93.</t>
+  </si>
+  <si>
+    <t>Which triangle is the color "carmine"? Draw a shape that conains it!</t>
+  </si>
+  <si>
+    <t>One of these shots is chartreuse… draw a shape that contains it!</t>
   </si>
 </sst>
 </file>
@@ -2169,7 +2169,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="99" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H1" s="73" t="s">
         <v>6</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F4" s="73"/>
       <c r="G4" s="77" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H4" s="73">
         <v>5</v>
@@ -2611,7 +2611,7 @@
       <c r="E11" s="73"/>
       <c r="F11" s="73"/>
       <c r="G11" s="77" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H11" s="73">
         <v>9</v>
@@ -2638,7 +2638,7 @@
         <v>165</v>
       </c>
       <c r="P11" s="81" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Q11" s="73"/>
     </row>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="73" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C13" s="73">
         <v>1</v>
@@ -2728,16 +2728,16 @@
         <v>12</v>
       </c>
       <c r="P13" s="81" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Q13" s="73"/>
     </row>
     <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="73" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B14" s="76" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C14" s="73">
         <v>10</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="F14" s="73"/>
       <c r="G14" s="77" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H14" s="73">
         <v>1</v>
@@ -2775,16 +2775,16 @@
         <v>110</v>
       </c>
       <c r="P14" s="81" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q14" s="73"/>
     </row>
     <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="73" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C15" s="73">
         <v>5</v>
@@ -2818,16 +2818,16 @@
         <v>27</v>
       </c>
       <c r="P15" s="81" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Q15" s="73"/>
     </row>
     <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="73" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C16" s="73">
         <v>10</v>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="F16" s="73"/>
       <c r="G16" s="77" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H16" s="73">
         <v>1</v>
@@ -2865,16 +2865,16 @@
         <v>42</v>
       </c>
       <c r="P16" s="81" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="Q16" s="73"/>
     </row>
     <row r="17" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="73" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C17" s="73">
         <v>10</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="F17" s="73"/>
       <c r="G17" s="77" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H17" s="73">
         <v>1</v>
@@ -2912,16 +2912,16 @@
         <v>93</v>
       </c>
       <c r="P17" s="81" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Q17" s="73"/>
     </row>
     <row r="18" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="73" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B18" s="76" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C18" s="73">
         <v>50</v>
@@ -2957,16 +2957,16 @@
         <v>435</v>
       </c>
       <c r="P18" s="81" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="Q18" s="73"/>
     </row>
     <row r="19" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A19" s="73" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B19" s="76" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C19" s="73">
         <v>50</v>
@@ -3002,15 +3002,15 @@
         <v>100</v>
       </c>
       <c r="P19" s="81" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="73" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C20" s="73">
         <v>1</v>
@@ -3044,15 +3044,15 @@
         <v>3</v>
       </c>
       <c r="P20" s="81" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="73" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B21" s="76" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C21" s="73">
         <v>1</v>
@@ -3086,15 +3086,15 @@
         <v>3</v>
       </c>
       <c r="P21" s="81" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="73" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B22" s="76" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C22" s="73">
         <v>1</v>
@@ -3128,15 +3128,15 @@
         <v>1</v>
       </c>
       <c r="P22" s="81" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="73" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B23" s="76" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C23" s="73">
         <v>10</v>
@@ -3169,15 +3169,15 @@
         <v>10</v>
       </c>
       <c r="P23" s="81" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="73" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C24" s="73">
         <v>5</v>
@@ -3207,15 +3207,15 @@
         <v>27</v>
       </c>
       <c r="P24" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="73" t="s">
+        <v>365</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>369</v>
       </c>
       <c r="C25" s="73">
         <v>10</v>
@@ -3227,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="75" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H25" s="73">
         <v>1</v>
@@ -3251,15 +3251,15 @@
         <v>3</v>
       </c>
       <c r="P25" s="81" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="73" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C26" s="73">
         <v>10</v>
@@ -3292,15 +3292,15 @@
         <v>1891</v>
       </c>
       <c r="P26" s="81" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="73" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C27" s="73">
         <v>10</v>
@@ -3333,15 +3333,15 @@
         <v>62</v>
       </c>
       <c r="P27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="73" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C28" s="73">
         <v>10</v>
@@ -3374,7 +3374,7 @@
         <v>2</v>
       </c>
       <c r="P28" s="81" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -3516,7 +3516,7 @@
         <v>61</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G4" t="s">
         <v>72</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="7" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
@@ -3612,10 +3612,10 @@
         <v>61</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -3629,10 +3629,10 @@
     </row>
     <row r="8" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C8" t="s">
         <v>59</v>
@@ -3644,10 +3644,10 @@
         <v>61</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H8">
         <v>9</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AC2" s="57" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AD2" s="37" t="b">
         <v>0</v>
@@ -4243,7 +4243,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J5" s="29" t="b">
         <v>1</v>
@@ -4261,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="30" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P5" s="29" t="b">
         <v>1</v>
@@ -4439,10 +4439,10 @@
     </row>
     <row r="7" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="55" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C7" s="92" t="s">
         <v>125</v>
@@ -4451,108 +4451,108 @@
         <v>20</v>
       </c>
       <c r="E7" s="28" t="s">
+        <v>256</v>
+      </c>
+      <c r="F7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="H7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="J7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="L7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="F7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="30" t="s">
+      <c r="N7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="P7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="R7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="T7" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="V7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="H7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>259</v>
-      </c>
-      <c r="J7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="30" t="s">
+      <c r="X7" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="Z7" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="AB7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="AD7" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="36" t="s">
         <v>266</v>
       </c>
-      <c r="L7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="N7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="P7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="R7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="T7" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="33" t="s">
+      <c r="AF7" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="V7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="31" t="s">
-        <v>269</v>
-      </c>
-      <c r="X7" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="31" t="s">
+      <c r="AJ7" s="39" t="s">
         <v>271</v>
-      </c>
-      <c r="Z7" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="33" t="s">
-        <v>264</v>
-      </c>
-      <c r="AB7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="AD7" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="AF7" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="27" t="s">
-        <v>272</v>
-      </c>
-      <c r="AJ7" s="39" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="55" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C8" s="92" t="s">
         <v>125</v>
@@ -4561,108 +4561,108 @@
         <v>20</v>
       </c>
       <c r="E8" s="28" t="s">
+        <v>281</v>
+      </c>
+      <c r="F8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="H8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="F8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="30" t="s">
+      <c r="J8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="H8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="30" t="s">
+      <c r="L8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="J8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="30" t="s">
+      <c r="N8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="L8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="30" t="s">
+      <c r="P8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="N8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="30" t="s">
+      <c r="R8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="P8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="30" t="s">
+      <c r="T8" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="33" t="s">
         <v>289</v>
       </c>
-      <c r="R8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S8" s="30" t="s">
+      <c r="V8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="31" t="s">
         <v>290</v>
       </c>
-      <c r="T8" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" s="33" t="s">
+      <c r="X8" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="Z8" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="33" t="s">
         <v>291</v>
       </c>
-      <c r="V8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="31" t="s">
+      <c r="AB8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="36" t="s">
         <v>292</v>
       </c>
-      <c r="X8" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="Z8" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="33" t="s">
+      <c r="AD8" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="36" t="s">
         <v>293</v>
       </c>
-      <c r="AB8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="36" t="s">
+      <c r="AF8" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="AJ8" s="39" t="s">
         <v>294</v>
-      </c>
-      <c r="AD8" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="36" t="s">
-        <v>295</v>
-      </c>
-      <c r="AF8" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH8" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="AJ8" s="39" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:36" s="85" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="87" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C9" s="94" t="s">
         <v>125</v>
@@ -4671,206 +4671,206 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="F9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="H9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="F9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="28" t="s">
+      <c r="J9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="H9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="28" t="s">
+      <c r="L9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="J9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="28" t="s">
+      <c r="N9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="L9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="28" t="s">
+      <c r="P9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="28" t="s">
+        <v>307</v>
+      </c>
+      <c r="R9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="T9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="N9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="28" t="s">
-        <v>307</v>
-      </c>
-      <c r="P9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="28" t="s">
+      <c r="V9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="R9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" s="28" t="s">
+      <c r="X9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="33" t="s">
         <v>310</v>
       </c>
-      <c r="T9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U9" s="33" t="s">
-        <v>308</v>
-      </c>
-      <c r="V9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="33" t="s">
+      <c r="Z9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="33" t="s">
         <v>311</v>
       </c>
-      <c r="X9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="33" t="s">
+      <c r="AB9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="33" t="s">
         <v>312</v>
       </c>
-      <c r="Z9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="33" t="s">
+      <c r="AD9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="33" t="s">
         <v>313</v>
       </c>
-      <c r="AB9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="33" t="s">
+      <c r="AF9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="AJ9" s="39" t="s">
         <v>314</v>
-      </c>
-      <c r="AD9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="33" t="s">
-        <v>315</v>
-      </c>
-      <c r="AF9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH9" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI9" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="AJ9" s="39" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:36" s="40" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="82" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C10" s="95"/>
       <c r="D10" s="96"/>
       <c r="E10" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="F10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="H10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="46" t="s">
         <v>319</v>
       </c>
-      <c r="F10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="46" t="s">
+      <c r="J10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="46" t="s">
         <v>320</v>
       </c>
-      <c r="H10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="46" t="s">
+      <c r="L10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="46" t="s">
         <v>321</v>
       </c>
-      <c r="J10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="46" t="s">
+      <c r="N10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="46" t="s">
+        <v>328</v>
+      </c>
+      <c r="P10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="46" t="s">
         <v>322</v>
       </c>
-      <c r="L10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="46" t="s">
+      <c r="R10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" s="46" t="s">
         <v>323</v>
       </c>
-      <c r="N10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" s="46" t="s">
-        <v>330</v>
-      </c>
-      <c r="P10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="46" t="s">
+      <c r="T10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="49" t="s">
+        <v>329</v>
+      </c>
+      <c r="V10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="X10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="47" t="s">
+        <v>333</v>
+      </c>
+      <c r="Z10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="49" t="s">
+        <v>325</v>
+      </c>
+      <c r="AB10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="52" t="s">
         <v>324</v>
       </c>
-      <c r="R10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10" s="46" t="s">
-        <v>325</v>
-      </c>
-      <c r="T10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10" s="49" t="s">
-        <v>331</v>
-      </c>
-      <c r="V10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" s="47" t="s">
-        <v>333</v>
-      </c>
-      <c r="X10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="47" t="s">
-        <v>335</v>
-      </c>
-      <c r="Z10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="49" t="s">
+      <c r="AD10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="52" t="s">
+        <v>332</v>
+      </c>
+      <c r="AF10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="27" t="s">
         <v>327</v>
       </c>
-      <c r="AB10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="52" t="s">
+      <c r="AJ10" s="39" t="s">
         <v>326</v>
-      </c>
-      <c r="AD10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="52" t="s">
-        <v>334</v>
-      </c>
-      <c r="AF10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="27" t="s">
-        <v>329</v>
-      </c>
-      <c r="AJ10" s="39" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="11" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
@@ -5227,7 +5227,7 @@
         <v>221</v>
       </c>
       <c r="G1" s="78" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H1" s="78" t="s">
         <v>14</v>
@@ -5241,7 +5241,7 @@
         <v>222</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>234</v>
+        <v>388</v>
       </c>
       <c r="C2" s="79" t="s">
         <v>223</v>
@@ -5270,7 +5270,7 @@
         <v>229</v>
       </c>
       <c r="B3" t="s">
-        <v>235</v>
+        <v>389</v>
       </c>
       <c r="C3" s="79" t="s">
         <v>230</v>
@@ -5296,16 +5296,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="79" t="s">
         <v>236</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" s="79" t="s">
         <v>237</v>
-      </c>
-      <c r="C4" s="79" t="s">
-        <v>238</v>
-      </c>
-      <c r="D4" s="79" t="s">
-        <v>239</v>
       </c>
       <c r="E4" s="79" t="s">
         <v>225</v>
@@ -5317,24 +5317,24 @@
         <v>1</v>
       </c>
       <c r="H4" s="79" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C5" s="79" t="s">
         <v>243</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" s="79" t="s">
         <v>244</v>
-      </c>
-      <c r="C5" s="79" t="s">
-        <v>245</v>
-      </c>
-      <c r="D5" s="79" t="s">
-        <v>246</v>
       </c>
       <c r="E5" s="79" t="s">
         <v>225</v>
@@ -5346,24 +5346,24 @@
         <v>1</v>
       </c>
       <c r="H5" s="79" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B6" t="s">
+        <v>379</v>
+      </c>
+      <c r="C6" s="79" t="s">
         <v>380</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" s="79" t="s">
         <v>381</v>
-      </c>
-      <c r="C6" s="79" t="s">
-        <v>382</v>
-      </c>
-      <c r="D6" s="79" t="s">
-        <v>383</v>
       </c>
       <c r="E6" s="79" t="s">
         <v>225</v>
@@ -5375,10 +5375,10 @@
         <v>1.4</v>
       </c>
       <c r="H6" s="79" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0DF959-C404-5D4D-B9D8-4C51980548DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3619835D-7C2C-5046-8B2E-56FA5D8B3C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="-18940" windowWidth="33360" windowHeight="15640" activeTab="3" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="740" yWindow="3400" windowWidth="33360" windowHeight="15640" activeTab="3" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -1205,10 +1205,10 @@
     <t>As literally everyone knows from an early age, the square root of 8649 is 93.</t>
   </si>
   <si>
-    <t>Which triangle is the color "carmine"? Draw a shape that conains it!</t>
-  </si>
-  <si>
     <t>One of these shots is chartreuse… draw a shape that contains it!</t>
+  </si>
+  <si>
+    <t>Which triangle is the color "carmine"? Draw a shape that contains it!</t>
   </si>
 </sst>
 </file>
@@ -5241,7 +5241,7 @@
         <v>222</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C2" s="79" t="s">
         <v>223</v>
@@ -5270,7 +5270,7 @@
         <v>229</v>
       </c>
       <c r="B3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C3" s="79" t="s">
         <v>230</v>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3619835D-7C2C-5046-8B2E-56FA5D8B3C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B3965B-BD7F-DB42-97F3-4316876595E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="740" yWindow="3400" windowWidth="33360" windowHeight="15640" activeTab="3" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="11580" yWindow="6560" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="393">
   <si>
     <t>question_id</t>
   </si>
@@ -1209,13 +1209,22 @@
   </si>
   <si>
     <t>Which triangle is the color "carmine"? Draw a shape that contains it!</t>
+  </si>
+  <si>
+    <t>What year were nachos invented?</t>
+  </si>
+  <si>
+    <t>pinch_a3</t>
+  </si>
+  <si>
+    <t>Nachos were invented in El Paso, Texas in 1943.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1517,7 +1526,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1792,9 +1801,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2135,8 +2141,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB832CB-3912-F247-8D46-62AA3D5AE696}">
-  <dimension ref="A1:Q28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Q29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="57.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
@@ -2149,7 +2155,7 @@
     <col min="17" max="17" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="17">
       <c r="A1" s="73" t="s">
         <v>0</v>
       </c>
@@ -2168,7 +2174,7 @@
       <c r="F1" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="99" t="s">
+      <c r="G1" s="73" t="s">
         <v>338</v>
       </c>
       <c r="H1" s="73" t="s">
@@ -2200,7 +2206,7 @@
       </c>
       <c r="Q1" s="73"/>
     </row>
-    <row r="2" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" ht="34">
       <c r="A2" s="73" t="s">
         <v>16</v>
       </c>
@@ -2245,7 +2251,7 @@
       </c>
       <c r="Q2" s="73"/>
     </row>
-    <row r="3" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="17">
       <c r="A3" s="73" t="s">
         <v>18</v>
       </c>
@@ -2288,7 +2294,7 @@
       </c>
       <c r="Q3" s="73"/>
     </row>
-    <row r="4" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="34">
       <c r="A4" s="73" t="s">
         <v>21</v>
       </c>
@@ -2335,7 +2341,7 @@
       </c>
       <c r="Q4" s="73"/>
     </row>
-    <row r="5" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="34">
       <c r="A5" s="73" t="s">
         <v>24</v>
       </c>
@@ -2378,7 +2384,7 @@
       </c>
       <c r="Q5" s="73"/>
     </row>
-    <row r="6" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="34">
       <c r="A6" s="73" t="s">
         <v>27</v>
       </c>
@@ -2421,7 +2427,7 @@
       </c>
       <c r="Q6" s="73"/>
     </row>
-    <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" ht="17">
       <c r="A7" s="73" t="s">
         <v>30</v>
       </c>
@@ -2466,7 +2472,7 @@
       </c>
       <c r="Q7" s="73"/>
     </row>
-    <row r="8" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" ht="17">
       <c r="A8" s="73" t="s">
         <v>33</v>
       </c>
@@ -2509,7 +2515,7 @@
       </c>
       <c r="Q8" s="73"/>
     </row>
-    <row r="9" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" ht="17">
       <c r="A9" s="73" t="s">
         <v>37</v>
       </c>
@@ -2554,7 +2560,7 @@
       </c>
       <c r="Q9" s="73"/>
     </row>
-    <row r="10" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" ht="17">
       <c r="A10" s="73" t="s">
         <v>40</v>
       </c>
@@ -2597,7 +2603,7 @@
       </c>
       <c r="Q10" s="73"/>
     </row>
-    <row r="11" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" ht="34">
       <c r="A11" s="73" t="s">
         <v>42</v>
       </c>
@@ -2642,7 +2648,7 @@
       </c>
       <c r="Q11" s="73"/>
     </row>
-    <row r="12" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" ht="34">
       <c r="A12" s="73" t="s">
         <v>45</v>
       </c>
@@ -2689,7 +2695,7 @@
       </c>
       <c r="Q12" s="73"/>
     </row>
-    <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" ht="17">
       <c r="A13" s="73" t="s">
         <v>250</v>
       </c>
@@ -2732,7 +2738,7 @@
       </c>
       <c r="Q13" s="73"/>
     </row>
-    <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" ht="17">
       <c r="A14" s="73" t="s">
         <v>251</v>
       </c>
@@ -2779,7 +2785,7 @@
       </c>
       <c r="Q14" s="73"/>
     </row>
-    <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" ht="17">
       <c r="A15" s="73" t="s">
         <v>273</v>
       </c>
@@ -2822,7 +2828,7 @@
       </c>
       <c r="Q15" s="73"/>
     </row>
-    <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" ht="17">
       <c r="A16" s="73" t="s">
         <v>278</v>
       </c>
@@ -2869,7 +2875,7 @@
       </c>
       <c r="Q16" s="73"/>
     </row>
-    <row r="17" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" ht="17">
       <c r="A17" s="73" t="s">
         <v>298</v>
       </c>
@@ -2916,7 +2922,7 @@
       </c>
       <c r="Q17" s="73"/>
     </row>
-    <row r="18" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" ht="17">
       <c r="A18" s="73" t="s">
         <v>347</v>
       </c>
@@ -2961,7 +2967,7 @@
       </c>
       <c r="Q18" s="73"/>
     </row>
-    <row r="19" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" ht="34">
       <c r="A19" s="73" t="s">
         <v>349</v>
       </c>
@@ -3005,7 +3011,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" ht="17">
       <c r="A20" s="73" t="s">
         <v>352</v>
       </c>
@@ -3047,7 +3053,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" ht="17">
       <c r="A21" s="73" t="s">
         <v>356</v>
       </c>
@@ -3089,7 +3095,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" ht="17">
       <c r="A22" s="73" t="s">
         <v>359</v>
       </c>
@@ -3131,7 +3137,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" ht="34">
       <c r="A23" s="73" t="s">
         <v>360</v>
       </c>
@@ -3172,7 +3178,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="34">
       <c r="A24" s="73" t="s">
         <v>363</v>
       </c>
@@ -3210,7 +3216,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" ht="17">
       <c r="A25" s="73" t="s">
         <v>365</v>
       </c>
@@ -3254,7 +3260,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" ht="17">
       <c r="A26" s="73" t="s">
         <v>370</v>
       </c>
@@ -3295,7 +3301,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" ht="17">
       <c r="A27" s="73" t="s">
         <v>373</v>
       </c>
@@ -3336,7 +3342,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" ht="17">
       <c r="A28" s="73" t="s">
         <v>376</v>
       </c>
@@ -3375,6 +3381,47 @@
       </c>
       <c r="P28" s="81" t="s">
         <v>377</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="17">
+      <c r="A29" s="73" t="s">
+        <v>391</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C29" s="73">
+        <v>10</v>
+      </c>
+      <c r="D29">
+        <v>5</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="H29" s="73">
+        <v>1</v>
+      </c>
+      <c r="I29" s="73">
+        <v>95</v>
+      </c>
+      <c r="J29" s="73">
+        <v>1860</v>
+      </c>
+      <c r="K29" s="73">
+        <v>1960</v>
+      </c>
+      <c r="L29" s="73">
+        <v>1875</v>
+      </c>
+      <c r="M29" s="73">
+        <v>1935</v>
+      </c>
+      <c r="O29" s="73">
+        <v>1943</v>
+      </c>
+      <c r="P29" s="81" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -3385,7 +3432,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0380E023-4B0F-5D41-A3D5-4A6D015B3367}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="33.83203125" customWidth="1"/>
     <col min="6" max="6" width="44.83203125" style="1" customWidth="1"/>
@@ -3394,7 +3441,7 @@
     <col min="12" max="12" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3435,7 +3482,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="34">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -3467,7 +3514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="51">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -3499,7 +3546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="34">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -3531,7 +3578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="34">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -3563,7 +3610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="17">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -3595,7 +3642,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="51">
       <c r="A7" t="s">
         <v>334</v>
       </c>
@@ -3627,7 +3674,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="51">
       <c r="A8" t="s">
         <v>342</v>
       </c>
@@ -3659,7 +3706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="85">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -3694,7 +3741,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="85">
       <c r="A10" t="s">
         <v>215</v>
       </c>
@@ -3737,7 +3784,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A722971B-16B6-2747-9012-3CB77F8500DE}">
   <dimension ref="A1:AJ19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="39.1640625" style="1" customWidth="1"/>
@@ -3777,7 +3824,7 @@
     <col min="36" max="36" width="28.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="60" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" s="60" customFormat="1" ht="45">
       <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
@@ -3887,7 +3934,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" s="40" customFormat="1" ht="34">
       <c r="A2" s="55" t="s">
         <v>123</v>
       </c>
@@ -3997,7 +4044,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:36" s="40" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" s="40" customFormat="1" ht="27">
       <c r="A3" s="55" t="s">
         <v>139</v>
       </c>
@@ -4107,7 +4154,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" s="40" customFormat="1" ht="34">
       <c r="A4" s="55" t="s">
         <v>152</v>
       </c>
@@ -4217,7 +4264,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="40" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" s="40" customFormat="1" ht="34">
       <c r="A5" s="55" t="s">
         <v>166</v>
       </c>
@@ -4327,7 +4374,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:36" s="26" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" s="26" customFormat="1" ht="27">
       <c r="A6" s="56" t="s">
         <v>178</v>
       </c>
@@ -4437,7 +4484,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="7" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" s="39" customFormat="1" ht="34">
       <c r="A7" s="55" t="s">
         <v>254</v>
       </c>
@@ -4547,7 +4594,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="39" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" s="39" customFormat="1" ht="34">
       <c r="A8" s="55" t="s">
         <v>280</v>
       </c>
@@ -4657,7 +4704,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="9" spans="1:36" s="85" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" s="85" customFormat="1" ht="34">
       <c r="A9" s="87" t="s">
         <v>299</v>
       </c>
@@ -4767,7 +4814,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="40" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" s="40" customFormat="1" ht="17">
       <c r="A10" s="82" t="s">
         <v>316</v>
       </c>
@@ -4873,7 +4920,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="11" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" s="40" customFormat="1">
       <c r="A11" s="42"/>
       <c r="B11" s="43"/>
       <c r="C11" s="95"/>
@@ -4908,7 +4955,7 @@
       <c r="AF11" s="54"/>
       <c r="AI11" s="43"/>
     </row>
-    <row r="12" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" s="40" customFormat="1">
       <c r="A12" s="42"/>
       <c r="B12" s="43"/>
       <c r="C12" s="95"/>
@@ -4943,7 +4990,7 @@
       <c r="AF12" s="54"/>
       <c r="AI12" s="43"/>
     </row>
-    <row r="13" spans="1:36" s="40" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" s="40" customFormat="1" ht="17" customHeight="1">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="95"/>
@@ -4978,7 +5025,7 @@
       <c r="AF13" s="54"/>
       <c r="AI13" s="43"/>
     </row>
-    <row r="14" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" s="40" customFormat="1">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="95"/>
@@ -5013,7 +5060,7 @@
       <c r="AF14" s="54"/>
       <c r="AI14" s="43"/>
     </row>
-    <row r="15" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" s="40" customFormat="1">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="95"/>
@@ -5048,7 +5095,7 @@
       <c r="AF15" s="54"/>
       <c r="AI15" s="43"/>
     </row>
-    <row r="16" spans="1:36" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" s="40" customFormat="1">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="95"/>
@@ -5083,7 +5130,7 @@
       <c r="AF16" s="54"/>
       <c r="AI16" s="43"/>
     </row>
-    <row r="17" spans="1:35" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" s="40" customFormat="1">
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="95"/>
@@ -5118,7 +5165,7 @@
       <c r="AF17" s="54"/>
       <c r="AI17" s="43"/>
     </row>
-    <row r="18" spans="1:35" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" s="40" customFormat="1">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="95"/>
@@ -5153,7 +5200,7 @@
       <c r="AF18" s="54"/>
       <c r="AI18" s="43"/>
     </row>
-    <row r="19" spans="1:35" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:35" s="40" customFormat="1">
       <c r="A19" s="42"/>
       <c r="B19" s="43"/>
       <c r="C19" s="95"/>
@@ -5196,7 +5243,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D7EE002-C8BB-8E47-A415-52259E56BE73}">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="39.5" customWidth="1"/>
     <col min="3" max="3" width="32.6640625" customWidth="1"/>
@@ -5207,7 +5254,7 @@
     <col min="9" max="9" width="28.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -5236,7 +5283,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" s="79" t="s">
         <v>222</v>
       </c>
@@ -5265,7 +5312,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>229</v>
       </c>
@@ -5294,7 +5341,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>234</v>
       </c>
@@ -5323,7 +5370,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>241</v>
       </c>
@@ -5352,7 +5399,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>378</v>
       </c>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B3965B-BD7F-DB42-97F3-4316876595E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2101AB2F-2D3D-C842-B743-490217BF6F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11580" yWindow="6560" windowWidth="33360" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="9880" yWindow="9200" windowWidth="33360" windowHeight="15640" activeTab="1" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="398">
   <si>
     <t>question_id</t>
   </si>
@@ -1218,6 +1218,21 @@
   </si>
   <si>
     <t>Nachos were invented in El Paso, Texas in 1943.</t>
+  </si>
+  <si>
+    <t>map_q_C</t>
+  </si>
+  <si>
+    <t>Which building is a landmark in Dallas, Texas?</t>
+  </si>
+  <si>
+    <t>IMAGES/IMAGE QUESTIONS/map_q_C_dallas.svg</t>
+  </si>
+  <si>
+    <t>IMAGES/IMAGE QUESTIONS/map_q_c_dallas.png</t>
+  </si>
+  <si>
+    <t>THIS IS DALLAS' REUNION TOWER:</t>
   </si>
 </sst>
 </file>
@@ -3431,10 +3446,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0380E023-4B0F-5D41-A3D5-4A6D015B3367}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="33.83203125" customWidth="1"/>
+    <col min="2" max="2" width="39.1640625" customWidth="1"/>
     <col min="6" max="6" width="44.83203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="11" max="11" width="29.5" style="1" customWidth="1"/>
@@ -3774,6 +3789,41 @@
       </c>
       <c r="M10" t="s">
         <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="85">
+      <c r="A11" t="s">
+        <v>393</v>
+      </c>
+      <c r="B11" t="s">
+        <v>394</v>
+      </c>
+      <c r="C11" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11">
+        <v>9</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="M11" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2101AB2F-2D3D-C842-B743-490217BF6F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54E0C6A-8806-BD4B-A26B-A92A83E60EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9880" yWindow="9200" windowWidth="33360" windowHeight="15640" activeTab="1" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -3450,6 +3450,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="39.1640625" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
     <col min="6" max="6" width="44.83203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="11" max="11" width="29.5" style="1" customWidth="1"/>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54E0C6A-8806-BD4B-A26B-A92A83E60EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A48372E-2491-314C-ACDC-EAF0EF4B6FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9880" yWindow="9200" windowWidth="33360" windowHeight="15640" activeTab="1" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="397">
   <si>
     <t>question_id</t>
   </si>
@@ -1218,9 +1218,6 @@
   </si>
   <si>
     <t>Nachos were invented in El Paso, Texas in 1943.</t>
-  </si>
-  <si>
-    <t>map_q_C</t>
   </si>
   <si>
     <t>Which building is a landmark in Dallas, Texas?</t>
@@ -3793,11 +3790,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="85">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>393</v>
-      </c>
-      <c r="B11" t="s">
-        <v>394</v>
       </c>
       <c r="C11" t="s">
         <v>85</v>
@@ -3818,13 +3812,13 @@
         <v>10</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="M11" t="s">
         <v>396</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="M11" t="s">
-        <v>397</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A48372E-2491-314C-ACDC-EAF0EF4B6FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE21603-29B2-C944-A2F9-5CD5A25FC0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9880" yWindow="9200" windowWidth="33360" windowHeight="15640" activeTab="1" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE21603-29B2-C944-A2F9-5CD5A25FC0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC28A97-397F-ED45-820A-93972F24EB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9880" yWindow="9200" windowWidth="33360" windowHeight="15640" activeTab="1" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="398">
   <si>
     <t>question_id</t>
   </si>
@@ -1218,6 +1218,9 @@
   </si>
   <si>
     <t>Nachos were invented in El Paso, Texas in 1943.</t>
+  </si>
+  <si>
+    <t>map_q_C</t>
   </si>
   <si>
     <t>Which building is a landmark in Dallas, Texas?</t>
@@ -3790,8 +3793,11 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="85">
+      <c r="A11" t="s">
+        <v>393</v>
+      </c>
       <c r="B11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C11" t="s">
         <v>85</v>
@@ -3812,13 +3818,13 @@
         <v>10</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="M11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC28A97-397F-ED45-820A-93972F24EB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2AF3DA-717A-5C4F-8D8C-5AA0CA3412BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9880" yWindow="9200" windowWidth="33360" windowHeight="15640" activeTab="1" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="9880" yWindow="9200" windowWidth="33360" windowHeight="15640" activeTab="3" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -1208,9 +1208,6 @@
     <t>One of these shots is chartreuse… draw a shape that contains it!</t>
   </si>
   <si>
-    <t>Which triangle is the color "carmine"? Draw a shape that contains it!</t>
-  </si>
-  <si>
     <t>What year were nachos invented?</t>
   </si>
   <si>
@@ -1233,6 +1230,9 @@
   </si>
   <si>
     <t>THIS IS DALLAS' REUNION TOWER:</t>
+  </si>
+  <si>
+    <t>Which triangle is the color "carmine"? Draw a shape that contains it (you can include more than one, but points go down the larger your shape gets)</t>
   </si>
 </sst>
 </file>
@@ -3400,10 +3400,10 @@
     </row>
     <row r="29" spans="1:17" ht="17">
       <c r="A29" s="73" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C29" s="73">
         <v>10</v>
@@ -3436,7 +3436,7 @@
         <v>1943</v>
       </c>
       <c r="P29" s="81" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="11" spans="1:13" ht="85">
       <c r="A11" t="s">
+        <v>392</v>
+      </c>
+      <c r="B11" t="s">
         <v>393</v>
-      </c>
-      <c r="B11" t="s">
-        <v>394</v>
       </c>
       <c r="C11" t="s">
         <v>85</v>
@@ -3818,13 +3818,13 @@
         <v>10</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="M11" t="s">
         <v>396</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="M11" t="s">
-        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -5339,7 +5339,7 @@
         <v>222</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C2" s="79" t="s">
         <v>223</v>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2AF3DA-717A-5C4F-8D8C-5AA0CA3412BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E8A227-7044-F34A-8205-50445ACE49D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9880" yWindow="9200" windowWidth="33360" windowHeight="15640" activeTab="3" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
@@ -1208,6 +1208,9 @@
     <t>One of these shots is chartreuse… draw a shape that contains it!</t>
   </si>
   <si>
+    <t>Which triangle is the color "carmine"? Draw a shape that contains it!</t>
+  </si>
+  <si>
     <t>What year were nachos invented?</t>
   </si>
   <si>
@@ -1230,9 +1233,6 @@
   </si>
   <si>
     <t>THIS IS DALLAS' REUNION TOWER:</t>
-  </si>
-  <si>
-    <t>Which triangle is the color "carmine"? Draw a shape that contains it (you can include more than one, but points go down the larger your shape gets)</t>
   </si>
 </sst>
 </file>
@@ -3400,10 +3400,10 @@
     </row>
     <row r="29" spans="1:17" ht="17">
       <c r="A29" s="73" t="s">
+        <v>391</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>389</v>
       </c>
       <c r="C29" s="73">
         <v>10</v>
@@ -3436,7 +3436,7 @@
         <v>1943</v>
       </c>
       <c r="P29" s="81" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="11" spans="1:13" ht="85">
       <c r="A11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C11" t="s">
         <v>85</v>
@@ -3818,13 +3818,13 @@
         <v>10</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="M11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -5339,7 +5339,7 @@
         <v>222</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C2" s="79" t="s">
         <v>223</v>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E8A227-7044-F34A-8205-50445ACE49D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84D6668-7684-3946-AD41-7449991F6EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9880" yWindow="9200" windowWidth="33360" windowHeight="15640" activeTab="3" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="9880" yWindow="9200" windowWidth="43080" windowHeight="15640" activeTab="4" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
     <sheet name="MAP" sheetId="2" r:id="rId2"/>
     <sheet name="BONUS" sheetId="3" r:id="rId3"/>
     <sheet name="DRAW" sheetId="4" r:id="rId4"/>
+    <sheet name="FINAL" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="481">
   <si>
     <t>question_id</t>
   </si>
@@ -413,9 +414,6 @@
     <t>bonus_q_uk_pm</t>
   </si>
   <si>
-    <t>Which of these people have been the Prime Minister of the UK?</t>
-  </si>
-  <si>
     <t>Pick as many as you like, but even one wrong choice means you get NO POINTS.</t>
   </si>
   <si>
@@ -461,9 +459,6 @@
     <t>bonus_q_dating</t>
   </si>
   <si>
-    <t>Which of these are actual dating apps?</t>
-  </si>
-  <si>
     <t>Tinder</t>
   </si>
   <si>
@@ -578,9 +573,6 @@
     <t>bonus_q_ikea</t>
   </si>
   <si>
-    <t>Which of these are real IKEA products?</t>
-  </si>
-  <si>
     <t>Billy</t>
   </si>
   <si>
@@ -623,18 +615,12 @@
     <t>NOT including echoes, how many times is the word "bye" sung in NSYNC's "Bye Bye Bye"?</t>
   </si>
   <si>
-    <t>The word "Kami" has many definitions in Japanese. Which are correct?</t>
-  </si>
-  <si>
     <t>What year was Velcro (A.K.A. "Hook &amp; Loop") invented?</t>
   </si>
   <si>
     <t>Poäng</t>
   </si>
   <si>
-    <t>Which of these planets exist in the &lt;i&gt;Star Trek&lt;/i&gt; universe?</t>
-  </si>
-  <si>
     <t>Bannister, Lord Broadstairs</t>
   </si>
   <si>
@@ -806,9 +792,6 @@
     <t>bonus_q_orioles</t>
   </si>
   <si>
-    <t>Which of these played baseball for the Baltimore Orioles ?</t>
-  </si>
-  <si>
     <t>Cal Ripken Jr.</t>
   </si>
   <si>
@@ -878,9 +861,6 @@
     <t>pinch_o</t>
   </si>
   <si>
-    <t>Which of these are actual Elvis Presley song titles?</t>
-  </si>
-  <si>
     <t>bonus_q_elvis</t>
   </si>
   <si>
@@ -1031,9 +1011,6 @@
     <t>Bulbasaurus</t>
   </si>
   <si>
-    <t>Which of these were actual dinosaurs?</t>
-  </si>
-  <si>
     <t>Ithinkshesaurus</t>
   </si>
   <si>
@@ -1145,9 +1122,6 @@
     <t>How many licks does it take to get to the center of a Tootsie Pop?</t>
   </si>
   <si>
-    <t>Which are real song titles from Disney's "Frozen" movies?</t>
-  </si>
-  <si>
     <t>What year was Basketball invented?</t>
   </si>
   <si>
@@ -1233,13 +1207,289 @@
   </si>
   <si>
     <t>THIS IS DALLAS' REUNION TOWER:</t>
+  </si>
+  <si>
+    <t>correct_answer</t>
+  </si>
+  <si>
+    <t>clue_1</t>
+  </si>
+  <si>
+    <t>clue_2</t>
+  </si>
+  <si>
+    <t>clue_3</t>
+  </si>
+  <si>
+    <t>clue_4</t>
+  </si>
+  <si>
+    <t>choice_1</t>
+  </si>
+  <si>
+    <t>choice_2</t>
+  </si>
+  <si>
+    <t>choice_3</t>
+  </si>
+  <si>
+    <t>choice_4</t>
+  </si>
+  <si>
+    <t>choice_5</t>
+  </si>
+  <si>
+    <t>choice_6</t>
+  </si>
+  <si>
+    <t>choice_7</t>
+  </si>
+  <si>
+    <t>choice_8</t>
+  </si>
+  <si>
+    <t>choice_9</t>
+  </si>
+  <si>
+    <t>choice_10</t>
+  </si>
+  <si>
+    <t>choice_11</t>
+  </si>
+  <si>
+    <t>choice_12</t>
+  </si>
+  <si>
+    <t>choice_13</t>
+  </si>
+  <si>
+    <t>choice_14</t>
+  </si>
+  <si>
+    <t>choice_15</t>
+  </si>
+  <si>
+    <t>choice_16</t>
+  </si>
+  <si>
+    <t>final_A</t>
+  </si>
+  <si>
+    <t>American Founding Fathers</t>
+  </si>
+  <si>
+    <t>Alexander Hamilton</t>
+  </si>
+  <si>
+    <t>Benjamin Franklin</t>
+  </si>
+  <si>
+    <t>John Adams</t>
+  </si>
+  <si>
+    <t>Thomas Jefferson</t>
+  </si>
+  <si>
+    <t>George Washington</t>
+  </si>
+  <si>
+    <t>Patrick Henry</t>
+  </si>
+  <si>
+    <t>Samuel Adams</t>
+  </si>
+  <si>
+    <t>Paul Revere</t>
+  </si>
+  <si>
+    <t>Aaron Burr</t>
+  </si>
+  <si>
+    <t>Han Jancock</t>
+  </si>
+  <si>
+    <t>Phil McCracken</t>
+  </si>
+  <si>
+    <t>St. Nicholas</t>
+  </si>
+  <si>
+    <t>King Mustin</t>
+  </si>
+  <si>
+    <t>There's a famous hip-hop musical about him.</t>
+  </si>
+  <si>
+    <t>He was killed by a sitting vice president.</t>
+  </si>
+  <si>
+    <t>His face appears on the $10 bill.</t>
+  </si>
+  <si>
+    <t>He founded the U.S. Coast Guard.</t>
+  </si>
+  <si>
+    <t>Lymon Hall</t>
+  </si>
+  <si>
+    <t>Sherman Edwards</t>
+  </si>
+  <si>
+    <t>Caesar Rodney</t>
+  </si>
+  <si>
+    <t>final_B</t>
+  </si>
+  <si>
+    <t>Wario</t>
+  </si>
+  <si>
+    <t>His name basically means "Bad Mario".</t>
+  </si>
+  <si>
+    <t>Bowser</t>
+  </si>
+  <si>
+    <t>Wart</t>
+  </si>
+  <si>
+    <t>King Boo</t>
+  </si>
+  <si>
+    <t>Ganon</t>
+  </si>
+  <si>
+    <t>Wendy O'Koopa</t>
+  </si>
+  <si>
+    <t>Barrio</t>
+  </si>
+  <si>
+    <t>Shawarm-io</t>
+  </si>
+  <si>
+    <t>Bowser, Jr.</t>
+  </si>
+  <si>
+    <t>Jareth</t>
+  </si>
+  <si>
+    <t>Mother Brain</t>
+  </si>
+  <si>
+    <t>Solid Snake</t>
+  </si>
+  <si>
+    <t>Charro</t>
+  </si>
+  <si>
+    <t>Confucius</t>
+  </si>
+  <si>
+    <t>Chain Chomp</t>
+  </si>
+  <si>
+    <t>Nintendo Villains</t>
+  </si>
+  <si>
+    <t>Waluigi</t>
+  </si>
+  <si>
+    <t>Debuted in "Super Mario Land 2".</t>
+  </si>
+  <si>
+    <t>Starred in a Virtual Boy platformer.</t>
+  </si>
+  <si>
+    <t>Which of these people were NOT the Prime Minister of the UK?</t>
+  </si>
+  <si>
+    <t>Which of these are NOT actual dating apps?</t>
+  </si>
+  <si>
+    <t>The word "Kami" has many definitions in Japanese. Which are NOT correct?</t>
+  </si>
+  <si>
+    <t>Which of these planets DO NOT exist in the &lt;i&gt;Star Trek&lt;/i&gt; universe?</t>
+  </si>
+  <si>
+    <t>Which of these are NOT real IKEA products?</t>
+  </si>
+  <si>
+    <t>Which of these DID NOT play baseball for the Baltimore Orioles ?</t>
+  </si>
+  <si>
+    <t>Which of these are NOT actual Elvis Presley song titles?</t>
+  </si>
+  <si>
+    <t>Which are FAKE song titles from Disney's "Frozen" movies?</t>
+  </si>
+  <si>
+    <t>Which of these were NOT actual dinosaurs?</t>
+  </si>
+  <si>
+    <t>final_C</t>
+  </si>
+  <si>
+    <t>Starts with "W".</t>
+  </si>
+  <si>
+    <t>Planets</t>
+  </si>
+  <si>
+    <t>Named after a Greek god (not Roman)</t>
+  </si>
+  <si>
+    <t>Its name sparks bathroom humor.</t>
+  </si>
+  <si>
+    <t>Rotates on its side, not its axis.</t>
+  </si>
+  <si>
+    <t>It's a shade of blue.</t>
+  </si>
+  <si>
+    <t>Uranus</t>
+  </si>
+  <si>
+    <t>Venus</t>
+  </si>
+  <si>
+    <t>Planet X</t>
+  </si>
+  <si>
+    <t>Pluto</t>
+  </si>
+  <si>
+    <t>Neptune</t>
+  </si>
+  <si>
+    <t>Earth 2</t>
+  </si>
+  <si>
+    <t>Mars</t>
+  </si>
+  <si>
+    <t>Saturn</t>
+  </si>
+  <si>
+    <t>Mercury</t>
+  </si>
+  <si>
+    <t>Planet Nine</t>
+  </si>
+  <si>
+    <t>Tatooine</t>
+  </si>
+  <si>
+    <t>Cybertron</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1315,8 +1565,20 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1359,8 +1621,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1537,11 +1804,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1816,6 +2092,12 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2190,7 +2472,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="73" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="H1" s="73" t="s">
         <v>6</v>
@@ -2226,7 +2508,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C2" s="73">
         <v>10</v>
@@ -2327,7 +2609,7 @@
       </c>
       <c r="F4" s="73"/>
       <c r="G4" s="77" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="H4" s="73">
         <v>5</v>
@@ -2580,7 +2862,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C10" s="73">
         <v>10</v>
@@ -2632,7 +2914,7 @@
       <c r="E11" s="73"/>
       <c r="F11" s="73"/>
       <c r="G11" s="77" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="H11" s="73">
         <v>9</v>
@@ -2659,7 +2941,7 @@
         <v>165</v>
       </c>
       <c r="P11" s="81" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="Q11" s="73"/>
     </row>
@@ -2712,10 +2994,10 @@
     </row>
     <row r="13" spans="1:17" ht="17">
       <c r="A13" s="73" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C13" s="73">
         <v>1</v>
@@ -2749,16 +3031,16 @@
         <v>12</v>
       </c>
       <c r="P13" s="81" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="Q13" s="73"/>
     </row>
     <row r="14" spans="1:17" ht="17">
       <c r="A14" s="73" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B14" s="76" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C14" s="73">
         <v>10</v>
@@ -2771,7 +3053,7 @@
       </c>
       <c r="F14" s="73"/>
       <c r="G14" s="77" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="H14" s="73">
         <v>1</v>
@@ -2796,16 +3078,16 @@
         <v>110</v>
       </c>
       <c r="P14" s="81" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="Q14" s="73"/>
     </row>
     <row r="15" spans="1:17" ht="17">
       <c r="A15" s="73" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C15" s="73">
         <v>5</v>
@@ -2839,16 +3121,16 @@
         <v>27</v>
       </c>
       <c r="P15" s="81" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="Q15" s="73"/>
     </row>
     <row r="16" spans="1:17" ht="17">
       <c r="A16" s="73" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C16" s="73">
         <v>10</v>
@@ -2861,7 +3143,7 @@
       </c>
       <c r="F16" s="73"/>
       <c r="G16" s="77" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="H16" s="73">
         <v>1</v>
@@ -2886,16 +3168,16 @@
         <v>42</v>
       </c>
       <c r="P16" s="81" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="Q16" s="73"/>
     </row>
     <row r="17" spans="1:17" ht="17">
       <c r="A17" s="73" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C17" s="73">
         <v>10</v>
@@ -2908,7 +3190,7 @@
       </c>
       <c r="F17" s="73"/>
       <c r="G17" s="77" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="H17" s="73">
         <v>1</v>
@@ -2933,16 +3215,16 @@
         <v>93</v>
       </c>
       <c r="P17" s="81" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="Q17" s="73"/>
     </row>
     <row r="18" spans="1:17" ht="17">
       <c r="A18" s="73" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B18" s="76" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="C18" s="73">
         <v>50</v>
@@ -2978,16 +3260,16 @@
         <v>435</v>
       </c>
       <c r="P18" s="81" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="Q18" s="73"/>
     </row>
     <row r="19" spans="1:17" ht="34">
       <c r="A19" s="73" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B19" s="76" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C19" s="73">
         <v>50</v>
@@ -3023,15 +3305,15 @@
         <v>100</v>
       </c>
       <c r="P19" s="81" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="17">
       <c r="A20" s="73" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C20" s="73">
         <v>1</v>
@@ -3065,15 +3347,15 @@
         <v>3</v>
       </c>
       <c r="P20" s="81" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="17">
       <c r="A21" s="73" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B21" s="76" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C21" s="73">
         <v>1</v>
@@ -3107,15 +3389,15 @@
         <v>3</v>
       </c>
       <c r="P21" s="81" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="17">
       <c r="A22" s="73" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B22" s="76" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C22" s="73">
         <v>1</v>
@@ -3149,15 +3431,15 @@
         <v>1</v>
       </c>
       <c r="P22" s="81" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="34">
       <c r="A23" s="73" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B23" s="76" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C23" s="73">
         <v>10</v>
@@ -3190,15 +3472,15 @@
         <v>10</v>
       </c>
       <c r="P23" s="81" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="34">
       <c r="A24" s="73" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C24" s="73">
         <v>5</v>
@@ -3228,15 +3510,15 @@
         <v>27</v>
       </c>
       <c r="P24" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="17">
       <c r="A25" s="73" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C25" s="73">
         <v>10</v>
@@ -3248,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="75" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="H25" s="73">
         <v>1</v>
@@ -3272,15 +3554,15 @@
         <v>3</v>
       </c>
       <c r="P25" s="81" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="17">
       <c r="A26" s="73" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="C26" s="73">
         <v>10</v>
@@ -3313,15 +3595,15 @@
         <v>1891</v>
       </c>
       <c r="P26" s="81" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="17">
       <c r="A27" s="73" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="C27" s="73">
         <v>10</v>
@@ -3354,15 +3636,15 @@
         <v>62</v>
       </c>
       <c r="P27" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="17">
       <c r="A28" s="73" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C28" s="73">
         <v>10</v>
@@ -3395,15 +3677,15 @@
         <v>2</v>
       </c>
       <c r="P28" s="81" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="17">
       <c r="A29" s="73" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="C29" s="73">
         <v>10</v>
@@ -3436,7 +3718,7 @@
         <v>1943</v>
       </c>
       <c r="P29" s="81" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -3579,7 +3861,7 @@
         <v>61</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="G4" t="s">
         <v>72</v>
@@ -3660,10 +3942,10 @@
     </row>
     <row r="7" spans="1:13" ht="51">
       <c r="A7" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
@@ -3675,10 +3957,10 @@
         <v>61</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="G7" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -3692,10 +3974,10 @@
     </row>
     <row r="8" spans="1:13" ht="51">
       <c r="A8" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B8" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="C8" t="s">
         <v>59</v>
@@ -3707,10 +3989,10 @@
         <v>61</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G8" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="H8">
         <v>9</v>
@@ -3754,15 +4036,15 @@
         <v>89</v>
       </c>
       <c r="M9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="85">
       <c r="A10" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B10" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C10" t="s">
         <v>85</v>
@@ -3783,21 +4065,21 @@
         <v>10</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="M10" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="85">
       <c r="A11" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B11" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C11" t="s">
         <v>85</v>
@@ -3818,13 +4100,13 @@
         <v>10</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="M11" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -3990,985 +4272,985 @@
         <v>123</v>
       </c>
       <c r="B2" s="27" t="s">
+        <v>453</v>
+      </c>
+      <c r="C2" s="90" t="s">
         <v>124</v>
-      </c>
-      <c r="C2" s="90" t="s">
-        <v>125</v>
       </c>
       <c r="D2" s="91">
         <v>20</v>
       </c>
       <c r="E2" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="30" t="s">
+      <c r="H2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="H2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="30" t="s">
+      <c r="J2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="J2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" s="30" t="s">
+      <c r="L2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="L2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" s="30" t="s">
+      <c r="N2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="N2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" s="30" t="s">
+      <c r="P2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="P2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="30" t="s">
+      <c r="R2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="T2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="R2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S2" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="T2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U2" s="31" t="s">
+      <c r="V2" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="V2" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W2" s="31" t="s">
+      <c r="X2" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="X2" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="31" t="s">
+      <c r="Z2" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="Z2" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="33" t="s">
+      <c r="AB2" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="57" t="s">
+        <v>333</v>
+      </c>
+      <c r="AD2" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="AF2" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="AB2" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="57" t="s">
-        <v>341</v>
-      </c>
-      <c r="AD2" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="57" t="s">
-        <v>198</v>
-      </c>
-      <c r="AF2" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="27" t="s">
+      <c r="AJ2" s="39" t="s">
         <v>137</v>
-      </c>
-      <c r="AJ2" s="39" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:36" s="40" customFormat="1" ht="27">
       <c r="A3" s="55" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>140</v>
+        <v>454</v>
       </c>
       <c r="C3" s="90" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D3" s="91">
         <v>20</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F3" s="29" t="b">
         <v>1</v>
       </c>
       <c r="G3" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="J3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="H3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="30" t="s">
+      <c r="L3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="J3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" s="30" t="s">
+      <c r="N3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="L3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="30" t="s">
+      <c r="P3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="R3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="T3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="N3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" s="30" t="s">
+      <c r="V3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="X3" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="Z3" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="P3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="R3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" s="30" t="s">
-        <v>199</v>
-      </c>
-      <c r="T3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U3" s="33" t="s">
+      <c r="AB3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="V3" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W3" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="X3" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="Z3" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="33" t="s">
+      <c r="AD3" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="AB3" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="36" t="s">
+      <c r="AF3" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="AD3" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="36" t="s">
+      <c r="AJ3" s="39" t="s">
         <v>149</v>
-      </c>
-      <c r="AF3" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH3" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI3" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="AJ3" s="39" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:36" s="40" customFormat="1" ht="34">
       <c r="A4" s="55" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>194</v>
+        <v>455</v>
       </c>
       <c r="C4" s="90" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D4" s="91">
         <v>20</v>
       </c>
       <c r="E4" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="H4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="F4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="30" t="s">
+      <c r="J4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="H4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="30" t="s">
+      <c r="L4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="J4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" s="30" t="s">
+      <c r="N4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="L4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" s="30" t="s">
+      <c r="P4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="N4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="30" t="s">
+      <c r="R4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="T4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="P4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="30" t="s">
+      <c r="V4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="R4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S4" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="T4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U4" s="33" t="s">
+      <c r="X4" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="V4" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="31" t="s">
+      <c r="Z4" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="X4" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="31" t="s">
+      <c r="AB4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD4" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="AF4" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="Z4" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="33" t="s">
+      <c r="AJ4" s="39" t="s">
         <v>163</v>
-      </c>
-      <c r="AB4" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="36" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD4" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="36" t="s">
-        <v>202</v>
-      </c>
-      <c r="AF4" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI4" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="AJ4" s="39" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:36" s="40" customFormat="1" ht="34">
       <c r="A5" s="55" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>197</v>
+        <v>456</v>
       </c>
       <c r="C5" s="90" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D5" s="91">
         <v>20</v>
       </c>
       <c r="E5" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="F5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="H5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="J5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="F5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="30" t="s">
+      <c r="L5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="H5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="J5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="30" t="s">
+      <c r="N5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="P5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="L5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="30" t="s">
+      <c r="R5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="T5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="N5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="P5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="30" t="s">
+      <c r="V5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="R5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="T5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U5" s="33" t="s">
+      <c r="X5" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z5" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="V5" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" s="31" t="s">
+      <c r="AB5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="AD5" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="X5" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="Z5" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="33" t="s">
+      <c r="AF5" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="AB5" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="36" t="s">
-        <v>205</v>
-      </c>
-      <c r="AD5" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="36" t="s">
+      <c r="AJ5" s="39" t="s">
         <v>175</v>
-      </c>
-      <c r="AF5" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="AJ5" s="39" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:36" s="26" customFormat="1" ht="27">
       <c r="A6" s="56" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>179</v>
+        <v>457</v>
       </c>
       <c r="C6" s="92" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D6" s="93">
         <v>20</v>
       </c>
       <c r="E6" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="H6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="J6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="F6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="16" t="s">
+      <c r="L6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="N6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="H6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="16" t="s">
+      <c r="P6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="J6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="16" t="s">
+      <c r="R6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="T6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="L6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="N6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="16" t="s">
+      <c r="V6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="P6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="16" t="s">
+      <c r="X6" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="R6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="T6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" s="19" t="s">
+      <c r="Z6" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="AB6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="V6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="17" t="s">
+      <c r="AD6" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="X6" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="17" t="s">
+      <c r="AF6" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="Z6" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="AB6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="22" t="s">
+      <c r="AJ6" s="25" t="s">
         <v>189</v>
-      </c>
-      <c r="AD6" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="AF6" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="AJ6" s="25" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:36" s="39" customFormat="1" ht="34">
       <c r="A7" s="55" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>255</v>
+        <v>458</v>
       </c>
       <c r="C7" s="92" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D7" s="93">
         <v>20</v>
       </c>
       <c r="E7" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="F7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="H7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="J7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="L7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="N7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="P7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="R7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="T7" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="V7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="X7" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="Z7" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="F7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="30" t="s">
+      <c r="AB7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="36" t="s">
+        <v>257</v>
+      </c>
+      <c r="AD7" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="AF7" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="AJ7" s="39" t="s">
         <v>265</v>
-      </c>
-      <c r="H7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="J7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="L7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="N7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="30" t="s">
-        <v>259</v>
-      </c>
-      <c r="P7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="R7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="T7" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="V7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="X7" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="31" t="s">
-        <v>269</v>
-      </c>
-      <c r="Z7" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="33" t="s">
-        <v>262</v>
-      </c>
-      <c r="AB7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="AD7" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="36" t="s">
-        <v>266</v>
-      </c>
-      <c r="AF7" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="AJ7" s="39" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:36" s="39" customFormat="1" ht="34">
       <c r="A8" s="55" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>279</v>
+        <v>459</v>
       </c>
       <c r="C8" s="92" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D8" s="93">
         <v>20</v>
       </c>
       <c r="E8" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="F8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="H8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="J8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="30" t="s">
+        <v>277</v>
+      </c>
+      <c r="L8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="30" t="s">
+        <v>278</v>
+      </c>
+      <c r="N8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="P8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="R8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="F8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="30" t="s">
+      <c r="T8" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="33" t="s">
         <v>282</v>
       </c>
-      <c r="H8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="30" t="s">
+      <c r="V8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="J8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="30" t="s">
+      <c r="X8" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="Z8" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="33" t="s">
         <v>284</v>
       </c>
-      <c r="L8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="30" t="s">
+      <c r="AB8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="36" t="s">
         <v>285</v>
       </c>
-      <c r="N8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="30" t="s">
+      <c r="AD8" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="36" t="s">
         <v>286</v>
       </c>
-      <c r="P8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="30" t="s">
+      <c r="AF8" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="AJ8" s="39" t="s">
         <v>287</v>
-      </c>
-      <c r="R8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S8" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="T8" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="V8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="X8" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="31" t="s">
-        <v>296</v>
-      </c>
-      <c r="Z8" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="AB8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="36" t="s">
-        <v>292</v>
-      </c>
-      <c r="AD8" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="36" t="s">
-        <v>293</v>
-      </c>
-      <c r="AF8" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH8" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="AJ8" s="39" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:36" s="85" customFormat="1" ht="34">
       <c r="A9" s="87" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>368</v>
+        <v>460</v>
       </c>
       <c r="C9" s="94" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D9" s="93">
         <v>20</v>
       </c>
       <c r="E9" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="F9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="H9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="J9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="L9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="N9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="P9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="F9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="28" t="s">
+      <c r="R9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="H9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="28" t="s">
+      <c r="T9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="V9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="J9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="28" t="s">
+      <c r="X9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="L9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="28" t="s">
+      <c r="Z9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="N9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="28" t="s">
+      <c r="AB9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="P9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="28" t="s">
+      <c r="AD9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="AF9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="AJ9" s="39" t="s">
         <v>307</v>
-      </c>
-      <c r="R9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" s="28" t="s">
-        <v>308</v>
-      </c>
-      <c r="T9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U9" s="33" t="s">
-        <v>306</v>
-      </c>
-      <c r="V9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="X9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="Z9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="33" t="s">
-        <v>312</v>
-      </c>
-      <c r="AD9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="33" t="s">
-        <v>313</v>
-      </c>
-      <c r="AF9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH9" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI9" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="AJ9" s="39" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:36" s="40" customFormat="1" ht="17">
       <c r="A10" s="82" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>330</v>
+        <v>461</v>
       </c>
       <c r="C10" s="95"/>
       <c r="D10" s="96"/>
       <c r="E10" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="F10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="H10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="J10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="L10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="N10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="46" t="s">
+        <v>321</v>
+      </c>
+      <c r="P10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="R10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="T10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="49" t="s">
+        <v>322</v>
+      </c>
+      <c r="V10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="47" t="s">
+        <v>323</v>
+      </c>
+      <c r="X10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="47" t="s">
+        <v>325</v>
+      </c>
+      <c r="Z10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="49" t="s">
+        <v>318</v>
+      </c>
+      <c r="AB10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="52" t="s">
         <v>317</v>
       </c>
-      <c r="F10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="46" t="s">
-        <v>318</v>
-      </c>
-      <c r="H10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="46" t="s">
+      <c r="AD10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="52" t="s">
+        <v>324</v>
+      </c>
+      <c r="AF10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="27" t="s">
+        <v>320</v>
+      </c>
+      <c r="AJ10" s="39" t="s">
         <v>319</v>
-      </c>
-      <c r="J10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="46" t="s">
-        <v>320</v>
-      </c>
-      <c r="L10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="46" t="s">
-        <v>321</v>
-      </c>
-      <c r="N10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" s="46" t="s">
-        <v>328</v>
-      </c>
-      <c r="P10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="46" t="s">
-        <v>322</v>
-      </c>
-      <c r="R10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10" s="46" t="s">
-        <v>323</v>
-      </c>
-      <c r="T10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="V10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" s="47" t="s">
-        <v>331</v>
-      </c>
-      <c r="X10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="47" t="s">
-        <v>333</v>
-      </c>
-      <c r="Z10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="49" t="s">
-        <v>325</v>
-      </c>
-      <c r="AB10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="52" t="s">
-        <v>324</v>
-      </c>
-      <c r="AD10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="52" t="s">
-        <v>332</v>
-      </c>
-      <c r="AF10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="27" t="s">
-        <v>327</v>
-      </c>
-      <c r="AJ10" s="39" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:36" s="40" customFormat="1">
@@ -5316,39 +5598,39 @@
         <v>55</v>
       </c>
       <c r="D1" s="78" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E1" s="78" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F1" s="78" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G1" s="78" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H1" s="78" t="s">
         <v>14</v>
       </c>
       <c r="I1" s="80" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="79" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C2" s="79" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D2" s="79" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E2" s="79" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F2" s="79">
         <v>90</v>
@@ -5357,27 +5639,27 @@
         <v>1</v>
       </c>
       <c r="H2" s="79" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B3" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C3" s="79" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D3" s="79" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E3" s="79" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -5386,27 +5668,27 @@
         <v>1</v>
       </c>
       <c r="H3" s="79" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="I3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C4" s="79" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D4" s="79" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E4" s="79" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F4">
         <v>90</v>
@@ -5415,27 +5697,27 @@
         <v>1</v>
       </c>
       <c r="H4" s="79" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="I4" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B5" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C5" s="79" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D5" s="79" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E5" s="79" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F5">
         <v>90</v>
@@ -5444,27 +5726,27 @@
         <v>1</v>
       </c>
       <c r="H5" s="79" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="I5" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B6" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C6" s="79" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="D6" s="79" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E6" s="79" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F6">
         <v>80</v>
@@ -5473,10 +5755,314 @@
         <v>1.4</v>
       </c>
       <c r="H6" s="79" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="I6" t="s">
-        <v>383</v>
+        <v>374</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BCF57C0-509A-A249-9E2F-95FCB3F78081}">
+  <dimension ref="A1:W4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="18.1640625" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="19.5" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="30">
+      <c r="A1" s="99" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="99" t="s">
+        <v>389</v>
+      </c>
+      <c r="D1" s="99" t="s">
+        <v>390</v>
+      </c>
+      <c r="E1" s="99" t="s">
+        <v>391</v>
+      </c>
+      <c r="F1" s="99" t="s">
+        <v>392</v>
+      </c>
+      <c r="G1" s="99" t="s">
+        <v>393</v>
+      </c>
+      <c r="H1" s="99" t="s">
+        <v>394</v>
+      </c>
+      <c r="I1" s="99" t="s">
+        <v>395</v>
+      </c>
+      <c r="J1" s="99" t="s">
+        <v>396</v>
+      </c>
+      <c r="K1" s="99" t="s">
+        <v>397</v>
+      </c>
+      <c r="L1" s="99" t="s">
+        <v>398</v>
+      </c>
+      <c r="M1" s="99" t="s">
+        <v>399</v>
+      </c>
+      <c r="N1" s="99" t="s">
+        <v>400</v>
+      </c>
+      <c r="O1" s="99" t="s">
+        <v>401</v>
+      </c>
+      <c r="P1" s="99" t="s">
+        <v>402</v>
+      </c>
+      <c r="Q1" s="99" t="s">
+        <v>403</v>
+      </c>
+      <c r="R1" s="99" t="s">
+        <v>404</v>
+      </c>
+      <c r="S1" s="99" t="s">
+        <v>405</v>
+      </c>
+      <c r="T1" s="99" t="s">
+        <v>406</v>
+      </c>
+      <c r="U1" s="99" t="s">
+        <v>407</v>
+      </c>
+      <c r="V1" s="99" t="s">
+        <v>408</v>
+      </c>
+      <c r="W1" s="99" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="45">
+      <c r="A2" s="100" t="s">
+        <v>410</v>
+      </c>
+      <c r="B2" s="100" t="s">
+        <v>411</v>
+      </c>
+      <c r="C2" s="100" t="s">
+        <v>412</v>
+      </c>
+      <c r="D2" s="100" t="s">
+        <v>428</v>
+      </c>
+      <c r="E2" s="100" t="s">
+        <v>426</v>
+      </c>
+      <c r="F2" s="100" t="s">
+        <v>427</v>
+      </c>
+      <c r="G2" s="100" t="s">
+        <v>425</v>
+      </c>
+      <c r="H2" s="100" t="s">
+        <v>412</v>
+      </c>
+      <c r="I2" s="100" t="s">
+        <v>413</v>
+      </c>
+      <c r="J2" s="100" t="s">
+        <v>414</v>
+      </c>
+      <c r="K2" s="100" t="s">
+        <v>415</v>
+      </c>
+      <c r="L2" s="100" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2" s="100" t="s">
+        <v>416</v>
+      </c>
+      <c r="N2" s="100" t="s">
+        <v>429</v>
+      </c>
+      <c r="O2" s="100" t="s">
+        <v>417</v>
+      </c>
+      <c r="P2" s="100" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q2" s="100" t="s">
+        <v>419</v>
+      </c>
+      <c r="R2" s="100" t="s">
+        <v>420</v>
+      </c>
+      <c r="S2" s="100" t="s">
+        <v>421</v>
+      </c>
+      <c r="T2" s="100" t="s">
+        <v>422</v>
+      </c>
+      <c r="U2" s="100" t="s">
+        <v>423</v>
+      </c>
+      <c r="V2" s="100" t="s">
+        <v>424</v>
+      </c>
+      <c r="W2" s="100" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="34">
+      <c r="A3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="34">
+      <c r="A4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B4" t="s">
+        <v>464</v>
+      </c>
+      <c r="C4" t="s">
+        <v>469</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84D6668-7684-3946-AD41-7449991F6EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9248921-FAD9-C943-BAB6-D9048BE005B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9880" yWindow="9200" windowWidth="43080" windowHeight="15640" activeTab="4" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="9880" yWindow="9200" windowWidth="43080" windowHeight="15640" activeTab="2" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -438,9 +438,6 @@
     <t>Gordon Brown</t>
   </si>
   <si>
-    <t>James Merryweather</t>
-  </si>
-  <si>
     <t>Andrew Lloyd Webber</t>
   </si>
   <si>
@@ -1483,6 +1480,9 @@
   </si>
   <si>
     <t>Cybertron</t>
+  </si>
+  <si>
+    <t>Flora Fauna Merryweather</t>
   </si>
 </sst>
 </file>
@@ -2472,7 +2472,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="73" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1" s="73" t="s">
         <v>6</v>
@@ -2508,7 +2508,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C2" s="73">
         <v>10</v>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="F4" s="73"/>
       <c r="G4" s="77" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H4" s="73">
         <v>5</v>
@@ -2862,7 +2862,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C10" s="73">
         <v>10</v>
@@ -2914,7 +2914,7 @@
       <c r="E11" s="73"/>
       <c r="F11" s="73"/>
       <c r="G11" s="77" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H11" s="73">
         <v>9</v>
@@ -2941,7 +2941,7 @@
         <v>165</v>
       </c>
       <c r="P11" s="81" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q11" s="73"/>
     </row>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="13" spans="1:17" ht="17">
       <c r="A13" s="73" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C13" s="73">
         <v>1</v>
@@ -3031,16 +3031,16 @@
         <v>12</v>
       </c>
       <c r="P13" s="81" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q13" s="73"/>
     </row>
     <row r="14" spans="1:17" ht="17">
       <c r="A14" s="73" t="s">
+        <v>245</v>
+      </c>
+      <c r="B14" s="76" t="s">
         <v>246</v>
-      </c>
-      <c r="B14" s="76" t="s">
-        <v>247</v>
       </c>
       <c r="C14" s="73">
         <v>10</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="F14" s="73"/>
       <c r="G14" s="77" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H14" s="73">
         <v>1</v>
@@ -3078,16 +3078,16 @@
         <v>110</v>
       </c>
       <c r="P14" s="81" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q14" s="73"/>
     </row>
     <row r="15" spans="1:17" ht="17">
       <c r="A15" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C15" s="73">
         <v>5</v>
@@ -3121,16 +3121,16 @@
         <v>27</v>
       </c>
       <c r="P15" s="81" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q15" s="73"/>
     </row>
     <row r="16" spans="1:17" ht="17">
       <c r="A16" s="73" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C16" s="73">
         <v>10</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="F16" s="73"/>
       <c r="G16" s="77" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H16" s="73">
         <v>1</v>
@@ -3168,16 +3168,16 @@
         <v>42</v>
       </c>
       <c r="P16" s="81" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q16" s="73"/>
     </row>
     <row r="17" spans="1:17" ht="17">
       <c r="A17" s="73" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C17" s="73">
         <v>10</v>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F17" s="73"/>
       <c r="G17" s="77" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H17" s="73">
         <v>1</v>
@@ -3215,16 +3215,16 @@
         <v>93</v>
       </c>
       <c r="P17" s="81" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q17" s="73"/>
     </row>
     <row r="18" spans="1:17" ht="17">
       <c r="A18" s="73" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B18" s="76" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C18" s="73">
         <v>50</v>
@@ -3260,16 +3260,16 @@
         <v>435</v>
       </c>
       <c r="P18" s="81" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q18" s="73"/>
     </row>
     <row r="19" spans="1:17" ht="34">
       <c r="A19" s="73" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B19" s="76" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C19" s="73">
         <v>50</v>
@@ -3305,15 +3305,15 @@
         <v>100</v>
       </c>
       <c r="P19" s="81" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="17">
       <c r="A20" s="73" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C20" s="73">
         <v>1</v>
@@ -3347,15 +3347,15 @@
         <v>3</v>
       </c>
       <c r="P20" s="81" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="17">
       <c r="A21" s="73" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B21" s="76" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C21" s="73">
         <v>1</v>
@@ -3389,15 +3389,15 @@
         <v>3</v>
       </c>
       <c r="P21" s="81" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="17">
       <c r="A22" s="73" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B22" s="76" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C22" s="73">
         <v>1</v>
@@ -3431,15 +3431,15 @@
         <v>1</v>
       </c>
       <c r="P22" s="81" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="34">
       <c r="A23" s="73" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B23" s="76" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C23" s="73">
         <v>10</v>
@@ -3472,15 +3472,15 @@
         <v>10</v>
       </c>
       <c r="P23" s="81" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="34">
       <c r="A24" s="73" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C24" s="73">
         <v>5</v>
@@ -3510,15 +3510,15 @@
         <v>27</v>
       </c>
       <c r="P24" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="17">
       <c r="A25" s="73" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C25" s="73">
         <v>10</v>
@@ -3530,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H25" s="73">
         <v>1</v>
@@ -3554,15 +3554,15 @@
         <v>3</v>
       </c>
       <c r="P25" s="81" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="17">
       <c r="A26" s="73" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C26" s="73">
         <v>10</v>
@@ -3595,15 +3595,15 @@
         <v>1891</v>
       </c>
       <c r="P26" s="81" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="17">
       <c r="A27" s="73" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C27" s="73">
         <v>10</v>
@@ -3636,15 +3636,15 @@
         <v>62</v>
       </c>
       <c r="P27" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="17">
       <c r="A28" s="73" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C28" s="73">
         <v>10</v>
@@ -3677,15 +3677,15 @@
         <v>2</v>
       </c>
       <c r="P28" s="81" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="17">
       <c r="A29" s="73" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C29" s="73">
         <v>10</v>
@@ -3718,7 +3718,7 @@
         <v>1943</v>
       </c>
       <c r="P29" s="81" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -3861,7 +3861,7 @@
         <v>61</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G4" t="s">
         <v>72</v>
@@ -3942,10 +3942,10 @@
     </row>
     <row r="7" spans="1:13" ht="51">
       <c r="A7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B7" t="s">
         <v>326</v>
-      </c>
-      <c r="B7" t="s">
-        <v>327</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
@@ -3957,10 +3957,10 @@
         <v>61</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -3974,10 +3974,10 @@
     </row>
     <row r="8" spans="1:13" ht="51">
       <c r="A8" t="s">
+        <v>333</v>
+      </c>
+      <c r="B8" t="s">
         <v>334</v>
-      </c>
-      <c r="B8" t="s">
-        <v>335</v>
       </c>
       <c r="C8" t="s">
         <v>59</v>
@@ -3989,10 +3989,10 @@
         <v>61</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H8">
         <v>9</v>
@@ -4036,15 +4036,15 @@
         <v>89</v>
       </c>
       <c r="M9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="85">
       <c r="A10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C10" t="s">
         <v>85</v>
@@ -4065,21 +4065,21 @@
         <v>10</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="85">
       <c r="A11" t="s">
+        <v>383</v>
+      </c>
+      <c r="B11" t="s">
         <v>384</v>
-      </c>
-      <c r="B11" t="s">
-        <v>385</v>
       </c>
       <c r="C11" t="s">
         <v>85</v>
@@ -4100,13 +4100,13 @@
         <v>10</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="M11" t="s">
         <v>387</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="M11" t="s">
-        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -4272,7 +4272,7 @@
         <v>123</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C2" s="90" t="s">
         <v>124</v>
@@ -4323,66 +4323,66 @@
         <v>1</v>
       </c>
       <c r="S2" s="28" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T2" s="29" t="b">
         <v>1</v>
       </c>
       <c r="U2" s="31" t="s">
+        <v>480</v>
+      </c>
+      <c r="V2" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="V2" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W2" s="31" t="s">
+      <c r="X2" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="X2" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="31" t="s">
+      <c r="Z2" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="Z2" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="33" t="s">
+      <c r="AB2" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="57" t="s">
+        <v>332</v>
+      </c>
+      <c r="AD2" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF2" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="AB2" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="57" t="s">
-        <v>333</v>
-      </c>
-      <c r="AD2" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="AF2" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="27" t="s">
+      <c r="AJ2" s="39" t="s">
         <v>136</v>
-      </c>
-      <c r="AJ2" s="39" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:36" s="40" customFormat="1" ht="27">
       <c r="A3" s="55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C3" s="90" t="s">
         <v>124</v>
@@ -4391,108 +4391,108 @@
         <v>20</v>
       </c>
       <c r="E3" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="F3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="J3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="N3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="P3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="F3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="H3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="J3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="L3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="N3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" s="30" t="s">
+      <c r="R3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="T3" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="P3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="R3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="T3" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U3" s="33" t="s">
+      <c r="V3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" s="31" t="s">
+        <v>203</v>
+      </c>
+      <c r="X3" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="Z3" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="V3" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W3" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="X3" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="31" t="s">
-        <v>205</v>
-      </c>
-      <c r="Z3" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="33" t="s">
+      <c r="AB3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="AB3" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="36" t="s">
+      <c r="AD3" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="AD3" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="36" t="s">
+      <c r="AF3" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="AF3" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH3" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI3" s="27" t="s">
+      <c r="AJ3" s="39" t="s">
         <v>148</v>
-      </c>
-      <c r="AJ3" s="39" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:36" s="40" customFormat="1" ht="34">
       <c r="A4" s="55" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C4" s="90" t="s">
         <v>124</v>
@@ -4501,108 +4501,108 @@
         <v>20</v>
       </c>
       <c r="E4" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="F4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="30" t="s">
+      <c r="H4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="30" t="s">
+      <c r="J4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="J4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" s="30" t="s">
+      <c r="L4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="L4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" s="30" t="s">
+      <c r="N4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="N4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="30" t="s">
+      <c r="P4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="P4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="30" t="s">
+      <c r="R4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="T4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="R4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S4" s="30" t="s">
+      <c r="V4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="X4" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z4" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="36" t="s">
+        <v>202</v>
+      </c>
+      <c r="AD4" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="T4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U4" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="V4" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="X4" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="Z4" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="33" t="s">
+      <c r="AF4" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="AB4" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="36" t="s">
-        <v>203</v>
-      </c>
-      <c r="AD4" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="AF4" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI4" s="27" t="s">
+      <c r="AJ4" s="39" t="s">
         <v>162</v>
-      </c>
-      <c r="AJ4" s="39" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:36" s="40" customFormat="1" ht="34">
       <c r="A5" s="55" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C5" s="90" t="s">
         <v>124</v>
@@ -4611,108 +4611,108 @@
         <v>20</v>
       </c>
       <c r="E5" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="F5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="F5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="30" t="s">
+      <c r="H5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="J5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="H5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="30" t="s">
+      <c r="L5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="N5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="J5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="L5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="30" t="s">
+      <c r="P5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="N5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="30" t="s">
-        <v>243</v>
-      </c>
-      <c r="P5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="30" t="s">
+      <c r="R5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="T5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="R5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" s="30" t="s">
+      <c r="V5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="X5" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="T5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U5" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="V5" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" s="31" t="s">
+      <c r="Z5" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="X5" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="31" t="s">
+      <c r="AB5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="36" t="s">
         <v>199</v>
       </c>
-      <c r="Z5" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="33" t="s">
+      <c r="AD5" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="36" t="s">
         <v>172</v>
       </c>
-      <c r="AB5" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="36" t="s">
-        <v>200</v>
-      </c>
-      <c r="AD5" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="36" t="s">
+      <c r="AF5" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="AF5" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="27" t="s">
+      <c r="AJ5" s="39" t="s">
         <v>174</v>
-      </c>
-      <c r="AJ5" s="39" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:36" s="26" customFormat="1" ht="27">
       <c r="A6" s="56" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C6" s="92" t="s">
         <v>124</v>
@@ -4721,108 +4721,108 @@
         <v>20</v>
       </c>
       <c r="E6" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="F6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="F6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="16" t="s">
+      <c r="H6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="H6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="16" t="s">
+      <c r="J6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="J6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="16" t="s">
+      <c r="L6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="N6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="L6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="N6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="16" t="s">
+      <c r="P6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="P6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="16" t="s">
+      <c r="R6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="T6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="R6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="T6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" s="19" t="s">
+      <c r="V6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="V6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="17" t="s">
+      <c r="X6" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="X6" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="17" t="s">
+      <c r="Z6" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="Z6" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="22" t="s">
+      <c r="AD6" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="AD6" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="22" t="s">
+      <c r="AF6" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="AF6" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="13" t="s">
+      <c r="AJ6" s="25" t="s">
         <v>188</v>
-      </c>
-      <c r="AJ6" s="25" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:36" s="39" customFormat="1" ht="34">
       <c r="A7" s="55" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C7" s="92" t="s">
         <v>124</v>
@@ -4831,108 +4831,108 @@
         <v>20</v>
       </c>
       <c r="E7" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="F7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="H7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="F7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="30" t="s">
+      <c r="J7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="L7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="N7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="P7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="R7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="T7" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="V7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="X7" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="31" t="s">
+        <v>262</v>
+      </c>
+      <c r="Z7" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="AB7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="AD7" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="36" t="s">
         <v>259</v>
       </c>
-      <c r="H7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="J7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="L7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="N7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="P7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="R7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="T7" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="33" t="s">
-        <v>262</v>
-      </c>
-      <c r="V7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="31" t="s">
-        <v>261</v>
-      </c>
-      <c r="X7" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="31" t="s">
+      <c r="AF7" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="Z7" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="AB7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="36" t="s">
-        <v>257</v>
-      </c>
-      <c r="AD7" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="AF7" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="27" t="s">
+      <c r="AJ7" s="39" t="s">
         <v>264</v>
-      </c>
-      <c r="AJ7" s="39" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:36" s="39" customFormat="1" ht="34">
       <c r="A8" s="55" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C8" s="92" t="s">
         <v>124</v>
@@ -4941,108 +4941,108 @@
         <v>20</v>
       </c>
       <c r="E8" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="F8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="30" t="s">
         <v>274</v>
       </c>
-      <c r="F8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="30" t="s">
+      <c r="H8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="30" t="s">
         <v>275</v>
       </c>
-      <c r="H8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="30" t="s">
+      <c r="J8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="J8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="30" t="s">
+      <c r="L8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="30" t="s">
         <v>277</v>
       </c>
-      <c r="L8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="30" t="s">
+      <c r="N8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="30" t="s">
         <v>278</v>
       </c>
-      <c r="N8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="30" t="s">
+      <c r="P8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="P8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="30" t="s">
+      <c r="R8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="R8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S8" s="30" t="s">
+      <c r="T8" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="33" t="s">
         <v>281</v>
       </c>
-      <c r="T8" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" s="33" t="s">
+      <c r="V8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" s="31" t="s">
         <v>282</v>
       </c>
-      <c r="V8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="31" t="s">
+      <c r="X8" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="Z8" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="33" t="s">
         <v>283</v>
       </c>
-      <c r="X8" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="31" t="s">
-        <v>289</v>
-      </c>
-      <c r="Z8" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="33" t="s">
+      <c r="AB8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="36" t="s">
         <v>284</v>
       </c>
-      <c r="AB8" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="36" t="s">
+      <c r="AD8" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="36" t="s">
         <v>285</v>
       </c>
-      <c r="AD8" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="36" t="s">
+      <c r="AF8" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="AJ8" s="39" t="s">
         <v>286</v>
-      </c>
-      <c r="AF8" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH8" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="27" t="s">
-        <v>288</v>
-      </c>
-      <c r="AJ8" s="39" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:36" s="85" customFormat="1" ht="34">
       <c r="A9" s="87" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C9" s="94" t="s">
         <v>124</v>
@@ -5051,206 +5051,206 @@
         <v>20</v>
       </c>
       <c r="E9" s="28" t="s">
+        <v>292</v>
+      </c>
+      <c r="F9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="28" t="s">
         <v>293</v>
       </c>
-      <c r="F9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="28" t="s">
+      <c r="H9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="H9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="28" t="s">
+      <c r="J9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="J9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="28" t="s">
+      <c r="L9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="28" t="s">
         <v>296</v>
       </c>
-      <c r="L9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="28" t="s">
+      <c r="N9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="28" t="s">
         <v>297</v>
       </c>
-      <c r="N9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="28" t="s">
+      <c r="P9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="R9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="T9" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="P9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="R9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" s="28" t="s">
+      <c r="V9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="T9" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U9" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="V9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="33" t="s">
+      <c r="X9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="X9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="33" t="s">
+      <c r="Z9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="Z9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="33" t="s">
+      <c r="AB9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="AB9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="33" t="s">
+      <c r="AD9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="AD9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="33" t="s">
+      <c r="AF9" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="AJ9" s="39" t="s">
         <v>306</v>
-      </c>
-      <c r="AF9" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH9" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI9" s="27" t="s">
-        <v>308</v>
-      </c>
-      <c r="AJ9" s="39" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:36" s="40" customFormat="1" ht="17">
       <c r="A10" s="82" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C10" s="95"/>
       <c r="D10" s="96"/>
       <c r="E10" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="F10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="46" t="s">
         <v>310</v>
       </c>
-      <c r="F10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="46" t="s">
+      <c r="H10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="46" t="s">
         <v>311</v>
       </c>
-      <c r="H10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="46" t="s">
+      <c r="J10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="46" t="s">
         <v>312</v>
       </c>
-      <c r="J10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="46" t="s">
+      <c r="L10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="46" t="s">
         <v>313</v>
       </c>
-      <c r="L10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="46" t="s">
+      <c r="N10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="46" t="s">
+        <v>320</v>
+      </c>
+      <c r="P10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="46" t="s">
         <v>314</v>
       </c>
-      <c r="N10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" s="46" t="s">
+      <c r="R10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="T10" s="83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="49" t="s">
         <v>321</v>
       </c>
-      <c r="P10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="46" t="s">
-        <v>315</v>
-      </c>
-      <c r="R10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10" s="46" t="s">
+      <c r="V10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="47" t="s">
+        <v>322</v>
+      </c>
+      <c r="X10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="47" t="s">
+        <v>324</v>
+      </c>
+      <c r="Z10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="49" t="s">
+        <v>317</v>
+      </c>
+      <c r="AB10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="52" t="s">
         <v>316</v>
       </c>
-      <c r="T10" s="83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10" s="49" t="s">
-        <v>322</v>
-      </c>
-      <c r="V10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" s="47" t="s">
+      <c r="AD10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="52" t="s">
         <v>323</v>
       </c>
-      <c r="X10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="47" t="s">
-        <v>325</v>
-      </c>
-      <c r="Z10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="49" t="s">
+      <c r="AF10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="27" t="s">
+        <v>319</v>
+      </c>
+      <c r="AJ10" s="39" t="s">
         <v>318</v>
-      </c>
-      <c r="AB10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="52" t="s">
-        <v>317</v>
-      </c>
-      <c r="AD10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="52" t="s">
-        <v>324</v>
-      </c>
-      <c r="AF10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="27" t="s">
-        <v>320</v>
-      </c>
-      <c r="AJ10" s="39" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:36" s="40" customFormat="1">
@@ -5598,39 +5598,39 @@
         <v>55</v>
       </c>
       <c r="D1" s="78" t="s">
+        <v>213</v>
+      </c>
+      <c r="E1" s="78" t="s">
         <v>214</v>
       </c>
-      <c r="E1" s="78" t="s">
+      <c r="F1" s="78" t="s">
         <v>215</v>
       </c>
-      <c r="F1" s="78" t="s">
-        <v>216</v>
-      </c>
       <c r="G1" s="78" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1" s="78" t="s">
         <v>14</v>
       </c>
       <c r="I1" s="80" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="79" t="s">
+        <v>216</v>
+      </c>
+      <c r="B2" s="79" t="s">
+        <v>379</v>
+      </c>
+      <c r="C2" s="79" t="s">
         <v>217</v>
       </c>
-      <c r="B2" s="79" t="s">
-        <v>380</v>
-      </c>
-      <c r="C2" s="79" t="s">
+      <c r="D2" s="79" t="s">
         <v>218</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="E2" s="79" t="s">
         <v>219</v>
-      </c>
-      <c r="E2" s="79" t="s">
-        <v>220</v>
       </c>
       <c r="F2" s="79">
         <v>90</v>
@@ -5639,27 +5639,27 @@
         <v>1</v>
       </c>
       <c r="H2" s="79" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C3" s="79" t="s">
         <v>224</v>
       </c>
-      <c r="B3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C3" s="79" t="s">
+      <c r="D3" s="79" t="s">
         <v>225</v>
       </c>
-      <c r="D3" s="79" t="s">
-        <v>226</v>
-      </c>
       <c r="E3" s="79" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -5668,27 +5668,27 @@
         <v>1</v>
       </c>
       <c r="H3" s="79" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B4" t="s">
         <v>229</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="79" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="79" t="s">
+      <c r="D4" s="79" t="s">
         <v>231</v>
       </c>
-      <c r="D4" s="79" t="s">
-        <v>232</v>
-      </c>
       <c r="E4" s="79" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F4">
         <v>90</v>
@@ -5697,27 +5697,27 @@
         <v>1</v>
       </c>
       <c r="H4" s="79" t="s">
+        <v>232</v>
+      </c>
+      <c r="I4" t="s">
         <v>233</v>
-      </c>
-      <c r="I4" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B5" t="s">
         <v>236</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" s="79" t="s">
         <v>237</v>
       </c>
-      <c r="C5" s="79" t="s">
+      <c r="D5" s="79" t="s">
         <v>238</v>
       </c>
-      <c r="D5" s="79" t="s">
-        <v>239</v>
-      </c>
       <c r="E5" s="79" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F5">
         <v>90</v>
@@ -5726,27 +5726,27 @@
         <v>1</v>
       </c>
       <c r="H5" s="79" t="s">
+        <v>239</v>
+      </c>
+      <c r="I5" t="s">
         <v>240</v>
-      </c>
-      <c r="I5" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
+        <v>368</v>
+      </c>
+      <c r="B6" t="s">
         <v>369</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="79" t="s">
         <v>370</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="D6" s="79" t="s">
         <v>371</v>
       </c>
-      <c r="D6" s="79" t="s">
-        <v>372</v>
-      </c>
       <c r="E6" s="79" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F6">
         <v>80</v>
@@ -5755,10 +5755,10 @@
         <v>1.4</v>
       </c>
       <c r="H6" s="79" t="s">
+        <v>372</v>
+      </c>
+      <c r="I6" t="s">
         <v>373</v>
-      </c>
-      <c r="I6" t="s">
-        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -5789,280 +5789,280 @@
         <v>122</v>
       </c>
       <c r="C1" s="99" t="s">
+        <v>388</v>
+      </c>
+      <c r="D1" s="99" t="s">
         <v>389</v>
       </c>
-      <c r="D1" s="99" t="s">
+      <c r="E1" s="99" t="s">
         <v>390</v>
       </c>
-      <c r="E1" s="99" t="s">
+      <c r="F1" s="99" t="s">
         <v>391</v>
       </c>
-      <c r="F1" s="99" t="s">
+      <c r="G1" s="99" t="s">
         <v>392</v>
       </c>
-      <c r="G1" s="99" t="s">
+      <c r="H1" s="99" t="s">
         <v>393</v>
       </c>
-      <c r="H1" s="99" t="s">
+      <c r="I1" s="99" t="s">
         <v>394</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="J1" s="99" t="s">
         <v>395</v>
       </c>
-      <c r="J1" s="99" t="s">
+      <c r="K1" s="99" t="s">
         <v>396</v>
       </c>
-      <c r="K1" s="99" t="s">
+      <c r="L1" s="99" t="s">
         <v>397</v>
       </c>
-      <c r="L1" s="99" t="s">
+      <c r="M1" s="99" t="s">
         <v>398</v>
       </c>
-      <c r="M1" s="99" t="s">
+      <c r="N1" s="99" t="s">
         <v>399</v>
       </c>
-      <c r="N1" s="99" t="s">
+      <c r="O1" s="99" t="s">
         <v>400</v>
       </c>
-      <c r="O1" s="99" t="s">
+      <c r="P1" s="99" t="s">
         <v>401</v>
       </c>
-      <c r="P1" s="99" t="s">
+      <c r="Q1" s="99" t="s">
         <v>402</v>
       </c>
-      <c r="Q1" s="99" t="s">
+      <c r="R1" s="99" t="s">
         <v>403</v>
       </c>
-      <c r="R1" s="99" t="s">
+      <c r="S1" s="99" t="s">
         <v>404</v>
       </c>
-      <c r="S1" s="99" t="s">
+      <c r="T1" s="99" t="s">
         <v>405</v>
       </c>
-      <c r="T1" s="99" t="s">
+      <c r="U1" s="99" t="s">
         <v>406</v>
       </c>
-      <c r="U1" s="99" t="s">
+      <c r="V1" s="99" t="s">
         <v>407</v>
       </c>
-      <c r="V1" s="99" t="s">
+      <c r="W1" s="99" t="s">
         <v>408</v>
-      </c>
-      <c r="W1" s="99" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="45">
       <c r="A2" s="100" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2" s="100" t="s">
         <v>410</v>
       </c>
-      <c r="B2" s="100" t="s">
+      <c r="C2" s="100" t="s">
         <v>411</v>
       </c>
-      <c r="C2" s="100" t="s">
+      <c r="D2" s="100" t="s">
+        <v>427</v>
+      </c>
+      <c r="E2" s="100" t="s">
+        <v>425</v>
+      </c>
+      <c r="F2" s="100" t="s">
+        <v>426</v>
+      </c>
+      <c r="G2" s="100" t="s">
+        <v>424</v>
+      </c>
+      <c r="H2" s="100" t="s">
+        <v>411</v>
+      </c>
+      <c r="I2" s="100" t="s">
         <v>412</v>
       </c>
-      <c r="D2" s="100" t="s">
+      <c r="J2" s="100" t="s">
+        <v>413</v>
+      </c>
+      <c r="K2" s="100" t="s">
+        <v>414</v>
+      </c>
+      <c r="L2" s="100" t="s">
+        <v>429</v>
+      </c>
+      <c r="M2" s="100" t="s">
+        <v>415</v>
+      </c>
+      <c r="N2" s="100" t="s">
         <v>428</v>
       </c>
-      <c r="E2" s="100" t="s">
-        <v>426</v>
-      </c>
-      <c r="F2" s="100" t="s">
-        <v>427</v>
-      </c>
-      <c r="G2" s="100" t="s">
-        <v>425</v>
-      </c>
-      <c r="H2" s="100" t="s">
-        <v>412</v>
-      </c>
-      <c r="I2" s="100" t="s">
-        <v>413</v>
-      </c>
-      <c r="J2" s="100" t="s">
-        <v>414</v>
-      </c>
-      <c r="K2" s="100" t="s">
-        <v>415</v>
-      </c>
-      <c r="L2" s="100" t="s">
+      <c r="O2" s="100" t="s">
+        <v>416</v>
+      </c>
+      <c r="P2" s="100" t="s">
+        <v>417</v>
+      </c>
+      <c r="Q2" s="100" t="s">
+        <v>418</v>
+      </c>
+      <c r="R2" s="100" t="s">
+        <v>419</v>
+      </c>
+      <c r="S2" s="100" t="s">
+        <v>420</v>
+      </c>
+      <c r="T2" s="100" t="s">
+        <v>421</v>
+      </c>
+      <c r="U2" s="100" t="s">
+        <v>422</v>
+      </c>
+      <c r="V2" s="100" t="s">
+        <v>423</v>
+      </c>
+      <c r="W2" s="100" t="s">
         <v>430</v>
-      </c>
-      <c r="M2" s="100" t="s">
-        <v>416</v>
-      </c>
-      <c r="N2" s="100" t="s">
-        <v>429</v>
-      </c>
-      <c r="O2" s="100" t="s">
-        <v>417</v>
-      </c>
-      <c r="P2" s="100" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q2" s="100" t="s">
-        <v>419</v>
-      </c>
-      <c r="R2" s="100" t="s">
-        <v>420</v>
-      </c>
-      <c r="S2" s="100" t="s">
-        <v>421</v>
-      </c>
-      <c r="T2" s="100" t="s">
-        <v>422</v>
-      </c>
-      <c r="U2" s="100" t="s">
-        <v>423</v>
-      </c>
-      <c r="V2" s="100" t="s">
-        <v>424</v>
-      </c>
-      <c r="W2" s="100" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="34">
       <c r="A3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C3" t="s">
         <v>432</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="C3" t="s">
-        <v>433</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="P3" s="1" t="s">
+      <c r="R3" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="Q3" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="34">
       <c r="A4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C4" t="s">
+        <v>468</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="K4" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q4" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="R4" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="T4" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="S4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="T4" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9248921-FAD9-C943-BAB6-D9048BE005B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48B9ACA-5B75-224E-B5A1-68B970F58FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9880" yWindow="9200" windowWidth="43080" windowHeight="15640" activeTab="2" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="9880" yWindow="9200" windowWidth="43080" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48B9ACA-5B75-224E-B5A1-68B970F58FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F6719F-2DB5-5747-A1F5-E69907728D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9880" yWindow="9200" windowWidth="43080" windowHeight="15640" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="9880" yWindow="9200" windowWidth="43080" windowHeight="15640" activeTab="4" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -1272,9 +1272,6 @@
     <t>final_A</t>
   </si>
   <si>
-    <t>American Founding Fathers</t>
-  </si>
-  <si>
     <t>Alexander Hamilton</t>
   </si>
   <si>
@@ -1386,9 +1383,6 @@
     <t>Chain Chomp</t>
   </si>
   <si>
-    <t>Nintendo Villains</t>
-  </si>
-  <si>
     <t>Waluigi</t>
   </si>
   <si>
@@ -1431,15 +1425,9 @@
     <t>Starts with "W".</t>
   </si>
   <si>
-    <t>Planets</t>
-  </si>
-  <si>
     <t>Named after a Greek god (not Roman)</t>
   </si>
   <si>
-    <t>Its name sparks bathroom humor.</t>
-  </si>
-  <si>
     <t>Rotates on its side, not its axis.</t>
   </si>
   <si>
@@ -1483,6 +1471,18 @@
   </si>
   <si>
     <t>Flora Fauna Merryweather</t>
+  </si>
+  <si>
+    <t>PLANETS</t>
+  </si>
+  <si>
+    <t>NINTENDO VILLAINS</t>
+  </si>
+  <si>
+    <t>AMERICAN FOUNDING FATHERS</t>
+  </si>
+  <si>
+    <t>Its name inspires bathroom humor.</t>
   </si>
 </sst>
 </file>
@@ -4272,7 +4272,7 @@
         <v>123</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C2" s="90" t="s">
         <v>124</v>
@@ -4329,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="U2" s="31" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="V2" s="34" t="b">
         <v>0</v>
@@ -4382,7 +4382,7 @@
         <v>137</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C3" s="90" t="s">
         <v>124</v>
@@ -4492,7 +4492,7 @@
         <v>149</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C4" s="90" t="s">
         <v>124</v>
@@ -4602,7 +4602,7 @@
         <v>163</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C5" s="90" t="s">
         <v>124</v>
@@ -4712,7 +4712,7 @@
         <v>175</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C6" s="92" t="s">
         <v>124</v>
@@ -4822,7 +4822,7 @@
         <v>248</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C7" s="92" t="s">
         <v>124</v>
@@ -4932,7 +4932,7 @@
         <v>272</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C8" s="92" t="s">
         <v>124</v>
@@ -5042,7 +5042,7 @@
         <v>291</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C9" s="94" t="s">
         <v>124</v>
@@ -5152,7 +5152,7 @@
         <v>308</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C10" s="95"/>
       <c r="D10" s="96"/>
@@ -5857,212 +5857,212 @@
         <v>409</v>
       </c>
       <c r="B2" s="100" t="s">
+        <v>479</v>
+      </c>
+      <c r="C2" s="100" t="s">
         <v>410</v>
       </c>
-      <c r="C2" s="100" t="s">
+      <c r="D2" s="100" t="s">
+        <v>426</v>
+      </c>
+      <c r="E2" s="100" t="s">
+        <v>424</v>
+      </c>
+      <c r="F2" s="100" t="s">
+        <v>425</v>
+      </c>
+      <c r="G2" s="100" t="s">
+        <v>423</v>
+      </c>
+      <c r="H2" s="100" t="s">
+        <v>410</v>
+      </c>
+      <c r="I2" s="100" t="s">
         <v>411</v>
       </c>
-      <c r="D2" s="100" t="s">
+      <c r="J2" s="100" t="s">
+        <v>412</v>
+      </c>
+      <c r="K2" s="100" t="s">
+        <v>413</v>
+      </c>
+      <c r="L2" s="100" t="s">
+        <v>428</v>
+      </c>
+      <c r="M2" s="100" t="s">
+        <v>414</v>
+      </c>
+      <c r="N2" s="100" t="s">
         <v>427</v>
       </c>
-      <c r="E2" s="100" t="s">
-        <v>425</v>
-      </c>
-      <c r="F2" s="100" t="s">
-        <v>426</v>
-      </c>
-      <c r="G2" s="100" t="s">
-        <v>424</v>
-      </c>
-      <c r="H2" s="100" t="s">
-        <v>411</v>
-      </c>
-      <c r="I2" s="100" t="s">
-        <v>412</v>
-      </c>
-      <c r="J2" s="100" t="s">
-        <v>413</v>
-      </c>
-      <c r="K2" s="100" t="s">
-        <v>414</v>
-      </c>
-      <c r="L2" s="100" t="s">
+      <c r="O2" s="100" t="s">
+        <v>415</v>
+      </c>
+      <c r="P2" s="100" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q2" s="100" t="s">
+        <v>417</v>
+      </c>
+      <c r="R2" s="100" t="s">
+        <v>418</v>
+      </c>
+      <c r="S2" s="100" t="s">
+        <v>419</v>
+      </c>
+      <c r="T2" s="100" t="s">
+        <v>420</v>
+      </c>
+      <c r="U2" s="100" t="s">
+        <v>421</v>
+      </c>
+      <c r="V2" s="100" t="s">
+        <v>422</v>
+      </c>
+      <c r="W2" s="100" t="s">
         <v>429</v>
-      </c>
-      <c r="M2" s="100" t="s">
-        <v>415</v>
-      </c>
-      <c r="N2" s="100" t="s">
-        <v>428</v>
-      </c>
-      <c r="O2" s="100" t="s">
-        <v>416</v>
-      </c>
-      <c r="P2" s="100" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q2" s="100" t="s">
-        <v>418</v>
-      </c>
-      <c r="R2" s="100" t="s">
-        <v>419</v>
-      </c>
-      <c r="S2" s="100" t="s">
-        <v>420</v>
-      </c>
-      <c r="T2" s="100" t="s">
-        <v>421</v>
-      </c>
-      <c r="U2" s="100" t="s">
-        <v>422</v>
-      </c>
-      <c r="V2" s="100" t="s">
-        <v>423</v>
-      </c>
-      <c r="W2" s="100" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="34">
       <c r="A3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C3" t="s">
         <v>431</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="Q3" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="34">
       <c r="A4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B4" t="s">
+        <v>477</v>
+      </c>
+      <c r="C4" t="s">
+        <v>464</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F4" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C4" t="s">
-        <v>468</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>241</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>167</v>
       </c>
       <c r="L4" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>474</v>
       </c>
       <c r="Q4" s="1" t="s">
         <v>242</v>
       </c>
       <c r="R4" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="W4" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>479</v>
       </c>
     </row>
   </sheetData>

--- a/question_data.xlsx
+++ b/question_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brentalfloss/Dropbox/CLOSE ENOUGH TRIVIA/CET LATEST/Close-Enough-Trivia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F6719F-2DB5-5747-A1F5-E69907728D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECA1CB1-183A-8944-90C5-F9D512655EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9880" yWindow="9200" windowWidth="43080" windowHeight="15640" activeTab="4" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
+    <workbookView xWindow="9880" yWindow="9200" windowWidth="24720" windowHeight="15640" activeTab="4" xr2:uid="{23454F11-F39F-C74E-948E-1E82ADD758DE}"/>
   </bookViews>
   <sheets>
     <sheet name="PINCH" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="503">
   <si>
     <t>question_id</t>
   </si>
@@ -1483,6 +1483,72 @@
   </si>
   <si>
     <t>Its name inspires bathroom humor.</t>
+  </si>
+  <si>
+    <t>final_D</t>
+  </si>
+  <si>
+    <t>Best Picture of 1991</t>
+  </si>
+  <si>
+    <t>Chris Isaak had a cameo</t>
+  </si>
+  <si>
+    <t>Starred Jodie Foster</t>
+  </si>
+  <si>
+    <t>The Silence of the Lambs</t>
+  </si>
+  <si>
+    <t>Milk Money</t>
+  </si>
+  <si>
+    <t>Forrest Gump</t>
+  </si>
+  <si>
+    <t>The Apple</t>
+  </si>
+  <si>
+    <t>Fateful Findings</t>
+  </si>
+  <si>
+    <t>Out of Africa</t>
+  </si>
+  <si>
+    <t>Dances With Wolves</t>
+  </si>
+  <si>
+    <t>Jurassic Park</t>
+  </si>
+  <si>
+    <t>Joe's Apartment</t>
+  </si>
+  <si>
+    <t>Rain Man</t>
+  </si>
+  <si>
+    <t>Titanic</t>
+  </si>
+  <si>
+    <t>Goodfellas</t>
+  </si>
+  <si>
+    <t>Dick Tracy</t>
+  </si>
+  <si>
+    <t>The Room</t>
+  </si>
+  <si>
+    <t>"BEST PICTURE" WINNERS</t>
+  </si>
+  <si>
+    <t>The villain is "Buffalo Bill"</t>
+  </si>
+  <si>
+    <t>Tombstone</t>
+  </si>
+  <si>
+    <t>Wyatt Earp</t>
   </si>
 </sst>
 </file>
@@ -5768,17 +5834,24 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BCF57C0-509A-A249-9E2F-95FCB3F78081}">
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="18.1640625" customWidth="1"/>
-    <col min="2" max="2" width="22.1640625" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.1640625" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="24.1640625" customWidth="1"/>
+    <col min="5" max="5" width="19.1640625" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" customWidth="1"/>
     <col min="7" max="7" width="19.5" customWidth="1"/>
-    <col min="8" max="8" width="16.1640625" customWidth="1"/>
+    <col min="8" max="8" width="22.1640625" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" customWidth="1"/>
+    <col min="12" max="12" width="15.5" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" customWidth="1"/>
+    <col min="14" max="14" width="18.6640625" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" customWidth="1"/>
+    <col min="17" max="17" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="30">
@@ -6065,6 +6138,77 @@
         <v>475</v>
       </c>
     </row>
+    <row r="5" spans="1:23">
+      <c r="A5" t="s">
+        <v>481</v>
+      </c>
+      <c r="B5" t="s">
+        <v>499</v>
+      </c>
+      <c r="C5" t="s">
+        <v>485</v>
+      </c>
+      <c r="D5" t="s">
+        <v>483</v>
+      </c>
+      <c r="E5" t="s">
+        <v>482</v>
+      </c>
+      <c r="F5" t="s">
+        <v>500</v>
+      </c>
+      <c r="G5" t="s">
+        <v>484</v>
+      </c>
+      <c r="H5" t="s">
+        <v>485</v>
+      </c>
+      <c r="I5" t="s">
+        <v>486</v>
+      </c>
+      <c r="J5" t="s">
+        <v>487</v>
+      </c>
+      <c r="K5" t="s">
+        <v>488</v>
+      </c>
+      <c r="L5" t="s">
+        <v>489</v>
+      </c>
+      <c r="M5" t="s">
+        <v>490</v>
+      </c>
+      <c r="N5" t="s">
+        <v>491</v>
+      </c>
+      <c r="O5" t="s">
+        <v>492</v>
+      </c>
+      <c r="P5" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>493</v>
+      </c>
+      <c r="R5" t="s">
+        <v>494</v>
+      </c>
+      <c r="S5" t="s">
+        <v>495</v>
+      </c>
+      <c r="T5" t="s">
+        <v>496</v>
+      </c>
+      <c r="U5" t="s">
+        <v>497</v>
+      </c>
+      <c r="V5" t="s">
+        <v>498</v>
+      </c>
+      <c r="W5" t="s">
+        <v>501</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
